--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D00BF18-6DCC-400F-87BA-5BC0FAD183DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0ACF5A-2BC8-4ADA-BB3B-53942F1AE577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$J$809</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$B$1:$J$809</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1871,885 +1871,6 @@
     <t>CHI</t>
   </si>
   <si>
-    <t>PASSO_CZASTE</t>
-  </si>
-  <si>
-    <t>PASSO_ARTMRF</t>
-  </si>
-  <si>
-    <t>PASSO_ELDAME</t>
-  </si>
-  <si>
-    <t>PASSO_ALGDST</t>
-  </si>
-  <si>
-    <t>ACQUA_INFANTIL_PRETO</t>
-  </si>
-  <si>
-    <t>ACQUA_INFANTIL_ARENIT</t>
-  </si>
-  <si>
-    <t>ACQUA_INFANTIL_CHBORG</t>
-  </si>
-  <si>
-    <t>ACQUA_INFANTIL_MRHCRS</t>
-  </si>
-  <si>
-    <t>PERSIST_VDEMLT</t>
-  </si>
-  <si>
-    <t>PERSIST_PRETO</t>
-  </si>
-  <si>
-    <t>PERSIST_ARTPTO</t>
-  </si>
-  <si>
-    <t>PERSIST_CHUMBO</t>
-  </si>
-  <si>
-    <t>RUSH_PRETO</t>
-  </si>
-  <si>
-    <t>RUSH_ARENIT</t>
-  </si>
-  <si>
-    <t>RUSH_PEWTER</t>
-  </si>
-  <si>
-    <t>RUSH_ALGPSC</t>
-  </si>
-  <si>
-    <t>INVERSE_2_PRETO</t>
-  </si>
-  <si>
-    <t>INVERSE_2_LNRMLT</t>
-  </si>
-  <si>
-    <t>INVERSE_2_ARECHB</t>
-  </si>
-  <si>
-    <t>ZEX_2_BCOPTO</t>
-  </si>
-  <si>
-    <t>ROLE_PRETO</t>
-  </si>
-  <si>
-    <t>ROLE_CHUMBO</t>
-  </si>
-  <si>
-    <t>ROLE_ARENIT</t>
-  </si>
-  <si>
-    <t>RUA_MILTR</t>
-  </si>
-  <si>
-    <t>RUA_MUSGO</t>
-  </si>
-  <si>
-    <t>RUA_MARITM</t>
-  </si>
-  <si>
-    <t>VOLCAN_2_MHOLUN</t>
-  </si>
-  <si>
-    <t>COSMO_PRETO</t>
-  </si>
-  <si>
-    <t>COSMO_VDEMLT</t>
-  </si>
-  <si>
-    <t>DELTA_PTGREN</t>
-  </si>
-  <si>
-    <t>DELTA_LUNORG</t>
-  </si>
-  <si>
-    <t>DELTA_MRHPPL</t>
-  </si>
-  <si>
-    <t>SAGAZ_MLTVDM</t>
-  </si>
-  <si>
-    <t>SAGAZ_MRHSTO</t>
-  </si>
-  <si>
-    <t>SAGAZ_CZESPT</t>
-  </si>
-  <si>
-    <t>SOMA_2_GFTGRE</t>
-  </si>
-  <si>
-    <t>SOMA_2_ALGBEG</t>
-  </si>
-  <si>
-    <t>SOMA_2_AREMRH</t>
-  </si>
-  <si>
-    <t>SOMA_2_ARECZE</t>
-  </si>
-  <si>
-    <t>INDEX_4_MRTMHO</t>
-  </si>
-  <si>
-    <t>INDEX_4_VDEMLT</t>
-  </si>
-  <si>
-    <t>INDEX_4_ARTMRF</t>
-  </si>
-  <si>
-    <t>MARTE_PRETO</t>
-  </si>
-  <si>
-    <t>MARTE_PTRLEO</t>
-  </si>
-  <si>
-    <t>MARTE_MILITR</t>
-  </si>
-  <si>
-    <t>MARTE_ARENIT</t>
-  </si>
-  <si>
-    <t>ERA_PRETO</t>
-  </si>
-  <si>
-    <t>ERA_MILITR</t>
-  </si>
-  <si>
-    <t>ERA_ALGODA</t>
-  </si>
-  <si>
-    <t>LANCE_PRETO</t>
-  </si>
-  <si>
-    <t>LANCE_ARENIT</t>
-  </si>
-  <si>
-    <t>LANCE_LAVAND</t>
-  </si>
-  <si>
-    <t>JADE_MRHMRT</t>
-  </si>
-  <si>
-    <t>JADE_LUNCZE</t>
-  </si>
-  <si>
-    <t>JADE_ARTDST</t>
-  </si>
-  <si>
-    <t>DAY_CHUMBO</t>
-  </si>
-  <si>
-    <t>DAY_PRETO</t>
-  </si>
-  <si>
-    <t>DAY_STOAMS</t>
-  </si>
-  <si>
-    <t>VIBE_MRHO</t>
-  </si>
-  <si>
-    <t>VIBE_LAVAND</t>
-  </si>
-  <si>
-    <t>VIBE_ARENIT</t>
-  </si>
-  <si>
-    <t>BRUMA_PRETO</t>
-  </si>
-  <si>
-    <t>BRUMA_LAVAND</t>
-  </si>
-  <si>
-    <t>BRUMA_ARENIT</t>
-  </si>
-  <si>
-    <t>BRUMA_MARITM</t>
-  </si>
-  <si>
-    <t>130_G_ULTRA_LEVE_MUSGO</t>
-  </si>
-  <si>
-    <t>130_G_ULTRA_LEVE_PTRSCO</t>
-  </si>
-  <si>
-    <t>130_G_ULTRA_LEVE_MARITM</t>
-  </si>
-  <si>
-    <t>130_G_ULTRA_LEVE_PRETO</t>
-  </si>
-  <si>
-    <t>EASY_2_PTODST</t>
-  </si>
-  <si>
-    <t>EASY_2_MRHO</t>
-  </si>
-  <si>
-    <t>EASY_2_CHUMBO</t>
-  </si>
-  <si>
-    <t>EASY_2_VANGRD</t>
-  </si>
-  <si>
-    <t>ACQUA_ARENIT</t>
-  </si>
-  <si>
-    <t>ACQUA_PRETO</t>
-  </si>
-  <si>
-    <t>ACQUA_CHBORG</t>
-  </si>
-  <si>
-    <t>ACQUA_MRHC</t>
-  </si>
-  <si>
-    <t>APOLIS_BRSMRT</t>
-  </si>
-  <si>
-    <t>APOLIS_CHBHIB</t>
-  </si>
-  <si>
-    <t>APOLIS_MRHPSC</t>
-  </si>
-  <si>
-    <t>APOLIS_MUSVAN</t>
-  </si>
-  <si>
-    <t>NYX_STOCRL</t>
-  </si>
-  <si>
-    <t>NYX_CHUMBO</t>
-  </si>
-  <si>
-    <t>NYX_ARENIT</t>
-  </si>
-  <si>
-    <t>CITRUS_2_MRHMRT</t>
-  </si>
-  <si>
-    <t>CITRUS_2_CHBVNL</t>
-  </si>
-  <si>
-    <t>CITRUS_2_ARENIT</t>
-  </si>
-  <si>
-    <t>VENUS_3_MARFIM</t>
-  </si>
-  <si>
-    <t>VENUS_3_CHUMBO</t>
-  </si>
-  <si>
-    <t>VENUS_3_MRHRSA</t>
-  </si>
-  <si>
-    <t>ATMOS_MUSGO</t>
-  </si>
-  <si>
-    <t>ATMOS_ARTPES</t>
-  </si>
-  <si>
-    <t>ATMOS_PRETO</t>
-  </si>
-  <si>
-    <t>BEATS_PRETO</t>
-  </si>
-  <si>
-    <t>BEATS_ARECHB</t>
-  </si>
-  <si>
-    <t>GAMA_ARTPTO</t>
-  </si>
-  <si>
-    <t>DYNAMIC_MRHDRD</t>
-  </si>
-  <si>
-    <t>DYNAMIC_PRETO</t>
-  </si>
-  <si>
-    <t>ELEVADO_AREMRH</t>
-  </si>
-  <si>
-    <t>ELEVADO_PRETO</t>
-  </si>
-  <si>
-    <t>ELEVADO_RSANAL</t>
-  </si>
-  <si>
-    <t>ELEVADO_ALGCZE</t>
-  </si>
-  <si>
-    <t>PROOF_3_MRHPTR</t>
-  </si>
-  <si>
-    <t>PROOF_3_PTRMRH</t>
-  </si>
-  <si>
-    <t>FLUIR_PTRMRH</t>
-  </si>
-  <si>
-    <t>FLUIR_CHCZES</t>
-  </si>
-  <si>
-    <t>LUMI_PRETO</t>
-  </si>
-  <si>
-    <t>LUMI_VERMUS</t>
-  </si>
-  <si>
-    <t>LUMI_LILAS</t>
-  </si>
-  <si>
-    <t>PIXEL_ALFART</t>
-  </si>
-  <si>
-    <t>PIXEL_MHGREN</t>
-  </si>
-  <si>
-    <t>PIXEL_OLYVMH</t>
-  </si>
-  <si>
-    <t>STREAM_VDJLIS</t>
-  </si>
-  <si>
-    <t>STREAM_PRETO</t>
-  </si>
-  <si>
-    <t>STREAM_MRHRSA</t>
-  </si>
-  <si>
-    <t>MARTE_INFANTIL_PRETO</t>
-  </si>
-  <si>
-    <t>MARTE_INFANTIL_PTRLEO</t>
-  </si>
-  <si>
-    <t>MARTE_INFANTIL_MILITR</t>
-  </si>
-  <si>
-    <t>PROOF_3_INFANTIL_MRHPTR</t>
-  </si>
-  <si>
-    <t>PROOF_3_INFANTIL_PTRMRH</t>
-  </si>
-  <si>
-    <t>EASY_3_MCPTPT</t>
-  </si>
-  <si>
-    <t>EASY_3_MCSTON</t>
-  </si>
-  <si>
-    <t>EASY_3_MCVANG</t>
-  </si>
-  <si>
-    <t>VERSA_BRANCO</t>
-  </si>
-  <si>
-    <t>VERSA_BGMVML</t>
-  </si>
-  <si>
-    <t>VERSA_AREMIS</t>
-  </si>
-  <si>
-    <t>VERSA_BCODUN</t>
-  </si>
-  <si>
-    <t>CLIC_MRHO</t>
-  </si>
-  <si>
-    <t>CLIC_CHUMBO</t>
-  </si>
-  <si>
-    <t>WELLNESS_2_PRETO</t>
-  </si>
-  <si>
-    <t>WELLNESS_2_CHUMBO</t>
-  </si>
-  <si>
-    <t>WELLNESS_2_MRHO</t>
-  </si>
-  <si>
-    <t>INTUIT_PRETO</t>
-  </si>
-  <si>
-    <t>INTUIT_ARENIT</t>
-  </si>
-  <si>
-    <t>INTUIT_MARITM</t>
-  </si>
-  <si>
-    <t>SAFIRA_MRHO</t>
-  </si>
-  <si>
-    <t>SAFIRA_MUSGO</t>
-  </si>
-  <si>
-    <t>FLUTUA_2_PTODST</t>
-  </si>
-  <si>
-    <t>FLUTUA_2_CHBHIB</t>
-  </si>
-  <si>
-    <t>FLUTUA_2_MUSORG</t>
-  </si>
-  <si>
-    <t>ONLY_2_BRANCO</t>
-  </si>
-  <si>
-    <t>ONLY_2_MRHO</t>
-  </si>
-  <si>
-    <t>ONLY_2_PRETO</t>
-  </si>
-  <si>
-    <t>JOGGING_101_SE_MRFARE</t>
-  </si>
-  <si>
-    <t>JOGGING_101_SE_ARENIT</t>
-  </si>
-  <si>
-    <t>JOGGING_101_SE_VDMMLT</t>
-  </si>
-  <si>
-    <t>JOGGING_101_SE_LUNAR</t>
-  </si>
-  <si>
-    <t>EROS_2_BRANCO</t>
-  </si>
-  <si>
-    <t>EROS_2_PRETO</t>
-  </si>
-  <si>
-    <t>EROS_2_LUNAR</t>
-  </si>
-  <si>
-    <t>EROS_2_ALGODAO</t>
-  </si>
-  <si>
-    <t>EROS_2_ARENIT</t>
-  </si>
-  <si>
-    <t>JOGGING_100_PRETO</t>
-  </si>
-  <si>
-    <t>JOGGING_100_BRANCO</t>
-  </si>
-  <si>
-    <t>EROS_2_INFANTIL_BRANCO</t>
-  </si>
-  <si>
-    <t>EROS_2_INFANTIL_PRETO</t>
-  </si>
-  <si>
-    <t>EROS_2_INFANTIL_LUNAR</t>
-  </si>
-  <si>
-    <t>EROS_2_INFANTIL_ALGODAO</t>
-  </si>
-  <si>
-    <t>EROS_2_INFANTIL_ARENIT</t>
-  </si>
-  <si>
-    <t>LIVRE_PRETO</t>
-  </si>
-  <si>
-    <t>LIVRE_VDEMLT</t>
-  </si>
-  <si>
-    <t>LIVRE_PTOMAD</t>
-  </si>
-  <si>
-    <t>LIVRE_AREMRO</t>
-  </si>
-  <si>
-    <t>PLENO_PTLGRN</t>
-  </si>
-  <si>
-    <t>PLENO_BCOPTO</t>
-  </si>
-  <si>
-    <t>PLENO_LIMPTO</t>
-  </si>
-  <si>
-    <t>PLENO_NATPSG</t>
-  </si>
-  <si>
-    <t>MELBOURNE_2_MLTVDM</t>
-  </si>
-  <si>
-    <t>MELBOURNE_2_BCOPTO</t>
-  </si>
-  <si>
-    <t>MELBOURNE_2_ARENIT</t>
-  </si>
-  <si>
-    <t>SERENO_LIME</t>
-  </si>
-  <si>
-    <t>SERENO_PRETO</t>
-  </si>
-  <si>
-    <t>SERENO_BCOFLC</t>
-  </si>
-  <si>
-    <t>SERENO_MILITR</t>
-  </si>
-  <si>
-    <t>SERENO_ORGANZ</t>
-  </si>
-  <si>
-    <t>CORRE_SUPRA_2_ARENML</t>
-  </si>
-  <si>
-    <t>CORRE_GRAFENO_3_CHBARE</t>
-  </si>
-  <si>
-    <t>CORRE_TURBO_LNRMLT</t>
-  </si>
-  <si>
-    <t>CORRE_4_CHBARE</t>
-  </si>
-  <si>
-    <t>CORRE_4_BRANCO</t>
-  </si>
-  <si>
-    <t>NUVEM_PRETO</t>
-  </si>
-  <si>
-    <t>NUVEM_RYLMHO</t>
-  </si>
-  <si>
-    <t>NUVEM_LUNCHB</t>
-  </si>
-  <si>
-    <t>NUVEM_ARTPTO</t>
-  </si>
-  <si>
-    <t>NUVEM_AZCLBR</t>
-  </si>
-  <si>
-    <t>NUVEM_ALGMLT</t>
-  </si>
-  <si>
-    <t>VOA_2_BCOLUN</t>
-  </si>
-  <si>
-    <t>VOA_2_AMARIL</t>
-  </si>
-  <si>
-    <t>VOA_2_PRETO</t>
-  </si>
-  <si>
-    <t>VOA_2_LUNMHO</t>
-  </si>
-  <si>
-    <t>VOA_3_ARENIT</t>
-  </si>
-  <si>
-    <t>VOA_3_ROYAL</t>
-  </si>
-  <si>
-    <t>VOA_3_LUNAR</t>
-  </si>
-  <si>
-    <t>VOA_3_ALGODA</t>
-  </si>
-  <si>
-    <t>VOLTA_2_PRETO</t>
-  </si>
-  <si>
-    <t>VOLTA_2_ARTPTO</t>
-  </si>
-  <si>
-    <t>ADRENA_2_PRETO</t>
-  </si>
-  <si>
-    <t>ADRENA_2_ELDERB</t>
-  </si>
-  <si>
-    <t>ADRENA_2_PEWTER</t>
-  </si>
-  <si>
-    <t>ADRENA_2_ARENIT</t>
-  </si>
-  <si>
-    <t>ADRENA_2_CRSTAL</t>
-  </si>
-  <si>
-    <t>VELOZ_3_PRETO</t>
-  </si>
-  <si>
-    <t>VELOZ_3_PTRLEO</t>
-  </si>
-  <si>
-    <t>VELOZ_3_PSGCLR</t>
-  </si>
-  <si>
-    <t>VELOZ_3_ARENIT</t>
-  </si>
-  <si>
-    <t>CHALLENGER_6_RYLMHO</t>
-  </si>
-  <si>
-    <t>CHALLENGER_6_PECDUN</t>
-  </si>
-  <si>
-    <t>CHALLENGER_6_ALGCHB</t>
-  </si>
-  <si>
-    <t>CHALLENGER_6_ARTMRF</t>
-  </si>
-  <si>
-    <t>SWIFT_5_PRETO</t>
-  </si>
-  <si>
-    <t>SWIFT_5_AMEIXA</t>
-  </si>
-  <si>
-    <t>SWIFT_5_CEREJA</t>
-  </si>
-  <si>
-    <t>SWIFT_5_ARTPTO</t>
-  </si>
-  <si>
-    <t>SWIFT_5_LUNAR</t>
-  </si>
-  <si>
-    <t>TREINO_BCOPTO</t>
-  </si>
-  <si>
-    <t>TREINO_ARELLS</t>
-  </si>
-  <si>
-    <t>PASSO_PTO-PT</t>
-  </si>
-  <si>
-    <t>PASSO_CHB-PT</t>
-  </si>
-  <si>
-    <t>RUSH_MLT-PT</t>
-  </si>
-  <si>
-    <t>INVERSE_2_PTO-PT</t>
-  </si>
-  <si>
-    <t>ZEX_2_PTO-CH</t>
-  </si>
-  <si>
-    <t>ZEX_2_PTR-PT</t>
-  </si>
-  <si>
-    <t>ZEX_2_CHB-PT</t>
-  </si>
-  <si>
-    <t>RUA_PTO-PT</t>
-  </si>
-  <si>
-    <t>RUA_PWT-PT</t>
-  </si>
-  <si>
-    <t>VOLCAN_2_PT-DRD</t>
-  </si>
-  <si>
-    <t>VOLCAN_2_PTO-PT</t>
-  </si>
-  <si>
-    <t>COSMO_PTO-PT</t>
-  </si>
-  <si>
-    <t>DELTA_PTO-CH</t>
-  </si>
-  <si>
-    <t>DELTA_PT-VMH</t>
-  </si>
-  <si>
-    <t>SAGAZ_PWT-PT</t>
-  </si>
-  <si>
-    <t>SOMA_2_PTO-PT</t>
-  </si>
-  <si>
-    <t>INDEX_4_PTO-PT</t>
-  </si>
-  <si>
-    <t>INDEX_4_MRH-VM</t>
-  </si>
-  <si>
-    <t>MARTE_PT-DRD</t>
-  </si>
-  <si>
-    <t>LANCE_VD-JAD</t>
-  </si>
-  <si>
-    <t>JADE_PTO-CH</t>
-  </si>
-  <si>
-    <t>VIBE_PTO-PT</t>
-  </si>
-  <si>
-    <t>EASY_2_PTO-BC</t>
-  </si>
-  <si>
-    <t>NYX_PTO-CH</t>
-  </si>
-  <si>
-    <t>CITRUS_2_PT-BRZ</t>
-  </si>
-  <si>
-    <t>BEATS_MRH-PT</t>
-  </si>
-  <si>
-    <t>BEATS_MLT-PT</t>
-  </si>
-  <si>
-    <t>GAMA_PTO-PT</t>
-  </si>
-  <si>
-    <t>GAMA_CHB-PT</t>
-  </si>
-  <si>
-    <t>DYNAMIC_PT-LJA</t>
-  </si>
-  <si>
-    <t>ELEVADO_PTO-PT</t>
-  </si>
-  <si>
-    <t>PROOF_3_PTO-CH</t>
-  </si>
-  <si>
-    <t>PROOF_3_PT-MLT</t>
-  </si>
-  <si>
-    <t>FLUIR_PTO-CH</t>
-  </si>
-  <si>
-    <t>LUMI_PTO-PT</t>
-  </si>
-  <si>
-    <t>PIXEL_PTO-PT</t>
-  </si>
-  <si>
-    <t>STREAM_MLT-PT</t>
-  </si>
-  <si>
-    <t>STREAM_PT-VMH</t>
-  </si>
-  <si>
-    <t>PROOF_3_INFANTIL_PTO-CH</t>
-  </si>
-  <si>
-    <t>PROOF_3_INFANTIL_PT-MLT</t>
-  </si>
-  <si>
-    <t>EASY_3_MC-PTO</t>
-  </si>
-  <si>
-    <t>VERSA_PTO-PT</t>
-  </si>
-  <si>
-    <t>VERSA_CHB-PT</t>
-  </si>
-  <si>
-    <t>CLIC_PTO-PT</t>
-  </si>
-  <si>
-    <t>WELLNESS_2_PTO-BC</t>
-  </si>
-  <si>
-    <t>INTUIT_PTO-PT</t>
-  </si>
-  <si>
-    <t>SAFIRA_PTO-PT</t>
-  </si>
-  <si>
-    <t>FLUTUA_2_PTO-PT</t>
-  </si>
-  <si>
-    <t>EROS_2_PTO-PT</t>
-  </si>
-  <si>
-    <t>EROS_2_INFANTIL_PTO-PT</t>
-  </si>
-  <si>
-    <t>LIVRE_AZL-CL</t>
-  </si>
-  <si>
-    <t>PLENO_PTO-PT</t>
-  </si>
-  <si>
-    <t>PLENO_CHB-PT</t>
-  </si>
-  <si>
-    <t>MELBOURNE_2_PTO-PT</t>
-  </si>
-  <si>
-    <t>MELBOURNE_2_PTO-BC</t>
-  </si>
-  <si>
-    <t>OLYMPIKUS-921_PTO-CH</t>
-  </si>
-  <si>
-    <t>OLYMPIKUS-921_CHOCST</t>
-  </si>
-  <si>
-    <t>OLYMPIKUS-921_CZCAVC</t>
-  </si>
-  <si>
-    <t>OLYMPIKUS-921_ST-PET</t>
-  </si>
-  <si>
-    <t>CORRE_SUPRA_2_CHB-PT</t>
-  </si>
-  <si>
-    <t>CORRE_MAX_MLT-PT</t>
-  </si>
-  <si>
-    <t>CORRE_MAX_PTO-GF</t>
-  </si>
-  <si>
-    <t>CORRE_MAX_PTO-PT</t>
-  </si>
-  <si>
-    <t>CORRE_TURBO_PTO-LM</t>
-  </si>
-  <si>
-    <t>CORRE_4_PTO-PT</t>
-  </si>
-  <si>
-    <t>NUVEM_PTO-PT</t>
-  </si>
-  <si>
-    <t>VOA_2_CHB-PT</t>
-  </si>
-  <si>
-    <t>VOA_3_PTO-CH</t>
-  </si>
-  <si>
-    <t>VOA_3_CHB-PT</t>
-  </si>
-  <si>
-    <t>VOA_3_PTO-PT</t>
-  </si>
-  <si>
-    <t>VOLTA_2_PTO-PT</t>
-  </si>
-  <si>
-    <t>VOLTA_2_MLT-PT</t>
-  </si>
-  <si>
-    <t>CHALLENGER_6_PTO-GF</t>
-  </si>
-  <si>
-    <t>CHALLENGER_6_PTO-PT</t>
-  </si>
-  <si>
-    <t>TREINO_PTO-CH</t>
-  </si>
-  <si>
-    <t>QU4DRA_2_PTO-PT</t>
-  </si>
-  <si>
-    <t>QU4DRA_2_CHB-LM</t>
-  </si>
-  <si>
     <t>OIUWL25653_BCOPTC</t>
   </si>
   <si>
@@ -2996,21 +2117,12 @@
     <t>OIWB251805_CAMEL</t>
   </si>
   <si>
-    <t>OIWA241929_BCO/MR</t>
-  </si>
-  <si>
-    <t>OIWA241929_PTO/BC</t>
-  </si>
-  <si>
     <t>OIWA241929_VDMGPT</t>
   </si>
   <si>
     <t>OIWA241929_CAMPRT</t>
   </si>
   <si>
-    <t>OIWA241929_BC/PTO</t>
-  </si>
-  <si>
     <t>OIWSA21196_MESCLA</t>
   </si>
   <si>
@@ -3095,21 +2207,12 @@
     <t>OIWSA22193_PRETO</t>
   </si>
   <si>
-    <t>OIMA241930_BCO/MR</t>
-  </si>
-  <si>
-    <t>OIMA241930_PTO/BC</t>
-  </si>
-  <si>
     <t>OIMA241930_VDMGPT</t>
   </si>
   <si>
     <t>OIMA241930_CAMPRT</t>
   </si>
   <si>
-    <t>OIMA241930_BC/PTO</t>
-  </si>
-  <si>
     <t>OIMSA21195_MESCLA</t>
   </si>
   <si>
@@ -3215,9 +2318,6 @@
     <t>OIWCR25103_SKY</t>
   </si>
   <si>
-    <t>OIWCR25103_PT/PRT</t>
-  </si>
-  <si>
     <t>OIWCR25703_DARK</t>
   </si>
   <si>
@@ -3227,12 +2327,6 @@
     <t>OIWCR25703_VANILA</t>
   </si>
   <si>
-    <t>OIWCR25703_PT/PRT</t>
-  </si>
-  <si>
-    <t>OIWCR24601_PT/PRT</t>
-  </si>
-  <si>
     <t>OIWCR24601_OCEANO</t>
   </si>
   <si>
@@ -3245,9 +2339,6 @@
     <t>OIWCR24802_SKY</t>
   </si>
   <si>
-    <t>OIWCR24804_PT/PRT</t>
-  </si>
-  <si>
     <t>OIWCR24804_OCEANO</t>
   </si>
   <si>
@@ -3257,9 +2348,6 @@
     <t>OIWCR25118_PRETO</t>
   </si>
   <si>
-    <t>OIMCR24702_PT/PRT</t>
-  </si>
-  <si>
     <t>OIMCR24702_DARK</t>
   </si>
   <si>
@@ -3275,24 +2363,15 @@
     <t>OIMCR24605_MACVRD</t>
   </si>
   <si>
-    <t>OIMCR24605_PTO/PR</t>
-  </si>
-  <si>
     <t>OIMCR24605_BRANCO</t>
   </si>
   <si>
-    <t>OIMCR24301_PT/PRT</t>
-  </si>
-  <si>
     <t>OIMCR24301_NAVAL</t>
   </si>
   <si>
     <t>OIMCR24301_OCEANO</t>
   </si>
   <si>
-    <t>OIMCR24302_PT/PRT</t>
-  </si>
-  <si>
     <t>OIMCR25119_BRANCO</t>
   </si>
   <si>
@@ -3317,9 +2396,6 @@
     <t>OICR241713_CASARE</t>
   </si>
   <si>
-    <t>OBWA251921_BC/ORG</t>
-  </si>
-  <si>
     <t>OBWA251921_PTPCOR</t>
   </si>
   <si>
@@ -3338,9 +2414,6 @@
     <t>OBWA251921_ORVARE</t>
   </si>
   <si>
-    <t>OBMA251922_BC/ORG</t>
-  </si>
-  <si>
     <t>OBMA251922_PTPCOR</t>
   </si>
   <si>
@@ -3536,9 +2609,6 @@
     <t>OIWC231704_BLUSH</t>
   </si>
   <si>
-    <t>OBWW251933_PT/BCO</t>
-  </si>
-  <si>
     <t>OBWW251933_BCNZSF</t>
   </si>
   <si>
@@ -3602,9 +2672,6 @@
     <t>OBWSR241921_CBCLOL</t>
   </si>
   <si>
-    <t>OBMW251934_PT/BCO</t>
-  </si>
-  <si>
     <t>OBMW251934_BCNZSF</t>
   </si>
   <si>
@@ -4007,15 +3074,9 @@
     <t>OBMST24643_BCOAPR</t>
   </si>
   <si>
-    <t>OBMST24643_PTO/PT</t>
-  </si>
-  <si>
     <t>OBMST24643_MARGRE</t>
   </si>
   <si>
-    <t>OBMST24643_BCO/BC</t>
-  </si>
-  <si>
     <t>OIMST25312_PTOPTC</t>
   </si>
   <si>
@@ -4049,9 +3110,6 @@
     <t>OIWB241803_PRETO</t>
   </si>
   <si>
-    <t>OIWB241803_MRH/PR</t>
-  </si>
-  <si>
     <t>OIWB241803_PTCPTO</t>
   </si>
   <si>
@@ -4064,15 +3122,9 @@
     <t>OIWB241803_CASCAL</t>
   </si>
   <si>
-    <t>OIWB221802_PT/PRT</t>
-  </si>
-  <si>
     <t>OIWB221802_PCGRAY</t>
   </si>
   <si>
-    <t>OIWB221802_MRH/PR</t>
-  </si>
-  <si>
     <t>OIWB221802_NVLPRT</t>
   </si>
   <si>
@@ -4091,9 +3143,6 @@
     <t>OIWB231809_CASCAL</t>
   </si>
   <si>
-    <t>OIWB231810_PTO/BC</t>
-  </si>
-  <si>
     <t>OIWB231810_NVALNA</t>
   </si>
   <si>
@@ -4196,54 +3245,9 @@
     <t>OIWC221703_PCGRAY</t>
   </si>
   <si>
-    <t>APICE_MRHO</t>
-  </si>
-  <si>
-    <t>APICE_PTO-PT</t>
-  </si>
-  <si>
-    <t>APICE_VDEESC</t>
-  </si>
-  <si>
-    <t>APICE_PRETO</t>
-  </si>
-  <si>
-    <t>POS-CORRE_PTO-PT</t>
-  </si>
-  <si>
-    <t>POS-CORRE_BCOFLC</t>
-  </si>
-  <si>
-    <t>POS-CORRE_AMR-LM</t>
-  </si>
-  <si>
-    <t>POS-CORRE_ARENIT</t>
-  </si>
-  <si>
-    <t>VIBRACAO_MRH-PT</t>
-  </si>
-  <si>
-    <t>VIBRACAO_CHB-PT</t>
-  </si>
-  <si>
-    <t>VIBRACAO_MRHPTR</t>
-  </si>
-  <si>
-    <t>VIBRACAO_ALGODA</t>
-  </si>
-  <si>
     <t>POS/CORRE</t>
   </si>
   <si>
-    <t>VERTICE_PRETO</t>
-  </si>
-  <si>
-    <t>VERTICE_ARENIT</t>
-  </si>
-  <si>
-    <t>VERTICE_MIST</t>
-  </si>
-  <si>
     <t>VERTICE</t>
   </si>
   <si>
@@ -4331,10 +3335,1006 @@
     <t>LRJPTO</t>
   </si>
   <si>
-    <t>VOA_3_LAVAND</t>
-  </si>
-  <si>
-    <t>ACQUA_MRHO</t>
+    <t>43242437_CZASTE</t>
+  </si>
+  <si>
+    <t>43242437_ARTMRF</t>
+  </si>
+  <si>
+    <t>43242437_ELDAME</t>
+  </si>
+  <si>
+    <t>43242437_ALGDST</t>
+  </si>
+  <si>
+    <t>43306412_PRETO</t>
+  </si>
+  <si>
+    <t>43306412_ARENIT</t>
+  </si>
+  <si>
+    <t>43306412_CHBORG</t>
+  </si>
+  <si>
+    <t>43306412_MRHCRS</t>
+  </si>
+  <si>
+    <t>43404452_VDEMLT</t>
+  </si>
+  <si>
+    <t>43404452_PRETO</t>
+  </si>
+  <si>
+    <t>43404452_ARTPTO</t>
+  </si>
+  <si>
+    <t>43404452_CHUMBO</t>
+  </si>
+  <si>
+    <t>43667419_PRETO</t>
+  </si>
+  <si>
+    <t>43667419_ARENIT</t>
+  </si>
+  <si>
+    <t>43667419_PEWTER</t>
+  </si>
+  <si>
+    <t>43667419_ALGPSC</t>
+  </si>
+  <si>
+    <t>43354465_VDEESC</t>
+  </si>
+  <si>
+    <t>43354465_PRETO</t>
+  </si>
+  <si>
+    <t>43354465_MRHO</t>
+  </si>
+  <si>
+    <t>43358451_PRETO</t>
+  </si>
+  <si>
+    <t>43358451_LNRMLT</t>
+  </si>
+  <si>
+    <t>43358451_ARECHB</t>
+  </si>
+  <si>
+    <t>43584380_BCOPTO</t>
+  </si>
+  <si>
+    <t>43224430_PRETO</t>
+  </si>
+  <si>
+    <t>43224430_CHUMBO</t>
+  </si>
+  <si>
+    <t>43224430_ARENIT</t>
+  </si>
+  <si>
+    <t>43369229_MILTR</t>
+  </si>
+  <si>
+    <t>43369229_MUSGO</t>
+  </si>
+  <si>
+    <t>43369229_MARITM</t>
+  </si>
+  <si>
+    <t>43538342_MHOLUN</t>
+  </si>
+  <si>
+    <t>43554334_PRETO</t>
+  </si>
+  <si>
+    <t>43554334_VDEMLT</t>
+  </si>
+  <si>
+    <t>43321122_PTGREN</t>
+  </si>
+  <si>
+    <t>43321122_LUNORG</t>
+  </si>
+  <si>
+    <t>43321122_MRHPPL</t>
+  </si>
+  <si>
+    <t>43588382_MLTVDM</t>
+  </si>
+  <si>
+    <t>43588382_MRHSTO</t>
+  </si>
+  <si>
+    <t>43588382_CZESPT</t>
+  </si>
+  <si>
+    <t>43407464_GFTGRE</t>
+  </si>
+  <si>
+    <t>43407464_ALGBEG</t>
+  </si>
+  <si>
+    <t>43407464_AREMRH</t>
+  </si>
+  <si>
+    <t>43407464_ARECZE</t>
+  </si>
+  <si>
+    <t>43376462_MRTMHO</t>
+  </si>
+  <si>
+    <t>43376462_VDEMLT</t>
+  </si>
+  <si>
+    <t>43376462_ARTMRF</t>
+  </si>
+  <si>
+    <t>43395156_PRETO</t>
+  </si>
+  <si>
+    <t>43395156_PTRLEO</t>
+  </si>
+  <si>
+    <t>43395156_MILITR</t>
+  </si>
+  <si>
+    <t>43395156_ARENIT</t>
+  </si>
+  <si>
+    <t>43394132_MRHPTR</t>
+  </si>
+  <si>
+    <t>43394132_ALGODA</t>
+  </si>
+  <si>
+    <t>43293443_PRETO</t>
+  </si>
+  <si>
+    <t>43293443_MILITR</t>
+  </si>
+  <si>
+    <t>43293443_ALGODA</t>
+  </si>
+  <si>
+    <t>43596370_PRETO</t>
+  </si>
+  <si>
+    <t>43596370_ARENIT</t>
+  </si>
+  <si>
+    <t>43596370_LAVAND</t>
+  </si>
+  <si>
+    <t>43385453_MRHMRT</t>
+  </si>
+  <si>
+    <t>43385453_LUNCZE</t>
+  </si>
+  <si>
+    <t>43385453_ARTDST</t>
+  </si>
+  <si>
+    <t>43927547_CHUMBO</t>
+  </si>
+  <si>
+    <t>43927547_PRETO</t>
+  </si>
+  <si>
+    <t>43927547_STOAMS</t>
+  </si>
+  <si>
+    <t>43697386_MRHO</t>
+  </si>
+  <si>
+    <t>43697386_LAVAND</t>
+  </si>
+  <si>
+    <t>43697386_ARENIT</t>
+  </si>
+  <si>
+    <t>43632407_PRETO</t>
+  </si>
+  <si>
+    <t>43632407_LAVAND</t>
+  </si>
+  <si>
+    <t>43632407_ARENIT</t>
+  </si>
+  <si>
+    <t>43632407_MARITM</t>
+  </si>
+  <si>
+    <t>43336749_MUSGO</t>
+  </si>
+  <si>
+    <t>43336749_PTRSCO</t>
+  </si>
+  <si>
+    <t>43336749_MARITM</t>
+  </si>
+  <si>
+    <t>43336749_PRETO</t>
+  </si>
+  <si>
+    <t>43605213_PTODST</t>
+  </si>
+  <si>
+    <t>43605213_MRHO</t>
+  </si>
+  <si>
+    <t>43605213_CHUMBO</t>
+  </si>
+  <si>
+    <t>43605213_VANGRD</t>
+  </si>
+  <si>
+    <t>43299316_ARENIT</t>
+  </si>
+  <si>
+    <t>43299316_PRETO</t>
+  </si>
+  <si>
+    <t>43299316_MRHO</t>
+  </si>
+  <si>
+    <t>43299316_CHBORG</t>
+  </si>
+  <si>
+    <t>43299316_MRHC</t>
+  </si>
+  <si>
+    <t>43616206_BRSMRT</t>
+  </si>
+  <si>
+    <t>43616206_CHBHIB</t>
+  </si>
+  <si>
+    <t>43616206_MRHPSC</t>
+  </si>
+  <si>
+    <t>43616206_MUSVAN</t>
+  </si>
+  <si>
+    <t>43784228_STOCRL</t>
+  </si>
+  <si>
+    <t>43784228_CHUMBO</t>
+  </si>
+  <si>
+    <t>43784228_ARENIT</t>
+  </si>
+  <si>
+    <t>43606391_PRETO</t>
+  </si>
+  <si>
+    <t>43606391_ARENIT</t>
+  </si>
+  <si>
+    <t>43606391_MIST</t>
+  </si>
+  <si>
+    <t>43759258_MRHMRT</t>
+  </si>
+  <si>
+    <t>43759258_CHBVNL</t>
+  </si>
+  <si>
+    <t>43759258_ARENIT</t>
+  </si>
+  <si>
+    <t>43547338_MARFIM</t>
+  </si>
+  <si>
+    <t>43547338_CHUMBO</t>
+  </si>
+  <si>
+    <t>43547338_MRHRSA</t>
+  </si>
+  <si>
+    <t>43286101_MUSGO</t>
+  </si>
+  <si>
+    <t>43286101_ARTPES</t>
+  </si>
+  <si>
+    <t>43286101_PRETO</t>
+  </si>
+  <si>
+    <t>43701259_PRETO</t>
+  </si>
+  <si>
+    <t>43701259_ARECHB</t>
+  </si>
+  <si>
+    <t>43235442_ARTPTO</t>
+  </si>
+  <si>
+    <t>43298343_MRHDRD</t>
+  </si>
+  <si>
+    <t>43298343_PRETO</t>
+  </si>
+  <si>
+    <t>43353470_AREMRH</t>
+  </si>
+  <si>
+    <t>43353470_PRETO</t>
+  </si>
+  <si>
+    <t>43353470_RSANAL</t>
+  </si>
+  <si>
+    <t>43353470_ALGCZE</t>
+  </si>
+  <si>
+    <t>43320114_MRHPTR</t>
+  </si>
+  <si>
+    <t>43320114_PTRMRH</t>
+  </si>
+  <si>
+    <t>43542347_PTRMRH</t>
+  </si>
+  <si>
+    <t>43542347_CHCZES</t>
+  </si>
+  <si>
+    <t>43393460_PRETO</t>
+  </si>
+  <si>
+    <t>43393460_VERMUS</t>
+  </si>
+  <si>
+    <t>43393460_LILAS</t>
+  </si>
+  <si>
+    <t>43233414_ALFART</t>
+  </si>
+  <si>
+    <t>43233414_MHGREN</t>
+  </si>
+  <si>
+    <t>43233414_OLYVMH</t>
+  </si>
+  <si>
+    <t>43772253_VDJLIS</t>
+  </si>
+  <si>
+    <t>43772253_PRETO</t>
+  </si>
+  <si>
+    <t>43772253_MRHRSA</t>
+  </si>
+  <si>
+    <t>43649393_PRETO</t>
+  </si>
+  <si>
+    <t>43649393_PTRLEO</t>
+  </si>
+  <si>
+    <t>43649393_MILITR</t>
+  </si>
+  <si>
+    <t>43213474_MRHPTR</t>
+  </si>
+  <si>
+    <t>43213474_PTRMRH</t>
+  </si>
+  <si>
+    <t>43609415_MCPTPT</t>
+  </si>
+  <si>
+    <t>43609415_MCSTON</t>
+  </si>
+  <si>
+    <t>43609415_MCVANG</t>
+  </si>
+  <si>
+    <t>43752263_BRANCO</t>
+  </si>
+  <si>
+    <t>43752263_BGMVML</t>
+  </si>
+  <si>
+    <t>43752263_AREMIS</t>
+  </si>
+  <si>
+    <t>43752263_BCODUN</t>
+  </si>
+  <si>
+    <t>43303329_MRHO</t>
+  </si>
+  <si>
+    <t>43303329_CHUMBO</t>
+  </si>
+  <si>
+    <t>43338186_PRETO</t>
+  </si>
+  <si>
+    <t>43338186_CHUMBO</t>
+  </si>
+  <si>
+    <t>43338186_MRHO</t>
+  </si>
+  <si>
+    <t>43418328_PRETO</t>
+  </si>
+  <si>
+    <t>43418328_ARENIT</t>
+  </si>
+  <si>
+    <t>43418328_MARITM</t>
+  </si>
+  <si>
+    <t>43608374_MRHO</t>
+  </si>
+  <si>
+    <t>43608374_MUSGO</t>
+  </si>
+  <si>
+    <t>43389459_PTODST</t>
+  </si>
+  <si>
+    <t>43389459_CHBHIB</t>
+  </si>
+  <si>
+    <t>43389459_MUSORG</t>
+  </si>
+  <si>
+    <t>43711902_BRANCO</t>
+  </si>
+  <si>
+    <t>43711902_MRHO</t>
+  </si>
+  <si>
+    <t>43711902_PRETO</t>
+  </si>
+  <si>
+    <t>43627383_MRFARE</t>
+  </si>
+  <si>
+    <t>43627383_ARENIT</t>
+  </si>
+  <si>
+    <t>43627383_VDMMLT</t>
+  </si>
+  <si>
+    <t>43627383_LUNAR</t>
+  </si>
+  <si>
+    <t>43409454_BRANCO</t>
+  </si>
+  <si>
+    <t>43409454_PRETO</t>
+  </si>
+  <si>
+    <t>43409454_LUNAR</t>
+  </si>
+  <si>
+    <t>43409454_ALGODAO</t>
+  </si>
+  <si>
+    <t>43409454_ARENIT</t>
+  </si>
+  <si>
+    <t>OBTN068_PRETO</t>
+  </si>
+  <si>
+    <t>OBTN068_BRANCO</t>
+  </si>
+  <si>
+    <t>43406455_BRANCO</t>
+  </si>
+  <si>
+    <t>43406455_PRETO</t>
+  </si>
+  <si>
+    <t>43406455_LUNAR</t>
+  </si>
+  <si>
+    <t>43406455_ALGODA</t>
+  </si>
+  <si>
+    <t>43406455_ARENIT</t>
+  </si>
+  <si>
+    <t>54110438_PRETO</t>
+  </si>
+  <si>
+    <t>54110438_VDEMLT</t>
+  </si>
+  <si>
+    <t>54110438_PTOMAD</t>
+  </si>
+  <si>
+    <t>54110438_AREMRO</t>
+  </si>
+  <si>
+    <t>54113468_PTLGRN</t>
+  </si>
+  <si>
+    <t>54113468_BCOPTO</t>
+  </si>
+  <si>
+    <t>54113468_LIMPTO</t>
+  </si>
+  <si>
+    <t>54113468_NATPSG</t>
+  </si>
+  <si>
+    <t>54111405_BCOFLC</t>
+  </si>
+  <si>
+    <t>54111405_ARENIT</t>
+  </si>
+  <si>
+    <t>54107376_MLTVDM</t>
+  </si>
+  <si>
+    <t>54107376_BCOPTO</t>
+  </si>
+  <si>
+    <t>54107376_ARENIT</t>
+  </si>
+  <si>
+    <t>54104269_LIME</t>
+  </si>
+  <si>
+    <t>54104269_PRETO</t>
+  </si>
+  <si>
+    <t>54104269_BCOFLC</t>
+  </si>
+  <si>
+    <t>54104269_MILITR</t>
+  </si>
+  <si>
+    <t>54104269_ORGANZ</t>
+  </si>
+  <si>
+    <t>54827630_CHOCST</t>
+  </si>
+  <si>
+    <t>54827630_CZCAVC</t>
+  </si>
+  <si>
+    <t>43777397_ARENML</t>
+  </si>
+  <si>
+    <t>43245330_CHBARE</t>
+  </si>
+  <si>
+    <t>43790399_LNRMLT</t>
+  </si>
+  <si>
+    <t>43720366_CHBARE</t>
+  </si>
+  <si>
+    <t>43720366_BRANCO</t>
+  </si>
+  <si>
+    <t>43342471_PRETO</t>
+  </si>
+  <si>
+    <t>43342471_RYLMHO</t>
+  </si>
+  <si>
+    <t>43342471_LUNCHB</t>
+  </si>
+  <si>
+    <t>43342471_ARTPTO</t>
+  </si>
+  <si>
+    <t>43342471_AZCLBR</t>
+  </si>
+  <si>
+    <t>43342471_ALGMLT</t>
+  </si>
+  <si>
+    <t>43533261_BCOLUN</t>
+  </si>
+  <si>
+    <t>43533261_AMARIL</t>
+  </si>
+  <si>
+    <t>43533261_PRETO</t>
+  </si>
+  <si>
+    <t>43533261_LUNMHO</t>
+  </si>
+  <si>
+    <t>43263432_ARENIT</t>
+  </si>
+  <si>
+    <t>43263432_ROYAL</t>
+  </si>
+  <si>
+    <t>43263432_LUNAR</t>
+  </si>
+  <si>
+    <t>43263432_LAVAND</t>
+  </si>
+  <si>
+    <t>43263432_ALGODA</t>
+  </si>
+  <si>
+    <t>43343458_PRETO</t>
+  </si>
+  <si>
+    <t>43343458_ARTPTO</t>
+  </si>
+  <si>
+    <t>43344456_PRETO</t>
+  </si>
+  <si>
+    <t>43344456_ELDERB</t>
+  </si>
+  <si>
+    <t>43344456_PEWTER</t>
+  </si>
+  <si>
+    <t>43344456_ARENIT</t>
+  </si>
+  <si>
+    <t>43344456_CRSTAL</t>
+  </si>
+  <si>
+    <t>43502346_PRETO</t>
+  </si>
+  <si>
+    <t>43502346_PTRLEO</t>
+  </si>
+  <si>
+    <t>43502346_PSGCLR</t>
+  </si>
+  <si>
+    <t>43502346_ARENIT</t>
+  </si>
+  <si>
+    <t>43341472_RYLMHO</t>
+  </si>
+  <si>
+    <t>43341472_PECDUN</t>
+  </si>
+  <si>
+    <t>43341472_ALGCHB</t>
+  </si>
+  <si>
+    <t>43341472_ARTMRF</t>
+  </si>
+  <si>
+    <t>43559375_PRETO</t>
+  </si>
+  <si>
+    <t>43559375_AMEIXA</t>
+  </si>
+  <si>
+    <t>43559375_CEREJA</t>
+  </si>
+  <si>
+    <t>43559375_ARTPTO</t>
+  </si>
+  <si>
+    <t>43559375_LUNAR</t>
+  </si>
+  <si>
+    <t>43210417_BCOPTO</t>
+  </si>
+  <si>
+    <t>43210417_ARELLS</t>
+  </si>
+  <si>
+    <t>43242437_PTO_PT</t>
+  </si>
+  <si>
+    <t>43242437_CHB_PT</t>
+  </si>
+  <si>
+    <t>43667419_MLT_PT</t>
+  </si>
+  <si>
+    <t>43354465_PTO_PT</t>
+  </si>
+  <si>
+    <t>43358451_PTO_PT</t>
+  </si>
+  <si>
+    <t>43584380_PTO_CH</t>
+  </si>
+  <si>
+    <t>43584380_PTR_PT</t>
+  </si>
+  <si>
+    <t>43584380_CHB_PT</t>
+  </si>
+  <si>
+    <t>43369229_PTO_PT</t>
+  </si>
+  <si>
+    <t>43369229_PWT_PT</t>
+  </si>
+  <si>
+    <t>43538342_PT_DRD</t>
+  </si>
+  <si>
+    <t>43538342_PTO_PT</t>
+  </si>
+  <si>
+    <t>43554334_PTO_PT</t>
+  </si>
+  <si>
+    <t>43321122_PTO_CH</t>
+  </si>
+  <si>
+    <t>43321122_PT_VMH</t>
+  </si>
+  <si>
+    <t>43588382_PWT_PT</t>
+  </si>
+  <si>
+    <t>43407464_PTO_PT</t>
+  </si>
+  <si>
+    <t>43376462_PTO_PT</t>
+  </si>
+  <si>
+    <t>43376462_MRH_VM</t>
+  </si>
+  <si>
+    <t>43395156_PT_DRD</t>
+  </si>
+  <si>
+    <t>43394132_MRH_PT</t>
+  </si>
+  <si>
+    <t>43394132_CHB_PT</t>
+  </si>
+  <si>
+    <t>43596370_VD_JAD</t>
+  </si>
+  <si>
+    <t>43385453_PTO_CH</t>
+  </si>
+  <si>
+    <t>43697386_PTO_PT</t>
+  </si>
+  <si>
+    <t>43605213_PTO_BC</t>
+  </si>
+  <si>
+    <t>43784228_PTO_CH</t>
+  </si>
+  <si>
+    <t>43759258_PT_BRZ</t>
+  </si>
+  <si>
+    <t>43701259_MRH_PT</t>
+  </si>
+  <si>
+    <t>43701259_MLT_PT</t>
+  </si>
+  <si>
+    <t>43235442_PTO_PT</t>
+  </si>
+  <si>
+    <t>43235442_CHB_PT</t>
+  </si>
+  <si>
+    <t>43298343_PT_LJA</t>
+  </si>
+  <si>
+    <t>43353470_PTO_PT</t>
+  </si>
+  <si>
+    <t>43320114_PTO_CH</t>
+  </si>
+  <si>
+    <t>43320114_PT_MLT</t>
+  </si>
+  <si>
+    <t>43542347_PTO_CH</t>
+  </si>
+  <si>
+    <t>43393460_PTO_PT</t>
+  </si>
+  <si>
+    <t>43233414_PTO_PT</t>
+  </si>
+  <si>
+    <t>43772253_MLT_PT</t>
+  </si>
+  <si>
+    <t>43772253_PT_VMH</t>
+  </si>
+  <si>
+    <t>43213474_PTO_CH</t>
+  </si>
+  <si>
+    <t>43213474_PT_MLT</t>
+  </si>
+  <si>
+    <t>43609415_MC_PTO</t>
+  </si>
+  <si>
+    <t>43752263_PTO_PT</t>
+  </si>
+  <si>
+    <t>43752263_CHB_PT</t>
+  </si>
+  <si>
+    <t>43303329_PTO_PT</t>
+  </si>
+  <si>
+    <t>43338186_PTO_BC</t>
+  </si>
+  <si>
+    <t>43418328_PTO_PT</t>
+  </si>
+  <si>
+    <t>43608374_PTO_PT</t>
+  </si>
+  <si>
+    <t>43389459_PTO_PT</t>
+  </si>
+  <si>
+    <t>43409454_PTO_PT</t>
+  </si>
+  <si>
+    <t>43406455_PTO_PT</t>
+  </si>
+  <si>
+    <t>54110438_AZL_CL</t>
+  </si>
+  <si>
+    <t>54113468_PTO_PT</t>
+  </si>
+  <si>
+    <t>54113468_CHB_PT</t>
+  </si>
+  <si>
+    <t>54111405_PTO_PT</t>
+  </si>
+  <si>
+    <t>54111405_AMR_LM</t>
+  </si>
+  <si>
+    <t>54107376_PTO_PT</t>
+  </si>
+  <si>
+    <t>54107376_PTO_BC</t>
+  </si>
+  <si>
+    <t>54827630_PTO_CH</t>
+  </si>
+  <si>
+    <t>54827630_ST_PET</t>
+  </si>
+  <si>
+    <t>43777397_CHB_PT</t>
+  </si>
+  <si>
+    <t>43758365_MLT_PT</t>
+  </si>
+  <si>
+    <t>43758365_PTO_GF</t>
+  </si>
+  <si>
+    <t>43758365_PTO_PT</t>
+  </si>
+  <si>
+    <t>43790399_PTO_LM</t>
+  </si>
+  <si>
+    <t>43720366_PTO_PT</t>
+  </si>
+  <si>
+    <t>43342471_PTO_PT</t>
+  </si>
+  <si>
+    <t>43533261_CHB_PT</t>
+  </si>
+  <si>
+    <t>43263432_PTO_CH</t>
+  </si>
+  <si>
+    <t>43263432_CHB_PT</t>
+  </si>
+  <si>
+    <t>43263432_PTO_PT</t>
+  </si>
+  <si>
+    <t>43343458_PTO_PT</t>
+  </si>
+  <si>
+    <t>43343458_MLT_PT</t>
+  </si>
+  <si>
+    <t>43341472_PTO_GF</t>
+  </si>
+  <si>
+    <t>43341472_PTO_PT</t>
+  </si>
+  <si>
+    <t>43210417_PTO_CH</t>
+  </si>
+  <si>
+    <t>43346463_PTO_PT</t>
+  </si>
+  <si>
+    <t>43346463_CHB_LM</t>
+  </si>
+  <si>
+    <t>OIWA241929_BCO_MR</t>
+  </si>
+  <si>
+    <t>OIWA241929_PTO_BC</t>
+  </si>
+  <si>
+    <t>OIWA241929_BC_PTO</t>
+  </si>
+  <si>
+    <t>OIMA241930_BCO_MR</t>
+  </si>
+  <si>
+    <t>OIMA241930_PTO_BC</t>
+  </si>
+  <si>
+    <t>OIMA241930_BC_PTO</t>
+  </si>
+  <si>
+    <t>OIWCR25103_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWCR25703_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWCR24601_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWCR24804_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIMCR24702_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIMCR24605_PTO_PR</t>
+  </si>
+  <si>
+    <t>OIMCR24301_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIMCR24302_PT_PRT</t>
+  </si>
+  <si>
+    <t>OBWA251921_BC_ORG</t>
+  </si>
+  <si>
+    <t>OBMA251922_BC_ORG</t>
+  </si>
+  <si>
+    <t>OBWW251933_PT_BCO</t>
+  </si>
+  <si>
+    <t>OBMW251934_PT_BCO</t>
+  </si>
+  <si>
+    <t>OBMST24643_PTO_PT</t>
+  </si>
+  <si>
+    <t>OBMST24643_BCO_BC</t>
+  </si>
+  <si>
+    <t>OIWB241803_MRH_PR</t>
+  </si>
+  <si>
+    <t>OIWB221802_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWB221802_MRH_PR</t>
+  </si>
+  <si>
+    <t>OIWB231810_PTO_BC</t>
   </si>
 </sst>
 </file>
@@ -4744,7 +4744,8 @@
   <dimension ref="A1:M809"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="15.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="15.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" style="1" customWidth="1"/>
     <col min="6" max="10" width="15.85546875" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
@@ -4784,7 +4785,7 @@
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>827</v>
+        <v>1329</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>220</v>
@@ -4816,7 +4817,7 @@
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>828</v>
+        <v>1330</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>220</v>
@@ -4848,7 +4849,7 @@
     </row>
     <row r="4" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>611</v>
+        <v>1099</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>220</v>
@@ -4880,7 +4881,7 @@
     </row>
     <row r="5" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>612</v>
+        <v>1100</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>220</v>
@@ -4913,7 +4914,7 @@
     </row>
     <row r="6" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>613</v>
+        <v>1101</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>220</v>
@@ -4945,7 +4946,7 @@
     </row>
     <row r="7" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>614</v>
+        <v>1102</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>220</v>
@@ -4977,7 +4978,7 @@
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>615</v>
+        <v>1103</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>220</v>
@@ -5009,7 +5010,7 @@
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>616</v>
+        <v>1104</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>220</v>
@@ -5041,7 +5042,7 @@
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>617</v>
+        <v>1105</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>220</v>
@@ -5073,7 +5074,7 @@
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>618</v>
+        <v>1106</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>220</v>
@@ -5105,7 +5106,7 @@
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>619</v>
+        <v>1107</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>220</v>
@@ -5137,7 +5138,7 @@
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>620</v>
+        <v>1108</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>220</v>
@@ -5169,7 +5170,7 @@
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>621</v>
+        <v>1109</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>220</v>
@@ -5201,7 +5202,7 @@
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>622</v>
+        <v>1110</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>220</v>
@@ -5233,7 +5234,7 @@
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>623</v>
+        <v>1111</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>220</v>
@@ -5265,7 +5266,7 @@
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>829</v>
+        <v>1331</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>220</v>
@@ -5297,7 +5298,7 @@
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>624</v>
+        <v>1112</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>220</v>
@@ -5329,7 +5330,7 @@
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>625</v>
+        <v>1113</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>220</v>
@@ -5361,7 +5362,7 @@
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>626</v>
+        <v>1114</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>220</v>
@@ -5393,7 +5394,7 @@
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1387</v>
+        <v>1332</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>220</v>
@@ -5405,7 +5406,7 @@
         <v>43354465</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1403</v>
+        <v>1071</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
@@ -5425,7 +5426,7 @@
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>1388</v>
+        <v>1115</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>220</v>
@@ -5437,7 +5438,7 @@
         <v>43354465</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1403</v>
+        <v>1071</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>32</v>
@@ -5457,7 +5458,7 @@
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1389</v>
+        <v>1116</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>220</v>
@@ -5469,7 +5470,7 @@
         <v>43354465</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1403</v>
+        <v>1071</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>19</v>
@@ -5489,7 +5490,7 @@
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1386</v>
+        <v>1117</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>220</v>
@@ -5501,7 +5502,7 @@
         <v>43354465</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1403</v>
+        <v>1071</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>33</v>
@@ -5521,7 +5522,7 @@
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>830</v>
+        <v>1333</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>220</v>
@@ -5553,7 +5554,7 @@
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>627</v>
+        <v>1118</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>220</v>
@@ -5585,7 +5586,7 @@
     </row>
     <row r="27" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>628</v>
+        <v>1119</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>220</v>
@@ -5617,7 +5618,7 @@
     </row>
     <row r="28" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>629</v>
+        <v>1120</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>220</v>
@@ -5649,7 +5650,7 @@
     </row>
     <row r="29" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>831</v>
+        <v>1334</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>220</v>
@@ -5681,7 +5682,7 @@
     </row>
     <row r="30" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>832</v>
+        <v>1335</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>220</v>
@@ -5713,7 +5714,7 @@
     </row>
     <row r="31" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>833</v>
+        <v>1336</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>220</v>
@@ -5745,7 +5746,7 @@
     </row>
     <row r="32" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>630</v>
+        <v>1121</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>220</v>
@@ -5777,7 +5778,7 @@
     </row>
     <row r="33" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>631</v>
+        <v>1122</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>220</v>
@@ -5809,7 +5810,7 @@
     </row>
     <row r="34" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>632</v>
+        <v>1123</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>220</v>
@@ -5841,7 +5842,7 @@
     </row>
     <row r="35" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>633</v>
+        <v>1124</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>220</v>
@@ -5873,7 +5874,7 @@
     </row>
     <row r="36" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>834</v>
+        <v>1337</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>220</v>
@@ -5905,7 +5906,7 @@
     </row>
     <row r="37" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>634</v>
+        <v>1125</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>220</v>
@@ -5937,7 +5938,7 @@
     </row>
     <row r="38" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>835</v>
+        <v>1338</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>220</v>
@@ -5969,7 +5970,7 @@
     </row>
     <row r="39" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>635</v>
+        <v>1126</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>220</v>
@@ -6001,7 +6002,7 @@
     </row>
     <row r="40" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>636</v>
+        <v>1127</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>220</v>
@@ -6033,7 +6034,7 @@
     </row>
     <row r="41" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>836</v>
+        <v>1339</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>220</v>
@@ -6065,7 +6066,7 @@
     </row>
     <row r="42" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>837</v>
+        <v>1340</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>220</v>
@@ -6097,7 +6098,7 @@
     </row>
     <row r="43" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>637</v>
+        <v>1128</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>220</v>
@@ -6129,7 +6130,7 @@
     </row>
     <row r="44" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>638</v>
+        <v>1129</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>220</v>
@@ -6161,7 +6162,7 @@
     </row>
     <row r="45" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>838</v>
+        <v>1341</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>220</v>
@@ -6193,7 +6194,7 @@
     </row>
     <row r="46" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>639</v>
+        <v>1130</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>220</v>
@@ -6225,7 +6226,7 @@
     </row>
     <row r="47" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>640</v>
+        <v>1131</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>220</v>
@@ -6257,7 +6258,7 @@
     </row>
     <row r="48" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>839</v>
+        <v>1342</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>220</v>
@@ -6289,7 +6290,7 @@
     </row>
     <row r="49" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>641</v>
+        <v>1132</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>220</v>
@@ -6321,7 +6322,7 @@
     </row>
     <row r="50" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>840</v>
+        <v>1343</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>220</v>
@@ -6353,7 +6354,7 @@
     </row>
     <row r="51" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>642</v>
+        <v>1133</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>220</v>
@@ -6385,7 +6386,7 @@
     </row>
     <row r="52" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>841</v>
+        <v>1344</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>220</v>
@@ -6417,7 +6418,7 @@
     </row>
     <row r="53" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>643</v>
+        <v>1134</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>220</v>
@@ -6449,7 +6450,7 @@
     </row>
     <row r="54" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>644</v>
+        <v>1135</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>220</v>
@@ -6481,7 +6482,7 @@
     </row>
     <row r="55" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>645</v>
+        <v>1136</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>220</v>
@@ -6513,7 +6514,7 @@
     </row>
     <row r="56" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>842</v>
+        <v>1345</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>220</v>
@@ -6545,7 +6546,7 @@
     </row>
     <row r="57" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>646</v>
+        <v>1137</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>220</v>
@@ -6577,7 +6578,7 @@
     </row>
     <row r="58" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>647</v>
+        <v>1138</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>220</v>
@@ -6609,7 +6610,7 @@
     </row>
     <row r="59" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>648</v>
+        <v>1139</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>220</v>
@@ -6641,7 +6642,7 @@
     </row>
     <row r="60" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>649</v>
+        <v>1140</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>220</v>
@@ -6673,7 +6674,7 @@
     </row>
     <row r="61" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>843</v>
+        <v>1346</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>220</v>
@@ -6705,7 +6706,7 @@
     </row>
     <row r="62" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>650</v>
+        <v>1141</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>220</v>
@@ -6737,7 +6738,7 @@
     </row>
     <row r="63" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>651</v>
+        <v>1142</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>220</v>
@@ -6769,7 +6770,7 @@
     </row>
     <row r="64" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>652</v>
+        <v>1143</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>220</v>
@@ -6801,7 +6802,7 @@
     </row>
     <row r="65" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>844</v>
+        <v>1347</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>220</v>
@@ -6833,7 +6834,7 @@
     </row>
     <row r="66" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>845</v>
+        <v>1348</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>220</v>
@@ -6865,7 +6866,7 @@
     </row>
     <row r="67" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>653</v>
+        <v>1144</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>220</v>
@@ -6897,7 +6898,7 @@
     </row>
     <row r="68" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>654</v>
+        <v>1145</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>220</v>
@@ -6929,7 +6930,7 @@
     </row>
     <row r="69" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>655</v>
+        <v>1146</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>220</v>
@@ -6961,7 +6962,7 @@
     </row>
     <row r="70" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>656</v>
+        <v>1147</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>220</v>
@@ -6993,7 +6994,7 @@
     </row>
     <row r="71" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>1394</v>
+        <v>1349</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>220</v>
@@ -7025,7 +7026,7 @@
     </row>
     <row r="72" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>1395</v>
+        <v>1350</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>220</v>
@@ -7057,7 +7058,7 @@
     </row>
     <row r="73" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>1396</v>
+        <v>1148</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>220</v>
@@ -7089,7 +7090,7 @@
     </row>
     <row r="74" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>1397</v>
+        <v>1149</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>220</v>
@@ -7121,7 +7122,7 @@
     </row>
     <row r="75" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>657</v>
+        <v>1150</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>220</v>
@@ -7153,7 +7154,7 @@
     </row>
     <row r="76" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>658</v>
+        <v>1151</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>220</v>
@@ -7185,7 +7186,7 @@
     </row>
     <row r="77" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>659</v>
+        <v>1152</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>220</v>
@@ -7217,7 +7218,7 @@
     </row>
     <row r="78" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>660</v>
+        <v>1153</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>220</v>
@@ -7249,7 +7250,7 @@
     </row>
     <row r="79" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>846</v>
+        <v>1351</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>220</v>
@@ -7281,7 +7282,7 @@
     </row>
     <row r="80" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>661</v>
+        <v>1154</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>220</v>
@@ -7313,7 +7314,7 @@
     </row>
     <row r="81" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>662</v>
+        <v>1155</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>220</v>
@@ -7345,7 +7346,7 @@
     </row>
     <row r="82" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>847</v>
+        <v>1352</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>220</v>
@@ -7377,7 +7378,7 @@
     </row>
     <row r="83" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>663</v>
+        <v>1156</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>220</v>
@@ -7409,7 +7410,7 @@
     </row>
     <row r="84" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>664</v>
+        <v>1157</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>220</v>
@@ -7441,7 +7442,7 @@
     </row>
     <row r="85" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>665</v>
+        <v>1158</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>220</v>
@@ -7473,7 +7474,7 @@
     </row>
     <row r="86" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>666</v>
+        <v>1159</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>220</v>
@@ -7505,7 +7506,7 @@
     </row>
     <row r="87" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>667</v>
+        <v>1160</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>220</v>
@@ -7537,7 +7538,7 @@
     </row>
     <row r="88" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>668</v>
+        <v>1161</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>220</v>
@@ -7569,7 +7570,7 @@
     </row>
     <row r="89" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>669</v>
+        <v>1162</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>220</v>
@@ -7601,7 +7602,7 @@
     </row>
     <row r="90" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>670</v>
+        <v>1163</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>220</v>
@@ -7633,7 +7634,7 @@
     </row>
     <row r="91" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>671</v>
+        <v>1164</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>220</v>
@@ -7665,7 +7666,7 @@
     </row>
     <row r="92" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>848</v>
+        <v>1353</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>220</v>
@@ -7697,7 +7698,7 @@
     </row>
     <row r="93" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>672</v>
+        <v>1165</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>220</v>
@@ -7729,7 +7730,7 @@
     </row>
     <row r="94" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>673</v>
+        <v>1166</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>220</v>
@@ -7761,7 +7762,7 @@
     </row>
     <row r="95" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>674</v>
+        <v>1167</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>220</v>
@@ -7793,7 +7794,7 @@
     </row>
     <row r="96" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>675</v>
+        <v>1168</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>220</v>
@@ -7825,7 +7826,7 @@
     </row>
     <row r="97" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>676</v>
+        <v>1169</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>220</v>
@@ -7857,7 +7858,7 @@
     </row>
     <row r="98" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>677</v>
+        <v>1170</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>220</v>
@@ -7889,7 +7890,7 @@
     </row>
     <row r="99" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>678</v>
+        <v>1171</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>220</v>
@@ -7921,7 +7922,7 @@
     </row>
     <row r="100" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>679</v>
+        <v>1172</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>220</v>
@@ -7953,7 +7954,7 @@
     </row>
     <row r="101" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>680</v>
+        <v>1173</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>220</v>
@@ -7985,7 +7986,7 @@
     </row>
     <row r="102" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>849</v>
+        <v>1354</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>220</v>
@@ -8017,7 +8018,7 @@
     </row>
     <row r="103" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>681</v>
+        <v>1174</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>220</v>
@@ -8049,7 +8050,7 @@
     </row>
     <row r="104" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>682</v>
+        <v>1175</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>220</v>
@@ -8081,7 +8082,7 @@
     </row>
     <row r="105" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>683</v>
+        <v>1176</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>220</v>
@@ -8113,7 +8114,7 @@
     </row>
     <row r="106" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>684</v>
+        <v>1177</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>220</v>
@@ -8145,7 +8146,7 @@
     </row>
     <row r="107" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>685</v>
+        <v>1178</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>220</v>
@@ -8177,7 +8178,7 @@
     </row>
     <row r="108" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>1432</v>
+        <v>1179</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>220</v>
@@ -8209,7 +8210,7 @@
     </row>
     <row r="109" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>686</v>
+        <v>1180</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>220</v>
@@ -8241,7 +8242,7 @@
     </row>
     <row r="110" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>687</v>
+        <v>1181</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>220</v>
@@ -8273,7 +8274,7 @@
     </row>
     <row r="111" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>688</v>
+        <v>1182</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>220</v>
@@ -8305,7 +8306,7 @@
     </row>
     <row r="112" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>689</v>
+        <v>1183</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>220</v>
@@ -8337,7 +8338,7 @@
     </row>
     <row r="113" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>690</v>
+        <v>1184</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>220</v>
@@ -8369,7 +8370,7 @@
     </row>
     <row r="114" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>691</v>
+        <v>1185</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>220</v>
@@ -8401,7 +8402,7 @@
     </row>
     <row r="115" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>692</v>
+        <v>1186</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>220</v>
@@ -8433,7 +8434,7 @@
     </row>
     <row r="116" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>850</v>
+        <v>1355</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>220</v>
@@ -8465,7 +8466,7 @@
     </row>
     <row r="117" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>693</v>
+        <v>1187</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>220</v>
@@ -8497,7 +8498,7 @@
     </row>
     <row r="118" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>694</v>
+        <v>1188</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>220</v>
@@ -8529,7 +8530,7 @@
     </row>
     <row r="119" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>1399</v>
+        <v>1189</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>220</v>
@@ -8541,7 +8542,7 @@
         <v>43606391</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1402</v>
+        <v>1070</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>19</v>
@@ -8561,7 +8562,7 @@
     </row>
     <row r="120" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1400</v>
+        <v>1190</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>220</v>
@@ -8573,7 +8574,7 @@
         <v>43606391</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>1402</v>
+        <v>1070</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>21</v>
@@ -8593,7 +8594,7 @@
     </row>
     <row r="121" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>1401</v>
+        <v>1191</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>220</v>
@@ -8605,7 +8606,7 @@
         <v>43606391</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>1402</v>
+        <v>1070</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>102</v>
@@ -8625,7 +8626,7 @@
     </row>
     <row r="122" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>695</v>
+        <v>1192</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>220</v>
@@ -8657,7 +8658,7 @@
     </row>
     <row r="123" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>851</v>
+        <v>1356</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>220</v>
@@ -8689,7 +8690,7 @@
     </row>
     <row r="124" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>696</v>
+        <v>1193</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>220</v>
@@ -8721,7 +8722,7 @@
     </row>
     <row r="125" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>697</v>
+        <v>1194</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>220</v>
@@ -8753,7 +8754,7 @@
     </row>
     <row r="126" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>698</v>
+        <v>1195</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>220</v>
@@ -8785,7 +8786,7 @@
     </row>
     <row r="127" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>699</v>
+        <v>1196</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>220</v>
@@ -8817,7 +8818,7 @@
     </row>
     <row r="128" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>700</v>
+        <v>1197</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>220</v>
@@ -8849,7 +8850,7 @@
     </row>
     <row r="129" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>701</v>
+        <v>1198</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>220</v>
@@ -8881,7 +8882,7 @@
     </row>
     <row r="130" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>702</v>
+        <v>1199</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>220</v>
@@ -8913,7 +8914,7 @@
     </row>
     <row r="131" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>703</v>
+        <v>1200</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>220</v>
@@ -8945,7 +8946,7 @@
     </row>
     <row r="132" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>704</v>
+        <v>1201</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>220</v>
@@ -8977,7 +8978,7 @@
     </row>
     <row r="133" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>852</v>
+        <v>1357</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>220</v>
@@ -9009,7 +9010,7 @@
     </row>
     <row r="134" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>705</v>
+        <v>1202</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>220</v>
@@ -9041,7 +9042,7 @@
     </row>
     <row r="135" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>853</v>
+        <v>1358</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>220</v>
@@ -9073,7 +9074,7 @@
     </row>
     <row r="136" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>854</v>
+        <v>1359</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>220</v>
@@ -9105,7 +9106,7 @@
     </row>
     <row r="137" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>706</v>
+        <v>1203</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>220</v>
@@ -9137,7 +9138,7 @@
     </row>
     <row r="138" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>855</v>
+        <v>1360</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>220</v>
@@ -9169,7 +9170,7 @@
     </row>
     <row r="139" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>707</v>
+        <v>1204</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>220</v>
@@ -9201,7 +9202,7 @@
     </row>
     <row r="140" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>856</v>
+        <v>1361</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>220</v>
@@ -9233,7 +9234,7 @@
     </row>
     <row r="141" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>708</v>
+        <v>1205</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>220</v>
@@ -9265,7 +9266,7 @@
     </row>
     <row r="142" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>857</v>
+        <v>1362</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>220</v>
@@ -9297,7 +9298,7 @@
     </row>
     <row r="143" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>709</v>
+        <v>1206</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>220</v>
@@ -9329,7 +9330,7 @@
     </row>
     <row r="144" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>710</v>
+        <v>1207</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>220</v>
@@ -9361,7 +9362,7 @@
     </row>
     <row r="145" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>711</v>
+        <v>1208</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>220</v>
@@ -9393,7 +9394,7 @@
     </row>
     <row r="146" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>712</v>
+        <v>1209</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>220</v>
@@ -9425,7 +9426,7 @@
     </row>
     <row r="147" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>713</v>
+        <v>1210</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>220</v>
@@ -9457,7 +9458,7 @@
     </row>
     <row r="148" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>858</v>
+        <v>1363</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>220</v>
@@ -9489,7 +9490,7 @@
     </row>
     <row r="149" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>714</v>
+        <v>1211</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>220</v>
@@ -9521,7 +9522,7 @@
     </row>
     <row r="150" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>859</v>
+        <v>1364</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>220</v>
@@ -9553,7 +9554,7 @@
     </row>
     <row r="151" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>860</v>
+        <v>1365</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>220</v>
@@ -9585,7 +9586,7 @@
     </row>
     <row r="152" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>715</v>
+        <v>1212</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>220</v>
@@ -9617,7 +9618,7 @@
     </row>
     <row r="153" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>716</v>
+        <v>1213</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>220</v>
@@ -9649,7 +9650,7 @@
     </row>
     <row r="154" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>717</v>
+        <v>1214</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>220</v>
@@ -9681,7 +9682,7 @@
     </row>
     <row r="155" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>861</v>
+        <v>1366</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>220</v>
@@ -9713,7 +9714,7 @@
     </row>
     <row r="156" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>718</v>
+        <v>1215</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>220</v>
@@ -9745,7 +9746,7 @@
     </row>
     <row r="157" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>719</v>
+        <v>1216</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>220</v>
@@ -9777,7 +9778,7 @@
     </row>
     <row r="158" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>862</v>
+        <v>1367</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>220</v>
@@ -9809,7 +9810,7 @@
     </row>
     <row r="159" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>720</v>
+        <v>1217</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>220</v>
@@ -9841,7 +9842,7 @@
     </row>
     <row r="160" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>721</v>
+        <v>1218</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>220</v>
@@ -9873,7 +9874,7 @@
     </row>
     <row r="161" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>722</v>
+        <v>1219</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>220</v>
@@ -9905,7 +9906,7 @@
     </row>
     <row r="162" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>863</v>
+        <v>1368</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>220</v>
@@ -9937,7 +9938,7 @@
     </row>
     <row r="163" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>723</v>
+        <v>1220</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>220</v>
@@ -9969,7 +9970,7 @@
     </row>
     <row r="164" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>724</v>
+        <v>1221</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>220</v>
@@ -10001,7 +10002,7 @@
     </row>
     <row r="165" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>725</v>
+        <v>1222</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>220</v>
@@ -10033,7 +10034,7 @@
     </row>
     <row r="166" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>864</v>
+        <v>1369</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>220</v>
@@ -10065,7 +10066,7 @@
     </row>
     <row r="167" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>726</v>
+        <v>1223</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>220</v>
@@ -10097,7 +10098,7 @@
     </row>
     <row r="168" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>727</v>
+        <v>1224</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>220</v>
@@ -10129,7 +10130,7 @@
     </row>
     <row r="169" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>728</v>
+        <v>1225</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>220</v>
@@ -10161,7 +10162,7 @@
     </row>
     <row r="170" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>729</v>
+        <v>1226</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>220</v>
@@ -10193,7 +10194,7 @@
     </row>
     <row r="171" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>865</v>
+        <v>1370</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>220</v>
@@ -10225,7 +10226,7 @@
     </row>
     <row r="172" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>730</v>
+        <v>1227</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>220</v>
@@ -10257,7 +10258,7 @@
     </row>
     <row r="173" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>866</v>
+        <v>1371</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>220</v>
@@ -10289,7 +10290,7 @@
     </row>
     <row r="174" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>731</v>
+        <v>1228</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>220</v>
@@ -10321,7 +10322,7 @@
     </row>
     <row r="175" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>867</v>
+        <v>1372</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>220</v>
@@ -10353,7 +10354,7 @@
     </row>
     <row r="176" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>732</v>
+        <v>1229</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>220</v>
@@ -10385,7 +10386,7 @@
     </row>
     <row r="177" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>733</v>
+        <v>1230</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>220</v>
@@ -10417,7 +10418,7 @@
     </row>
     <row r="178" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>734</v>
+        <v>1231</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>220</v>
@@ -10449,7 +10450,7 @@
     </row>
     <row r="179" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>868</v>
+        <v>1373</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>220</v>
@@ -10481,7 +10482,7 @@
     </row>
     <row r="180" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>869</v>
+        <v>1374</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>220</v>
@@ -10513,7 +10514,7 @@
     </row>
     <row r="181" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>735</v>
+        <v>1232</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>220</v>
@@ -10545,7 +10546,7 @@
     </row>
     <row r="182" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>736</v>
+        <v>1233</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>220</v>
@@ -10577,7 +10578,7 @@
     </row>
     <row r="183" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>737</v>
+        <v>1234</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>220</v>
@@ -10609,7 +10610,7 @@
     </row>
     <row r="184" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>870</v>
+        <v>1375</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>220</v>
@@ -10641,7 +10642,7 @@
     </row>
     <row r="185" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>738</v>
+        <v>1235</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>220</v>
@@ -10673,7 +10674,7 @@
     </row>
     <row r="186" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>739</v>
+        <v>1236</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>220</v>
@@ -10705,7 +10706,7 @@
     </row>
     <row r="187" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>871</v>
+        <v>1376</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>220</v>
@@ -10737,7 +10738,7 @@
     </row>
     <row r="188" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>740</v>
+        <v>1237</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>220</v>
@@ -10769,7 +10770,7 @@
     </row>
     <row r="189" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>741</v>
+        <v>1238</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>220</v>
@@ -10801,7 +10802,7 @@
     </row>
     <row r="190" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>742</v>
+        <v>1239</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>220</v>
@@ -10833,7 +10834,7 @@
     </row>
     <row r="191" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>872</v>
+        <v>1377</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>220</v>
@@ -10865,7 +10866,7 @@
     </row>
     <row r="192" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>743</v>
+        <v>1240</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>220</v>
@@ -10897,7 +10898,7 @@
     </row>
     <row r="193" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>744</v>
+        <v>1241</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>220</v>
@@ -10929,7 +10930,7 @@
     </row>
     <row r="194" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>745</v>
+        <v>1242</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>220</v>
@@ -10961,7 +10962,7 @@
     </row>
     <row r="195" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>873</v>
+        <v>1378</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>220</v>
@@ -10993,7 +10994,7 @@
     </row>
     <row r="196" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>746</v>
+        <v>1243</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>220</v>
@@ -11025,7 +11026,7 @@
     </row>
     <row r="197" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>747</v>
+        <v>1244</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>220</v>
@@ -11057,7 +11058,7 @@
     </row>
     <row r="198" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>874</v>
+        <v>1379</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>220</v>
@@ -11089,7 +11090,7 @@
     </row>
     <row r="199" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>748</v>
+        <v>1245</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>220</v>
@@ -11121,7 +11122,7 @@
     </row>
     <row r="200" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>749</v>
+        <v>1246</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>220</v>
@@ -11153,7 +11154,7 @@
     </row>
     <row r="201" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>750</v>
+        <v>1247</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>220</v>
@@ -11185,7 +11186,7 @@
     </row>
     <row r="202" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>751</v>
+        <v>1248</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>220</v>
@@ -11217,7 +11218,7 @@
     </row>
     <row r="203" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>752</v>
+        <v>1249</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>220</v>
@@ -11249,7 +11250,7 @@
     </row>
     <row r="204" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>753</v>
+        <v>1250</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>220</v>
@@ -11281,7 +11282,7 @@
     </row>
     <row r="205" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>754</v>
+        <v>1251</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>220</v>
@@ -11313,7 +11314,7 @@
     </row>
     <row r="206" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>755</v>
+        <v>1252</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>220</v>
@@ -11345,7 +11346,7 @@
     </row>
     <row r="207" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>756</v>
+        <v>1253</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>220</v>
@@ -11377,7 +11378,7 @@
     </row>
     <row r="208" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>757</v>
+        <v>1254</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>220</v>
@@ -11409,7 +11410,7 @@
     </row>
     <row r="209" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>758</v>
+        <v>1255</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>220</v>
@@ -11441,7 +11442,7 @@
     </row>
     <row r="210" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>875</v>
+        <v>1380</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>220</v>
@@ -11473,7 +11474,7 @@
     </row>
     <row r="211" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>759</v>
+        <v>1256</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>220</v>
@@ -11505,7 +11506,7 @@
     </row>
     <row r="212" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>760</v>
+        <v>1257</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>220</v>
@@ -11537,7 +11538,7 @@
     </row>
     <row r="213" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>761</v>
+        <v>1258</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>220</v>
@@ -11569,7 +11570,7 @@
     </row>
     <row r="214" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>762</v>
+        <v>1259</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>220</v>
@@ -11601,7 +11602,7 @@
     </row>
     <row r="215" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>763</v>
+        <v>1260</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>220</v>
@@ -11633,7 +11634,7 @@
     </row>
     <row r="216" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>764</v>
+        <v>1261</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>220</v>
@@ -11665,7 +11666,7 @@
     </row>
     <row r="217" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>765</v>
+        <v>1262</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>220</v>
@@ -11697,7 +11698,7 @@
     </row>
     <row r="218" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>876</v>
+        <v>1381</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>220</v>
@@ -11729,7 +11730,7 @@
     </row>
     <row r="219" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>766</v>
+        <v>1263</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>220</v>
@@ -11761,7 +11762,7 @@
     </row>
     <row r="220" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>767</v>
+        <v>1264</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>220</v>
@@ -11793,7 +11794,7 @@
     </row>
     <row r="221" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>768</v>
+        <v>1265</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>220</v>
@@ -11825,7 +11826,7 @@
     </row>
     <row r="222" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>769</v>
+        <v>1266</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>220</v>
@@ -11857,7 +11858,7 @@
     </row>
     <row r="223" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>770</v>
+        <v>1267</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>610</v>
@@ -11889,7 +11890,7 @@
     </row>
     <row r="224" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>771</v>
+        <v>1268</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>610</v>
@@ -11921,7 +11922,7 @@
     </row>
     <row r="225" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>772</v>
+        <v>1269</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>610</v>
@@ -11953,7 +11954,7 @@
     </row>
     <row r="226" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>773</v>
+        <v>1270</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>610</v>
@@ -11985,7 +11986,7 @@
     </row>
     <row r="227" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>877</v>
+        <v>1382</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>610</v>
@@ -12017,7 +12018,7 @@
     </row>
     <row r="228" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>878</v>
+        <v>1383</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>610</v>
@@ -12049,7 +12050,7 @@
     </row>
     <row r="229" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>879</v>
+        <v>1384</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>610</v>
@@ -12081,7 +12082,7 @@
     </row>
     <row r="230" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>774</v>
+        <v>1271</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>610</v>
@@ -12113,7 +12114,7 @@
     </row>
     <row r="231" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>775</v>
+        <v>1272</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>610</v>
@@ -12145,7 +12146,7 @@
     </row>
     <row r="232" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>776</v>
+        <v>1273</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>610</v>
@@ -12177,7 +12178,7 @@
     </row>
     <row r="233" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>777</v>
+        <v>1274</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>610</v>
@@ -12209,7 +12210,7 @@
     </row>
     <row r="234" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>610</v>
@@ -12221,7 +12222,7 @@
         <v>54111405</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>1398</v>
+        <v>1069</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>10</v>
@@ -12241,7 +12242,7 @@
     </row>
     <row r="235" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>1391</v>
+        <v>1275</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>610</v>
@@ -12253,7 +12254,7 @@
         <v>54111405</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>1398</v>
+        <v>1069</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>172</v>
@@ -12273,7 +12274,7 @@
     </row>
     <row r="236" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>610</v>
@@ -12285,7 +12286,7 @@
         <v>54111405</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>1398</v>
+        <v>1069</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>173</v>
@@ -12305,7 +12306,7 @@
     </row>
     <row r="237" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>1393</v>
+        <v>1276</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>610</v>
@@ -12317,7 +12318,7 @@
         <v>54111405</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>1398</v>
+        <v>1069</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>21</v>
@@ -12337,7 +12338,7 @@
     </row>
     <row r="238" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>880</v>
+        <v>1387</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>610</v>
@@ -12369,7 +12370,7 @@
     </row>
     <row r="239" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>778</v>
+        <v>1277</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>610</v>
@@ -12401,7 +12402,7 @@
     </row>
     <row r="240" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>779</v>
+        <v>1278</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>610</v>
@@ -12433,7 +12434,7 @@
     </row>
     <row r="241" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>780</v>
+        <v>1279</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>610</v>
@@ -12465,7 +12466,7 @@
     </row>
     <row r="242" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>881</v>
+        <v>1388</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>610</v>
@@ -12497,7 +12498,7 @@
     </row>
     <row r="243" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>781</v>
+        <v>1280</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>610</v>
@@ -12529,7 +12530,7 @@
     </row>
     <row r="244" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>782</v>
+        <v>1281</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>610</v>
@@ -12561,7 +12562,7 @@
     </row>
     <row r="245" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>783</v>
+        <v>1282</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>610</v>
@@ -12593,7 +12594,7 @@
     </row>
     <row r="246" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>784</v>
+        <v>1283</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>610</v>
@@ -12625,7 +12626,7 @@
     </row>
     <row r="247" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>785</v>
+        <v>1284</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>610</v>
@@ -12657,7 +12658,7 @@
     </row>
     <row r="248" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>882</v>
+        <v>1389</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>610</v>
@@ -12689,7 +12690,7 @@
     </row>
     <row r="249" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>883</v>
+        <v>1285</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>610</v>
@@ -12721,7 +12722,7 @@
     </row>
     <row r="250" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>884</v>
+        <v>1286</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>610</v>
@@ -12753,7 +12754,7 @@
     </row>
     <row r="251" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>885</v>
+        <v>1390</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>610</v>
@@ -12785,7 +12786,7 @@
     </row>
     <row r="252" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>786</v>
+        <v>1287</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>220</v>
@@ -12817,7 +12818,7 @@
     </row>
     <row r="253" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>886</v>
+        <v>1391</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>220</v>
@@ -12849,7 +12850,7 @@
     </row>
     <row r="254" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>887</v>
+        <v>1392</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>220</v>
@@ -12881,7 +12882,7 @@
     </row>
     <row r="255" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>888</v>
+        <v>1393</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>220</v>
@@ -12913,7 +12914,7 @@
     </row>
     <row r="256" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>889</v>
+        <v>1394</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>220</v>
@@ -12945,7 +12946,7 @@
     </row>
     <row r="257" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>787</v>
+        <v>1288</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>220</v>
@@ -12977,7 +12978,7 @@
     </row>
     <row r="258" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>788</v>
+        <v>1289</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>220</v>
@@ -13009,7 +13010,7 @@
     </row>
     <row r="259" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>890</v>
+        <v>1395</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>220</v>
@@ -13041,7 +13042,7 @@
     </row>
     <row r="260" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>789</v>
+        <v>1290</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>220</v>
@@ -13073,7 +13074,7 @@
     </row>
     <row r="261" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>891</v>
+        <v>1396</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>220</v>
@@ -13105,7 +13106,7 @@
     </row>
     <row r="262" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>790</v>
+        <v>1291</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>220</v>
@@ -13137,7 +13138,7 @@
     </row>
     <row r="263" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>892</v>
+        <v>1397</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>220</v>
@@ -13169,7 +13170,7 @@
     </row>
     <row r="264" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>791</v>
+        <v>1292</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>220</v>
@@ -13201,7 +13202,7 @@
     </row>
     <row r="265" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>792</v>
+        <v>1293</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>220</v>
@@ -13233,7 +13234,7 @@
     </row>
     <row r="266" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>793</v>
+        <v>1294</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>220</v>
@@ -13265,7 +13266,7 @@
     </row>
     <row r="267" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>794</v>
+        <v>1295</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>220</v>
@@ -13297,7 +13298,7 @@
     </row>
     <row r="268" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>795</v>
+        <v>1296</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>220</v>
@@ -13329,7 +13330,7 @@
     </row>
     <row r="269" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>796</v>
+        <v>1297</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>220</v>
@@ -13361,7 +13362,7 @@
     </row>
     <row r="270" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>797</v>
+        <v>1298</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>220</v>
@@ -13393,7 +13394,7 @@
     </row>
     <row r="271" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>798</v>
+        <v>1299</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>220</v>
@@ -13425,7 +13426,7 @@
     </row>
     <row r="272" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>799</v>
+        <v>1300</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>220</v>
@@ -13457,7 +13458,7 @@
     </row>
     <row r="273" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>893</v>
+        <v>1398</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>220</v>
@@ -13489,7 +13490,7 @@
     </row>
     <row r="274" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>800</v>
+        <v>1301</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>220</v>
@@ -13521,7 +13522,7 @@
     </row>
     <row r="275" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>894</v>
+        <v>1399</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>220</v>
@@ -13553,7 +13554,7 @@
     </row>
     <row r="276" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>801</v>
+        <v>1302</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>220</v>
@@ -13585,7 +13586,7 @@
     </row>
     <row r="277" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>802</v>
+        <v>1303</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>220</v>
@@ -13617,7 +13618,7 @@
     </row>
     <row r="278" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>803</v>
+        <v>1304</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>220</v>
@@ -13649,7 +13650,7 @@
     </row>
     <row r="279" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>895</v>
+        <v>1400</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>220</v>
@@ -13680,8 +13681,8 @@
       </c>
     </row>
     <row r="280" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="6" t="s">
-        <v>1431</v>
+      <c r="A280" s="2" t="s">
+        <v>1305</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>220</v>
@@ -13713,7 +13714,7 @@
     </row>
     <row r="281" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>896</v>
+        <v>1401</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>220</v>
@@ -13745,7 +13746,7 @@
     </row>
     <row r="282" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>804</v>
+        <v>1306</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>220</v>
@@ -13777,7 +13778,7 @@
     </row>
     <row r="283" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>897</v>
+        <v>1402</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>220</v>
@@ -13809,7 +13810,7 @@
     </row>
     <row r="284" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>805</v>
+        <v>1307</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>220</v>
@@ -13841,7 +13842,7 @@
     </row>
     <row r="285" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>898</v>
+        <v>1403</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>220</v>
@@ -13873,7 +13874,7 @@
     </row>
     <row r="286" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>806</v>
+        <v>1308</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>220</v>
@@ -13905,7 +13906,7 @@
     </row>
     <row r="287" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>807</v>
+        <v>1309</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>220</v>
@@ -13937,7 +13938,7 @@
     </row>
     <row r="288" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>808</v>
+        <v>1310</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>220</v>
@@ -13969,7 +13970,7 @@
     </row>
     <row r="289" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>809</v>
+        <v>1311</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>220</v>
@@ -14001,7 +14002,7 @@
     </row>
     <row r="290" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>810</v>
+        <v>1312</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>220</v>
@@ -14033,7 +14034,7 @@
     </row>
     <row r="291" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>811</v>
+        <v>1313</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>220</v>
@@ -14065,7 +14066,7 @@
     </row>
     <row r="292" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>812</v>
+        <v>1314</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>220</v>
@@ -14097,7 +14098,7 @@
     </row>
     <row r="293" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>813</v>
+        <v>1315</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>220</v>
@@ -14129,7 +14130,7 @@
     </row>
     <row r="294" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>814</v>
+        <v>1316</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>220</v>
@@ -14161,7 +14162,7 @@
     </row>
     <row r="295" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>815</v>
+        <v>1317</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>220</v>
@@ -14193,7 +14194,7 @@
     </row>
     <row r="296" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>899</v>
+        <v>1404</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>220</v>
@@ -14225,7 +14226,7 @@
     </row>
     <row r="297" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>816</v>
+        <v>1318</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>220</v>
@@ -14257,7 +14258,7 @@
     </row>
     <row r="298" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>817</v>
+        <v>1319</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>220</v>
@@ -14289,7 +14290,7 @@
     </row>
     <row r="299" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>818</v>
+        <v>1320</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>220</v>
@@ -14321,7 +14322,7 @@
     </row>
     <row r="300" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>819</v>
+        <v>1321</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>220</v>
@@ -14353,7 +14354,7 @@
     </row>
     <row r="301" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>900</v>
+        <v>1405</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>220</v>
@@ -14385,7 +14386,7 @@
     </row>
     <row r="302" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>820</v>
+        <v>1322</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>220</v>
@@ -14417,7 +14418,7 @@
     </row>
     <row r="303" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>821</v>
+        <v>1323</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>220</v>
@@ -14449,7 +14450,7 @@
     </row>
     <row r="304" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>822</v>
+        <v>1324</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>220</v>
@@ -14481,7 +14482,7 @@
     </row>
     <row r="305" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>823</v>
+        <v>1325</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>220</v>
@@ -14513,7 +14514,7 @@
     </row>
     <row r="306" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>824</v>
+        <v>1326</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>220</v>
@@ -14545,7 +14546,7 @@
     </row>
     <row r="307" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>901</v>
+        <v>1406</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>220</v>
@@ -14577,7 +14578,7 @@
     </row>
     <row r="308" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>825</v>
+        <v>1327</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>220</v>
@@ -14609,7 +14610,7 @@
     </row>
     <row r="309" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>826</v>
+        <v>1328</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>220</v>
@@ -14641,7 +14642,7 @@
     </row>
     <row r="310" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>902</v>
+        <v>1407</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>220</v>
@@ -14673,7 +14674,7 @@
     </row>
     <row r="311" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>903</v>
+        <v>1408</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>220</v>
@@ -14705,7 +14706,7 @@
     </row>
     <row r="312" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>904</v>
+        <v>611</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>221</v>
@@ -14737,7 +14738,7 @@
     </row>
     <row r="313" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>905</v>
+        <v>612</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>221</v>
@@ -14769,7 +14770,7 @@
     </row>
     <row r="314" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>906</v>
+        <v>613</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>221</v>
@@ -14801,7 +14802,7 @@
     </row>
     <row r="315" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>907</v>
+        <v>614</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>221</v>
@@ -14833,7 +14834,7 @@
     </row>
     <row r="316" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>908</v>
+        <v>615</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>221</v>
@@ -14865,7 +14866,7 @@
     </row>
     <row r="317" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>909</v>
+        <v>616</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>221</v>
@@ -14897,7 +14898,7 @@
     </row>
     <row r="318" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>910</v>
+        <v>617</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>221</v>
@@ -14929,7 +14930,7 @@
     </row>
     <row r="319" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>911</v>
+        <v>618</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>221</v>
@@ -14961,7 +14962,7 @@
     </row>
     <row r="320" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>912</v>
+        <v>619</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>221</v>
@@ -14993,7 +14994,7 @@
     </row>
     <row r="321" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>913</v>
+        <v>620</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>221</v>
@@ -15025,7 +15026,7 @@
     </row>
     <row r="322" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>914</v>
+        <v>621</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>221</v>
@@ -15057,7 +15058,7 @@
     </row>
     <row r="323" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>915</v>
+        <v>622</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>221</v>
@@ -15089,7 +15090,7 @@
     </row>
     <row r="324" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>916</v>
+        <v>623</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>221</v>
@@ -15121,7 +15122,7 @@
     </row>
     <row r="325" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>917</v>
+        <v>624</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>221</v>
@@ -15153,7 +15154,7 @@
     </row>
     <row r="326" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>918</v>
+        <v>625</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>221</v>
@@ -15185,7 +15186,7 @@
     </row>
     <row r="327" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>919</v>
+        <v>626</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>221</v>
@@ -15217,7 +15218,7 @@
     </row>
     <row r="328" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>920</v>
+        <v>627</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>221</v>
@@ -15249,7 +15250,7 @@
     </row>
     <row r="329" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>921</v>
+        <v>628</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>221</v>
@@ -15281,7 +15282,7 @@
     </row>
     <row r="330" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>922</v>
+        <v>629</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>221</v>
@@ -15313,7 +15314,7 @@
     </row>
     <row r="331" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>923</v>
+        <v>630</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>221</v>
@@ -15345,7 +15346,7 @@
     </row>
     <row r="332" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>924</v>
+        <v>631</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>221</v>
@@ -15377,7 +15378,7 @@
     </row>
     <row r="333" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>925</v>
+        <v>632</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>221</v>
@@ -15409,7 +15410,7 @@
     </row>
     <row r="334" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>926</v>
+        <v>633</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>221</v>
@@ -15441,7 +15442,7 @@
     </row>
     <row r="335" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>927</v>
+        <v>634</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>221</v>
@@ -15473,7 +15474,7 @@
     </row>
     <row r="336" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>928</v>
+        <v>635</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>221</v>
@@ -15505,7 +15506,7 @@
     </row>
     <row r="337" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>929</v>
+        <v>636</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>221</v>
@@ -15537,7 +15538,7 @@
     </row>
     <row r="338" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>930</v>
+        <v>637</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>221</v>
@@ -15569,7 +15570,7 @@
     </row>
     <row r="339" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>931</v>
+        <v>638</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>221</v>
@@ -15601,7 +15602,7 @@
     </row>
     <row r="340" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>932</v>
+        <v>639</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>221</v>
@@ -15633,7 +15634,7 @@
     </row>
     <row r="341" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>933</v>
+        <v>640</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>221</v>
@@ -15665,7 +15666,7 @@
     </row>
     <row r="342" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>934</v>
+        <v>641</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>221</v>
@@ -15697,7 +15698,7 @@
     </row>
     <row r="343" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>935</v>
+        <v>642</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>221</v>
@@ -15729,7 +15730,7 @@
     </row>
     <row r="344" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>936</v>
+        <v>643</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>221</v>
@@ -15761,7 +15762,7 @@
     </row>
     <row r="345" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>937</v>
+        <v>644</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>221</v>
@@ -15793,7 +15794,7 @@
     </row>
     <row r="346" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>938</v>
+        <v>645</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>221</v>
@@ -15825,7 +15826,7 @@
     </row>
     <row r="347" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>939</v>
+        <v>646</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>221</v>
@@ -15857,7 +15858,7 @@
     </row>
     <row r="348" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>940</v>
+        <v>647</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>221</v>
@@ -15889,7 +15890,7 @@
     </row>
     <row r="349" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>941</v>
+        <v>648</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>221</v>
@@ -15921,7 +15922,7 @@
     </row>
     <row r="350" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>942</v>
+        <v>649</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>221</v>
@@ -15953,7 +15954,7 @@
     </row>
     <row r="351" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>943</v>
+        <v>650</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>221</v>
@@ -15985,7 +15986,7 @@
     </row>
     <row r="352" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>944</v>
+        <v>651</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>221</v>
@@ -16017,7 +16018,7 @@
     </row>
     <row r="353" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>945</v>
+        <v>652</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>221</v>
@@ -16049,7 +16050,7 @@
     </row>
     <row r="354" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>946</v>
+        <v>653</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>221</v>
@@ -16081,7 +16082,7 @@
     </row>
     <row r="355" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>947</v>
+        <v>654</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>221</v>
@@ -16113,7 +16114,7 @@
     </row>
     <row r="356" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>948</v>
+        <v>655</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>273</v>
@@ -16145,7 +16146,7 @@
     </row>
     <row r="357" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>949</v>
+        <v>656</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>273</v>
@@ -16177,7 +16178,7 @@
     </row>
     <row r="358" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>950</v>
+        <v>657</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>273</v>
@@ -16209,7 +16210,7 @@
     </row>
     <row r="359" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>951</v>
+        <v>658</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>273</v>
@@ -16241,7 +16242,7 @@
     </row>
     <row r="360" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>952</v>
+        <v>659</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>273</v>
@@ -16273,7 +16274,7 @@
     </row>
     <row r="361" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>953</v>
+        <v>660</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>273</v>
@@ -16305,7 +16306,7 @@
     </row>
     <row r="362" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>954</v>
+        <v>661</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>273</v>
@@ -16337,7 +16338,7 @@
     </row>
     <row r="363" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>955</v>
+        <v>662</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>273</v>
@@ -16369,7 +16370,7 @@
     </row>
     <row r="364" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>956</v>
+        <v>663</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>273</v>
@@ -16401,7 +16402,7 @@
     </row>
     <row r="365" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>957</v>
+        <v>664</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>273</v>
@@ -16433,7 +16434,7 @@
     </row>
     <row r="366" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>958</v>
+        <v>665</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>273</v>
@@ -16465,7 +16466,7 @@
     </row>
     <row r="367" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>959</v>
+        <v>666</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>273</v>
@@ -16497,7 +16498,7 @@
     </row>
     <row r="368" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>960</v>
+        <v>667</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>273</v>
@@ -16529,7 +16530,7 @@
     </row>
     <row r="369" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>961</v>
+        <v>668</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>273</v>
@@ -16561,7 +16562,7 @@
     </row>
     <row r="370" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>962</v>
+        <v>669</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>273</v>
@@ -16593,7 +16594,7 @@
     </row>
     <row r="371" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>963</v>
+        <v>670</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>273</v>
@@ -16625,7 +16626,7 @@
     </row>
     <row r="372" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>964</v>
+        <v>671</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>273</v>
@@ -16657,7 +16658,7 @@
     </row>
     <row r="373" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>965</v>
+        <v>672</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>273</v>
@@ -16689,7 +16690,7 @@
     </row>
     <row r="374" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>966</v>
+        <v>673</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>273</v>
@@ -16721,7 +16722,7 @@
     </row>
     <row r="375" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>967</v>
+        <v>674</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>273</v>
@@ -16753,7 +16754,7 @@
     </row>
     <row r="376" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>968</v>
+        <v>675</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>273</v>
@@ -16785,7 +16786,7 @@
     </row>
     <row r="377" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>969</v>
+        <v>676</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>273</v>
@@ -16817,7 +16818,7 @@
     </row>
     <row r="378" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>970</v>
+        <v>677</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>273</v>
@@ -16849,7 +16850,7 @@
     </row>
     <row r="379" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>971</v>
+        <v>678</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>273</v>
@@ -16881,7 +16882,7 @@
     </row>
     <row r="380" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>972</v>
+        <v>679</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>273</v>
@@ -16913,7 +16914,7 @@
     </row>
     <row r="381" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>973</v>
+        <v>680</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>273</v>
@@ -16945,7 +16946,7 @@
     </row>
     <row r="382" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>974</v>
+        <v>681</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>273</v>
@@ -16977,7 +16978,7 @@
     </row>
     <row r="383" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>975</v>
+        <v>682</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>273</v>
@@ -17009,7 +17010,7 @@
     </row>
     <row r="384" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>976</v>
+        <v>683</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>273</v>
@@ -17041,7 +17042,7 @@
     </row>
     <row r="385" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>977</v>
+        <v>684</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>273</v>
@@ -17073,7 +17074,7 @@
     </row>
     <row r="386" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>978</v>
+        <v>685</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>273</v>
@@ -17105,7 +17106,7 @@
     </row>
     <row r="387" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>979</v>
+        <v>686</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>273</v>
@@ -17137,7 +17138,7 @@
     </row>
     <row r="388" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>980</v>
+        <v>687</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>273</v>
@@ -17169,7 +17170,7 @@
     </row>
     <row r="389" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>981</v>
+        <v>688</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>273</v>
@@ -17201,7 +17202,7 @@
     </row>
     <row r="390" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>982</v>
+        <v>689</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>273</v>
@@ -17233,7 +17234,7 @@
     </row>
     <row r="391" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>983</v>
+        <v>690</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>273</v>
@@ -17265,7 +17266,7 @@
     </row>
     <row r="392" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>984</v>
+        <v>691</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>221</v>
@@ -17297,7 +17298,7 @@
     </row>
     <row r="393" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>985</v>
+        <v>692</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>221</v>
@@ -17329,7 +17330,7 @@
     </row>
     <row r="394" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>986</v>
+        <v>1409</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>304</v>
@@ -17361,7 +17362,7 @@
     </row>
     <row r="395" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>987</v>
+        <v>1410</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>304</v>
@@ -17393,7 +17394,7 @@
     </row>
     <row r="396" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>988</v>
+        <v>693</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>304</v>
@@ -17425,7 +17426,7 @@
     </row>
     <row r="397" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>989</v>
+        <v>694</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>304</v>
@@ -17457,7 +17458,7 @@
     </row>
     <row r="398" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>990</v>
+        <v>1411</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>304</v>
@@ -17489,7 +17490,7 @@
     </row>
     <row r="399" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>991</v>
+        <v>695</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>304</v>
@@ -17521,7 +17522,7 @@
     </row>
     <row r="400" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>992</v>
+        <v>696</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>304</v>
@@ -17553,7 +17554,7 @@
     </row>
     <row r="401" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>993</v>
+        <v>697</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>304</v>
@@ -17585,7 +17586,7 @@
     </row>
     <row r="402" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>994</v>
+        <v>698</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>304</v>
@@ -17617,7 +17618,7 @@
     </row>
     <row r="403" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>995</v>
+        <v>699</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>304</v>
@@ -17649,7 +17650,7 @@
     </row>
     <row r="404" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>996</v>
+        <v>700</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>304</v>
@@ -17681,7 +17682,7 @@
     </row>
     <row r="405" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>997</v>
+        <v>701</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>304</v>
@@ -17713,7 +17714,7 @@
     </row>
     <row r="406" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>998</v>
+        <v>702</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>304</v>
@@ -17745,7 +17746,7 @@
     </row>
     <row r="407" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>999</v>
+        <v>703</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>304</v>
@@ -17777,7 +17778,7 @@
     </row>
     <row r="408" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>1000</v>
+        <v>704</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>304</v>
@@ -17809,7 +17810,7 @@
     </row>
     <row r="409" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>1001</v>
+        <v>705</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>304</v>
@@ -17841,7 +17842,7 @@
     </row>
     <row r="410" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>1002</v>
+        <v>706</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>304</v>
@@ -17873,7 +17874,7 @@
     </row>
     <row r="411" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>1003</v>
+        <v>707</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>304</v>
@@ -17905,7 +17906,7 @@
     </row>
     <row r="412" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>1004</v>
+        <v>708</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>304</v>
@@ -17937,7 +17938,7 @@
     </row>
     <row r="413" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>1005</v>
+        <v>709</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>304</v>
@@ -17969,7 +17970,7 @@
     </row>
     <row r="414" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>1006</v>
+        <v>710</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>304</v>
@@ -18001,7 +18002,7 @@
     </row>
     <row r="415" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>1007</v>
+        <v>711</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>304</v>
@@ -18033,7 +18034,7 @@
     </row>
     <row r="416" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>1008</v>
+        <v>712</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>304</v>
@@ -18065,7 +18066,7 @@
     </row>
     <row r="417" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>1009</v>
+        <v>713</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>304</v>
@@ -18097,7 +18098,7 @@
     </row>
     <row r="418" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>1010</v>
+        <v>714</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>304</v>
@@ -18129,7 +18130,7 @@
     </row>
     <row r="419" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>1011</v>
+        <v>715</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>304</v>
@@ -18161,7 +18162,7 @@
     </row>
     <row r="420" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>1012</v>
+        <v>716</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>304</v>
@@ -18193,7 +18194,7 @@
     </row>
     <row r="421" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>1013</v>
+        <v>717</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>304</v>
@@ -18225,7 +18226,7 @@
     </row>
     <row r="422" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>1014</v>
+        <v>718</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>304</v>
@@ -18257,7 +18258,7 @@
     </row>
     <row r="423" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>1015</v>
+        <v>719</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>304</v>
@@ -18289,7 +18290,7 @@
     </row>
     <row r="424" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>1016</v>
+        <v>720</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>304</v>
@@ -18321,7 +18322,7 @@
     </row>
     <row r="425" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>1017</v>
+        <v>721</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>304</v>
@@ -18353,7 +18354,7 @@
     </row>
     <row r="426" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>1018</v>
+        <v>722</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>304</v>
@@ -18385,7 +18386,7 @@
     </row>
     <row r="427" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>1019</v>
+        <v>1412</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>304</v>
@@ -18417,7 +18418,7 @@
     </row>
     <row r="428" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>1020</v>
+        <v>1413</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>304</v>
@@ -18449,7 +18450,7 @@
     </row>
     <row r="429" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>1021</v>
+        <v>723</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>304</v>
@@ -18481,7 +18482,7 @@
     </row>
     <row r="430" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>1022</v>
+        <v>724</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>304</v>
@@ -18513,7 +18514,7 @@
     </row>
     <row r="431" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>1023</v>
+        <v>1414</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>304</v>
@@ -18545,7 +18546,7 @@
     </row>
     <row r="432" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>1024</v>
+        <v>725</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>304</v>
@@ -18577,7 +18578,7 @@
     </row>
     <row r="433" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>1025</v>
+        <v>726</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>304</v>
@@ -18609,7 +18610,7 @@
     </row>
     <row r="434" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>1026</v>
+        <v>727</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>304</v>
@@ -18641,7 +18642,7 @@
     </row>
     <row r="435" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>1027</v>
+        <v>728</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>304</v>
@@ -18673,7 +18674,7 @@
     </row>
     <row r="436" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>1028</v>
+        <v>729</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>304</v>
@@ -18705,7 +18706,7 @@
     </row>
     <row r="437" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>1029</v>
+        <v>730</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>304</v>
@@ -18737,7 +18738,7 @@
     </row>
     <row r="438" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>1030</v>
+        <v>731</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>304</v>
@@ -18769,7 +18770,7 @@
     </row>
     <row r="439" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>1031</v>
+        <v>732</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>304</v>
@@ -18801,7 +18802,7 @@
     </row>
     <row r="440" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>1032</v>
+        <v>733</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>304</v>
@@ -18833,7 +18834,7 @@
     </row>
     <row r="441" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>1033</v>
+        <v>734</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>304</v>
@@ -18865,7 +18866,7 @@
     </row>
     <row r="442" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>1034</v>
+        <v>735</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>304</v>
@@ -18897,7 +18898,7 @@
     </row>
     <row r="443" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>1035</v>
+        <v>736</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>304</v>
@@ -18929,7 +18930,7 @@
     </row>
     <row r="444" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>1036</v>
+        <v>737</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>304</v>
@@ -18961,7 +18962,7 @@
     </row>
     <row r="445" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>1037</v>
+        <v>738</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>304</v>
@@ -18993,7 +18994,7 @@
     </row>
     <row r="446" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>1038</v>
+        <v>739</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>304</v>
@@ -19025,7 +19026,7 @@
     </row>
     <row r="447" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>1039</v>
+        <v>740</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>304</v>
@@ -19057,7 +19058,7 @@
     </row>
     <row r="448" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>1040</v>
+        <v>741</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>304</v>
@@ -19089,7 +19090,7 @@
     </row>
     <row r="449" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>1041</v>
+        <v>742</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>304</v>
@@ -19121,7 +19122,7 @@
     </row>
     <row r="450" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>1042</v>
+        <v>743</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>304</v>
@@ -19153,7 +19154,7 @@
     </row>
     <row r="451" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1043</v>
+        <v>744</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>304</v>
@@ -19185,7 +19186,7 @@
     </row>
     <row r="452" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>1044</v>
+        <v>745</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>304</v>
@@ -19217,7 +19218,7 @@
     </row>
     <row r="453" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1045</v>
+        <v>746</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>304</v>
@@ -19249,7 +19250,7 @@
     </row>
     <row r="454" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>1046</v>
+        <v>747</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>304</v>
@@ -19281,7 +19282,7 @@
     </row>
     <row r="455" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>1047</v>
+        <v>748</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>304</v>
@@ -19313,7 +19314,7 @@
     </row>
     <row r="456" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>1048</v>
+        <v>749</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>304</v>
@@ -19345,7 +19346,7 @@
     </row>
     <row r="457" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>1049</v>
+        <v>750</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>304</v>
@@ -19377,7 +19378,7 @@
     </row>
     <row r="458" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>1050</v>
+        <v>751</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>304</v>
@@ -19409,7 +19410,7 @@
     </row>
     <row r="459" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>1051</v>
+        <v>752</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>304</v>
@@ -19441,7 +19442,7 @@
     </row>
     <row r="460" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>1052</v>
+        <v>753</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>304</v>
@@ -19473,7 +19474,7 @@
     </row>
     <row r="461" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>1053</v>
+        <v>754</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>304</v>
@@ -19505,7 +19506,7 @@
     </row>
     <row r="462" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1054</v>
+        <v>755</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>304</v>
@@ -19537,7 +19538,7 @@
     </row>
     <row r="463" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1055</v>
+        <v>756</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>221</v>
@@ -19569,7 +19570,7 @@
     </row>
     <row r="464" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>1056</v>
+        <v>757</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>221</v>
@@ -19601,7 +19602,7 @@
     </row>
     <row r="465" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>1057</v>
+        <v>758</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>221</v>
@@ -19633,7 +19634,7 @@
     </row>
     <row r="466" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>1058</v>
+        <v>759</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>221</v>
@@ -19665,7 +19666,7 @@
     </row>
     <row r="467" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>1059</v>
+        <v>1415</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>221</v>
@@ -19697,7 +19698,7 @@
     </row>
     <row r="468" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>1060</v>
+        <v>760</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>221</v>
@@ -19729,7 +19730,7 @@
     </row>
     <row r="469" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>1061</v>
+        <v>761</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>221</v>
@@ -19761,7 +19762,7 @@
     </row>
     <row r="470" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>1062</v>
+        <v>762</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>221</v>
@@ -19793,7 +19794,7 @@
     </row>
     <row r="471" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>1063</v>
+        <v>1416</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>221</v>
@@ -19825,7 +19826,7 @@
     </row>
     <row r="472" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>1064</v>
+        <v>1417</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>221</v>
@@ -19857,7 +19858,7 @@
     </row>
     <row r="473" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>1065</v>
+        <v>763</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>221</v>
@@ -19889,7 +19890,7 @@
     </row>
     <row r="474" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>1066</v>
+        <v>764</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>221</v>
@@ -19921,7 +19922,7 @@
     </row>
     <row r="475" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>1067</v>
+        <v>765</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>221</v>
@@ -19953,7 +19954,7 @@
     </row>
     <row r="476" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>1068</v>
+        <v>766</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>221</v>
@@ -19985,7 +19986,7 @@
     </row>
     <row r="477" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>1069</v>
+        <v>1418</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>221</v>
@@ -20017,7 +20018,7 @@
     </row>
     <row r="478" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>1070</v>
+        <v>767</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>221</v>
@@ -20049,7 +20050,7 @@
     </row>
     <row r="479" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>1071</v>
+        <v>768</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>221</v>
@@ -20081,7 +20082,7 @@
     </row>
     <row r="480" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>1072</v>
+        <v>769</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>221</v>
@@ -20113,7 +20114,7 @@
     </row>
     <row r="481" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1073</v>
+        <v>1419</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>221</v>
@@ -20145,7 +20146,7 @@
     </row>
     <row r="482" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1074</v>
+        <v>770</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>221</v>
@@ -20177,7 +20178,7 @@
     </row>
     <row r="483" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1075</v>
+        <v>771</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>221</v>
@@ -20209,7 +20210,7 @@
     </row>
     <row r="484" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1076</v>
+        <v>772</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>221</v>
@@ -20241,7 +20242,7 @@
     </row>
     <row r="485" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1077</v>
+        <v>773</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>221</v>
@@ -20273,7 +20274,7 @@
     </row>
     <row r="486" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1078</v>
+        <v>774</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>221</v>
@@ -20305,7 +20306,7 @@
     </row>
     <row r="487" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1079</v>
+        <v>1420</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>221</v>
@@ -20337,7 +20338,7 @@
     </row>
     <row r="488" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>1080</v>
+        <v>775</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>221</v>
@@ -20369,7 +20370,7 @@
     </row>
     <row r="489" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1081</v>
+        <v>1421</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>221</v>
@@ -20401,7 +20402,7 @@
     </row>
     <row r="490" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>1082</v>
+        <v>776</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>221</v>
@@ -20433,7 +20434,7 @@
     </row>
     <row r="491" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>1083</v>
+        <v>777</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>221</v>
@@ -20465,7 +20466,7 @@
     </row>
     <row r="492" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>1084</v>
+        <v>1422</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>221</v>
@@ -20497,7 +20498,7 @@
     </row>
     <row r="493" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1085</v>
+        <v>778</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>221</v>
@@ -20529,7 +20530,7 @@
     </row>
     <row r="494" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>1086</v>
+        <v>779</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>221</v>
@@ -20561,7 +20562,7 @@
     </row>
     <row r="495" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>1087</v>
+        <v>780</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>221</v>
@@ -20593,7 +20594,7 @@
     </row>
     <row r="496" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>1088</v>
+        <v>781</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>221</v>
@@ -20625,7 +20626,7 @@
     </row>
     <row r="497" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>1089</v>
+        <v>782</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>273</v>
@@ -20657,7 +20658,7 @@
     </row>
     <row r="498" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>1090</v>
+        <v>783</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>273</v>
@@ -20689,7 +20690,7 @@
     </row>
     <row r="499" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>1091</v>
+        <v>784</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>273</v>
@@ -20721,7 +20722,7 @@
     </row>
     <row r="500" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>1092</v>
+        <v>785</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>273</v>
@@ -20753,7 +20754,7 @@
     </row>
     <row r="501" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>1093</v>
+        <v>1423</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>304</v>
@@ -20785,7 +20786,7 @@
     </row>
     <row r="502" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>1094</v>
+        <v>786</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>304</v>
@@ -20817,7 +20818,7 @@
     </row>
     <row r="503" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>1095</v>
+        <v>787</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>304</v>
@@ -20849,7 +20850,7 @@
     </row>
     <row r="504" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>1096</v>
+        <v>788</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>304</v>
@@ -20881,7 +20882,7 @@
     </row>
     <row r="505" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>1097</v>
+        <v>789</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>304</v>
@@ -20913,7 +20914,7 @@
     </row>
     <row r="506" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>1098</v>
+        <v>790</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>304</v>
@@ -20945,7 +20946,7 @@
     </row>
     <row r="507" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>1099</v>
+        <v>791</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>304</v>
@@ -20977,7 +20978,7 @@
     </row>
     <row r="508" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>1100</v>
+        <v>1424</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>304</v>
@@ -21009,7 +21010,7 @@
     </row>
     <row r="509" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>1101</v>
+        <v>792</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>304</v>
@@ -21041,7 +21042,7 @@
     </row>
     <row r="510" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>1102</v>
+        <v>793</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>304</v>
@@ -21073,7 +21074,7 @@
     </row>
     <row r="511" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>1103</v>
+        <v>794</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>304</v>
@@ -21105,7 +21106,7 @@
     </row>
     <row r="512" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>1104</v>
+        <v>795</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>304</v>
@@ -21137,7 +21138,7 @@
     </row>
     <row r="513" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>1105</v>
+        <v>796</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>304</v>
@@ -21169,7 +21170,7 @@
     </row>
     <row r="514" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>1106</v>
+        <v>797</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>304</v>
@@ -21201,7 +21202,7 @@
     </row>
     <row r="515" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>1107</v>
+        <v>798</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>221</v>
@@ -21233,7 +21234,7 @@
     </row>
     <row r="516" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>1108</v>
+        <v>799</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>221</v>
@@ -21265,7 +21266,7 @@
     </row>
     <row r="517" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>1109</v>
+        <v>800</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>221</v>
@@ -21297,7 +21298,7 @@
     </row>
     <row r="518" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>1110</v>
+        <v>801</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>221</v>
@@ -21329,7 +21330,7 @@
     </row>
     <row r="519" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>1111</v>
+        <v>802</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>221</v>
@@ -21361,7 +21362,7 @@
     </row>
     <row r="520" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>1112</v>
+        <v>803</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>221</v>
@@ -21393,7 +21394,7 @@
     </row>
     <row r="521" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
-        <v>1113</v>
+        <v>804</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>221</v>
@@ -21425,7 +21426,7 @@
     </row>
     <row r="522" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
-        <v>1114</v>
+        <v>805</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>221</v>
@@ -21457,7 +21458,7 @@
     </row>
     <row r="523" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>1115</v>
+        <v>806</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>221</v>
@@ -21489,7 +21490,7 @@
     </row>
     <row r="524" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>1116</v>
+        <v>807</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>221</v>
@@ -21521,7 +21522,7 @@
     </row>
     <row r="525" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>1117</v>
+        <v>808</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>221</v>
@@ -21553,7 +21554,7 @@
     </row>
     <row r="526" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>1118</v>
+        <v>809</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>221</v>
@@ -21585,7 +21586,7 @@
     </row>
     <row r="527" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>1119</v>
+        <v>810</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>221</v>
@@ -21617,7 +21618,7 @@
     </row>
     <row r="528" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
-        <v>1120</v>
+        <v>811</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>221</v>
@@ -21649,7 +21650,7 @@
     </row>
     <row r="529" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>1121</v>
+        <v>812</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>221</v>
@@ -21681,7 +21682,7 @@
     </row>
     <row r="530" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>1122</v>
+        <v>813</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>221</v>
@@ -21713,7 +21714,7 @@
     </row>
     <row r="531" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>1123</v>
+        <v>814</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>221</v>
@@ -21745,7 +21746,7 @@
     </row>
     <row r="532" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>1124</v>
+        <v>815</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>221</v>
@@ -21777,7 +21778,7 @@
     </row>
     <row r="533" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1125</v>
+        <v>816</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>221</v>
@@ -21809,7 +21810,7 @@
     </row>
     <row r="534" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1126</v>
+        <v>817</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>221</v>
@@ -21841,7 +21842,7 @@
     </row>
     <row r="535" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>1127</v>
+        <v>818</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>221</v>
@@ -21873,7 +21874,7 @@
     </row>
     <row r="536" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>1128</v>
+        <v>819</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>221</v>
@@ -21905,7 +21906,7 @@
     </row>
     <row r="537" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1129</v>
+        <v>820</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>221</v>
@@ -21937,7 +21938,7 @@
     </row>
     <row r="538" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>1130</v>
+        <v>821</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>221</v>
@@ -21969,7 +21970,7 @@
     </row>
     <row r="539" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>1131</v>
+        <v>822</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>221</v>
@@ -22001,7 +22002,7 @@
     </row>
     <row r="540" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>1132</v>
+        <v>823</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>221</v>
@@ -22033,7 +22034,7 @@
     </row>
     <row r="541" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>1133</v>
+        <v>824</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>221</v>
@@ -22065,7 +22066,7 @@
     </row>
     <row r="542" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>1134</v>
+        <v>825</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>221</v>
@@ -22097,7 +22098,7 @@
     </row>
     <row r="543" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>1135</v>
+        <v>826</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>221</v>
@@ -22129,7 +22130,7 @@
     </row>
     <row r="544" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>1136</v>
+        <v>827</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>221</v>
@@ -22161,7 +22162,7 @@
     </row>
     <row r="545" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>1137</v>
+        <v>828</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>221</v>
@@ -22193,7 +22194,7 @@
     </row>
     <row r="546" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>1138</v>
+        <v>829</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>221</v>
@@ -22225,7 +22226,7 @@
     </row>
     <row r="547" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
-        <v>1139</v>
+        <v>830</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>221</v>
@@ -22257,7 +22258,7 @@
     </row>
     <row r="548" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
-        <v>1140</v>
+        <v>831</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>221</v>
@@ -22289,7 +22290,7 @@
     </row>
     <row r="549" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
-        <v>1141</v>
+        <v>832</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>221</v>
@@ -22321,7 +22322,7 @@
     </row>
     <row r="550" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
-        <v>1142</v>
+        <v>833</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>221</v>
@@ -22353,7 +22354,7 @@
     </row>
     <row r="551" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
-        <v>1143</v>
+        <v>834</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>221</v>
@@ -22385,7 +22386,7 @@
     </row>
     <row r="552" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
-        <v>1144</v>
+        <v>835</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>221</v>
@@ -22417,7 +22418,7 @@
     </row>
     <row r="553" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>1145</v>
+        <v>836</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>221</v>
@@ -22449,7 +22450,7 @@
     </row>
     <row r="554" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
-        <v>1146</v>
+        <v>837</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>221</v>
@@ -22481,7 +22482,7 @@
     </row>
     <row r="555" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
-        <v>1147</v>
+        <v>838</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>221</v>
@@ -22513,7 +22514,7 @@
     </row>
     <row r="556" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
-        <v>1148</v>
+        <v>839</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>221</v>
@@ -22545,7 +22546,7 @@
     </row>
     <row r="557" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
-        <v>1149</v>
+        <v>840</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>221</v>
@@ -22577,7 +22578,7 @@
     </row>
     <row r="558" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>1150</v>
+        <v>841</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>221</v>
@@ -22609,7 +22610,7 @@
     </row>
     <row r="559" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
-        <v>1151</v>
+        <v>842</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>221</v>
@@ -22641,7 +22642,7 @@
     </row>
     <row r="560" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>1152</v>
+        <v>843</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>221</v>
@@ -22673,7 +22674,7 @@
     </row>
     <row r="561" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>1153</v>
+        <v>844</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>221</v>
@@ -22705,7 +22706,7 @@
     </row>
     <row r="562" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>1154</v>
+        <v>845</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>221</v>
@@ -22737,7 +22738,7 @@
     </row>
     <row r="563" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>1155</v>
+        <v>846</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>221</v>
@@ -22769,7 +22770,7 @@
     </row>
     <row r="564" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>1156</v>
+        <v>847</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>273</v>
@@ -22801,7 +22802,7 @@
     </row>
     <row r="565" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>1157</v>
+        <v>848</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>273</v>
@@ -22833,7 +22834,7 @@
     </row>
     <row r="566" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>1158</v>
+        <v>849</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>273</v>
@@ -22865,7 +22866,7 @@
     </row>
     <row r="567" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>1159</v>
+        <v>850</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>273</v>
@@ -22897,7 +22898,7 @@
     </row>
     <row r="568" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>1160</v>
+        <v>851</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>273</v>
@@ -22929,7 +22930,7 @@
     </row>
     <row r="569" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>1161</v>
+        <v>852</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>273</v>
@@ -22961,7 +22962,7 @@
     </row>
     <row r="570" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>1162</v>
+        <v>853</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>273</v>
@@ -22993,7 +22994,7 @@
     </row>
     <row r="571" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>1163</v>
+        <v>854</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>221</v>
@@ -23025,7 +23026,7 @@
     </row>
     <row r="572" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>1164</v>
+        <v>855</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>221</v>
@@ -23057,7 +23058,7 @@
     </row>
     <row r="573" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>1165</v>
+        <v>856</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>221</v>
@@ -23089,7 +23090,7 @@
     </row>
     <row r="574" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>1166</v>
+        <v>1425</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>304</v>
@@ -23121,7 +23122,7 @@
     </row>
     <row r="575" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
-        <v>1167</v>
+        <v>857</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>304</v>
@@ -23153,7 +23154,7 @@
     </row>
     <row r="576" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
-        <v>1168</v>
+        <v>858</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>304</v>
@@ -23185,7 +23186,7 @@
     </row>
     <row r="577" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
-        <v>1169</v>
+        <v>859</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>304</v>
@@ -23217,7 +23218,7 @@
     </row>
     <row r="578" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
-        <v>1170</v>
+        <v>860</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>304</v>
@@ -23249,7 +23250,7 @@
     </row>
     <row r="579" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
-        <v>1171</v>
+        <v>861</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>304</v>
@@ -23281,7 +23282,7 @@
     </row>
     <row r="580" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>1172</v>
+        <v>862</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>304</v>
@@ -23313,7 +23314,7 @@
     </row>
     <row r="581" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>1173</v>
+        <v>863</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>304</v>
@@ -23345,7 +23346,7 @@
     </row>
     <row r="582" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
-        <v>1174</v>
+        <v>864</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>304</v>
@@ -23377,7 +23378,7 @@
     </row>
     <row r="583" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>1175</v>
+        <v>865</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>304</v>
@@ -23409,7 +23410,7 @@
     </row>
     <row r="584" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>1176</v>
+        <v>866</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>304</v>
@@ -23441,7 +23442,7 @@
     </row>
     <row r="585" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>1177</v>
+        <v>867</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>304</v>
@@ -23473,7 +23474,7 @@
     </row>
     <row r="586" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>1178</v>
+        <v>868</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>304</v>
@@ -23505,7 +23506,7 @@
     </row>
     <row r="587" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>1179</v>
+        <v>869</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>304</v>
@@ -23537,7 +23538,7 @@
     </row>
     <row r="588" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>1180</v>
+        <v>870</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>304</v>
@@ -23569,7 +23570,7 @@
     </row>
     <row r="589" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>1181</v>
+        <v>871</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>304</v>
@@ -23601,7 +23602,7 @@
     </row>
     <row r="590" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>1182</v>
+        <v>872</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>304</v>
@@ -23633,7 +23634,7 @@
     </row>
     <row r="591" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>1183</v>
+        <v>873</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>304</v>
@@ -23665,7 +23666,7 @@
     </row>
     <row r="592" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>1184</v>
+        <v>874</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>304</v>
@@ -23697,7 +23698,7 @@
     </row>
     <row r="593" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>1185</v>
+        <v>875</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>304</v>
@@ -23729,7 +23730,7 @@
     </row>
     <row r="594" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
-        <v>1186</v>
+        <v>876</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>304</v>
@@ -23761,7 +23762,7 @@
     </row>
     <row r="595" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
-        <v>1187</v>
+        <v>877</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>304</v>
@@ -23793,7 +23794,7 @@
     </row>
     <row r="596" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
-        <v>1188</v>
+        <v>1426</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>304</v>
@@ -23825,7 +23826,7 @@
     </row>
     <row r="597" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
-        <v>1189</v>
+        <v>878</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>304</v>
@@ -23857,7 +23858,7 @@
     </row>
     <row r="598" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
-        <v>1190</v>
+        <v>879</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>304</v>
@@ -23889,7 +23890,7 @@
     </row>
     <row r="599" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
-        <v>1191</v>
+        <v>880</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>304</v>
@@ -23921,7 +23922,7 @@
     </row>
     <row r="600" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
-        <v>1192</v>
+        <v>881</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>304</v>
@@ -23953,7 +23954,7 @@
     </row>
     <row r="601" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
-        <v>1193</v>
+        <v>882</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>304</v>
@@ -23985,7 +23986,7 @@
     </row>
     <row r="602" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>1194</v>
+        <v>883</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>304</v>
@@ -24017,7 +24018,7 @@
     </row>
     <row r="603" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
-        <v>1195</v>
+        <v>884</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>304</v>
@@ -24049,7 +24050,7 @@
     </row>
     <row r="604" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
-        <v>1196</v>
+        <v>885</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>304</v>
@@ -24081,7 +24082,7 @@
     </row>
     <row r="605" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>1197</v>
+        <v>886</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>304</v>
@@ -24113,7 +24114,7 @@
     </row>
     <row r="606" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
-        <v>1198</v>
+        <v>887</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>304</v>
@@ -24145,7 +24146,7 @@
     </row>
     <row r="607" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>1199</v>
+        <v>888</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>304</v>
@@ -24177,7 +24178,7 @@
     </row>
     <row r="608" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
-        <v>1200</v>
+        <v>889</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>304</v>
@@ -24209,7 +24210,7 @@
     </row>
     <row r="609" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>1201</v>
+        <v>890</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>304</v>
@@ -24241,7 +24242,7 @@
     </row>
     <row r="610" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>1202</v>
+        <v>891</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>304</v>
@@ -24273,7 +24274,7 @@
     </row>
     <row r="611" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>1203</v>
+        <v>892</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>304</v>
@@ -24305,7 +24306,7 @@
     </row>
     <row r="612" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>1204</v>
+        <v>893</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>304</v>
@@ -24337,7 +24338,7 @@
     </row>
     <row r="613" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
-        <v>1205</v>
+        <v>894</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>304</v>
@@ -24369,7 +24370,7 @@
     </row>
     <row r="614" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>1206</v>
+        <v>895</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>304</v>
@@ -24401,7 +24402,7 @@
     </row>
     <row r="615" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
-        <v>1207</v>
+        <v>896</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>304</v>
@@ -24433,7 +24434,7 @@
     </row>
     <row r="616" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
-        <v>1208</v>
+        <v>897</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>304</v>
@@ -24465,7 +24466,7 @@
     </row>
     <row r="617" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>304</v>
@@ -24497,7 +24498,7 @@
     </row>
     <row r="618" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
-        <v>1210</v>
+        <v>899</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>221</v>
@@ -24529,7 +24530,7 @@
     </row>
     <row r="619" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
-        <v>1211</v>
+        <v>900</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>221</v>
@@ -24561,7 +24562,7 @@
     </row>
     <row r="620" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
-        <v>1212</v>
+        <v>901</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>221</v>
@@ -24593,7 +24594,7 @@
     </row>
     <row r="621" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
-        <v>1213</v>
+        <v>902</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>221</v>
@@ -24625,7 +24626,7 @@
     </row>
     <row r="622" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
-        <v>1214</v>
+        <v>903</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>221</v>
@@ -24657,7 +24658,7 @@
     </row>
     <row r="623" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
-        <v>1215</v>
+        <v>904</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>221</v>
@@ -24689,7 +24690,7 @@
     </row>
     <row r="624" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
-        <v>1216</v>
+        <v>905</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>221</v>
@@ -24721,7 +24722,7 @@
     </row>
     <row r="625" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
-        <v>1217</v>
+        <v>906</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>221</v>
@@ -24753,7 +24754,7 @@
     </row>
     <row r="626" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
-        <v>1218</v>
+        <v>907</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>221</v>
@@ -24785,7 +24786,7 @@
     </row>
     <row r="627" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
-        <v>1219</v>
+        <v>908</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>221</v>
@@ -24817,7 +24818,7 @@
     </row>
     <row r="628" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>1220</v>
+        <v>909</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>221</v>
@@ -24849,7 +24850,7 @@
     </row>
     <row r="629" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
-        <v>1221</v>
+        <v>910</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>221</v>
@@ -24881,7 +24882,7 @@
     </row>
     <row r="630" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
-        <v>1222</v>
+        <v>911</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>221</v>
@@ -24913,7 +24914,7 @@
     </row>
     <row r="631" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
-        <v>1223</v>
+        <v>912</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>221</v>
@@ -24945,7 +24946,7 @@
     </row>
     <row r="632" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
-        <v>1224</v>
+        <v>913</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>221</v>
@@ -24977,7 +24978,7 @@
     </row>
     <row r="633" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
-        <v>1225</v>
+        <v>914</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>221</v>
@@ -25009,7 +25010,7 @@
     </row>
     <row r="634" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
-        <v>1226</v>
+        <v>915</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>221</v>
@@ -25041,7 +25042,7 @@
     </row>
     <row r="635" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
-        <v>1227</v>
+        <v>916</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>221</v>
@@ -25073,7 +25074,7 @@
     </row>
     <row r="636" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
-        <v>1228</v>
+        <v>917</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>221</v>
@@ -25105,7 +25106,7 @@
     </row>
     <row r="637" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>1229</v>
+        <v>918</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>221</v>
@@ -25137,7 +25138,7 @@
     </row>
     <row r="638" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>1230</v>
+        <v>919</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>221</v>
@@ -25169,7 +25170,7 @@
     </row>
     <row r="639" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>1231</v>
+        <v>920</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>221</v>
@@ -25201,7 +25202,7 @@
     </row>
     <row r="640" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>1232</v>
+        <v>921</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>221</v>
@@ -25233,7 +25234,7 @@
     </row>
     <row r="641" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>1233</v>
+        <v>922</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>221</v>
@@ -25265,7 +25266,7 @@
     </row>
     <row r="642" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
-        <v>1234</v>
+        <v>923</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>221</v>
@@ -25297,7 +25298,7 @@
     </row>
     <row r="643" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
-        <v>1235</v>
+        <v>924</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>221</v>
@@ -25329,7 +25330,7 @@
     </row>
     <row r="644" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
-        <v>1236</v>
+        <v>925</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>221</v>
@@ -25361,7 +25362,7 @@
     </row>
     <row r="645" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
-        <v>1237</v>
+        <v>926</v>
       </c>
       <c r="B645" s="2" t="s">
         <v>221</v>
@@ -25393,7 +25394,7 @@
     </row>
     <row r="646" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
-        <v>1238</v>
+        <v>927</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>221</v>
@@ -25425,7 +25426,7 @@
     </row>
     <row r="647" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
-        <v>1239</v>
+        <v>928</v>
       </c>
       <c r="B647" s="2" t="s">
         <v>221</v>
@@ -25457,7 +25458,7 @@
     </row>
     <row r="648" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
-        <v>1240</v>
+        <v>929</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>221</v>
@@ -25489,7 +25490,7 @@
     </row>
     <row r="649" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>1241</v>
+        <v>930</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>221</v>
@@ -25521,7 +25522,7 @@
     </row>
     <row r="650" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
-        <v>1242</v>
+        <v>931</v>
       </c>
       <c r="B650" s="2" t="s">
         <v>221</v>
@@ -25553,7 +25554,7 @@
     </row>
     <row r="651" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
-        <v>1243</v>
+        <v>932</v>
       </c>
       <c r="B651" s="2" t="s">
         <v>221</v>
@@ -25585,7 +25586,7 @@
     </row>
     <row r="652" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
-        <v>1244</v>
+        <v>933</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>221</v>
@@ -25617,7 +25618,7 @@
     </row>
     <row r="653" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
-        <v>1245</v>
+        <v>934</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>221</v>
@@ -25649,7 +25650,7 @@
     </row>
     <row r="654" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
-        <v>1246</v>
+        <v>935</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>221</v>
@@ -25681,7 +25682,7 @@
     </row>
     <row r="655" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
-        <v>1247</v>
+        <v>936</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>221</v>
@@ -25713,7 +25714,7 @@
     </row>
     <row r="656" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
-        <v>1248</v>
+        <v>937</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>221</v>
@@ -25745,7 +25746,7 @@
     </row>
     <row r="657" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
-        <v>1249</v>
+        <v>938</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>221</v>
@@ -25777,7 +25778,7 @@
     </row>
     <row r="658" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
-        <v>1250</v>
+        <v>939</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>221</v>
@@ -25809,7 +25810,7 @@
     </row>
     <row r="659" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
-        <v>1251</v>
+        <v>940</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>221</v>
@@ -25841,7 +25842,7 @@
     </row>
     <row r="660" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
-        <v>1252</v>
+        <v>941</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>221</v>
@@ -25873,7 +25874,7 @@
     </row>
     <row r="661" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
-        <v>1253</v>
+        <v>942</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>221</v>
@@ -25905,7 +25906,7 @@
     </row>
     <row r="662" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
-        <v>1254</v>
+        <v>943</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>221</v>
@@ -25937,7 +25938,7 @@
     </row>
     <row r="663" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
-        <v>1255</v>
+        <v>944</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>221</v>
@@ -25969,7 +25970,7 @@
     </row>
     <row r="664" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
-        <v>1256</v>
+        <v>945</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>221</v>
@@ -26001,7 +26002,7 @@
     </row>
     <row r="665" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>1257</v>
+        <v>946</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>221</v>
@@ -26033,7 +26034,7 @@
     </row>
     <row r="666" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>1258</v>
+        <v>947</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>221</v>
@@ -26065,7 +26066,7 @@
     </row>
     <row r="667" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>1259</v>
+        <v>948</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>221</v>
@@ -26097,7 +26098,7 @@
     </row>
     <row r="668" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>1260</v>
+        <v>949</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>221</v>
@@ -26129,7 +26130,7 @@
     </row>
     <row r="669" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
-        <v>1261</v>
+        <v>950</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>221</v>
@@ -26161,7 +26162,7 @@
     </row>
     <row r="670" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
-        <v>1262</v>
+        <v>951</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>221</v>
@@ -26193,7 +26194,7 @@
     </row>
     <row r="671" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>1263</v>
+        <v>952</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>221</v>
@@ -26225,7 +26226,7 @@
     </row>
     <row r="672" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
-        <v>1264</v>
+        <v>953</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>221</v>
@@ -26257,7 +26258,7 @@
     </row>
     <row r="673" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>1265</v>
+        <v>954</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>221</v>
@@ -26289,7 +26290,7 @@
     </row>
     <row r="674" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
-        <v>1266</v>
+        <v>955</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>221</v>
@@ -26321,7 +26322,7 @@
     </row>
     <row r="675" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
-        <v>1267</v>
+        <v>956</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>221</v>
@@ -26353,7 +26354,7 @@
     </row>
     <row r="676" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
-        <v>1268</v>
+        <v>957</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>221</v>
@@ -26385,7 +26386,7 @@
     </row>
     <row r="677" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
-        <v>1269</v>
+        <v>958</v>
       </c>
       <c r="B677" s="2" t="s">
         <v>221</v>
@@ -26417,7 +26418,7 @@
     </row>
     <row r="678" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
-        <v>1270</v>
+        <v>959</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>221</v>
@@ -26449,7 +26450,7 @@
     </row>
     <row r="679" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
-        <v>1271</v>
+        <v>960</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>221</v>
@@ -26481,7 +26482,7 @@
     </row>
     <row r="680" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
-        <v>1272</v>
+        <v>961</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>221</v>
@@ -26513,7 +26514,7 @@
     </row>
     <row r="681" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
-        <v>1273</v>
+        <v>962</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>221</v>
@@ -26545,7 +26546,7 @@
     </row>
     <row r="682" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
-        <v>1274</v>
+        <v>963</v>
       </c>
       <c r="B682" s="2" t="s">
         <v>221</v>
@@ -26577,7 +26578,7 @@
     </row>
     <row r="683" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>1275</v>
+        <v>964</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>221</v>
@@ -26609,7 +26610,7 @@
     </row>
     <row r="684" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1276</v>
+        <v>965</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>221</v>
@@ -26641,7 +26642,7 @@
     </row>
     <row r="685" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>1277</v>
+        <v>966</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>221</v>
@@ -26673,7 +26674,7 @@
     </row>
     <row r="686" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>1278</v>
+        <v>967</v>
       </c>
       <c r="B686" s="2" t="s">
         <v>221</v>
@@ -26705,7 +26706,7 @@
     </row>
     <row r="687" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>1279</v>
+        <v>968</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>221</v>
@@ -26737,7 +26738,7 @@
     </row>
     <row r="688" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>1280</v>
+        <v>969</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>221</v>
@@ -26769,7 +26770,7 @@
     </row>
     <row r="689" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>1281</v>
+        <v>970</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>221</v>
@@ -26801,7 +26802,7 @@
     </row>
     <row r="690" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>1282</v>
+        <v>971</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>221</v>
@@ -26833,7 +26834,7 @@
     </row>
     <row r="691" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>1283</v>
+        <v>972</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>221</v>
@@ -26865,7 +26866,7 @@
     </row>
     <row r="692" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
-        <v>1284</v>
+        <v>973</v>
       </c>
       <c r="B692" s="2" t="s">
         <v>221</v>
@@ -26897,7 +26898,7 @@
     </row>
     <row r="693" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>1285</v>
+        <v>974</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>221</v>
@@ -26929,7 +26930,7 @@
     </row>
     <row r="694" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>1286</v>
+        <v>975</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>221</v>
@@ -26961,7 +26962,7 @@
     </row>
     <row r="695" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>1287</v>
+        <v>976</v>
       </c>
       <c r="B695" s="2" t="s">
         <v>221</v>
@@ -26993,7 +26994,7 @@
     </row>
     <row r="696" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>1288</v>
+        <v>977</v>
       </c>
       <c r="B696" s="2" t="s">
         <v>221</v>
@@ -27025,7 +27026,7 @@
     </row>
     <row r="697" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
-        <v>1289</v>
+        <v>978</v>
       </c>
       <c r="B697" s="2" t="s">
         <v>221</v>
@@ -27057,7 +27058,7 @@
     </row>
     <row r="698" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
-        <v>1290</v>
+        <v>979</v>
       </c>
       <c r="B698" s="2" t="s">
         <v>221</v>
@@ -27089,7 +27090,7 @@
     </row>
     <row r="699" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
-        <v>1291</v>
+        <v>980</v>
       </c>
       <c r="B699" s="2" t="s">
         <v>221</v>
@@ -27121,7 +27122,7 @@
     </row>
     <row r="700" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
-        <v>1292</v>
+        <v>981</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>221</v>
@@ -27153,7 +27154,7 @@
     </row>
     <row r="701" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
-        <v>1293</v>
+        <v>982</v>
       </c>
       <c r="B701" s="2" t="s">
         <v>221</v>
@@ -27185,7 +27186,7 @@
     </row>
     <row r="702" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>1294</v>
+        <v>983</v>
       </c>
       <c r="B702" s="2" t="s">
         <v>221</v>
@@ -27217,7 +27218,7 @@
     </row>
     <row r="703" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
-        <v>1295</v>
+        <v>984</v>
       </c>
       <c r="B703" s="2" t="s">
         <v>221</v>
@@ -27249,7 +27250,7 @@
     </row>
     <row r="704" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
-        <v>1296</v>
+        <v>985</v>
       </c>
       <c r="B704" s="2" t="s">
         <v>221</v>
@@ -27281,7 +27282,7 @@
     </row>
     <row r="705" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
-        <v>1297</v>
+        <v>986</v>
       </c>
       <c r="B705" s="2" t="s">
         <v>221</v>
@@ -27313,7 +27314,7 @@
     </row>
     <row r="706" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
-        <v>1298</v>
+        <v>987</v>
       </c>
       <c r="B706" s="2" t="s">
         <v>221</v>
@@ -27345,7 +27346,7 @@
     </row>
     <row r="707" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>1299</v>
+        <v>988</v>
       </c>
       <c r="B707" s="2" t="s">
         <v>221</v>
@@ -27377,7 +27378,7 @@
     </row>
     <row r="708" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1300</v>
+        <v>989</v>
       </c>
       <c r="B708" s="2" t="s">
         <v>221</v>
@@ -27409,7 +27410,7 @@
     </row>
     <row r="709" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
-        <v>1301</v>
+        <v>990</v>
       </c>
       <c r="B709" s="2" t="s">
         <v>221</v>
@@ -27441,7 +27442,7 @@
     </row>
     <row r="710" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
-        <v>1302</v>
+        <v>991</v>
       </c>
       <c r="B710" s="2" t="s">
         <v>221</v>
@@ -27473,7 +27474,7 @@
     </row>
     <row r="711" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
-        <v>1303</v>
+        <v>992</v>
       </c>
       <c r="B711" s="2" t="s">
         <v>221</v>
@@ -27505,7 +27506,7 @@
     </row>
     <row r="712" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
-        <v>1304</v>
+        <v>993</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>221</v>
@@ -27537,7 +27538,7 @@
     </row>
     <row r="713" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
-        <v>1305</v>
+        <v>994</v>
       </c>
       <c r="B713" s="2" t="s">
         <v>221</v>
@@ -27569,7 +27570,7 @@
     </row>
     <row r="714" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
-        <v>1306</v>
+        <v>995</v>
       </c>
       <c r="B714" s="2" t="s">
         <v>221</v>
@@ -27601,7 +27602,7 @@
     </row>
     <row r="715" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>1307</v>
+        <v>996</v>
       </c>
       <c r="B715" s="2" t="s">
         <v>221</v>
@@ -27633,7 +27634,7 @@
     </row>
     <row r="716" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
-        <v>1308</v>
+        <v>997</v>
       </c>
       <c r="B716" s="2" t="s">
         <v>221</v>
@@ -27665,7 +27666,7 @@
     </row>
     <row r="717" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>1309</v>
+        <v>998</v>
       </c>
       <c r="B717" s="2" t="s">
         <v>221</v>
@@ -27697,7 +27698,7 @@
     </row>
     <row r="718" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>1310</v>
+        <v>999</v>
       </c>
       <c r="B718" s="2" t="s">
         <v>221</v>
@@ -27729,7 +27730,7 @@
     </row>
     <row r="719" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>1311</v>
+        <v>1000</v>
       </c>
       <c r="B719" s="2" t="s">
         <v>221</v>
@@ -27761,7 +27762,7 @@
     </row>
     <row r="720" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
-        <v>1312</v>
+        <v>1001</v>
       </c>
       <c r="B720" s="2" t="s">
         <v>221</v>
@@ -27793,7 +27794,7 @@
     </row>
     <row r="721" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
-        <v>1313</v>
+        <v>1002</v>
       </c>
       <c r="B721" s="2" t="s">
         <v>221</v>
@@ -27825,7 +27826,7 @@
     </row>
     <row r="722" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
-        <v>1314</v>
+        <v>1003</v>
       </c>
       <c r="B722" s="2" t="s">
         <v>221</v>
@@ -27857,7 +27858,7 @@
     </row>
     <row r="723" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>1315</v>
+        <v>1004</v>
       </c>
       <c r="B723" s="2" t="s">
         <v>221</v>
@@ -27889,7 +27890,7 @@
     </row>
     <row r="724" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
-        <v>1316</v>
+        <v>1005</v>
       </c>
       <c r="B724" s="2" t="s">
         <v>221</v>
@@ -27921,7 +27922,7 @@
     </row>
     <row r="725" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
-        <v>1317</v>
+        <v>1006</v>
       </c>
       <c r="B725" s="2" t="s">
         <v>221</v>
@@ -27953,7 +27954,7 @@
     </row>
     <row r="726" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
-        <v>1318</v>
+        <v>1007</v>
       </c>
       <c r="B726" s="2" t="s">
         <v>221</v>
@@ -27985,7 +27986,7 @@
     </row>
     <row r="727" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
-        <v>1319</v>
+        <v>1008</v>
       </c>
       <c r="B727" s="2" t="s">
         <v>221</v>
@@ -28017,7 +28018,7 @@
     </row>
     <row r="728" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
-        <v>1320</v>
+        <v>1009</v>
       </c>
       <c r="B728" s="2" t="s">
         <v>221</v>
@@ -28049,7 +28050,7 @@
     </row>
     <row r="729" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
-        <v>1321</v>
+        <v>1010</v>
       </c>
       <c r="B729" s="2" t="s">
         <v>221</v>
@@ -28081,7 +28082,7 @@
     </row>
     <row r="730" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
-        <v>1322</v>
+        <v>1011</v>
       </c>
       <c r="B730" s="2" t="s">
         <v>221</v>
@@ -28113,7 +28114,7 @@
     </row>
     <row r="731" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>1323</v>
+        <v>1427</v>
       </c>
       <c r="B731" s="2" t="s">
         <v>221</v>
@@ -28145,7 +28146,7 @@
     </row>
     <row r="732" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
-        <v>1324</v>
+        <v>1012</v>
       </c>
       <c r="B732" s="2" t="s">
         <v>221</v>
@@ -28177,7 +28178,7 @@
     </row>
     <row r="733" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
-        <v>1325</v>
+        <v>1428</v>
       </c>
       <c r="B733" s="2" t="s">
         <v>221</v>
@@ -28209,7 +28210,7 @@
     </row>
     <row r="734" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>1326</v>
+        <v>1013</v>
       </c>
       <c r="B734" s="2" t="s">
         <v>221</v>
@@ -28241,7 +28242,7 @@
     </row>
     <row r="735" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>1327</v>
+        <v>1014</v>
       </c>
       <c r="B735" s="2" t="s">
         <v>221</v>
@@ -28273,7 +28274,7 @@
     </row>
     <row r="736" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
-        <v>1328</v>
+        <v>1015</v>
       </c>
       <c r="B736" s="2" t="s">
         <v>221</v>
@@ -28305,7 +28306,7 @@
     </row>
     <row r="737" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
-        <v>1329</v>
+        <v>1016</v>
       </c>
       <c r="B737" s="2" t="s">
         <v>221</v>
@@ -28337,7 +28338,7 @@
     </row>
     <row r="738" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
-        <v>1330</v>
+        <v>1017</v>
       </c>
       <c r="B738" s="2" t="s">
         <v>221</v>
@@ -28369,7 +28370,7 @@
     </row>
     <row r="739" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
-        <v>1331</v>
+        <v>1018</v>
       </c>
       <c r="B739" s="2" t="s">
         <v>221</v>
@@ -28401,7 +28402,7 @@
     </row>
     <row r="740" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
-        <v>1332</v>
+        <v>1019</v>
       </c>
       <c r="B740" s="2" t="s">
         <v>221</v>
@@ -28433,7 +28434,7 @@
     </row>
     <row r="741" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>1333</v>
+        <v>1020</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>273</v>
@@ -28465,7 +28466,7 @@
     </row>
     <row r="742" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
-        <v>1334</v>
+        <v>1021</v>
       </c>
       <c r="B742" s="2" t="s">
         <v>273</v>
@@ -28497,7 +28498,7 @@
     </row>
     <row r="743" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
-        <v>1335</v>
+        <v>1022</v>
       </c>
       <c r="B743" s="2" t="s">
         <v>273</v>
@@ -28529,7 +28530,7 @@
     </row>
     <row r="744" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
-        <v>1336</v>
+        <v>1023</v>
       </c>
       <c r="B744" s="2" t="s">
         <v>273</v>
@@ -28561,7 +28562,7 @@
     </row>
     <row r="745" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
-        <v>1337</v>
+        <v>1429</v>
       </c>
       <c r="B745" s="2" t="s">
         <v>273</v>
@@ -28593,7 +28594,7 @@
     </row>
     <row r="746" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>1338</v>
+        <v>1024</v>
       </c>
       <c r="B746" s="2" t="s">
         <v>273</v>
@@ -28625,7 +28626,7 @@
     </row>
     <row r="747" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
-        <v>1339</v>
+        <v>1025</v>
       </c>
       <c r="B747" s="2" t="s">
         <v>273</v>
@@ -28657,7 +28658,7 @@
     </row>
     <row r="748" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
-        <v>1340</v>
+        <v>1026</v>
       </c>
       <c r="B748" s="2" t="s">
         <v>273</v>
@@ -28689,7 +28690,7 @@
     </row>
     <row r="749" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
-        <v>1341</v>
+        <v>1027</v>
       </c>
       <c r="B749" s="2" t="s">
         <v>273</v>
@@ -28721,7 +28722,7 @@
     </row>
     <row r="750" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
-        <v>1342</v>
+        <v>1430</v>
       </c>
       <c r="B750" s="2" t="s">
         <v>273</v>
@@ -28753,7 +28754,7 @@
     </row>
     <row r="751" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
-        <v>1343</v>
+        <v>1028</v>
       </c>
       <c r="B751" s="2" t="s">
         <v>273</v>
@@ -28785,7 +28786,7 @@
     </row>
     <row r="752" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
-        <v>1344</v>
+        <v>1431</v>
       </c>
       <c r="B752" s="2" t="s">
         <v>273</v>
@@ -28817,7 +28818,7 @@
     </row>
     <row r="753" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
-        <v>1345</v>
+        <v>1029</v>
       </c>
       <c r="B753" s="2" t="s">
         <v>273</v>
@@ -28849,7 +28850,7 @@
     </row>
     <row r="754" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
-        <v>1346</v>
+        <v>1030</v>
       </c>
       <c r="B754" s="2" t="s">
         <v>273</v>
@@ -28881,7 +28882,7 @@
     </row>
     <row r="755" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
-        <v>1347</v>
+        <v>1031</v>
       </c>
       <c r="B755" s="2" t="s">
         <v>273</v>
@@ -28913,7 +28914,7 @@
     </row>
     <row r="756" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
-        <v>1348</v>
+        <v>1032</v>
       </c>
       <c r="B756" s="2" t="s">
         <v>273</v>
@@ -28945,7 +28946,7 @@
     </row>
     <row r="757" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
-        <v>1349</v>
+        <v>1033</v>
       </c>
       <c r="B757" s="2" t="s">
         <v>273</v>
@@ -28977,7 +28978,7 @@
     </row>
     <row r="758" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
-        <v>1350</v>
+        <v>1034</v>
       </c>
       <c r="B758" s="2" t="s">
         <v>273</v>
@@ -29009,7 +29010,7 @@
     </row>
     <row r="759" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
-        <v>1351</v>
+        <v>1432</v>
       </c>
       <c r="B759" s="2" t="s">
         <v>273</v>
@@ -29041,7 +29042,7 @@
     </row>
     <row r="760" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
-        <v>1352</v>
+        <v>1035</v>
       </c>
       <c r="B760" s="2" t="s">
         <v>273</v>
@@ -29073,7 +29074,7 @@
     </row>
     <row r="761" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
-        <v>1353</v>
+        <v>1036</v>
       </c>
       <c r="B761" s="2" t="s">
         <v>273</v>
@@ -29105,7 +29106,7 @@
     </row>
     <row r="762" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
-        <v>1354</v>
+        <v>1037</v>
       </c>
       <c r="B762" s="2" t="s">
         <v>273</v>
@@ -29137,7 +29138,7 @@
     </row>
     <row r="763" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
-        <v>1355</v>
+        <v>1038</v>
       </c>
       <c r="B763" s="2" t="s">
         <v>273</v>
@@ -29169,7 +29170,7 @@
     </row>
     <row r="764" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
-        <v>1356</v>
+        <v>1039</v>
       </c>
       <c r="B764" s="2" t="s">
         <v>273</v>
@@ -29201,7 +29202,7 @@
     </row>
     <row r="765" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
-        <v>1357</v>
+        <v>1040</v>
       </c>
       <c r="B765" s="2" t="s">
         <v>273</v>
@@ -29233,7 +29234,7 @@
     </row>
     <row r="766" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
-        <v>1358</v>
+        <v>1041</v>
       </c>
       <c r="B766" s="2" t="s">
         <v>273</v>
@@ -29265,7 +29266,7 @@
     </row>
     <row r="767" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
-        <v>1359</v>
+        <v>1042</v>
       </c>
       <c r="B767" s="2" t="s">
         <v>273</v>
@@ -29297,7 +29298,7 @@
     </row>
     <row r="768" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
-        <v>1360</v>
+        <v>1043</v>
       </c>
       <c r="B768" s="2" t="s">
         <v>273</v>
@@ -29329,7 +29330,7 @@
     </row>
     <row r="769" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
-        <v>1361</v>
+        <v>1044</v>
       </c>
       <c r="B769" s="2" t="s">
         <v>273</v>
@@ -29361,7 +29362,7 @@
     </row>
     <row r="770" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
-        <v>1362</v>
+        <v>1045</v>
       </c>
       <c r="B770" s="2" t="s">
         <v>273</v>
@@ -29393,7 +29394,7 @@
     </row>
     <row r="771" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
-        <v>1363</v>
+        <v>1046</v>
       </c>
       <c r="B771" s="2" t="s">
         <v>273</v>
@@ -29425,7 +29426,7 @@
     </row>
     <row r="772" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
-        <v>1364</v>
+        <v>1047</v>
       </c>
       <c r="B772" s="2" t="s">
         <v>273</v>
@@ -29457,7 +29458,7 @@
     </row>
     <row r="773" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
-        <v>1365</v>
+        <v>1048</v>
       </c>
       <c r="B773" s="2" t="s">
         <v>273</v>
@@ -29489,7 +29490,7 @@
     </row>
     <row r="774" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
-        <v>1366</v>
+        <v>1049</v>
       </c>
       <c r="B774" s="2" t="s">
         <v>273</v>
@@ -29521,7 +29522,7 @@
     </row>
     <row r="775" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
-        <v>1367</v>
+        <v>1050</v>
       </c>
       <c r="B775" s="2" t="s">
         <v>273</v>
@@ -29553,7 +29554,7 @@
     </row>
     <row r="776" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
-        <v>1368</v>
+        <v>1051</v>
       </c>
       <c r="B776" s="2" t="s">
         <v>273</v>
@@ -29585,7 +29586,7 @@
     </row>
     <row r="777" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
-        <v>1369</v>
+        <v>1052</v>
       </c>
       <c r="B777" s="2" t="s">
         <v>273</v>
@@ -29617,7 +29618,7 @@
     </row>
     <row r="778" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
-        <v>1370</v>
+        <v>1053</v>
       </c>
       <c r="B778" s="2" t="s">
         <v>273</v>
@@ -29649,7 +29650,7 @@
     </row>
     <row r="779" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
-        <v>1371</v>
+        <v>1054</v>
       </c>
       <c r="B779" s="2" t="s">
         <v>273</v>
@@ -29681,7 +29682,7 @@
     </row>
     <row r="780" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
-        <v>1372</v>
+        <v>1055</v>
       </c>
       <c r="B780" s="2" t="s">
         <v>273</v>
@@ -29713,7 +29714,7 @@
     </row>
     <row r="781" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
-        <v>1373</v>
+        <v>1056</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>273</v>
@@ -29745,7 +29746,7 @@
     </row>
     <row r="782" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
-        <v>1374</v>
+        <v>1057</v>
       </c>
       <c r="B782" s="2" t="s">
         <v>273</v>
@@ -29777,7 +29778,7 @@
     </row>
     <row r="783" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
-        <v>1375</v>
+        <v>1058</v>
       </c>
       <c r="B783" s="2" t="s">
         <v>273</v>
@@ -29809,7 +29810,7 @@
     </row>
     <row r="784" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
-        <v>1376</v>
+        <v>1059</v>
       </c>
       <c r="B784" s="2" t="s">
         <v>273</v>
@@ -29841,7 +29842,7 @@
     </row>
     <row r="785" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>1377</v>
+        <v>1060</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>273</v>
@@ -29873,7 +29874,7 @@
     </row>
     <row r="786" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
-        <v>1378</v>
+        <v>1061</v>
       </c>
       <c r="B786" s="2" t="s">
         <v>273</v>
@@ -29905,7 +29906,7 @@
     </row>
     <row r="787" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
-        <v>1379</v>
+        <v>1062</v>
       </c>
       <c r="B787" s="2" t="s">
         <v>273</v>
@@ -29937,7 +29938,7 @@
     </row>
     <row r="788" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
-        <v>1380</v>
+        <v>1063</v>
       </c>
       <c r="B788" s="2" t="s">
         <v>273</v>
@@ -29969,7 +29970,7 @@
     </row>
     <row r="789" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
-        <v>1381</v>
+        <v>1064</v>
       </c>
       <c r="B789" s="2" t="s">
         <v>273</v>
@@ -30001,7 +30002,7 @@
     </row>
     <row r="790" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
-        <v>1382</v>
+        <v>1065</v>
       </c>
       <c r="B790" s="2" t="s">
         <v>273</v>
@@ -30033,7 +30034,7 @@
     </row>
     <row r="791" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
-        <v>1383</v>
+        <v>1066</v>
       </c>
       <c r="B791" s="2" t="s">
         <v>273</v>
@@ -30065,7 +30066,7 @@
     </row>
     <row r="792" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
-        <v>1384</v>
+        <v>1067</v>
       </c>
       <c r="B792" s="2" t="s">
         <v>273</v>
@@ -30097,7 +30098,7 @@
     </row>
     <row r="793" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
-        <v>1385</v>
+        <v>1068</v>
       </c>
       <c r="B793" s="2" t="s">
         <v>273</v>
@@ -30128,14 +30129,14 @@
       </c>
     </row>
     <row r="794" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A794" s="1" t="s">
-        <v>1404</v>
+      <c r="A794" s="2" t="s">
+        <v>1072</v>
       </c>
       <c r="B794" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C794" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D794" s="1">
         <v>43758365</v>
@@ -30160,14 +30161,14 @@
       </c>
     </row>
     <row r="795" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A795" s="1" t="s">
-        <v>1406</v>
+      <c r="A795" s="2" t="s">
+        <v>1074</v>
       </c>
       <c r="B795" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C795" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D795" s="1">
         <v>43758365</v>
@@ -30192,14 +30193,14 @@
       </c>
     </row>
     <row r="796" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A796" s="1" t="s">
-        <v>1407</v>
+      <c r="A796" s="2" t="s">
+        <v>1075</v>
       </c>
       <c r="B796" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C796" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D796" s="1">
         <v>43758365</v>
@@ -30224,14 +30225,14 @@
       </c>
     </row>
     <row r="797" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A797" s="1" t="s">
-        <v>1408</v>
+      <c r="A797" s="2" t="s">
+        <v>1076</v>
       </c>
       <c r="B797" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C797" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D797" s="1">
         <v>43758365</v>
@@ -30256,14 +30257,14 @@
       </c>
     </row>
     <row r="798" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A798" s="1" t="s">
-        <v>1409</v>
+      <c r="A798" s="2" t="s">
+        <v>1077</v>
       </c>
       <c r="B798" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C798" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D798" s="1">
         <v>43245330</v>
@@ -30272,10 +30273,10 @@
         <v>187</v>
       </c>
       <c r="F798" s="1" t="s">
-        <v>1424</v>
+        <v>1092</v>
       </c>
       <c r="G798" s="1" t="s">
-        <v>1424</v>
+        <v>1092</v>
       </c>
       <c r="H798" s="2" t="s">
         <v>164</v>
@@ -30288,14 +30289,14 @@
       </c>
     </row>
     <row r="799" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A799" s="1" t="s">
-        <v>1410</v>
+      <c r="A799" s="2" t="s">
+        <v>1078</v>
       </c>
       <c r="B799" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C799" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D799" s="1">
         <v>43790399</v>
@@ -30320,20 +30321,20 @@
       </c>
     </row>
     <row r="800" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A800" s="1" t="s">
-        <v>1411</v>
+      <c r="A800" s="2" t="s">
+        <v>1079</v>
       </c>
       <c r="B800" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C800" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D800" s="1">
         <v>43206446</v>
       </c>
       <c r="E800" s="1" t="s">
-        <v>1412</v>
+        <v>1080</v>
       </c>
       <c r="F800" s="1" t="s">
         <v>26</v>
@@ -30352,26 +30353,26 @@
       </c>
     </row>
     <row r="801" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A801" s="1" t="s">
-        <v>1413</v>
+      <c r="A801" s="2" t="s">
+        <v>1081</v>
       </c>
       <c r="B801" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C801" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D801" s="1">
         <v>43206446</v>
       </c>
       <c r="E801" s="1" t="s">
-        <v>1412</v>
+        <v>1080</v>
       </c>
       <c r="F801" s="1" t="s">
-        <v>1425</v>
+        <v>1093</v>
       </c>
       <c r="G801" s="1" t="s">
-        <v>1425</v>
+        <v>1093</v>
       </c>
       <c r="H801" s="2" t="s">
         <v>164</v>
@@ -30384,26 +30385,26 @@
       </c>
     </row>
     <row r="802" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A802" s="1" t="s">
-        <v>1414</v>
+      <c r="A802" s="2" t="s">
+        <v>1082</v>
       </c>
       <c r="B802" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C802" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D802" s="1">
         <v>43340469</v>
       </c>
       <c r="E802" s="1" t="s">
-        <v>1415</v>
+        <v>1083</v>
       </c>
       <c r="F802" s="1" t="s">
-        <v>1426</v>
+        <v>1094</v>
       </c>
       <c r="G802" s="1" t="s">
-        <v>1426</v>
+        <v>1094</v>
       </c>
       <c r="H802" s="2" t="s">
         <v>164</v>
@@ -30416,26 +30417,26 @@
       </c>
     </row>
     <row r="803" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A803" s="1" t="s">
-        <v>1416</v>
+      <c r="A803" s="2" t="s">
+        <v>1084</v>
       </c>
       <c r="B803" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C803" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D803" s="1">
         <v>43340469</v>
       </c>
       <c r="E803" s="1" t="s">
-        <v>1415</v>
+        <v>1083</v>
       </c>
       <c r="F803" s="1" t="s">
-        <v>1427</v>
+        <v>1095</v>
       </c>
       <c r="G803" s="1" t="s">
-        <v>1427</v>
+        <v>1095</v>
       </c>
       <c r="H803" s="2" t="s">
         <v>164</v>
@@ -30448,20 +30449,20 @@
       </c>
     </row>
     <row r="804" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A804" s="1" t="s">
-        <v>1417</v>
+      <c r="A804" s="2" t="s">
+        <v>1085</v>
       </c>
       <c r="B804" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C804" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D804" s="1">
         <v>43447473</v>
       </c>
       <c r="E804" s="1" t="s">
-        <v>1418</v>
+        <v>1086</v>
       </c>
       <c r="F804" s="1" t="s">
         <v>38</v>
@@ -30480,20 +30481,20 @@
       </c>
     </row>
     <row r="805" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A805" s="1" t="s">
-        <v>1419</v>
+      <c r="A805" s="2" t="s">
+        <v>1087</v>
       </c>
       <c r="B805" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C805" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D805" s="1">
         <v>43447473</v>
       </c>
       <c r="E805" s="1" t="s">
-        <v>1418</v>
+        <v>1086</v>
       </c>
       <c r="F805" s="1" t="s">
         <v>26</v>
@@ -30512,26 +30513,26 @@
       </c>
     </row>
     <row r="806" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A806" s="1" t="s">
-        <v>1420</v>
+      <c r="A806" s="2" t="s">
+        <v>1088</v>
       </c>
       <c r="B806" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C806" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D806" s="1">
         <v>43447473</v>
       </c>
       <c r="E806" s="1" t="s">
-        <v>1418</v>
+        <v>1086</v>
       </c>
       <c r="F806" s="1" t="s">
-        <v>1428</v>
+        <v>1096</v>
       </c>
       <c r="G806" s="1" t="s">
-        <v>1428</v>
+        <v>1096</v>
       </c>
       <c r="H806" s="2" t="s">
         <v>164</v>
@@ -30544,20 +30545,20 @@
       </c>
     </row>
     <row r="807" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A807" s="1" t="s">
-        <v>1421</v>
+      <c r="A807" s="2" t="s">
+        <v>1089</v>
       </c>
       <c r="B807" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C807" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D807" s="1">
         <v>43447473</v>
       </c>
       <c r="E807" s="1" t="s">
-        <v>1418</v>
+        <v>1086</v>
       </c>
       <c r="F807" s="1" t="s">
         <v>196</v>
@@ -30576,26 +30577,26 @@
       </c>
     </row>
     <row r="808" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A808" s="1" t="s">
-        <v>1422</v>
+      <c r="A808" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="B808" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C808" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D808" s="1">
         <v>43447473</v>
       </c>
       <c r="E808" s="1" t="s">
-        <v>1418</v>
+        <v>1086</v>
       </c>
       <c r="F808" s="1" t="s">
-        <v>1429</v>
+        <v>1097</v>
       </c>
       <c r="G808" s="1" t="s">
-        <v>1429</v>
+        <v>1097</v>
       </c>
       <c r="H808" s="2" t="s">
         <v>164</v>
@@ -30608,26 +30609,26 @@
       </c>
     </row>
     <row r="809" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A809" s="1" t="s">
-        <v>1423</v>
+      <c r="A809" s="2" t="s">
+        <v>1091</v>
       </c>
       <c r="B809" s="1" t="s">
         <v>220</v>
       </c>
       <c r="C809" s="1" t="s">
-        <v>1405</v>
+        <v>1073</v>
       </c>
       <c r="D809" s="1">
         <v>43447473</v>
       </c>
       <c r="E809" s="1" t="s">
-        <v>1418</v>
+        <v>1086</v>
       </c>
       <c r="F809" s="1" t="s">
-        <v>1430</v>
+        <v>1098</v>
       </c>
       <c r="G809" s="1" t="s">
-        <v>1430</v>
+        <v>1098</v>
       </c>
       <c r="H809" s="2" t="s">
         <v>164</v>
@@ -30640,7 +30641,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J809" xr:uid="{3A91E150-05DE-47E3-9A71-EF43C5F49301}"/>
+  <autoFilter ref="B1:J809" xr:uid="{3A91E150-05DE-47E3-9A71-EF43C5F49301}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0ACF5A-2BC8-4ADA-BB3B-53942F1AE577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095BD1AC-0E62-48C2-BB05-03E368DE60D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -4741,13 +4741,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M809"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="15.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="1" customWidth="1"/>
-    <col min="6" max="10" width="15.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="39.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="15.85546875" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -4783,7 +4785,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1329</v>
       </c>
@@ -4815,7 +4817,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1330</v>
       </c>
@@ -4847,7 +4849,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1099</v>
       </c>
@@ -4879,7 +4881,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1100</v>
       </c>
@@ -4912,7 +4914,7 @@
       </c>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1101</v>
       </c>
@@ -4944,7 +4946,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>1102</v>
       </c>
@@ -4976,7 +4978,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>1103</v>
       </c>
@@ -5008,7 +5010,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>1104</v>
       </c>
@@ -5040,7 +5042,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>1105</v>
       </c>
@@ -5072,7 +5074,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>1106</v>
       </c>
@@ -5104,7 +5106,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>1107</v>
       </c>
@@ -5136,7 +5138,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>1108</v>
       </c>
@@ -5168,7 +5170,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>1109</v>
       </c>
@@ -5200,7 +5202,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>1110</v>
       </c>
@@ -5232,7 +5234,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>1111</v>
       </c>
@@ -5264,7 +5266,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>1331</v>
       </c>
@@ -5296,7 +5298,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>1112</v>
       </c>
@@ -5328,7 +5330,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>1113</v>
       </c>
@@ -5360,7 +5362,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>1114</v>
       </c>
@@ -5392,7 +5394,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>1332</v>
       </c>
@@ -5424,7 +5426,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>1115</v>
       </c>
@@ -5456,7 +5458,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>1116</v>
       </c>
@@ -5488,7 +5490,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>1117</v>
       </c>
@@ -5520,7 +5522,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>1333</v>
       </c>
@@ -5552,7 +5554,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>1118</v>
       </c>
@@ -5584,7 +5586,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>1119</v>
       </c>
@@ -5616,7 +5618,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>1120</v>
       </c>
@@ -5648,7 +5650,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>1334</v>
       </c>
@@ -5680,7 +5682,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>1335</v>
       </c>
@@ -5712,7 +5714,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>1336</v>
       </c>
@@ -5744,7 +5746,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>1121</v>
       </c>
@@ -5776,7 +5778,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>1122</v>
       </c>
@@ -5808,7 +5810,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>1123</v>
       </c>
@@ -5840,7 +5842,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>1124</v>
       </c>
@@ -5872,7 +5874,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>1337</v>
       </c>
@@ -5904,7 +5906,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>1125</v>
       </c>
@@ -5936,7 +5938,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>1338</v>
       </c>
@@ -5968,7 +5970,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>1126</v>
       </c>
@@ -6000,7 +6002,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>1127</v>
       </c>
@@ -6032,7 +6034,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>1339</v>
       </c>
@@ -6064,7 +6066,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>1340</v>
       </c>
@@ -6096,7 +6098,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>1128</v>
       </c>
@@ -6128,7 +6130,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>1129</v>
       </c>
@@ -6160,7 +6162,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>1341</v>
       </c>
@@ -6192,7 +6194,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>1130</v>
       </c>
@@ -6224,7 +6226,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="47" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>1131</v>
       </c>
@@ -6256,7 +6258,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>1342</v>
       </c>
@@ -6288,7 +6290,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>1132</v>
       </c>
@@ -6320,7 +6322,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>1343</v>
       </c>
@@ -6352,7 +6354,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="51" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>1133</v>
       </c>
@@ -6384,7 +6386,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>1344</v>
       </c>
@@ -6416,7 +6418,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>1134</v>
       </c>
@@ -6448,7 +6450,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>1135</v>
       </c>
@@ -6480,7 +6482,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>1136</v>
       </c>
@@ -6512,7 +6514,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>1345</v>
       </c>
@@ -6544,7 +6546,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>1137</v>
       </c>
@@ -6576,7 +6578,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>1138</v>
       </c>
@@ -6608,7 +6610,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>1139</v>
       </c>
@@ -6640,7 +6642,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="60" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>1140</v>
       </c>
@@ -6672,7 +6674,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="61" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>1346</v>
       </c>
@@ -6704,7 +6706,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="62" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>1141</v>
       </c>
@@ -6736,7 +6738,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>1142</v>
       </c>
@@ -6768,7 +6770,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>1143</v>
       </c>
@@ -6800,7 +6802,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>1347</v>
       </c>
@@ -6832,7 +6834,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>1348</v>
       </c>
@@ -6864,7 +6866,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>1144</v>
       </c>
@@ -6896,7 +6898,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>1145</v>
       </c>
@@ -6928,7 +6930,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>1146</v>
       </c>
@@ -6960,7 +6962,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>1147</v>
       </c>
@@ -6992,7 +6994,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="71" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>1349</v>
       </c>
@@ -7024,7 +7026,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>1350</v>
       </c>
@@ -7056,7 +7058,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>1148</v>
       </c>
@@ -7088,7 +7090,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="74" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>1149</v>
       </c>
@@ -7120,7 +7122,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>1150</v>
       </c>
@@ -7152,7 +7154,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="76" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>1151</v>
       </c>
@@ -7184,7 +7186,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="77" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>1152</v>
       </c>
@@ -7216,7 +7218,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="78" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>1153</v>
       </c>
@@ -7248,7 +7250,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>1351</v>
       </c>
@@ -7280,7 +7282,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="80" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>1154</v>
       </c>
@@ -7312,7 +7314,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="81" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>1155</v>
       </c>
@@ -7344,7 +7346,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="82" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>1352</v>
       </c>
@@ -7376,7 +7378,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="83" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>1156</v>
       </c>
@@ -7408,7 +7410,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="84" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>1157</v>
       </c>
@@ -7440,7 +7442,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="85" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>1158</v>
       </c>
@@ -7472,7 +7474,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="86" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>1159</v>
       </c>
@@ -7504,7 +7506,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="87" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>1160</v>
       </c>
@@ -7536,7 +7538,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="88" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>1161</v>
       </c>
@@ -7568,7 +7570,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="89" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>1162</v>
       </c>
@@ -7600,7 +7602,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="90" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>1163</v>
       </c>
@@ -7632,7 +7634,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="91" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>1164</v>
       </c>
@@ -7664,7 +7666,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="92" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>1353</v>
       </c>
@@ -7696,7 +7698,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="93" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>1165</v>
       </c>
@@ -7728,7 +7730,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="94" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>1166</v>
       </c>
@@ -7760,7 +7762,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="95" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>1167</v>
       </c>
@@ -7792,7 +7794,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="96" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>1168</v>
       </c>
@@ -7824,7 +7826,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="97" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>1169</v>
       </c>
@@ -7856,7 +7858,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="98" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>1170</v>
       </c>
@@ -7888,7 +7890,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="99" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>1171</v>
       </c>
@@ -7920,7 +7922,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="100" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>1172</v>
       </c>
@@ -7952,7 +7954,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="101" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>1173</v>
       </c>
@@ -7984,7 +7986,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="102" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>1354</v>
       </c>
@@ -8016,7 +8018,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="103" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>1174</v>
       </c>
@@ -8048,7 +8050,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="104" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>1175</v>
       </c>
@@ -8080,7 +8082,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="105" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>1176</v>
       </c>
@@ -8112,7 +8114,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="106" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>1177</v>
       </c>
@@ -8144,7 +8146,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="107" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>1178</v>
       </c>
@@ -8176,7 +8178,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="108" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>1179</v>
       </c>
@@ -8208,7 +8210,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="109" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>1180</v>
       </c>
@@ -8240,7 +8242,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="110" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>1181</v>
       </c>
@@ -8272,7 +8274,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="111" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>1182</v>
       </c>
@@ -8304,7 +8306,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="112" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>1183</v>
       </c>
@@ -8336,7 +8338,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="113" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>1184</v>
       </c>
@@ -8368,7 +8370,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="114" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>1185</v>
       </c>
@@ -8400,7 +8402,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="115" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>1186</v>
       </c>
@@ -8432,7 +8434,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="116" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>1355</v>
       </c>
@@ -8464,7 +8466,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="117" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>1187</v>
       </c>
@@ -8496,7 +8498,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="118" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>1188</v>
       </c>
@@ -8528,7 +8530,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="119" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>1189</v>
       </c>
@@ -8560,7 +8562,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="120" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>1190</v>
       </c>
@@ -8592,7 +8594,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="121" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>1191</v>
       </c>
@@ -8624,7 +8626,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="122" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>1192</v>
       </c>
@@ -8656,7 +8658,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="123" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>1356</v>
       </c>
@@ -8688,7 +8690,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="124" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>1193</v>
       </c>
@@ -8720,7 +8722,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="125" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>1194</v>
       </c>
@@ -8752,7 +8754,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="126" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>1195</v>
       </c>
@@ -8784,7 +8786,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="127" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>1196</v>
       </c>
@@ -8816,7 +8818,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="128" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>1197</v>
       </c>
@@ -8848,7 +8850,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="129" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>1198</v>
       </c>
@@ -8880,7 +8882,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="130" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>1199</v>
       </c>
@@ -8912,7 +8914,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="131" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>1200</v>
       </c>
@@ -8944,7 +8946,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="132" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>1201</v>
       </c>
@@ -8976,7 +8978,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="133" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>1357</v>
       </c>
@@ -9008,7 +9010,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="134" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>1202</v>
       </c>
@@ -9040,7 +9042,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="135" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>1358</v>
       </c>
@@ -9072,7 +9074,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="136" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>1359</v>
       </c>
@@ -9104,7 +9106,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="137" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>1203</v>
       </c>
@@ -9136,7 +9138,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="138" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>1360</v>
       </c>
@@ -9168,7 +9170,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="139" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>1204</v>
       </c>
@@ -9200,7 +9202,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="140" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>1361</v>
       </c>
@@ -9232,7 +9234,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="141" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>1205</v>
       </c>
@@ -9264,7 +9266,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="142" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>1362</v>
       </c>
@@ -9296,7 +9298,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="143" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>1206</v>
       </c>
@@ -9328,7 +9330,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="144" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>1207</v>
       </c>
@@ -9360,7 +9362,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="145" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>1208</v>
       </c>
@@ -9392,7 +9394,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="146" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>1209</v>
       </c>
@@ -9424,7 +9426,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="147" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>1210</v>
       </c>
@@ -9456,7 +9458,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="148" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>1363</v>
       </c>
@@ -9488,7 +9490,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="149" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>1211</v>
       </c>
@@ -9520,7 +9522,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="150" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>1364</v>
       </c>
@@ -9552,7 +9554,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="151" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>1365</v>
       </c>
@@ -9584,7 +9586,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="152" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>1212</v>
       </c>
@@ -9616,7 +9618,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="153" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>1213</v>
       </c>
@@ -9648,7 +9650,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="154" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>1214</v>
       </c>
@@ -9680,7 +9682,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="155" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>1366</v>
       </c>
@@ -9712,7 +9714,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="156" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>1215</v>
       </c>
@@ -9744,7 +9746,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="157" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>1216</v>
       </c>
@@ -9776,7 +9778,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="158" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>1367</v>
       </c>
@@ -9808,7 +9810,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="159" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>1217</v>
       </c>
@@ -9840,7 +9842,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="160" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>1218</v>
       </c>
@@ -9872,7 +9874,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="161" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>1219</v>
       </c>
@@ -9904,7 +9906,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="162" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>1368</v>
       </c>
@@ -9936,7 +9938,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="163" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>1220</v>
       </c>
@@ -9968,7 +9970,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="164" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>1221</v>
       </c>
@@ -10000,7 +10002,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="165" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>1222</v>
       </c>
@@ -10032,7 +10034,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="166" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>1369</v>
       </c>
@@ -10064,7 +10066,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="167" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>1223</v>
       </c>
@@ -10096,7 +10098,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="168" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>1224</v>
       </c>
@@ -10128,7 +10130,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="169" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>1225</v>
       </c>
@@ -10160,7 +10162,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="170" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>1226</v>
       </c>
@@ -10192,7 +10194,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="171" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>1370</v>
       </c>
@@ -10224,7 +10226,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="172" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>1227</v>
       </c>
@@ -10256,7 +10258,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="173" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>1371</v>
       </c>
@@ -10288,7 +10290,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="174" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>1228</v>
       </c>
@@ -10320,7 +10322,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="175" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>1372</v>
       </c>
@@ -10352,7 +10354,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="176" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>1229</v>
       </c>
@@ -10384,7 +10386,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="177" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>1230</v>
       </c>
@@ -10416,7 +10418,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="178" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>1231</v>
       </c>
@@ -10448,7 +10450,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="179" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>1373</v>
       </c>
@@ -10480,7 +10482,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="180" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>1374</v>
       </c>
@@ -10512,7 +10514,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="181" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>1232</v>
       </c>
@@ -10544,7 +10546,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="182" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>1233</v>
       </c>
@@ -10576,7 +10578,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="183" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>1234</v>
       </c>
@@ -10608,7 +10610,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="184" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>1375</v>
       </c>
@@ -10640,7 +10642,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="185" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>1235</v>
       </c>
@@ -10672,7 +10674,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="186" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>1236</v>
       </c>
@@ -10704,7 +10706,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="187" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>1376</v>
       </c>
@@ -10736,7 +10738,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="188" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>1237</v>
       </c>
@@ -10768,7 +10770,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="189" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>1238</v>
       </c>
@@ -10800,7 +10802,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="190" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>1239</v>
       </c>
@@ -10832,7 +10834,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="191" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>1377</v>
       </c>
@@ -10864,7 +10866,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="192" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>1240</v>
       </c>
@@ -10896,7 +10898,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="193" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>1241</v>
       </c>
@@ -10928,7 +10930,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="194" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>1242</v>
       </c>
@@ -10960,7 +10962,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="195" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>1378</v>
       </c>
@@ -10992,7 +10994,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="196" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>1243</v>
       </c>
@@ -11024,7 +11026,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="197" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>1244</v>
       </c>
@@ -11056,7 +11058,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="198" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>1379</v>
       </c>
@@ -11088,7 +11090,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="199" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>1245</v>
       </c>
@@ -11120,7 +11122,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="200" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>1246</v>
       </c>
@@ -11152,7 +11154,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="201" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>1247</v>
       </c>
@@ -11184,7 +11186,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="202" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>1248</v>
       </c>
@@ -11216,7 +11218,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="203" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>1249</v>
       </c>
@@ -11248,7 +11250,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="204" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>1250</v>
       </c>
@@ -11280,7 +11282,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="205" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>1251</v>
       </c>
@@ -11312,7 +11314,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="206" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>1252</v>
       </c>
@@ -11344,7 +11346,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="207" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>1253</v>
       </c>
@@ -11376,7 +11378,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="208" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>1254</v>
       </c>
@@ -11408,7 +11410,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="209" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>1255</v>
       </c>
@@ -11440,7 +11442,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="210" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>1380</v>
       </c>
@@ -11472,7 +11474,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="211" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>1256</v>
       </c>
@@ -11504,7 +11506,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="212" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>1257</v>
       </c>
@@ -11536,7 +11538,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="213" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>1258</v>
       </c>
@@ -11568,7 +11570,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="214" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>1259</v>
       </c>
@@ -11600,7 +11602,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>1260</v>
       </c>
@@ -11632,7 +11634,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="216" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>1261</v>
       </c>
@@ -11664,7 +11666,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>1262</v>
       </c>
@@ -11696,7 +11698,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="218" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>1381</v>
       </c>
@@ -11728,7 +11730,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="219" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>1263</v>
       </c>
@@ -11760,7 +11762,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="220" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>1264</v>
       </c>
@@ -11792,7 +11794,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="221" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>1265</v>
       </c>
@@ -11824,7 +11826,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="222" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>1266</v>
       </c>
@@ -11856,7 +11858,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="223" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>1267</v>
       </c>
@@ -11888,7 +11890,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="224" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>1268</v>
       </c>
@@ -11920,7 +11922,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="225" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>1269</v>
       </c>
@@ -11952,7 +11954,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="226" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>1270</v>
       </c>
@@ -11984,7 +11986,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="227" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>1382</v>
       </c>
@@ -12016,7 +12018,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="228" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>1383</v>
       </c>
@@ -12048,7 +12050,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="229" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>1384</v>
       </c>
@@ -12080,7 +12082,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="230" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>1271</v>
       </c>
@@ -12112,7 +12114,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="231" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>1272</v>
       </c>
@@ -12144,7 +12146,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="232" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>1273</v>
       </c>
@@ -12176,7 +12178,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="233" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>1274</v>
       </c>
@@ -12208,7 +12210,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="234" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>1385</v>
       </c>
@@ -12240,7 +12242,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="235" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>1275</v>
       </c>
@@ -12272,7 +12274,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="236" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>1386</v>
       </c>
@@ -12304,7 +12306,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="237" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>1276</v>
       </c>
@@ -12336,7 +12338,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="238" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>1387</v>
       </c>
@@ -12368,7 +12370,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="239" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>1277</v>
       </c>
@@ -12400,7 +12402,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="240" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>1278</v>
       </c>
@@ -12432,7 +12434,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="241" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>1279</v>
       </c>
@@ -12464,7 +12466,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="242" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>1388</v>
       </c>
@@ -12496,7 +12498,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="243" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>1280</v>
       </c>
@@ -12528,7 +12530,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="244" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>1281</v>
       </c>
@@ -12560,7 +12562,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="245" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>1282</v>
       </c>
@@ -12592,7 +12594,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="246" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>1283</v>
       </c>
@@ -12624,7 +12626,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="247" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>1284</v>
       </c>
@@ -12656,7 +12658,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="248" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>1389</v>
       </c>
@@ -12688,7 +12690,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="249" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>1285</v>
       </c>
@@ -12720,7 +12722,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="250" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>1286</v>
       </c>
@@ -12752,7 +12754,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="251" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>1390</v>
       </c>
@@ -12784,7 +12786,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="252" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>1287</v>
       </c>
@@ -12816,7 +12818,7 @@
         <v>649.995</v>
       </c>
     </row>
-    <row r="253" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>1391</v>
       </c>
@@ -12848,7 +12850,7 @@
         <v>649.995</v>
       </c>
     </row>
-    <row r="254" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>1392</v>
       </c>
@@ -12880,7 +12882,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="255" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>1393</v>
       </c>
@@ -12912,7 +12914,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="256" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>1394</v>
       </c>
@@ -12944,7 +12946,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="257" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>1288</v>
       </c>
@@ -12976,7 +12978,7 @@
         <v>399.995</v>
       </c>
     </row>
-    <row r="258" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>1289</v>
       </c>
@@ -13008,7 +13010,7 @@
         <v>349.995</v>
       </c>
     </row>
-    <row r="259" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>1395</v>
       </c>
@@ -13040,7 +13042,7 @@
         <v>349.995</v>
       </c>
     </row>
-    <row r="260" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>1290</v>
       </c>
@@ -13072,7 +13074,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="261" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>1396</v>
       </c>
@@ -13104,7 +13106,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="262" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>1291</v>
       </c>
@@ -13136,7 +13138,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="263" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>1397</v>
       </c>
@@ -13168,7 +13170,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="264" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>1292</v>
       </c>
@@ -13200,7 +13202,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="265" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>1293</v>
       </c>
@@ -13232,7 +13234,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="266" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>1294</v>
       </c>
@@ -13264,7 +13266,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="267" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>1295</v>
       </c>
@@ -13296,7 +13298,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="268" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>1296</v>
       </c>
@@ -13328,7 +13330,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="269" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>1297</v>
       </c>
@@ -13360,7 +13362,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="270" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>1298</v>
       </c>
@@ -13392,7 +13394,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="271" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>1299</v>
       </c>
@@ -13424,7 +13426,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="272" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>1300</v>
       </c>
@@ -13456,7 +13458,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="273" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>1398</v>
       </c>
@@ -13488,7 +13490,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="274" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>1301</v>
       </c>
@@ -13520,7 +13522,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="275" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>1399</v>
       </c>
@@ -13552,7 +13554,7 @@
         <v>189.995</v>
       </c>
     </row>
-    <row r="276" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>1302</v>
       </c>
@@ -13584,7 +13586,7 @@
         <v>189.995</v>
       </c>
     </row>
-    <row r="277" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>1303</v>
       </c>
@@ -13616,7 +13618,7 @@
         <v>189.995</v>
       </c>
     </row>
-    <row r="278" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>1304</v>
       </c>
@@ -13648,7 +13650,7 @@
         <v>189.995</v>
       </c>
     </row>
-    <row r="279" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>1400</v>
       </c>
@@ -13680,7 +13682,7 @@
         <v>189.995</v>
       </c>
     </row>
-    <row r="280" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>1305</v>
       </c>
@@ -13712,7 +13714,7 @@
         <v>189.995</v>
       </c>
     </row>
-    <row r="281" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>1401</v>
       </c>
@@ -13744,7 +13746,7 @@
         <v>189.995</v>
       </c>
     </row>
-    <row r="282" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>1306</v>
       </c>
@@ -13776,7 +13778,7 @@
         <v>189.995</v>
       </c>
     </row>
-    <row r="283" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>1402</v>
       </c>
@@ -13808,7 +13810,7 @@
         <v>174.995</v>
       </c>
     </row>
-    <row r="284" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>1307</v>
       </c>
@@ -13840,7 +13842,7 @@
         <v>174.995</v>
       </c>
     </row>
-    <row r="285" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>1403</v>
       </c>
@@ -13872,7 +13874,7 @@
         <v>174.995</v>
       </c>
     </row>
-    <row r="286" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>1308</v>
       </c>
@@ -13904,7 +13906,7 @@
         <v>174.995</v>
       </c>
     </row>
-    <row r="287" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>1309</v>
       </c>
@@ -13936,7 +13938,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="288" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>1310</v>
       </c>
@@ -13968,7 +13970,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="289" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>1311</v>
       </c>
@@ -14000,7 +14002,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="290" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>1312</v>
       </c>
@@ -14032,7 +14034,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="291" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>1313</v>
       </c>
@@ -14064,7 +14066,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="292" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>1314</v>
       </c>
@@ -14096,7 +14098,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="293" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>1315</v>
       </c>
@@ -14128,7 +14130,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="294" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>1316</v>
       </c>
@@ -14160,7 +14162,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="295" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>1317</v>
       </c>
@@ -14192,7 +14194,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="296" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>1404</v>
       </c>
@@ -14224,7 +14226,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="297" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>1318</v>
       </c>
@@ -14256,7 +14258,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="298" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>1319</v>
       </c>
@@ -14288,7 +14290,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="299" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>1320</v>
       </c>
@@ -14320,7 +14322,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="300" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>1321</v>
       </c>
@@ -14352,7 +14354,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="301" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>1405</v>
       </c>
@@ -14384,7 +14386,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="302" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>1322</v>
       </c>
@@ -14416,7 +14418,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>1323</v>
       </c>
@@ -14448,7 +14450,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>1324</v>
       </c>
@@ -14480,7 +14482,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="305" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>1325</v>
       </c>
@@ -14512,7 +14514,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="306" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>1326</v>
       </c>
@@ -14544,7 +14546,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="307" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>1406</v>
       </c>
@@ -14576,7 +14578,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="308" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>1327</v>
       </c>
@@ -14608,7 +14610,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="309" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>1328</v>
       </c>
@@ -14640,7 +14642,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="310" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>1407</v>
       </c>
@@ -14672,7 +14674,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="311" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>1408</v>
       </c>
@@ -14704,7 +14706,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="312" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>611</v>
       </c>
@@ -14736,7 +14738,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="313" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>612</v>
       </c>
@@ -14768,7 +14770,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="314" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>613</v>
       </c>
@@ -14800,7 +14802,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="315" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>614</v>
       </c>
@@ -14832,7 +14834,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="316" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>615</v>
       </c>
@@ -14864,7 +14866,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="317" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>616</v>
       </c>
@@ -14896,7 +14898,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="318" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>617</v>
       </c>
@@ -14928,7 +14930,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="319" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>618</v>
       </c>
@@ -14960,7 +14962,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="320" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>619</v>
       </c>
@@ -14992,7 +14994,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="321" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>620</v>
       </c>
@@ -15024,7 +15026,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="322" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>621</v>
       </c>
@@ -15056,7 +15058,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="323" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>622</v>
       </c>
@@ -15088,7 +15090,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="324" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>623</v>
       </c>
@@ -15120,7 +15122,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="325" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>624</v>
       </c>
@@ -15152,7 +15154,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="326" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>625</v>
       </c>
@@ -15184,7 +15186,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="327" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>626</v>
       </c>
@@ -15216,7 +15218,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="328" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>627</v>
       </c>
@@ -15248,7 +15250,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="329" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>628</v>
       </c>
@@ -15280,7 +15282,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="330" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>629</v>
       </c>
@@ -15312,7 +15314,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="331" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>630</v>
       </c>
@@ -15344,7 +15346,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="332" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>631</v>
       </c>
@@ -15376,7 +15378,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="333" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>632</v>
       </c>
@@ -15408,7 +15410,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="334" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>633</v>
       </c>
@@ -15440,7 +15442,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="335" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>634</v>
       </c>
@@ -15472,7 +15474,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="336" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>635</v>
       </c>
@@ -15504,7 +15506,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="337" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>636</v>
       </c>
@@ -15536,7 +15538,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="338" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>637</v>
       </c>
@@ -15568,7 +15570,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="339" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>638</v>
       </c>
@@ -15600,7 +15602,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="340" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>639</v>
       </c>
@@ -15632,7 +15634,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="341" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>640</v>
       </c>
@@ -15664,7 +15666,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="342" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>641</v>
       </c>
@@ -15696,7 +15698,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="343" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>642</v>
       </c>
@@ -15728,7 +15730,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="344" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>643</v>
       </c>
@@ -15760,7 +15762,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="345" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>644</v>
       </c>
@@ -15792,7 +15794,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="346" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>645</v>
       </c>
@@ -15824,7 +15826,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="347" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>646</v>
       </c>
@@ -15856,7 +15858,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="348" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>647</v>
       </c>
@@ -15888,7 +15890,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="349" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>648</v>
       </c>
@@ -15920,7 +15922,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="350" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>649</v>
       </c>
@@ -15952,7 +15954,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="351" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>650</v>
       </c>
@@ -15984,7 +15986,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="352" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>651</v>
       </c>
@@ -16016,7 +16018,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="353" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>652</v>
       </c>
@@ -16048,7 +16050,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="354" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>653</v>
       </c>
@@ -16080,7 +16082,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="355" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>654</v>
       </c>
@@ -16112,7 +16114,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="356" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>655</v>
       </c>
@@ -16144,7 +16146,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="357" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>656</v>
       </c>
@@ -16176,7 +16178,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="358" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>657</v>
       </c>
@@ -16208,7 +16210,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="359" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>658</v>
       </c>
@@ -16240,7 +16242,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="360" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>659</v>
       </c>
@@ -16272,7 +16274,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="361" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>660</v>
       </c>
@@ -16304,7 +16306,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="362" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>661</v>
       </c>
@@ -16336,7 +16338,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="363" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>662</v>
       </c>
@@ -16368,7 +16370,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="364" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>663</v>
       </c>
@@ -16400,7 +16402,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="365" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>664</v>
       </c>
@@ -16432,7 +16434,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="366" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>665</v>
       </c>
@@ -16464,7 +16466,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="367" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>666</v>
       </c>
@@ -16496,7 +16498,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="368" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>667</v>
       </c>
@@ -16528,7 +16530,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="369" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>668</v>
       </c>
@@ -16560,7 +16562,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="370" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>669</v>
       </c>
@@ -16592,7 +16594,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="371" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>670</v>
       </c>
@@ -16624,7 +16626,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="372" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>671</v>
       </c>
@@ -16656,7 +16658,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="373" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>672</v>
       </c>
@@ -16688,7 +16690,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="374" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>673</v>
       </c>
@@ -16720,7 +16722,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="375" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>674</v>
       </c>
@@ -16752,7 +16754,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="376" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>675</v>
       </c>
@@ -16784,7 +16786,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="377" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>676</v>
       </c>
@@ -16816,7 +16818,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="378" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>677</v>
       </c>
@@ -16848,7 +16850,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="379" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>678</v>
       </c>
@@ -16880,7 +16882,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="380" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>679</v>
       </c>
@@ -16912,7 +16914,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="381" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>680</v>
       </c>
@@ -16944,7 +16946,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="382" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>681</v>
       </c>
@@ -16976,7 +16978,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="383" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>682</v>
       </c>
@@ -17008,7 +17010,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="384" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>683</v>
       </c>
@@ -17040,7 +17042,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="385" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>684</v>
       </c>
@@ -17072,7 +17074,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="386" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>685</v>
       </c>
@@ -17104,7 +17106,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="387" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>686</v>
       </c>
@@ -17136,7 +17138,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="388" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>687</v>
       </c>
@@ -17168,7 +17170,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="389" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>688</v>
       </c>
@@ -17200,7 +17202,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="390" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>689</v>
       </c>
@@ -17232,7 +17234,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="391" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>690</v>
       </c>
@@ -17264,7 +17266,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="392" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>691</v>
       </c>
@@ -17296,7 +17298,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="393" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>692</v>
       </c>
@@ -17328,7 +17330,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="394" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>1409</v>
       </c>
@@ -17360,7 +17362,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="395" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>1410</v>
       </c>
@@ -17392,7 +17394,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="396" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>693</v>
       </c>
@@ -17424,7 +17426,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="397" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>694</v>
       </c>
@@ -17456,7 +17458,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="398" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>1411</v>
       </c>
@@ -17488,7 +17490,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="399" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>695</v>
       </c>
@@ -17520,7 +17522,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="400" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>696</v>
       </c>
@@ -17552,7 +17554,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="401" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>697</v>
       </c>
@@ -17584,7 +17586,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="402" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>698</v>
       </c>
@@ -17616,7 +17618,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="403" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>699</v>
       </c>
@@ -17648,7 +17650,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="404" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>700</v>
       </c>
@@ -17680,7 +17682,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="405" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>701</v>
       </c>
@@ -17712,7 +17714,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="406" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>702</v>
       </c>
@@ -17744,7 +17746,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="407" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>703</v>
       </c>
@@ -17776,7 +17778,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="408" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>704</v>
       </c>
@@ -17808,7 +17810,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="409" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>705</v>
       </c>
@@ -17840,7 +17842,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="410" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>706</v>
       </c>
@@ -17872,7 +17874,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="411" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>707</v>
       </c>
@@ -17904,7 +17906,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>708</v>
       </c>
@@ -17936,7 +17938,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="413" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>709</v>
       </c>
@@ -17968,7 +17970,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>710</v>
       </c>
@@ -18000,7 +18002,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>711</v>
       </c>
@@ -18032,7 +18034,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="416" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>712</v>
       </c>
@@ -18064,7 +18066,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="417" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>713</v>
       </c>
@@ -18096,7 +18098,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="418" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>714</v>
       </c>
@@ -18128,7 +18130,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>715</v>
       </c>
@@ -18160,7 +18162,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="420" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>716</v>
       </c>
@@ -18192,7 +18194,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="421" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>717</v>
       </c>
@@ -18224,7 +18226,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="422" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>718</v>
       </c>
@@ -18256,7 +18258,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>719</v>
       </c>
@@ -18288,7 +18290,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="424" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>720</v>
       </c>
@@ -18320,7 +18322,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="425" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>721</v>
       </c>
@@ -18352,7 +18354,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="426" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>722</v>
       </c>
@@ -18384,7 +18386,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="427" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>1412</v>
       </c>
@@ -18416,7 +18418,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="428" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>1413</v>
       </c>
@@ -18448,7 +18450,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="429" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>723</v>
       </c>
@@ -18480,7 +18482,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="430" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>724</v>
       </c>
@@ -18512,7 +18514,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="431" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>1414</v>
       </c>
@@ -18544,7 +18546,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="432" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>725</v>
       </c>
@@ -18576,7 +18578,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="433" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>726</v>
       </c>
@@ -18608,7 +18610,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="434" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>727</v>
       </c>
@@ -18640,7 +18642,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="435" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>728</v>
       </c>
@@ -18672,7 +18674,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="436" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>729</v>
       </c>
@@ -18704,7 +18706,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="437" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>730</v>
       </c>
@@ -18736,7 +18738,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="438" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>731</v>
       </c>
@@ -18768,7 +18770,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="439" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>732</v>
       </c>
@@ -18800,7 +18802,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="440" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>733</v>
       </c>
@@ -18832,7 +18834,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="441" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>734</v>
       </c>
@@ -18864,7 +18866,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="442" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>735</v>
       </c>
@@ -18896,7 +18898,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="443" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>736</v>
       </c>
@@ -18928,7 +18930,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="444" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>737</v>
       </c>
@@ -18960,7 +18962,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="445" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>738</v>
       </c>
@@ -18992,7 +18994,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="446" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>739</v>
       </c>
@@ -19024,7 +19026,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="447" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>740</v>
       </c>
@@ -19056,7 +19058,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="448" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>741</v>
       </c>
@@ -19088,7 +19090,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="449" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>742</v>
       </c>
@@ -19120,7 +19122,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="450" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>743</v>
       </c>
@@ -19152,7 +19154,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="451" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>744</v>
       </c>
@@ -19184,7 +19186,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="452" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>745</v>
       </c>
@@ -19216,7 +19218,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="453" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>746</v>
       </c>
@@ -19248,7 +19250,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="454" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>747</v>
       </c>
@@ -19280,7 +19282,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="455" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>748</v>
       </c>
@@ -19312,7 +19314,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="456" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>749</v>
       </c>
@@ -19344,7 +19346,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="457" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>750</v>
       </c>
@@ -19376,7 +19378,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="458" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>751</v>
       </c>
@@ -19408,7 +19410,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="459" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>752</v>
       </c>
@@ -19440,7 +19442,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="460" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>753</v>
       </c>
@@ -19472,7 +19474,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="461" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>754</v>
       </c>
@@ -19504,7 +19506,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="462" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>755</v>
       </c>
@@ -19536,7 +19538,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="463" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>756</v>
       </c>
@@ -19568,7 +19570,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="464" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>757</v>
       </c>
@@ -19600,7 +19602,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="465" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>758</v>
       </c>
@@ -19632,7 +19634,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>759</v>
       </c>
@@ -19664,7 +19666,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="467" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>1415</v>
       </c>
@@ -19696,7 +19698,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="468" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>760</v>
       </c>
@@ -19728,7 +19730,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="469" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>761</v>
       </c>
@@ -19760,7 +19762,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="470" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>762</v>
       </c>
@@ -19792,7 +19794,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>1416</v>
       </c>
@@ -19824,7 +19826,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="472" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>1417</v>
       </c>
@@ -19856,7 +19858,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="473" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>763</v>
       </c>
@@ -19888,7 +19890,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="474" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>764</v>
       </c>
@@ -19920,7 +19922,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="475" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>765</v>
       </c>
@@ -19952,7 +19954,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="476" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>766</v>
       </c>
@@ -19984,7 +19986,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="477" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>1418</v>
       </c>
@@ -20016,7 +20018,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="478" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>767</v>
       </c>
@@ -20112,7 +20114,7 @@
         <v>179.995</v>
       </c>
     </row>
-    <row r="481" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>1419</v>
       </c>
@@ -20144,7 +20146,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="482" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>770</v>
       </c>
@@ -20176,7 +20178,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="483" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>771</v>
       </c>
@@ -20208,7 +20210,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="484" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>772</v>
       </c>
@@ -20240,7 +20242,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="485" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>773</v>
       </c>
@@ -20272,7 +20274,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="486" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>774</v>
       </c>
@@ -20304,7 +20306,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="487" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>1420</v>
       </c>
@@ -20336,7 +20338,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="488" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>775</v>
       </c>
@@ -20368,7 +20370,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="489" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>1421</v>
       </c>
@@ -20400,7 +20402,7 @@
         <v>109.995</v>
       </c>
     </row>
-    <row r="490" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>776</v>
       </c>
@@ -20432,7 +20434,7 @@
         <v>109.995</v>
       </c>
     </row>
-    <row r="491" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>777</v>
       </c>
@@ -20464,7 +20466,7 @@
         <v>109.995</v>
       </c>
     </row>
-    <row r="492" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>1422</v>
       </c>
@@ -20560,7 +20562,7 @@
         <v>179.995</v>
       </c>
     </row>
-    <row r="495" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>780</v>
       </c>
@@ -20592,7 +20594,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="496" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>781</v>
       </c>
@@ -20624,7 +20626,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="497" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>782</v>
       </c>
@@ -20656,7 +20658,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="498" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>783</v>
       </c>
@@ -20688,7 +20690,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="499" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>784</v>
       </c>
@@ -20720,7 +20722,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="500" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>785</v>
       </c>
@@ -20752,7 +20754,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="501" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>1423</v>
       </c>
@@ -20784,7 +20786,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="502" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>786</v>
       </c>
@@ -20816,7 +20818,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="503" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>787</v>
       </c>
@@ -20848,7 +20850,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="504" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>788</v>
       </c>
@@ -20880,7 +20882,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="505" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>789</v>
       </c>
@@ -20912,7 +20914,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="506" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>790</v>
       </c>
@@ -20944,7 +20946,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="507" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>791</v>
       </c>
@@ -20976,7 +20978,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="508" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>1424</v>
       </c>
@@ -21008,7 +21010,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="509" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>792</v>
       </c>
@@ -21040,7 +21042,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="510" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>793</v>
       </c>
@@ -21072,7 +21074,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="511" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>794</v>
       </c>
@@ -21104,7 +21106,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="512" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>795</v>
       </c>
@@ -21136,7 +21138,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="513" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>796</v>
       </c>
@@ -21168,7 +21170,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="514" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>797</v>
       </c>
@@ -21200,7 +21202,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="515" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>798</v>
       </c>
@@ -21232,7 +21234,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="516" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>799</v>
       </c>
@@ -21264,7 +21266,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="517" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>800</v>
       </c>
@@ -21296,7 +21298,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="518" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>801</v>
       </c>
@@ -21328,7 +21330,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="519" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>802</v>
       </c>
@@ -21360,7 +21362,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="520" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>803</v>
       </c>
@@ -21392,7 +21394,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="521" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>804</v>
       </c>
@@ -21424,7 +21426,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="522" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>805</v>
       </c>
@@ -21456,7 +21458,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="523" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>806</v>
       </c>
@@ -21488,7 +21490,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="524" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>807</v>
       </c>
@@ -21520,7 +21522,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="525" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>808</v>
       </c>
@@ -21552,7 +21554,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="526" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>809</v>
       </c>
@@ -21584,7 +21586,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="527" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>810</v>
       </c>
@@ -21616,7 +21618,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>811</v>
       </c>
@@ -21648,7 +21650,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="529" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>812</v>
       </c>
@@ -21680,7 +21682,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="530" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>813</v>
       </c>
@@ -21712,7 +21714,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="531" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>814</v>
       </c>
@@ -21744,7 +21746,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="532" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>815</v>
       </c>
@@ -21776,7 +21778,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="533" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>816</v>
       </c>
@@ -21808,7 +21810,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="534" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>817</v>
       </c>
@@ -21840,7 +21842,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="535" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>818</v>
       </c>
@@ -21872,7 +21874,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="536" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>819</v>
       </c>
@@ -21904,7 +21906,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="537" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>820</v>
       </c>
@@ -21936,7 +21938,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="538" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>821</v>
       </c>
@@ -21968,7 +21970,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="539" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>822</v>
       </c>
@@ -22000,7 +22002,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="540" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>823</v>
       </c>
@@ -22032,7 +22034,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="541" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>824</v>
       </c>
@@ -22064,7 +22066,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="542" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>825</v>
       </c>
@@ -22096,7 +22098,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="543" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>826</v>
       </c>
@@ -22128,7 +22130,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="544" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>827</v>
       </c>
@@ -22160,7 +22162,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="545" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>828</v>
       </c>
@@ -22192,7 +22194,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="546" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>829</v>
       </c>
@@ -22224,7 +22226,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="547" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>830</v>
       </c>
@@ -22256,7 +22258,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="548" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>831</v>
       </c>
@@ -22288,7 +22290,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="549" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>832</v>
       </c>
@@ -22320,7 +22322,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="550" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>833</v>
       </c>
@@ -22352,7 +22354,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="551" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>834</v>
       </c>
@@ -22384,7 +22386,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="552" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>835</v>
       </c>
@@ -22416,7 +22418,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="553" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>836</v>
       </c>
@@ -22448,7 +22450,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="554" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>837</v>
       </c>
@@ -22480,7 +22482,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="555" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>838</v>
       </c>
@@ -22512,7 +22514,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="556" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>839</v>
       </c>
@@ -22544,7 +22546,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="557" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>840</v>
       </c>
@@ -22576,7 +22578,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="558" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>841</v>
       </c>
@@ -22608,7 +22610,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="559" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>842</v>
       </c>
@@ -22640,7 +22642,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="560" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>843</v>
       </c>
@@ -22672,7 +22674,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="561" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>844</v>
       </c>
@@ -22704,7 +22706,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="562" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>845</v>
       </c>
@@ -22736,7 +22738,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="563" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>846</v>
       </c>
@@ -22768,7 +22770,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="564" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>847</v>
       </c>
@@ -22800,7 +22802,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="565" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>848</v>
       </c>
@@ -22832,7 +22834,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="566" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>849</v>
       </c>
@@ -22864,7 +22866,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="567" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>850</v>
       </c>
@@ -22896,7 +22898,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="568" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>851</v>
       </c>
@@ -22928,7 +22930,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="569" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>852</v>
       </c>
@@ -22960,7 +22962,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="570" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>853</v>
       </c>
@@ -22992,7 +22994,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="571" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>854</v>
       </c>
@@ -23024,7 +23026,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="572" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>855</v>
       </c>
@@ -23056,7 +23058,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="573" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>856</v>
       </c>
@@ -23088,7 +23090,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="574" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>1425</v>
       </c>
@@ -23120,7 +23122,7 @@
         <v>34.994999999999997</v>
       </c>
     </row>
-    <row r="575" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>857</v>
       </c>
@@ -23152,7 +23154,7 @@
         <v>34.994999999999997</v>
       </c>
     </row>
-    <row r="576" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>858</v>
       </c>
@@ -23184,7 +23186,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="577" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>859</v>
       </c>
@@ -23216,7 +23218,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="578" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>860</v>
       </c>
@@ -23248,7 +23250,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="579" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>861</v>
       </c>
@@ -23280,7 +23282,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="580" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>862</v>
       </c>
@@ -23312,7 +23314,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="581" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>863</v>
       </c>
@@ -23344,7 +23346,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="582" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>864</v>
       </c>
@@ -23376,7 +23378,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="583" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>865</v>
       </c>
@@ -23408,7 +23410,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="584" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>866</v>
       </c>
@@ -23440,7 +23442,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="585" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>867</v>
       </c>
@@ -23472,7 +23474,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="586" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>868</v>
       </c>
@@ -23504,7 +23506,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="587" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>869</v>
       </c>
@@ -23536,7 +23538,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="588" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>870</v>
       </c>
@@ -23568,7 +23570,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="589" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>871</v>
       </c>
@@ -23600,7 +23602,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="590" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>872</v>
       </c>
@@ -23632,7 +23634,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="591" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>873</v>
       </c>
@@ -23664,7 +23666,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="592" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>874</v>
       </c>
@@ -23696,7 +23698,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="593" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>875</v>
       </c>
@@ -23728,7 +23730,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="594" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>876</v>
       </c>
@@ -23760,7 +23762,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="595" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>877</v>
       </c>
@@ -23792,7 +23794,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="596" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>1426</v>
       </c>
@@ -23824,7 +23826,7 @@
         <v>34.994999999999997</v>
       </c>
     </row>
-    <row r="597" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>878</v>
       </c>
@@ -23856,7 +23858,7 @@
         <v>34.994999999999997</v>
       </c>
     </row>
-    <row r="598" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>879</v>
       </c>
@@ -23888,7 +23890,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="599" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>880</v>
       </c>
@@ -23920,7 +23922,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="600" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>881</v>
       </c>
@@ -23952,7 +23954,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="601" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>882</v>
       </c>
@@ -23984,7 +23986,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="602" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>883</v>
       </c>
@@ -24016,7 +24018,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="603" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>884</v>
       </c>
@@ -24048,7 +24050,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="604" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>885</v>
       </c>
@@ -24080,7 +24082,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="605" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>886</v>
       </c>
@@ -24112,7 +24114,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="606" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>887</v>
       </c>
@@ -24144,7 +24146,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="607" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>888</v>
       </c>
@@ -24176,7 +24178,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="608" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>889</v>
       </c>
@@ -24208,7 +24210,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="609" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>890</v>
       </c>
@@ -24240,7 +24242,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="610" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>891</v>
       </c>
@@ -24272,7 +24274,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="611" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>892</v>
       </c>
@@ -24304,7 +24306,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="612" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>893</v>
       </c>
@@ -24336,7 +24338,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="613" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>894</v>
       </c>
@@ -24368,7 +24370,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="614" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>895</v>
       </c>
@@ -24400,7 +24402,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="615" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>896</v>
       </c>
@@ -24432,7 +24434,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="616" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>897</v>
       </c>
@@ -24464,7 +24466,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="617" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>898</v>
       </c>
@@ -24496,7 +24498,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="618" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>899</v>
       </c>
@@ -24528,7 +24530,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="619" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>900</v>
       </c>
@@ -24560,7 +24562,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="620" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>901</v>
       </c>
@@ -24592,7 +24594,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="621" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>902</v>
       </c>
@@ -24624,7 +24626,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="622" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>903</v>
       </c>
@@ -24656,7 +24658,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="623" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>904</v>
       </c>
@@ -24688,7 +24690,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="624" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>905</v>
       </c>
@@ -24720,7 +24722,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="625" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>906</v>
       </c>
@@ -24752,7 +24754,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="626" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>907</v>
       </c>
@@ -24784,7 +24786,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="627" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>908</v>
       </c>
@@ -24816,7 +24818,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="628" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>909</v>
       </c>
@@ -24848,7 +24850,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="629" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>910</v>
       </c>
@@ -24880,7 +24882,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="630" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>911</v>
       </c>
@@ -24912,7 +24914,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="631" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>912</v>
       </c>
@@ -24944,7 +24946,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="632" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>913</v>
       </c>
@@ -24976,7 +24978,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="633" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>914</v>
       </c>
@@ -25008,7 +25010,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="634" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>915</v>
       </c>
@@ -25040,7 +25042,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="635" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>916</v>
       </c>
@@ -25072,7 +25074,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="636" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>917</v>
       </c>
@@ -25104,7 +25106,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="637" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>918</v>
       </c>
@@ -25136,7 +25138,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="638" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>919</v>
       </c>
@@ -25168,7 +25170,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="639" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>920</v>
       </c>
@@ -25200,7 +25202,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="640" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>921</v>
       </c>
@@ -25232,7 +25234,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="641" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>922</v>
       </c>
@@ -25264,7 +25266,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="642" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>923</v>
       </c>
@@ -25296,7 +25298,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="643" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>924</v>
       </c>
@@ -25328,7 +25330,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="644" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>925</v>
       </c>
@@ -25360,7 +25362,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="645" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>926</v>
       </c>
@@ -25392,7 +25394,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="646" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>927</v>
       </c>
@@ -25424,7 +25426,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="647" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>928</v>
       </c>
@@ -25456,7 +25458,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="648" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>929</v>
       </c>
@@ -25488,7 +25490,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="649" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>930</v>
       </c>
@@ -25520,7 +25522,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="650" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>931</v>
       </c>
@@ -25552,7 +25554,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="651" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>932</v>
       </c>
@@ -25584,7 +25586,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="652" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>933</v>
       </c>
@@ -25616,7 +25618,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="653" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>934</v>
       </c>
@@ -25648,7 +25650,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="654" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>935</v>
       </c>
@@ -25680,7 +25682,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="655" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>936</v>
       </c>
@@ -25712,7 +25714,7 @@
         <v>79.995000000000005</v>
       </c>
     </row>
-    <row r="656" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>937</v>
       </c>
@@ -25744,7 +25746,7 @@
         <v>79.995000000000005</v>
       </c>
     </row>
-    <row r="657" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>938</v>
       </c>
@@ -25776,7 +25778,7 @@
         <v>79.995000000000005</v>
       </c>
     </row>
-    <row r="658" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>939</v>
       </c>
@@ -25808,7 +25810,7 @@
         <v>79.995000000000005</v>
       </c>
     </row>
-    <row r="659" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>940</v>
       </c>
@@ -25840,7 +25842,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="660" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>941</v>
       </c>
@@ -25872,7 +25874,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="661" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>942</v>
       </c>
@@ -25904,7 +25906,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="662" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>943</v>
       </c>
@@ -25936,7 +25938,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="663" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>944</v>
       </c>
@@ -25968,7 +25970,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="664" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>945</v>
       </c>
@@ -26064,7 +26066,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="667" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>948</v>
       </c>
@@ -26096,7 +26098,7 @@
         <v>144.995</v>
       </c>
     </row>
-    <row r="668" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>949</v>
       </c>
@@ -26128,7 +26130,7 @@
         <v>144.995</v>
       </c>
     </row>
-    <row r="669" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>950</v>
       </c>
@@ -26160,7 +26162,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="670" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>951</v>
       </c>
@@ -26192,7 +26194,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="671" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>952</v>
       </c>
@@ -26224,7 +26226,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="672" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>953</v>
       </c>
@@ -26256,7 +26258,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="673" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>954</v>
       </c>
@@ -26288,7 +26290,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="674" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>955</v>
       </c>
@@ -26320,7 +26322,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="675" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>956</v>
       </c>
@@ -26352,7 +26354,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="676" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>957</v>
       </c>
@@ -26384,7 +26386,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="677" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>958</v>
       </c>
@@ -26416,7 +26418,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="678" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>959</v>
       </c>
@@ -26448,7 +26450,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="679" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>960</v>
       </c>
@@ -26480,7 +26482,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="680" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>961</v>
       </c>
@@ -26512,7 +26514,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="681" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>962</v>
       </c>
@@ -26544,7 +26546,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="682" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>963</v>
       </c>
@@ -26576,7 +26578,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="683" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>964</v>
       </c>
@@ -26608,7 +26610,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="684" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>965</v>
       </c>
@@ -26640,7 +26642,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="685" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>966</v>
       </c>
@@ -26672,7 +26674,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="686" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>967</v>
       </c>
@@ -26704,7 +26706,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="687" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>968</v>
       </c>
@@ -26736,7 +26738,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="688" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>969</v>
       </c>
@@ -26768,7 +26770,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="689" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>970</v>
       </c>
@@ -26800,7 +26802,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="690" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>971</v>
       </c>
@@ -26832,7 +26834,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="691" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>972</v>
       </c>
@@ -26864,7 +26866,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="692" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>973</v>
       </c>
@@ -26896,7 +26898,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="693" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>974</v>
       </c>
@@ -26928,7 +26930,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="694" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>975</v>
       </c>
@@ -26960,7 +26962,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="695" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>976</v>
       </c>
@@ -26992,7 +26994,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="696" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>977</v>
       </c>
@@ -27024,7 +27026,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="697" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>978</v>
       </c>
@@ -27056,7 +27058,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="698" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>979</v>
       </c>
@@ -27088,7 +27090,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="699" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>980</v>
       </c>
@@ -27120,7 +27122,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="700" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>981</v>
       </c>
@@ -27152,7 +27154,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="701" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>982</v>
       </c>
@@ -27184,7 +27186,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="702" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>983</v>
       </c>
@@ -27216,7 +27218,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="703" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>984</v>
       </c>
@@ -27248,7 +27250,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="704" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>985</v>
       </c>
@@ -27280,7 +27282,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="705" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>986</v>
       </c>
@@ -27312,7 +27314,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="706" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>987</v>
       </c>
@@ -27344,7 +27346,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="707" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>988</v>
       </c>
@@ -27376,7 +27378,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="708" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>989</v>
       </c>
@@ -27408,7 +27410,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="709" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>990</v>
       </c>
@@ -27440,7 +27442,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="710" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>991</v>
       </c>
@@ -27472,7 +27474,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="711" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>992</v>
       </c>
@@ -27504,7 +27506,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="712" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>993</v>
       </c>
@@ -27536,7 +27538,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="713" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>994</v>
       </c>
@@ -27568,7 +27570,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="714" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>995</v>
       </c>
@@ -27600,7 +27602,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="715" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>996</v>
       </c>
@@ -27632,7 +27634,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="716" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>997</v>
       </c>
@@ -27664,7 +27666,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="717" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>998</v>
       </c>
@@ -27696,7 +27698,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="718" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>999</v>
       </c>
@@ -27728,7 +27730,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="719" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>1000</v>
       </c>
@@ -27760,7 +27762,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="720" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>1001</v>
       </c>
@@ -27792,7 +27794,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="721" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1002</v>
       </c>
@@ -27824,7 +27826,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="722" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1003</v>
       </c>
@@ -27920,7 +27922,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="725" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1006</v>
       </c>
@@ -27952,7 +27954,7 @@
         <v>144.995</v>
       </c>
     </row>
-    <row r="726" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1007</v>
       </c>
@@ -27984,7 +27986,7 @@
         <v>144.995</v>
       </c>
     </row>
-    <row r="727" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1008</v>
       </c>
@@ -28016,7 +28018,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="728" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>1009</v>
       </c>
@@ -28048,7 +28050,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="729" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>1010</v>
       </c>
@@ -28080,7 +28082,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="730" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>1011</v>
       </c>
@@ -28112,7 +28114,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="731" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>1427</v>
       </c>
@@ -28144,7 +28146,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="732" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>1012</v>
       </c>
@@ -28176,7 +28178,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="733" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>1428</v>
       </c>
@@ -28208,7 +28210,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="734" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>1013</v>
       </c>
@@ -28240,7 +28242,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="735" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>1014</v>
       </c>
@@ -28272,7 +28274,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="736" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>1015</v>
       </c>
@@ -28304,7 +28306,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="737" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>1016</v>
       </c>
@@ -28336,7 +28338,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="738" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>1017</v>
       </c>
@@ -28368,7 +28370,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="739" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>1018</v>
       </c>
@@ -28400,7 +28402,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="740" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>1019</v>
       </c>
@@ -28432,7 +28434,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="741" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>1020</v>
       </c>
@@ -28464,7 +28466,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="742" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>1021</v>
       </c>
@@ -28496,7 +28498,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="743" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>1022</v>
       </c>
@@ -28528,7 +28530,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="744" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>1023</v>
       </c>
@@ -28560,7 +28562,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="745" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>1429</v>
       </c>
@@ -28592,7 +28594,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="746" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>1024</v>
       </c>
@@ -28624,7 +28626,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="747" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>1025</v>
       </c>
@@ -28656,7 +28658,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="748" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>1026</v>
       </c>
@@ -28688,7 +28690,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="749" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>1027</v>
       </c>
@@ -28720,7 +28722,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="750" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>1430</v>
       </c>
@@ -28752,7 +28754,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="751" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>1028</v>
       </c>
@@ -28784,7 +28786,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="752" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>1431</v>
       </c>
@@ -28816,7 +28818,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="753" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>1029</v>
       </c>
@@ -28848,7 +28850,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="754" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>1030</v>
       </c>
@@ -28880,7 +28882,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="755" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>1031</v>
       </c>
@@ -28912,7 +28914,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="756" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>1032</v>
       </c>
@@ -28944,7 +28946,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="757" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>1033</v>
       </c>
@@ -28976,7 +28978,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="758" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1034</v>
       </c>
@@ -29008,7 +29010,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="759" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1432</v>
       </c>
@@ -29040,7 +29042,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="760" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>1035</v>
       </c>
@@ -29072,7 +29074,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="761" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>1036</v>
       </c>
@@ -29104,7 +29106,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="762" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>1037</v>
       </c>
@@ -29136,7 +29138,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="763" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>1038</v>
       </c>
@@ -29168,7 +29170,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="764" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>1039</v>
       </c>
@@ -29200,7 +29202,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="765" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1040</v>
       </c>
@@ -29232,7 +29234,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="766" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1041</v>
       </c>
@@ -29264,7 +29266,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="767" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>1042</v>
       </c>
@@ -29296,7 +29298,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="768" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>1043</v>
       </c>
@@ -29328,7 +29330,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="769" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>1044</v>
       </c>
@@ -29360,7 +29362,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="770" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>1045</v>
       </c>
@@ -29392,7 +29394,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="771" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>1046</v>
       </c>
@@ -29424,7 +29426,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="772" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>1047</v>
       </c>
@@ -29456,7 +29458,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="773" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>1048</v>
       </c>
@@ -29488,7 +29490,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="774" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1049</v>
       </c>
@@ -29520,7 +29522,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="775" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>1050</v>
       </c>
@@ -29552,7 +29554,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="776" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>1051</v>
       </c>
@@ -29584,7 +29586,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="777" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>1052</v>
       </c>
@@ -29616,7 +29618,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="778" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1053</v>
       </c>
@@ -29648,7 +29650,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="779" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>1054</v>
       </c>
@@ -29680,7 +29682,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="780" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1055</v>
       </c>
@@ -29712,7 +29714,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="781" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1056</v>
       </c>
@@ -29744,7 +29746,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="782" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>1057</v>
       </c>
@@ -29776,7 +29778,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="783" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>1058</v>
       </c>
@@ -29808,7 +29810,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>1059</v>
       </c>
@@ -29840,7 +29842,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="785" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>1060</v>
       </c>
@@ -29872,7 +29874,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="786" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>1061</v>
       </c>
@@ -29904,7 +29906,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="787" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>1062</v>
       </c>
@@ -29936,7 +29938,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="788" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1063</v>
       </c>
@@ -29968,7 +29970,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="789" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>1064</v>
       </c>
@@ -30000,7 +30002,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="790" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>1065</v>
       </c>
@@ -30032,7 +30034,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="791" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>1066</v>
       </c>
@@ -30064,7 +30066,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="792" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>1067</v>
       </c>
@@ -30096,7 +30098,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="793" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>1068</v>
       </c>
@@ -30128,7 +30130,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="794" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>1072</v>
       </c>
@@ -30160,7 +30162,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="795" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>1074</v>
       </c>
@@ -30192,7 +30194,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="796" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>1075</v>
       </c>
@@ -30224,7 +30226,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="797" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
         <v>1076</v>
       </c>
@@ -30256,7 +30258,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="798" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>1077</v>
       </c>
@@ -30288,7 +30290,7 @@
         <v>399.995</v>
       </c>
     </row>
-    <row r="799" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>1078</v>
       </c>
@@ -30320,7 +30322,7 @@
         <v>349.995</v>
       </c>
     </row>
-    <row r="800" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>1079</v>
       </c>
@@ -30352,7 +30354,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="801" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1081</v>
       </c>
@@ -30384,7 +30386,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="802" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>1082</v>
       </c>
@@ -30416,7 +30418,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="803" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>1084</v>
       </c>
@@ -30641,7 +30643,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:J809" xr:uid="{3A91E150-05DE-47E3-9A71-EF43C5F49301}"/>
+  <autoFilter ref="B1:J809" xr:uid="{3A91E150-05DE-47E3-9A71-EF43C5F49301}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="CORRE VENTO 3"/>
+        <filter val="JAQUETA CORTA/VENTO CORRE F"/>
+        <filter val="JAQUETA CORTA/VENTO CORRE M"/>
+        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL F"/>
+        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL M"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92AE9E5E-90C5-483E-8DD2-CDE6361609B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3802C6-69C6-4A54-A54F-4517D8D64ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$J$809</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$J$1026</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13144" uniqueCount="1599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13534" uniqueCount="1737">
   <si>
     <t>Imagem</t>
   </si>
@@ -4834,6 +4834,420 @@
   </si>
   <si>
     <t>OIMA241930_BCPTO</t>
+  </si>
+  <si>
+    <t>6014730_BFDGFL</t>
+  </si>
+  <si>
+    <t>UA CHARGED NONSTOP</t>
+  </si>
+  <si>
+    <t>BFDGFL</t>
+  </si>
+  <si>
+    <t>6014730_SWSWEB</t>
+  </si>
+  <si>
+    <t>SWSWEB</t>
+  </si>
+  <si>
+    <t>6014730_BKBKMP</t>
+  </si>
+  <si>
+    <t>BKBKMP</t>
+  </si>
+  <si>
+    <t>6014730_BKBKTX</t>
+  </si>
+  <si>
+    <t>BKBKTX</t>
+  </si>
+  <si>
+    <t>6014732_SADTEB</t>
+  </si>
+  <si>
+    <t>UA CHARGED ENDLESS</t>
+  </si>
+  <si>
+    <t>SADTEB</t>
+  </si>
+  <si>
+    <t>6014732_CABKBO</t>
+  </si>
+  <si>
+    <t>CABKBO</t>
+  </si>
+  <si>
+    <t>6014732_BKCAMP</t>
+  </si>
+  <si>
+    <t>BKCAMP</t>
+  </si>
+  <si>
+    <t>6014732_BFDGFL</t>
+  </si>
+  <si>
+    <t>6014732_WHPEPK</t>
+  </si>
+  <si>
+    <t>WHPEPK</t>
+  </si>
+  <si>
+    <t>6014736_BKBKCR</t>
+  </si>
+  <si>
+    <t>UA CHARGED SKYLINE 5</t>
+  </si>
+  <si>
+    <t>BKBKCR</t>
+  </si>
+  <si>
+    <t>6014736_RYRYWH</t>
+  </si>
+  <si>
+    <t>RYRYWH</t>
+  </si>
+  <si>
+    <t>6014736_STSTWH</t>
+  </si>
+  <si>
+    <t>STSTWH</t>
+  </si>
+  <si>
+    <t>6014736_SGBKSG</t>
+  </si>
+  <si>
+    <t>SGBKSG</t>
+  </si>
+  <si>
+    <t>6006985_CACAMG</t>
+  </si>
+  <si>
+    <t>UA CHARGED QUICKER 2</t>
+  </si>
+  <si>
+    <t>CACAMG</t>
+  </si>
+  <si>
+    <t>6006985_CABKMS</t>
+  </si>
+  <si>
+    <t>CABKMS</t>
+  </si>
+  <si>
+    <t>6006985_FOFOBR</t>
+  </si>
+  <si>
+    <t>FOFOBR</t>
+  </si>
+  <si>
+    <t>6006985_CRCRMP</t>
+  </si>
+  <si>
+    <t>CRCRMP</t>
+  </si>
+  <si>
+    <t>6006985_MGMGBK</t>
+  </si>
+  <si>
+    <t>MGMGBK</t>
+  </si>
+  <si>
+    <t>6006985_SWSWTU</t>
+  </si>
+  <si>
+    <t>SWSWTU</t>
+  </si>
+  <si>
+    <t>6006985_MGRAYB</t>
+  </si>
+  <si>
+    <t>MGRAYB</t>
+  </si>
+  <si>
+    <t>6020667_ACBKDG</t>
+  </si>
+  <si>
+    <t>UA CHARGED SLIGHT 4</t>
+  </si>
+  <si>
+    <t>ACBKDG</t>
+  </si>
+  <si>
+    <t>6020667_TITIBK</t>
+  </si>
+  <si>
+    <t>TITIBK</t>
+  </si>
+  <si>
+    <t>6020667_SWCKEB</t>
+  </si>
+  <si>
+    <t>SWCKEB</t>
+  </si>
+  <si>
+    <t>6020667_BKMPMP</t>
+  </si>
+  <si>
+    <t>BKMPMP</t>
+  </si>
+  <si>
+    <t>6020667_BKCAMP</t>
+  </si>
+  <si>
+    <t>6014744_BKBKMP</t>
+  </si>
+  <si>
+    <t>UA CHARGED SUNNY</t>
+  </si>
+  <si>
+    <t>6014744_SGSGBK</t>
+  </si>
+  <si>
+    <t>SGSGBK</t>
+  </si>
+  <si>
+    <t>6014744_AGAGWH</t>
+  </si>
+  <si>
+    <t>AGAGWH</t>
+  </si>
+  <si>
+    <t>6014744_BNBKMP</t>
+  </si>
+  <si>
+    <t>BNBKMP</t>
+  </si>
+  <si>
+    <t>6014744_CASBMG</t>
+  </si>
+  <si>
+    <t>CASBMG</t>
+  </si>
+  <si>
+    <t>6014744_APAPPP</t>
+  </si>
+  <si>
+    <t>APAPPP</t>
+  </si>
+  <si>
+    <t>6020665_BKBKMP</t>
+  </si>
+  <si>
+    <t>UA CHARGED WING 2 SE</t>
+  </si>
+  <si>
+    <t>6020665_CRCRMP</t>
+  </si>
+  <si>
+    <t>6020665_MGMOMP</t>
+  </si>
+  <si>
+    <t>MGMOMP</t>
+  </si>
+  <si>
+    <t>6020665_ACACMP</t>
+  </si>
+  <si>
+    <t>ACACMP</t>
+  </si>
+  <si>
+    <t>6020665_SWSWCK</t>
+  </si>
+  <si>
+    <t>SWSWCK</t>
+  </si>
+  <si>
+    <t>6014745_CRFGVR</t>
+  </si>
+  <si>
+    <t>UA TRIBASE CROSS 2 SE</t>
+  </si>
+  <si>
+    <t>CRFGVR</t>
+  </si>
+  <si>
+    <t>6014745_FGLLPP</t>
+  </si>
+  <si>
+    <t>FGLLPP</t>
+  </si>
+  <si>
+    <t>6014745_BKCABK</t>
+  </si>
+  <si>
+    <t>BKCABK</t>
+  </si>
+  <si>
+    <t>6020660_MOGBGC</t>
+  </si>
+  <si>
+    <t>UA TRIBASE REPS 3</t>
+  </si>
+  <si>
+    <t>MOGBGC</t>
+  </si>
+  <si>
+    <t>6020660_VVVVLC</t>
+  </si>
+  <si>
+    <t>VVVVLC</t>
+  </si>
+  <si>
+    <t>6020660_SWSWPP</t>
+  </si>
+  <si>
+    <t>SWSWPP</t>
+  </si>
+  <si>
+    <t>6020660_BKRRSA</t>
+  </si>
+  <si>
+    <t>BKRRSA</t>
+  </si>
+  <si>
+    <t>6020660_SWSWBN</t>
+  </si>
+  <si>
+    <t>SWSWBN</t>
+  </si>
+  <si>
+    <t>6020660_BLKBKW</t>
+  </si>
+  <si>
+    <t>BLKBKW</t>
+  </si>
+  <si>
+    <t>6014748_MPPCTX</t>
+  </si>
+  <si>
+    <t>BASQUETE</t>
+  </si>
+  <si>
+    <t>UA LAYUP</t>
+  </si>
+  <si>
+    <t>MPPCTX</t>
+  </si>
+  <si>
+    <t>6014748_WMTGBK</t>
+  </si>
+  <si>
+    <t>WMTGBK</t>
+  </si>
+  <si>
+    <t>6014748_BKCAWH</t>
+  </si>
+  <si>
+    <t>BKCAWH</t>
+  </si>
+  <si>
+    <t>6020662_BKGMPU</t>
+  </si>
+  <si>
+    <t>UA BALLER</t>
+  </si>
+  <si>
+    <t>BKGMPU</t>
+  </si>
+  <si>
+    <t>6020662_BKWHPU</t>
+  </si>
+  <si>
+    <t>BKWHPU</t>
+  </si>
+  <si>
+    <t>6020662_WHMGWT</t>
+  </si>
+  <si>
+    <t>WHMGWT</t>
+  </si>
+  <si>
+    <t>3025902_BKBKWT</t>
+  </si>
+  <si>
+    <t>UA IGNITE VI SL</t>
+  </si>
+  <si>
+    <t>BKBKWT</t>
+  </si>
+  <si>
+    <t>3025902_WHWHBA</t>
+  </si>
+  <si>
+    <t>WHWHBA</t>
+  </si>
+  <si>
+    <t>3027787_WTWTBK</t>
+  </si>
+  <si>
+    <t>UA CORE 2</t>
+  </si>
+  <si>
+    <t>WTWTBK</t>
+  </si>
+  <si>
+    <t>3027787_BLKBKW</t>
+  </si>
+  <si>
+    <t>6006999_MNYDWG</t>
+  </si>
+  <si>
+    <t>UA ANSA LIGHT</t>
+  </si>
+  <si>
+    <t>MNYDWG</t>
+  </si>
+  <si>
+    <t>6006999_WTBKBK</t>
+  </si>
+  <si>
+    <t>WTBKBK</t>
+  </si>
+  <si>
+    <t>6006999_BLKBKW</t>
+  </si>
+  <si>
+    <t>6020663_WHPPPE</t>
+  </si>
+  <si>
+    <t>UA CHARGED FLEEK</t>
+  </si>
+  <si>
+    <t>WHPPPE</t>
+  </si>
+  <si>
+    <t>6020663_BFBFBF</t>
+  </si>
+  <si>
+    <t>BFBFBF</t>
+  </si>
+  <si>
+    <t>6020663_TITIPP</t>
+  </si>
+  <si>
+    <t>TITIPP</t>
+  </si>
+  <si>
+    <t>6020663_SARPBR</t>
+  </si>
+  <si>
+    <t>SARPBR</t>
+  </si>
+  <si>
+    <t>6020663_BKMTSC</t>
+  </si>
+  <si>
+    <t>BKMTSC</t>
+  </si>
+  <si>
+    <t>3027786_BLKBKW</t>
+  </si>
+  <si>
+    <t>UA DAILY</t>
+  </si>
+  <si>
+    <t>3027786_WTWTBK</t>
   </si>
 </sst>
 </file>
@@ -5240,7 +5654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}">
-  <dimension ref="A1:M1026"/>
+  <dimension ref="A1:M1091"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -32428,8 +32842,1698 @@
         <v>24.99</v>
       </c>
     </row>
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1027" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1027" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1027" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1027" s="1">
+        <v>6014730</v>
+      </c>
+      <c r="E1027" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G1027" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="H1027" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1027" s="1">
+        <v>599.99</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1028" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B1028" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1028" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1028" s="1">
+        <v>6014730</v>
+      </c>
+      <c r="E1028" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G1028" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H1028" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1028" s="1">
+        <v>599.99</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1029" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B1029" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1029" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1029" s="1">
+        <v>6014730</v>
+      </c>
+      <c r="E1029" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G1029" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H1029" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1029" s="1">
+        <v>599.99</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1030" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1030" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1030" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1030" s="1">
+        <v>6014730</v>
+      </c>
+      <c r="E1030" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G1030" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="H1030" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1030" s="1">
+        <v>599.99</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1031" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1031" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1031" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1031" s="1">
+        <v>6014732</v>
+      </c>
+      <c r="E1031" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G1031" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="H1031" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1031" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1032" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B1032" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1032" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1032" s="1">
+        <v>6014732</v>
+      </c>
+      <c r="E1032" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G1032" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="H1032" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1032" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1033" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B1033" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1033" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1033" s="1">
+        <v>6014732</v>
+      </c>
+      <c r="E1033" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G1033" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H1033" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1033" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1034" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B1034" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1034" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1034" s="1">
+        <v>6014732</v>
+      </c>
+      <c r="E1034" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G1034" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="H1034" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1034" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1035" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B1035" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1035" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1035" s="1">
+        <v>6014732</v>
+      </c>
+      <c r="E1035" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G1035" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H1035" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1035" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1036" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B1036" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1036" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1036" s="1">
+        <v>6014736</v>
+      </c>
+      <c r="E1036" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1036" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H1036" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1036" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1037" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1037" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1037" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1037" s="1">
+        <v>6014736</v>
+      </c>
+      <c r="E1037" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1037" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H1037" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1037" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1038" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B1038" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1038" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1038" s="1">
+        <v>6014736</v>
+      </c>
+      <c r="E1038" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1038" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="H1038" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1038" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1039" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1039" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1039" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1039" s="1">
+        <v>6014736</v>
+      </c>
+      <c r="E1039" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1039" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="H1039" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1039" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1040" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B1040" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1040" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1040" s="1">
+        <v>6006985</v>
+      </c>
+      <c r="E1040" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G1040" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="H1040" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1040" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1041" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B1041" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1041" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1041" s="1">
+        <v>6006985</v>
+      </c>
+      <c r="E1041" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G1041" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="H1041" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1041" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1042" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1042" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1042" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1042" s="1">
+        <v>6006985</v>
+      </c>
+      <c r="E1042" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G1042" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H1042" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1042" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1043" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B1043" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1043" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1043" s="1">
+        <v>6006985</v>
+      </c>
+      <c r="E1043" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G1043" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="H1043" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1043" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1044" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B1044" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1044" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1044" s="1">
+        <v>6006985</v>
+      </c>
+      <c r="E1044" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G1044" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="H1044" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1044" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1045" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B1045" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1045" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1045" s="1">
+        <v>6006985</v>
+      </c>
+      <c r="E1045" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G1045" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H1045" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1045" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1046" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B1046" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1046" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1046" s="1">
+        <v>6006985</v>
+      </c>
+      <c r="E1046" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G1046" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H1046" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1046" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1047" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B1047" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1047" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1047" s="1">
+        <v>6020667</v>
+      </c>
+      <c r="E1047" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G1047" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H1047" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1047" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1048" s="1" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B1048" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1048" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1048" s="1">
+        <v>6020667</v>
+      </c>
+      <c r="E1048" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G1048" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1048" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1048" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1049" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B1049" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1049" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1049" s="1">
+        <v>6020667</v>
+      </c>
+      <c r="E1049" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G1049" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H1049" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1049" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1050" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B1050" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1050" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1050" s="1">
+        <v>6020667</v>
+      </c>
+      <c r="E1050" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G1050" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H1050" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1050" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1051" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B1051" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1051" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1051" s="1">
+        <v>6020667</v>
+      </c>
+      <c r="E1051" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G1051" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H1051" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1051" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1052" s="1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B1052" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1052" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1052" s="1">
+        <v>6014744</v>
+      </c>
+      <c r="E1052" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G1052" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H1052" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1052" s="1">
+        <v>379.99</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1053" s="1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B1053" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1053" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1053" s="1">
+        <v>6014744</v>
+      </c>
+      <c r="E1053" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G1053" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H1053" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1053" s="1">
+        <v>379.99</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1054" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B1054" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1054" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1054" s="1">
+        <v>6014744</v>
+      </c>
+      <c r="E1054" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G1054" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="H1054" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1054" s="1">
+        <v>379.99</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1055" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B1055" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1055" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1055" s="1">
+        <v>6014744</v>
+      </c>
+      <c r="E1055" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G1055" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="H1055" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1055" s="1">
+        <v>379.99</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1056" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B1056" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1056" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1056" s="1">
+        <v>6014744</v>
+      </c>
+      <c r="E1056" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G1056" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H1056" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1056" s="1">
+        <v>379.99</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1057" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B1057" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1057" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1057" s="1">
+        <v>6014744</v>
+      </c>
+      <c r="E1057" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G1057" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="H1057" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1057" s="1">
+        <v>379.99</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1058" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B1058" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1058" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1058" s="1">
+        <v>6020665</v>
+      </c>
+      <c r="E1058" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G1058" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H1058" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1058" s="1">
+        <v>359.99</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1059" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1059" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1059" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1059" s="1">
+        <v>6020665</v>
+      </c>
+      <c r="E1059" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G1059" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="H1059" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1059" s="1">
+        <v>359.99</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1060" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B1060" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1060" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1060" s="1">
+        <v>6020665</v>
+      </c>
+      <c r="E1060" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G1060" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="H1060" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1060" s="1">
+        <v>359.99</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1061" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B1061" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1061" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1061" s="1">
+        <v>6020665</v>
+      </c>
+      <c r="E1061" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G1061" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="H1061" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1061" s="1">
+        <v>359.99</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1062" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B1062" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1062" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1062" s="1">
+        <v>6020665</v>
+      </c>
+      <c r="E1062" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G1062" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="H1062" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1062" s="1">
+        <v>359.99</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1063" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B1063" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1063" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1063" s="1">
+        <v>6014745</v>
+      </c>
+      <c r="E1063" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G1063" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H1063" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1063" s="1">
+        <v>599.99</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1064" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B1064" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1064" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1064" s="1">
+        <v>6014745</v>
+      </c>
+      <c r="E1064" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G1064" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H1064" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1064" s="1">
+        <v>599.99</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1065" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B1065" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1065" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1065" s="1">
+        <v>6014745</v>
+      </c>
+      <c r="E1065" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G1065" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H1065" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1065" s="1">
+        <v>599.99</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1066" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B1066" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1066" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1066" s="1">
+        <v>6020660</v>
+      </c>
+      <c r="E1066" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1066" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="H1066" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1066" s="1">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1067" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B1067" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1067" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1067" s="1">
+        <v>6020660</v>
+      </c>
+      <c r="E1067" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1067" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="H1067" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1067" s="1">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1068" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B1068" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1068" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1068" s="1">
+        <v>6020660</v>
+      </c>
+      <c r="E1068" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1068" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="H1068" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1068" s="1">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1069" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B1069" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1069" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1069" s="1">
+        <v>6020660</v>
+      </c>
+      <c r="E1069" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1069" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="H1069" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1069" s="1">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1070" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B1070" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1070" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1070" s="1">
+        <v>6020660</v>
+      </c>
+      <c r="E1070" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1070" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="H1070" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1070" s="1">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1071" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B1071" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1071" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1071" s="1">
+        <v>6020660</v>
+      </c>
+      <c r="E1071" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1071" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="H1071" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1071" s="1">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1072" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B1072" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1072" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D1072" s="1">
+        <v>6014748</v>
+      </c>
+      <c r="E1072" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G1072" s="1" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H1072" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1072" s="1">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1073" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B1073" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1073" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D1073" s="1">
+        <v>6014748</v>
+      </c>
+      <c r="E1073" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G1073" s="1" t="s">
+        <v>1698</v>
+      </c>
+      <c r="H1073" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1073" s="1">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1074" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1074" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1074" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D1074" s="1">
+        <v>6014748</v>
+      </c>
+      <c r="E1074" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G1074" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="H1074" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1074" s="1">
+        <v>549.99</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1075" s="1" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B1075" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1075" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D1075" s="1">
+        <v>6020662</v>
+      </c>
+      <c r="E1075" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="G1075" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="H1075" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1075" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1076" s="1" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1076" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1076" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D1076" s="1">
+        <v>6020662</v>
+      </c>
+      <c r="E1076" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="G1076" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="H1076" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1076" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1077" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B1077" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1077" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D1077" s="1">
+        <v>6020662</v>
+      </c>
+      <c r="E1077" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="G1077" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="H1077" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1077" s="1">
+        <v>499.99</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1078" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1078" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C1078" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1078" s="1">
+        <v>3025902</v>
+      </c>
+      <c r="E1078" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1078" s="1" t="s">
+        <v>1710</v>
+      </c>
+      <c r="H1078" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1078" s="1">
+        <v>229.99</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1079" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B1079" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C1079" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1079" s="1">
+        <v>3025902</v>
+      </c>
+      <c r="E1079" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1079" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="H1079" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1079" s="1">
+        <v>229.99</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1080" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B1080" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C1080" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1080" s="1">
+        <v>3027787</v>
+      </c>
+      <c r="E1080" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="G1080" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="H1080" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1080" s="1">
+        <v>139.99</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1081" s="1" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B1081" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C1081" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1081" s="1">
+        <v>3027787</v>
+      </c>
+      <c r="E1081" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="G1081" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="H1081" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1081" s="1">
+        <v>139.99</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1082" s="1" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1082" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C1082" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1082" s="1">
+        <v>6006999</v>
+      </c>
+      <c r="E1082" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G1082" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="H1082" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1082" s="1">
+        <v>129.99</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1083" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1083" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C1083" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1083" s="1">
+        <v>6006999</v>
+      </c>
+      <c r="E1083" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G1083" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="H1083" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1083" s="1">
+        <v>129.99</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1084" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B1084" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C1084" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1084" s="1">
+        <v>6006999</v>
+      </c>
+      <c r="E1084" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G1084" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="H1084" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1084" s="1">
+        <v>129.99</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1085" s="1" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B1085" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1085" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1085" s="1">
+        <v>6020663</v>
+      </c>
+      <c r="E1085" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G1085" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="H1085" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1085" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1086" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1086" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1086" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1086" s="1">
+        <v>6020663</v>
+      </c>
+      <c r="E1086" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G1086" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="H1086" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1086" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1087" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B1087" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1087" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1087" s="1">
+        <v>6020663</v>
+      </c>
+      <c r="E1087" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G1087" s="1" t="s">
+        <v>1729</v>
+      </c>
+      <c r="H1087" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1087" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1088" s="1" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B1088" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1088" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1088" s="1">
+        <v>6020663</v>
+      </c>
+      <c r="E1088" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G1088" s="1" t="s">
+        <v>1731</v>
+      </c>
+      <c r="H1088" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1088" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1089" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B1089" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1089" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1089" s="1">
+        <v>6020663</v>
+      </c>
+      <c r="E1089" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G1089" s="1" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H1089" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1089" s="1">
+        <v>399.99</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1090" s="1" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1090" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C1090" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1090" s="1">
+        <v>3027786</v>
+      </c>
+      <c r="E1090" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="G1090" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="H1090" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1090" s="1">
+        <v>149.99</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1091" s="1" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B1091" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C1091" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1091" s="1">
+        <v>3027786</v>
+      </c>
+      <c r="E1091" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="G1091" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="H1091" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1091" s="1">
+        <v>149.99</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J809" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}"/>
+  <autoFilter ref="A1:J1026" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894340B1-DEB1-4E63-9282-2E9EF3ED8DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BE0DE3-92A6-4A6C-B155-A87A2D9DA652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5641,6 +5641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AI1051"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5762,7 +5763,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -5869,7 +5870,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1678</v>
       </c>
@@ -5976,7 +5977,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>47</v>
       </c>
@@ -6083,7 +6084,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
@@ -6190,7 +6191,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>51</v>
       </c>
@@ -6297,7 +6298,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>53</v>
       </c>
@@ -6404,7 +6405,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>56</v>
       </c>
@@ -6511,7 +6512,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>58</v>
       </c>
@@ -6618,7 +6619,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -6725,7 +6726,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
@@ -6832,7 +6833,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -6939,7 +6940,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>67</v>
       </c>
@@ -7046,7 +7047,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>69</v>
       </c>
@@ -7153,7 +7154,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>71</v>
       </c>
@@ -7260,7 +7261,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -7367,7 +7368,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
@@ -7474,7 +7475,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>77</v>
       </c>
@@ -7581,7 +7582,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>79</v>
       </c>
@@ -7688,7 +7689,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>82</v>
       </c>
@@ -7795,7 +7796,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>83</v>
       </c>
@@ -7902,7 +7903,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>85</v>
       </c>
@@ -8009,7 +8010,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>87</v>
       </c>
@@ -8116,7 +8117,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>88</v>
       </c>
@@ -8223,7 +8224,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>89</v>
       </c>
@@ -8330,7 +8331,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>93</v>
       </c>
@@ -8437,7 +8438,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>96</v>
       </c>
@@ -8544,7 +8545,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>98</v>
       </c>
@@ -8651,7 +8652,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>100</v>
       </c>
@@ -8758,7 +8759,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>101</v>
       </c>
@@ -8865,7 +8866,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>103</v>
       </c>
@@ -8972,7 +8973,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>105</v>
       </c>
@@ -9079,7 +9080,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>106</v>
       </c>
@@ -9186,7 +9187,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>108</v>
       </c>
@@ -9293,7 +9294,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>113</v>
       </c>
@@ -9400,7 +9401,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>114</v>
       </c>
@@ -9507,7 +9508,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>116</v>
       </c>
@@ -9614,7 +9615,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>117</v>
       </c>
@@ -9721,7 +9722,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -9828,7 +9829,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>120</v>
       </c>
@@ -9935,7 +9936,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>122</v>
       </c>
@@ -10042,7 +10043,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>126</v>
       </c>
@@ -10149,7 +10150,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>128</v>
       </c>
@@ -10256,7 +10257,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>129</v>
       </c>
@@ -10363,7 +10364,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>131</v>
       </c>
@@ -10470,7 +10471,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>132</v>
       </c>
@@ -10577,7 +10578,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>134</v>
       </c>
@@ -10684,7 +10685,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>136</v>
       </c>
@@ -10791,7 +10792,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>138</v>
       </c>
@@ -10898,7 +10899,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>140</v>
       </c>
@@ -11005,7 +11006,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>141</v>
       </c>
@@ -11112,7 +11113,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>145</v>
       </c>
@@ -11219,7 +11220,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>146</v>
       </c>
@@ -11326,7 +11327,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>147</v>
       </c>
@@ -11433,7 +11434,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>149</v>
       </c>
@@ -11540,7 +11541,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>150</v>
       </c>
@@ -11647,7 +11648,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>152</v>
       </c>
@@ -11754,7 +11755,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>154</v>
       </c>
@@ -11861,7 +11862,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>156</v>
       </c>
@@ -11968,7 +11969,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>158</v>
       </c>
@@ -12075,7 +12076,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>160</v>
       </c>
@@ -12182,7 +12183,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>161</v>
       </c>
@@ -12289,7 +12290,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>163</v>
       </c>
@@ -12396,7 +12397,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>166</v>
       </c>
@@ -12503,7 +12504,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>168</v>
       </c>
@@ -12610,7 +12611,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>170</v>
       </c>
@@ -12717,7 +12718,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>172</v>
       </c>
@@ -12824,7 +12825,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>173</v>
       </c>
@@ -12931,7 +12932,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>175</v>
       </c>
@@ -13038,7 +13039,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>178</v>
       </c>
@@ -13145,7 +13146,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>179</v>
       </c>
@@ -13252,7 +13253,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>180</v>
       </c>
@@ -13359,7 +13360,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>181</v>
       </c>
@@ -13466,7 +13467,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>184</v>
       </c>
@@ -13573,7 +13574,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>186</v>
       </c>
@@ -13680,7 +13681,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>188</v>
       </c>
@@ -13787,7 +13788,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>190</v>
       </c>
@@ -13894,7 +13895,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>191</v>
       </c>
@@ -14001,7 +14002,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>194</v>
       </c>
@@ -14108,7 +14109,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>196</v>
       </c>
@@ -14215,7 +14216,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>197</v>
       </c>
@@ -14322,7 +14323,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>200</v>
       </c>
@@ -14429,7 +14430,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>201</v>
       </c>
@@ -14536,7 +14537,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>202</v>
       </c>
@@ -14643,7 +14644,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>205</v>
       </c>
@@ -14750,7 +14751,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>206</v>
       </c>
@@ -14857,7 +14858,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>208</v>
       </c>
@@ -14964,7 +14965,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
@@ -15071,7 +15072,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>213</v>
       </c>
@@ -15178,7 +15179,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>215</v>
       </c>
@@ -15285,7 +15286,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>216</v>
       </c>
@@ -15392,7 +15393,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>217</v>
       </c>
@@ -15499,7 +15500,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>220</v>
       </c>
@@ -15606,7 +15607,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>221</v>
       </c>
@@ -15713,7 +15714,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>223</v>
       </c>
@@ -15820,7 +15821,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>225</v>
       </c>
@@ -15927,7 +15928,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>229</v>
       </c>
@@ -16034,7 +16035,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>231</v>
       </c>
@@ -16141,7 +16142,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>233</v>
       </c>
@@ -16248,7 +16249,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>234</v>
       </c>
@@ -16355,7 +16356,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>237</v>
       </c>
@@ -16462,7 +16463,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>239</v>
       </c>
@@ -16569,7 +16570,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>240</v>
       </c>
@@ -16676,7 +16677,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>241</v>
       </c>
@@ -16783,7 +16784,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>243</v>
       </c>
@@ -16890,7 +16891,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>245</v>
       </c>
@@ -16997,7 +16998,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>248</v>
       </c>
@@ -17104,7 +17105,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>249</v>
       </c>
@@ -17211,7 +17212,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>250</v>
       </c>
@@ -17318,7 +17319,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>252</v>
       </c>
@@ -17425,7 +17426,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>253</v>
       </c>
@@ -17532,7 +17533,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>255</v>
       </c>
@@ -17639,7 +17640,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>257</v>
       </c>
@@ -17746,7 +17747,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>259</v>
       </c>
@@ -17853,7 +17854,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>260</v>
       </c>
@@ -17960,7 +17961,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>262</v>
       </c>
@@ -18067,7 +18068,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>264</v>
       </c>
@@ -18174,7 +18175,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>266</v>
       </c>
@@ -18281,7 +18282,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>268</v>
       </c>
@@ -18388,7 +18389,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>270</v>
       </c>
@@ -18495,7 +18496,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>271</v>
       </c>
@@ -18602,7 +18603,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>273</v>
       </c>
@@ -18709,7 +18710,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>275</v>
       </c>
@@ -18816,7 +18817,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>277</v>
       </c>
@@ -18923,7 +18924,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>278</v>
       </c>
@@ -19030,7 +19031,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>281</v>
       </c>
@@ -19137,7 +19138,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>282</v>
       </c>
@@ -19244,7 +19245,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>283</v>
       </c>
@@ -19351,7 +19352,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>284</v>
       </c>
@@ -19458,7 +19459,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>286</v>
       </c>
@@ -19565,7 +19566,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>288</v>
       </c>
@@ -19672,7 +19673,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>290</v>
       </c>
@@ -19779,7 +19780,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>291</v>
       </c>
@@ -19886,7 +19887,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>293</v>
       </c>
@@ -19993,7 +19994,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>294</v>
       </c>
@@ -20100,7 +20101,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>295</v>
       </c>
@@ -20207,7 +20208,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>296</v>
       </c>
@@ -20314,7 +20315,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>299</v>
       </c>
@@ -20421,7 +20422,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>300</v>
       </c>
@@ -20528,7 +20529,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>301</v>
       </c>
@@ -20635,7 +20636,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>302</v>
       </c>
@@ -20742,7 +20743,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>305</v>
       </c>
@@ -20849,7 +20850,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>307</v>
       </c>
@@ -20956,7 +20957,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>308</v>
       </c>
@@ -21063,7 +21064,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>310</v>
       </c>
@@ -21170,7 +21171,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>312</v>
       </c>
@@ -21277,7 +21278,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>313</v>
       </c>
@@ -21384,7 +21385,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>314</v>
       </c>
@@ -21491,7 +21492,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>316</v>
       </c>
@@ -21598,7 +21599,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>317</v>
       </c>
@@ -21705,7 +21706,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>318</v>
       </c>
@@ -21812,7 +21813,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>321</v>
       </c>
@@ -21919,7 +21920,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>322</v>
       </c>
@@ -22026,7 +22027,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>324</v>
       </c>
@@ -22133,7 +22134,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>325</v>
       </c>
@@ -22240,7 +22241,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>327</v>
       </c>
@@ -22347,7 +22348,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>328</v>
       </c>
@@ -22454,7 +22455,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>329</v>
       </c>
@@ -22561,7 +22562,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>330</v>
       </c>
@@ -22668,7 +22669,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>332</v>
       </c>
@@ -22775,7 +22776,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>334</v>
       </c>
@@ -22882,7 +22883,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>336</v>
       </c>
@@ -22989,7 +22990,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="163" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>337</v>
       </c>
@@ -23096,7 +23097,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>340</v>
       </c>
@@ -23203,7 +23204,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>342</v>
       </c>
@@ -23310,7 +23311,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>344</v>
       </c>
@@ -23417,7 +23418,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>346</v>
       </c>
@@ -23524,7 +23525,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>348</v>
       </c>
@@ -23631,7 +23632,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>349</v>
       </c>
@@ -23738,7 +23739,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>351</v>
       </c>
@@ -23845,7 +23846,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>352</v>
       </c>
@@ -23952,7 +23953,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>355</v>
       </c>
@@ -24059,7 +24060,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>356</v>
       </c>
@@ -24166,7 +24167,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="174" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>357</v>
       </c>
@@ -24273,7 +24274,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>358</v>
       </c>
@@ -24380,7 +24381,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>360</v>
       </c>
@@ -24487,7 +24488,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="177" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>361</v>
       </c>
@@ -24594,7 +24595,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>362</v>
       </c>
@@ -24701,7 +24702,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>365</v>
       </c>
@@ -24808,7 +24809,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>367</v>
       </c>
@@ -24915,7 +24916,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>368</v>
       </c>
@@ -25022,7 +25023,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="182" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>369</v>
       </c>
@@ -25129,7 +25130,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>372</v>
       </c>
@@ -25236,7 +25237,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="184" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>374</v>
       </c>
@@ -25343,7 +25344,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>376</v>
       </c>
@@ -25450,7 +25451,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>379</v>
       </c>
@@ -25557,7 +25558,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="187" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>380</v>
       </c>
@@ -25664,7 +25665,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>381</v>
       </c>
@@ -25771,7 +25772,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>385</v>
       </c>
@@ -25878,7 +25879,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>387</v>
       </c>
@@ -25985,7 +25986,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="191" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>389</v>
       </c>
@@ -26092,7 +26093,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>391</v>
       </c>
@@ -26199,7 +26200,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="193" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>392</v>
       </c>
@@ -26306,7 +26307,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="194" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>393</v>
       </c>
@@ -26413,7 +26414,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>396</v>
       </c>
@@ -26520,7 +26521,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>397</v>
       </c>
@@ -26627,7 +26628,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>400</v>
       </c>
@@ -26734,7 +26735,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>401</v>
       </c>
@@ -26841,7 +26842,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>402</v>
       </c>
@@ -26948,7 +26949,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>403</v>
       </c>
@@ -27055,7 +27056,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>404</v>
       </c>
@@ -27162,7 +27163,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>406</v>
       </c>
@@ -27269,7 +27270,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="203" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>408</v>
       </c>
@@ -27376,7 +27377,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="204" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>409</v>
       </c>
@@ -27483,7 +27484,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="205" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>410</v>
       </c>
@@ -27590,7 +27591,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="206" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>411</v>
       </c>
@@ -27697,7 +27698,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="207" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>412</v>
       </c>
@@ -27804,7 +27805,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="208" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>413</v>
       </c>
@@ -27911,7 +27912,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>417</v>
       </c>
@@ -28018,7 +28019,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="210" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>418</v>
       </c>
@@ -28125,7 +28126,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>419</v>
       </c>
@@ -28232,7 +28233,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="212" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>420</v>
       </c>
@@ -28339,7 +28340,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="213" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>421</v>
       </c>
@@ -28446,7 +28447,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="214" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>423</v>
       </c>
@@ -28553,7 +28554,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>424</v>
       </c>
@@ -28660,7 +28661,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="216" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>425</v>
       </c>
@@ -28767,7 +28768,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="217" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>426</v>
       </c>
@@ -28874,7 +28875,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="218" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>427</v>
       </c>
@@ -28981,7 +28982,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="219" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>428</v>
       </c>
@@ -29088,7 +29089,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="220" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>430</v>
       </c>
@@ -29195,7 +29196,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="221" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>432</v>
       </c>
@@ -29302,7 +29303,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="222" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>434</v>
       </c>
@@ -29409,7 +29410,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="223" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>435</v>
       </c>
@@ -29516,7 +29517,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="224" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>436</v>
       </c>
@@ -29623,7 +29624,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="225" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>438</v>
       </c>
@@ -29730,7 +29731,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="226" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>439</v>
       </c>
@@ -29837,7 +29838,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="227" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>440</v>
       </c>
@@ -29944,7 +29945,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>441</v>
       </c>
@@ -30051,7 +30052,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="229" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>442</v>
       </c>
@@ -30158,7 +30159,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="230" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>443</v>
       </c>
@@ -30265,7 +30266,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="231" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>445</v>
       </c>
@@ -30372,7 +30373,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>446</v>
       </c>
@@ -30479,7 +30480,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="233" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>447</v>
       </c>
@@ -30586,7 +30587,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="234" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>448</v>
       </c>
@@ -30693,7 +30694,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="235" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>449</v>
       </c>
@@ -30800,7 +30801,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="236" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>455</v>
       </c>
@@ -30907,7 +30908,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="237" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>456</v>
       </c>
@@ -31014,7 +31015,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="238" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>458</v>
       </c>
@@ -31121,7 +31122,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>460</v>
       </c>
@@ -31228,7 +31229,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="240" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>461</v>
       </c>
@@ -31335,7 +31336,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="241" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>462</v>
       </c>
@@ -31442,7 +31443,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="242" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>465</v>
       </c>
@@ -31549,7 +31550,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="243" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>466</v>
       </c>
@@ -31656,7 +31657,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="244" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>468</v>
       </c>
@@ -31763,7 +31764,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="245" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>469</v>
       </c>
@@ -31870,7 +31871,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="246" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>471</v>
       </c>
@@ -31977,7 +31978,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="247" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>472</v>
       </c>
@@ -32084,7 +32085,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="248" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>473</v>
       </c>
@@ -32191,7 +32192,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="249" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>474</v>
       </c>
@@ -32298,7 +32299,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="250" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>475</v>
       </c>
@@ -32405,7 +32406,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="251" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>478</v>
       </c>
@@ -32512,7 +32513,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>479</v>
       </c>
@@ -32619,7 +32620,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="253" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>481</v>
       </c>
@@ -32726,7 +32727,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="254" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>482</v>
       </c>
@@ -32833,7 +32834,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="255" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>485</v>
       </c>
@@ -32940,7 +32941,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="256" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>487</v>
       </c>
@@ -33047,7 +33048,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="257" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>489</v>
       </c>
@@ -33154,7 +33155,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="258" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>490</v>
       </c>
@@ -33261,7 +33262,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="259" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>492</v>
       </c>
@@ -33356,7 +33357,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>495</v>
       </c>
@@ -33451,7 +33452,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="261" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>496</v>
       </c>
@@ -33546,7 +33547,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>498</v>
       </c>
@@ -33641,7 +33642,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>499</v>
       </c>
@@ -33736,7 +33737,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>501</v>
       </c>
@@ -33831,7 +33832,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>503</v>
       </c>
@@ -33926,7 +33927,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="266" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>505</v>
       </c>
@@ -34021,7 +34022,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="267" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>506</v>
       </c>
@@ -34116,7 +34117,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="268" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>507</v>
       </c>
@@ -34211,7 +34212,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="269" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>508</v>
       </c>
@@ -34306,7 +34307,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="270" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>510</v>
       </c>
@@ -34401,7 +34402,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="271" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>511</v>
       </c>
@@ -34496,7 +34497,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="272" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>512</v>
       </c>
@@ -34591,7 +34592,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="273" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>513</v>
       </c>
@@ -34652,7 +34653,7 @@
       <c r="AH273" s="4"/>
       <c r="AI273" s="4"/>
     </row>
-    <row r="274" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>515</v>
       </c>
@@ -34713,7 +34714,7 @@
       <c r="AH274" s="4"/>
       <c r="AI274" s="4"/>
     </row>
-    <row r="275" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>516</v>
       </c>
@@ -34774,7 +34775,7 @@
       <c r="AH275" s="4"/>
       <c r="AI275" s="4"/>
     </row>
-    <row r="276" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>517</v>
       </c>
@@ -34835,7 +34836,7 @@
       <c r="AH276" s="4"/>
       <c r="AI276" s="4"/>
     </row>
-    <row r="277" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>518</v>
       </c>
@@ -34896,7 +34897,7 @@
       <c r="AH277" s="4"/>
       <c r="AI277" s="4"/>
     </row>
-    <row r="278" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>520</v>
       </c>
@@ -34991,7 +34992,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>522</v>
       </c>
@@ -35086,7 +35087,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="280" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>524</v>
       </c>
@@ -35181,7 +35182,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>525</v>
       </c>
@@ -35276,7 +35277,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>180</v>
       </c>
@@ -35371,7 +35372,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="283" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>179</v>
       </c>
@@ -35466,7 +35467,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="284" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>178</v>
       </c>
@@ -35561,7 +35562,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="285" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>175</v>
       </c>
@@ -35656,7 +35657,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="286" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>190</v>
       </c>
@@ -35751,7 +35752,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>526</v>
       </c>
@@ -35846,7 +35847,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>186</v>
       </c>
@@ -35941,7 +35942,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>181</v>
       </c>
@@ -36036,7 +36037,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>184</v>
       </c>
@@ -36131,7 +36132,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>528</v>
       </c>
@@ -36226,7 +36227,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="292" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>530</v>
       </c>
@@ -36321,7 +36322,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="293" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>531</v>
       </c>
@@ -36416,7 +36417,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="294" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>533</v>
       </c>
@@ -36477,7 +36478,7 @@
       <c r="AH294" s="4"/>
       <c r="AI294" s="4"/>
     </row>
-    <row r="295" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>535</v>
       </c>
@@ -36538,7 +36539,7 @@
       <c r="AH295" s="4"/>
       <c r="AI295" s="4"/>
     </row>
-    <row r="296" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>536</v>
       </c>
@@ -36599,7 +36600,7 @@
       <c r="AH296" s="4"/>
       <c r="AI296" s="4"/>
     </row>
-    <row r="297" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>220</v>
       </c>
@@ -36694,7 +36695,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="298" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>221</v>
       </c>
@@ -36789,7 +36790,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="299" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>217</v>
       </c>
@@ -36884,7 +36885,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="300" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>223</v>
       </c>
@@ -36979,7 +36980,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="301" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>205</v>
       </c>
@@ -37074,7 +37075,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="302" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>202</v>
       </c>
@@ -37169,7 +37170,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="303" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>537</v>
       </c>
@@ -37264,7 +37265,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="304" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>539</v>
       </c>
@@ -37359,7 +37360,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="305" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>541</v>
       </c>
@@ -37454,7 +37455,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="306" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>252</v>
       </c>
@@ -37549,7 +37550,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="307" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>250</v>
       </c>
@@ -37644,7 +37645,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="308" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>248</v>
       </c>
@@ -37739,7 +37740,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="309" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>245</v>
       </c>
@@ -37834,7 +37835,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="310" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>249</v>
       </c>
@@ -37929,7 +37930,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="311" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>257</v>
       </c>
@@ -38024,7 +38025,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="312" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>259</v>
       </c>
@@ -38119,7 +38120,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="313" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>255</v>
       </c>
@@ -38214,7 +38215,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="314" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>253</v>
       </c>
@@ -38309,7 +38310,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="315" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>543</v>
       </c>
@@ -38404,7 +38405,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="316" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>282</v>
       </c>
@@ -38499,7 +38500,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>281</v>
       </c>
@@ -38594,7 +38595,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>278</v>
       </c>
@@ -38689,7 +38690,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>290</v>
       </c>
@@ -38784,7 +38785,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="320" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>286</v>
       </c>
@@ -38879,7 +38880,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="321" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>284</v>
       </c>
@@ -38974,7 +38975,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>288</v>
       </c>
@@ -39069,7 +39070,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>544</v>
       </c>
@@ -39164,7 +39165,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="324" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>546</v>
       </c>
@@ -39259,7 +39260,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="325" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>548</v>
       </c>
@@ -39354,7 +39355,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="326" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>550</v>
       </c>
@@ -39449,7 +39450,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="327" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>551</v>
       </c>
@@ -39544,7 +39545,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="328" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>554</v>
       </c>
@@ -39639,7 +39640,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="329" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>555</v>
       </c>
@@ -39734,7 +39735,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="330" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>294</v>
       </c>
@@ -39829,7 +39830,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="331" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>293</v>
       </c>
@@ -39924,7 +39925,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="332" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>291</v>
       </c>
@@ -40019,7 +40020,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="333" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>295</v>
       </c>
@@ -40114,7 +40115,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="334" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>329</v>
       </c>
@@ -40209,7 +40210,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="335" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>327</v>
       </c>
@@ -40304,7 +40305,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="336" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>325</v>
       </c>
@@ -40399,7 +40400,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="337" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>328</v>
       </c>
@@ -40494,7 +40495,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="338" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>318</v>
       </c>
@@ -40589,7 +40590,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="339" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>322</v>
       </c>
@@ -40684,7 +40685,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="340" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>321</v>
       </c>
@@ -40779,7 +40780,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="341" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>324</v>
       </c>
@@ -40874,7 +40875,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="342" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>330</v>
       </c>
@@ -40969,7 +40970,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="343" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>336</v>
       </c>
@@ -41064,7 +41065,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="344" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>332</v>
       </c>
@@ -41159,7 +41160,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="345" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>557</v>
       </c>
@@ -41254,7 +41255,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="346" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>340</v>
       </c>
@@ -41349,7 +41350,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="347" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>344</v>
       </c>
@@ -41444,7 +41445,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="348" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>342</v>
       </c>
@@ -41539,7 +41540,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="349" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>337</v>
       </c>
@@ -41634,7 +41635,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="350" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>559</v>
       </c>
@@ -41741,7 +41742,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="351" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>561</v>
       </c>
@@ -41848,7 +41849,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="352" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>562</v>
       </c>
@@ -41955,7 +41956,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="353" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>564</v>
       </c>
@@ -42050,7 +42051,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="354" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>369</v>
       </c>
@@ -42145,7 +42146,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="355" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>372</v>
       </c>
@@ -42240,7 +42241,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="356" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>565</v>
       </c>
@@ -42335,7 +42336,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="357" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>365</v>
       </c>
@@ -42430,7 +42431,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="358" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>566</v>
       </c>
@@ -42525,7 +42526,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="359" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>362</v>
       </c>
@@ -42620,7 +42621,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="360" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>567</v>
       </c>
@@ -42715,7 +42716,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="361" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>568</v>
       </c>
@@ -42810,7 +42811,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="362" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>376</v>
       </c>
@@ -42905,7 +42906,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="363" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>147</v>
       </c>
@@ -43000,7 +43001,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="364" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>570</v>
       </c>
@@ -43095,7 +43096,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="365" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>150</v>
       </c>
@@ -43190,7 +43191,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="366" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>149</v>
       </c>
@@ -43285,7 +43286,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="367" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>141</v>
       </c>
@@ -43380,7 +43381,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="368" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>145</v>
       </c>
@@ -43475,7 +43476,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="369" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>146</v>
       </c>
@@ -43570,7 +43571,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="370" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>154</v>
       </c>
@@ -43665,7 +43666,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="371" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>571</v>
       </c>
@@ -43760,7 +43761,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="372" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>572</v>
       </c>
@@ -43855,7 +43856,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="373" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>573</v>
       </c>
@@ -43950,7 +43951,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="374" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>575</v>
       </c>
@@ -44045,7 +44046,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="375" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>229</v>
       </c>
@@ -44140,7 +44141,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="376" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>233</v>
       </c>
@@ -44235,7 +44236,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="377" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>225</v>
       </c>
@@ -44330,7 +44331,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="378" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>231</v>
       </c>
@@ -44425,7 +44426,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="379" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>312</v>
       </c>
@@ -44520,7 +44521,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="380" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>313</v>
       </c>
@@ -44615,7 +44616,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="381" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>310</v>
       </c>
@@ -44710,7 +44711,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="382" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>308</v>
       </c>
@@ -44805,7 +44806,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="383" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>577</v>
       </c>
@@ -44900,7 +44901,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="384" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>579</v>
       </c>
@@ -44995,7 +44996,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="385" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>581</v>
       </c>
@@ -45090,7 +45091,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="386" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>583</v>
       </c>
@@ -45185,7 +45186,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="387" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>434</v>
       </c>
@@ -45280,7 +45281,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="388" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>432</v>
       </c>
@@ -45375,7 +45376,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="389" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>435</v>
       </c>
@@ -45470,7 +45471,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="390" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>428</v>
       </c>
@@ -45565,7 +45566,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="391" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>430</v>
       </c>
@@ -45660,7 +45661,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="392" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>447</v>
       </c>
@@ -45755,7 +45756,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="393" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>445</v>
       </c>
@@ -45850,7 +45851,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="394" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>443</v>
       </c>
@@ -45945,7 +45946,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="395" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>585</v>
       </c>
@@ -46040,7 +46041,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="396" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>587</v>
       </c>
@@ -46135,7 +46136,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="397" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>588</v>
       </c>
@@ -46230,7 +46231,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="398" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>589</v>
       </c>
@@ -46325,7 +46326,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="399" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>590</v>
       </c>
@@ -46386,7 +46387,7 @@
       <c r="AH399" s="4"/>
       <c r="AI399" s="4"/>
     </row>
-    <row r="400" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>594</v>
       </c>
@@ -46447,7 +46448,7 @@
       <c r="AH400" s="4"/>
       <c r="AI400" s="4"/>
     </row>
-    <row r="401" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>596</v>
       </c>
@@ -46508,7 +46509,7 @@
       <c r="AH401" s="4"/>
       <c r="AI401" s="4"/>
     </row>
-    <row r="402" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>598</v>
       </c>
@@ -46569,7 +46570,7 @@
       <c r="AH402" s="4"/>
       <c r="AI402" s="4"/>
     </row>
-    <row r="403" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>381</v>
       </c>
@@ -46664,7 +46665,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="404" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>392</v>
       </c>
@@ -46759,7 +46760,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="405" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>391</v>
       </c>
@@ -46854,7 +46855,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="406" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>389</v>
       </c>
@@ -46949,7 +46950,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="407" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>385</v>
       </c>
@@ -47044,7 +47045,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="408" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>387</v>
       </c>
@@ -47139,7 +47140,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="409" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>196</v>
       </c>
@@ -47234,7 +47235,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>191</v>
       </c>
@@ -47329,7 +47330,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>194</v>
       </c>
@@ -47424,7 +47425,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>600</v>
       </c>
@@ -47519,7 +47520,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="413" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>602</v>
       </c>
@@ -47614,7 +47615,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="414" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>603</v>
       </c>
@@ -47709,7 +47710,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="415" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>604</v>
       </c>
@@ -47804,7 +47805,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="416" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>605</v>
       </c>
@@ -47899,7 +47900,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="417" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>607</v>
       </c>
@@ -47994,7 +47995,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="418" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>608</v>
       </c>
@@ -48089,7 +48090,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="419" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>609</v>
       </c>
@@ -48184,7 +48185,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="420" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>361</v>
       </c>
@@ -48279,7 +48280,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="421" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>360</v>
       </c>
@@ -48374,7 +48375,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="422" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>358</v>
       </c>
@@ -48469,7 +48470,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="423" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>357</v>
       </c>
@@ -48564,7 +48565,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="424" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>356</v>
       </c>
@@ -48659,7 +48660,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="425" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>355</v>
       </c>
@@ -48754,7 +48755,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="426" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>352</v>
       </c>
@@ -48849,7 +48850,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="427" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>610</v>
       </c>
@@ -48944,7 +48945,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="428" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>613</v>
       </c>
@@ -49039,7 +49040,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="429" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>614</v>
       </c>
@@ -49134,7 +49135,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="430" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>616</v>
       </c>
@@ -49229,7 +49230,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="431" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>406</v>
       </c>
@@ -49324,7 +49325,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="432" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>412</v>
       </c>
@@ -49419,7 +49420,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="433" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>411</v>
       </c>
@@ -49514,7 +49515,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="434" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>409</v>
       </c>
@@ -49609,7 +49610,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="435" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>617</v>
       </c>
@@ -49704,7 +49705,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="436" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>410</v>
       </c>
@@ -49799,7 +49800,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="437" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>396</v>
       </c>
@@ -49894,7 +49895,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="438" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>393</v>
       </c>
@@ -49989,7 +49990,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="439" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>436</v>
       </c>
@@ -50084,7 +50085,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="440" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>442</v>
       </c>
@@ -50179,7 +50180,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="441" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>441</v>
       </c>
@@ -50274,7 +50275,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="442" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>439</v>
       </c>
@@ -50369,7 +50370,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="443" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>440</v>
       </c>
@@ -50464,7 +50465,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="444" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>490</v>
       </c>
@@ -50559,7 +50560,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="445" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>489</v>
       </c>
@@ -50654,7 +50655,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="446" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>487</v>
       </c>
@@ -50749,7 +50750,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="447" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>485</v>
       </c>
@@ -50844,7 +50845,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="448" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>482</v>
       </c>
@@ -50939,7 +50940,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="449" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>461</v>
       </c>
@@ -51034,7 +51035,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="450" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>460</v>
       </c>
@@ -51129,7 +51130,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="451" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>458</v>
       </c>
@@ -51224,7 +51225,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="452" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>455</v>
       </c>
@@ -51319,7 +51320,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="453" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>456</v>
       </c>
@@ -51414,7 +51415,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="454" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>449</v>
       </c>
@@ -51509,7 +51510,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="455" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>620</v>
       </c>
@@ -51570,7 +51571,7 @@
       <c r="AH455" s="4"/>
       <c r="AI455" s="4"/>
     </row>
-    <row r="456" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>623</v>
       </c>
@@ -51631,7 +51632,7 @@
       <c r="AH456" s="4"/>
       <c r="AI456" s="4"/>
     </row>
-    <row r="457" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>625</v>
       </c>
@@ -51692,7 +51693,7 @@
       <c r="AH457" s="4"/>
       <c r="AI457" s="4"/>
     </row>
-    <row r="458" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>627</v>
       </c>
@@ -51753,7 +51754,7 @@
       <c r="AH458" s="4"/>
       <c r="AI458" s="4"/>
     </row>
-    <row r="459" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>474</v>
       </c>
@@ -51848,7 +51849,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="460" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>473</v>
       </c>
@@ -51943,7 +51944,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="461" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>469</v>
       </c>
@@ -52038,7 +52039,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="462" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>471</v>
       </c>
@@ -52133,7 +52134,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="463" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>472</v>
       </c>
@@ -52228,7 +52229,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="464" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>628</v>
       </c>
@@ -52323,7 +52324,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="465" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>475</v>
       </c>
@@ -52418,7 +52419,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>630</v>
       </c>
@@ -52513,7 +52514,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="467" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>631</v>
       </c>
@@ -52608,7 +52609,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="468" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>632</v>
       </c>
@@ -52703,7 +52704,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="469" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>633</v>
       </c>
@@ -52798,7 +52799,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="470" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>635</v>
       </c>
@@ -52893,7 +52894,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="471" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>637</v>
       </c>
@@ -52988,7 +52989,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="472" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>639</v>
       </c>
@@ -53083,7 +53084,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="473" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>641</v>
       </c>
@@ -53144,7 +53145,7 @@
       <c r="AH473" s="4"/>
       <c r="AI473" s="4"/>
     </row>
-    <row r="474" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>644</v>
       </c>
@@ -53205,7 +53206,7 @@
       <c r="AH474" s="4"/>
       <c r="AI474" s="4"/>
     </row>
-    <row r="475" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>645</v>
       </c>
@@ -53266,7 +53267,7 @@
       <c r="AH475" s="4"/>
       <c r="AI475" s="4"/>
     </row>
-    <row r="476" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>647</v>
       </c>
@@ -53327,7 +53328,7 @@
       <c r="AH476" s="4"/>
       <c r="AI476" s="4"/>
     </row>
-    <row r="477" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>649</v>
       </c>
@@ -53388,7 +53389,7 @@
       <c r="AH477" s="4"/>
       <c r="AI477" s="4"/>
     </row>
-    <row r="478" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>650</v>
       </c>
@@ -53449,7 +53450,7 @@
       <c r="AH478" s="4"/>
       <c r="AI478" s="4"/>
     </row>
-    <row r="479" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>654</v>
       </c>
@@ -53510,7 +53511,7 @@
       <c r="AH479" s="4"/>
       <c r="AI479" s="4"/>
     </row>
-    <row r="480" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>657</v>
       </c>
@@ -53571,7 +53572,7 @@
       <c r="AH480" s="4"/>
       <c r="AI480" s="4"/>
     </row>
-    <row r="481" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>659</v>
       </c>
@@ -53632,7 +53633,7 @@
       <c r="AH481" s="4"/>
       <c r="AI481" s="4"/>
     </row>
-    <row r="482" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>661</v>
       </c>
@@ -53693,7 +53694,7 @@
       <c r="AH482" s="4"/>
       <c r="AI482" s="4"/>
     </row>
-    <row r="483" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>662</v>
       </c>
@@ -53754,7 +53755,7 @@
       <c r="AH483" s="4"/>
       <c r="AI483" s="4"/>
     </row>
-    <row r="484" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>77</v>
       </c>
@@ -53849,7 +53850,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="485" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>75</v>
       </c>
@@ -53944,7 +53945,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="486" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>73</v>
       </c>
@@ -54039,7 +54040,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="487" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>69</v>
       </c>
@@ -54134,7 +54135,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="488" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>64</v>
       </c>
@@ -54229,7 +54230,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="489" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>71</v>
       </c>
@@ -54324,7 +54325,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="490" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>67</v>
       </c>
@@ -54419,7 +54420,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="491" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>663</v>
       </c>
@@ -54480,7 +54481,7 @@
       <c r="AH491" s="4"/>
       <c r="AI491" s="4"/>
     </row>
-    <row r="492" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>665</v>
       </c>
@@ -54541,7 +54542,7 @@
       <c r="AH492" s="4"/>
       <c r="AI492" s="4"/>
     </row>
-    <row r="493" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>667</v>
       </c>
@@ -54602,7 +54603,7 @@
       <c r="AH493" s="4"/>
       <c r="AI493" s="4"/>
     </row>
-    <row r="494" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>668</v>
       </c>
@@ -54663,7 +54664,7 @@
       <c r="AH494" s="4"/>
       <c r="AI494" s="4"/>
     </row>
-    <row r="495" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>669</v>
       </c>
@@ -54724,7 +54725,7 @@
       <c r="AH495" s="4"/>
       <c r="AI495" s="4"/>
     </row>
-    <row r="496" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>670</v>
       </c>
@@ -54785,7 +54786,7 @@
       <c r="AH496" s="4"/>
       <c r="AI496" s="4"/>
     </row>
-    <row r="497" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>671</v>
       </c>
@@ -54846,7 +54847,7 @@
       <c r="AH497" s="4"/>
       <c r="AI497" s="4"/>
     </row>
-    <row r="498" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>673</v>
       </c>
@@ -54907,7 +54908,7 @@
       <c r="AH498" s="4"/>
       <c r="AI498" s="4"/>
     </row>
-    <row r="499" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>674</v>
       </c>
@@ -54968,7 +54969,7 @@
       <c r="AH499" s="4"/>
       <c r="AI499" s="4"/>
     </row>
-    <row r="500" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>675</v>
       </c>
@@ -55029,7 +55030,7 @@
       <c r="AH500" s="4"/>
       <c r="AI500" s="4"/>
     </row>
-    <row r="501" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>270</v>
       </c>
@@ -55124,7 +55125,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="502" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>266</v>
       </c>
@@ -55219,7 +55220,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="503" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>268</v>
       </c>
@@ -55314,7 +55315,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="504" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>262</v>
       </c>
@@ -55409,7 +55410,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="505" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>264</v>
       </c>
@@ -55504,7 +55505,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="506" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>676</v>
       </c>
@@ -55599,7 +55600,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="507" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>93</v>
       </c>
@@ -55694,7 +55695,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="508" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>89</v>
       </c>
@@ -55789,7 +55790,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="509" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>677</v>
       </c>
@@ -55884,7 +55885,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="510" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>679</v>
       </c>
@@ -55979,7 +55980,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="511" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>680</v>
       </c>
@@ -56074,7 +56075,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="512" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>681</v>
       </c>
@@ -56169,7 +56170,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="513" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>683</v>
       </c>
@@ -56264,7 +56265,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="514" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>685</v>
       </c>
@@ -56359,7 +56360,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="515" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>687</v>
       </c>
@@ -56454,7 +56455,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="516" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>688</v>
       </c>
@@ -56549,7 +56550,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="517" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>689</v>
       </c>
@@ -56644,7 +56645,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="518" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>691</v>
       </c>
@@ -56739,7 +56740,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="519" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>692</v>
       </c>
@@ -56834,7 +56835,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="520" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>694</v>
       </c>
@@ -56929,7 +56930,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="521" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>695</v>
       </c>
@@ -57024,7 +57025,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="522" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>697</v>
       </c>
@@ -57085,7 +57086,7 @@
       <c r="AH522" s="4"/>
       <c r="AI522" s="4"/>
     </row>
-    <row r="523" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>703</v>
       </c>
@@ -57146,7 +57147,7 @@
       <c r="AH523" s="4"/>
       <c r="AI523" s="4"/>
     </row>
-    <row r="524" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>705</v>
       </c>
@@ -57207,7 +57208,7 @@
       <c r="AH524" s="4"/>
       <c r="AI524" s="4"/>
     </row>
-    <row r="525" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>710</v>
       </c>
@@ -57268,7 +57269,7 @@
       <c r="AH525" s="4"/>
       <c r="AI525" s="4"/>
     </row>
-    <row r="526" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>711</v>
       </c>
@@ -57329,7 +57330,7 @@
       <c r="AH526" s="4"/>
       <c r="AI526" s="4"/>
     </row>
-    <row r="527" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>712</v>
       </c>
@@ -57390,7 +57391,7 @@
       <c r="AH527" s="4"/>
       <c r="AI527" s="4"/>
     </row>
-    <row r="528" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>715</v>
       </c>
@@ -57451,7 +57452,7 @@
       <c r="AH528" s="4"/>
       <c r="AI528" s="4"/>
     </row>
-    <row r="529" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>716</v>
       </c>
@@ -57512,7 +57513,7 @@
       <c r="AH529" s="4"/>
       <c r="AI529" s="4"/>
     </row>
-    <row r="530" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>719</v>
       </c>
@@ -57573,7 +57574,7 @@
       <c r="AH530" s="4"/>
       <c r="AI530" s="4"/>
     </row>
-    <row r="531" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>720</v>
       </c>
@@ -57634,7 +57635,7 @@
       <c r="AH531" s="4"/>
       <c r="AI531" s="4"/>
     </row>
-    <row r="532" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>722</v>
       </c>
@@ -57695,7 +57696,7 @@
       <c r="AH532" s="4"/>
       <c r="AI532" s="4"/>
     </row>
-    <row r="533" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>723</v>
       </c>
@@ -57756,7 +57757,7 @@
       <c r="AH533" s="4"/>
       <c r="AI533" s="4"/>
     </row>
-    <row r="534" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>726</v>
       </c>
@@ -57817,7 +57818,7 @@
       <c r="AH534" s="4"/>
       <c r="AI534" s="4"/>
     </row>
-    <row r="535" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>727</v>
       </c>
@@ -57878,7 +57879,7 @@
       <c r="AH535" s="4"/>
       <c r="AI535" s="4"/>
     </row>
-    <row r="536" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>728</v>
       </c>
@@ -57939,7 +57940,7 @@
       <c r="AH536" s="4"/>
       <c r="AI536" s="4"/>
     </row>
-    <row r="537" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>1541</v>
       </c>
@@ -58000,7 +58001,7 @@
       <c r="AH537" s="4"/>
       <c r="AI537" s="4"/>
     </row>
-    <row r="538" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>734</v>
       </c>
@@ -58061,7 +58062,7 @@
       <c r="AH538" s="4"/>
       <c r="AI538" s="4"/>
     </row>
-    <row r="539" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>735</v>
       </c>
@@ -58122,7 +58123,7 @@
       <c r="AH539" s="4"/>
       <c r="AI539" s="4"/>
     </row>
-    <row r="540" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>739</v>
       </c>
@@ -58183,7 +58184,7 @@
       <c r="AH540" s="4"/>
       <c r="AI540" s="4"/>
     </row>
-    <row r="541" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>742</v>
       </c>
@@ -58244,7 +58245,7 @@
       <c r="AH541" s="4"/>
       <c r="AI541" s="4"/>
     </row>
-    <row r="542" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>744</v>
       </c>
@@ -58305,7 +58306,7 @@
       <c r="AH542" s="4"/>
       <c r="AI542" s="4"/>
     </row>
-    <row r="543" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>746</v>
       </c>
@@ -58366,7 +58367,7 @@
       <c r="AH543" s="4"/>
       <c r="AI543" s="4"/>
     </row>
-    <row r="544" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>748</v>
       </c>
@@ -58427,7 +58428,7 @@
       <c r="AH544" s="4"/>
       <c r="AI544" s="4"/>
     </row>
-    <row r="545" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>749</v>
       </c>
@@ -58488,7 +58489,7 @@
       <c r="AH545" s="4"/>
       <c r="AI545" s="4"/>
     </row>
-    <row r="546" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>750</v>
       </c>
@@ -58549,7 +58550,7 @@
       <c r="AH546" s="4"/>
       <c r="AI546" s="4"/>
     </row>
-    <row r="547" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>753</v>
       </c>
@@ -58610,7 +58611,7 @@
       <c r="AH547" s="4"/>
       <c r="AI547" s="4"/>
     </row>
-    <row r="548" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>754</v>
       </c>
@@ -58671,7 +58672,7 @@
       <c r="AH548" s="4"/>
       <c r="AI548" s="4"/>
     </row>
-    <row r="549" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>756</v>
       </c>
@@ -58732,7 +58733,7 @@
       <c r="AH549" s="4"/>
       <c r="AI549" s="4"/>
     </row>
-    <row r="550" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>758</v>
       </c>
@@ -58793,7 +58794,7 @@
       <c r="AH550" s="4"/>
       <c r="AI550" s="4"/>
     </row>
-    <row r="551" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>759</v>
       </c>
@@ -58854,7 +58855,7 @@
       <c r="AH551" s="4"/>
       <c r="AI551" s="4"/>
     </row>
-    <row r="552" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>761</v>
       </c>
@@ -58915,7 +58916,7 @@
       <c r="AH552" s="4"/>
       <c r="AI552" s="4"/>
     </row>
-    <row r="553" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>763</v>
       </c>
@@ -58976,7 +58977,7 @@
       <c r="AH553" s="4"/>
       <c r="AI553" s="4"/>
     </row>
-    <row r="554" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>766</v>
       </c>
@@ -59037,7 +59038,7 @@
       <c r="AH554" s="4"/>
       <c r="AI554" s="4"/>
     </row>
-    <row r="555" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>768</v>
       </c>
@@ -59098,7 +59099,7 @@
       <c r="AH555" s="4"/>
       <c r="AI555" s="4"/>
     </row>
-    <row r="556" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>769</v>
       </c>
@@ -59159,7 +59160,7 @@
       <c r="AH556" s="4"/>
       <c r="AI556" s="4"/>
     </row>
-    <row r="557" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>772</v>
       </c>
@@ -59220,7 +59221,7 @@
       <c r="AH557" s="4"/>
       <c r="AI557" s="4"/>
     </row>
-    <row r="558" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>773</v>
       </c>
@@ -59281,7 +59282,7 @@
       <c r="AH558" s="4"/>
       <c r="AI558" s="4"/>
     </row>
-    <row r="559" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>776</v>
       </c>
@@ -59342,7 +59343,7 @@
       <c r="AH559" s="4"/>
       <c r="AI559" s="4"/>
     </row>
-    <row r="560" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>777</v>
       </c>
@@ -59403,7 +59404,7 @@
       <c r="AH560" s="4"/>
       <c r="AI560" s="4"/>
     </row>
-    <row r="561" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>779</v>
       </c>
@@ -59464,7 +59465,7 @@
       <c r="AH561" s="4"/>
       <c r="AI561" s="4"/>
     </row>
-    <row r="562" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>782</v>
       </c>
@@ -59525,7 +59526,7 @@
       <c r="AH562" s="4"/>
       <c r="AI562" s="4"/>
     </row>
-    <row r="563" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>783</v>
       </c>
@@ -59586,7 +59587,7 @@
       <c r="AH563" s="4"/>
       <c r="AI563" s="4"/>
     </row>
-    <row r="564" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>786</v>
       </c>
@@ -59647,7 +59648,7 @@
       <c r="AH564" s="4"/>
       <c r="AI564" s="4"/>
     </row>
-    <row r="565" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>787</v>
       </c>
@@ -59708,7 +59709,7 @@
       <c r="AH565" s="4"/>
       <c r="AI565" s="4"/>
     </row>
-    <row r="566" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>791</v>
       </c>
@@ -59769,7 +59770,7 @@
       <c r="AH566" s="4"/>
       <c r="AI566" s="4"/>
     </row>
-    <row r="567" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>794</v>
       </c>
@@ -59830,7 +59831,7 @@
       <c r="AH567" s="4"/>
       <c r="AI567" s="4"/>
     </row>
-    <row r="568" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>800</v>
       </c>
@@ -59891,7 +59892,7 @@
       <c r="AH568" s="4"/>
       <c r="AI568" s="4"/>
     </row>
-    <row r="569" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>801</v>
       </c>
@@ -59952,7 +59953,7 @@
       <c r="AH569" s="4"/>
       <c r="AI569" s="4"/>
     </row>
-    <row r="570" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>803</v>
       </c>
@@ -60013,7 +60014,7 @@
       <c r="AH570" s="4"/>
       <c r="AI570" s="4"/>
     </row>
-    <row r="571" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>805</v>
       </c>
@@ -60074,7 +60075,7 @@
       <c r="AH571" s="4"/>
       <c r="AI571" s="4"/>
     </row>
-    <row r="572" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>807</v>
       </c>
@@ -60135,7 +60136,7 @@
       <c r="AH572" s="4"/>
       <c r="AI572" s="4"/>
     </row>
-    <row r="573" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>810</v>
       </c>
@@ -60196,7 +60197,7 @@
       <c r="AH573" s="4"/>
       <c r="AI573" s="4"/>
     </row>
-    <row r="574" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>811</v>
       </c>
@@ -60257,7 +60258,7 @@
       <c r="AH574" s="4"/>
       <c r="AI574" s="4"/>
     </row>
-    <row r="575" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>812</v>
       </c>
@@ -60318,7 +60319,7 @@
       <c r="AH575" s="4"/>
       <c r="AI575" s="4"/>
     </row>
-    <row r="576" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>815</v>
       </c>
@@ -60379,7 +60380,7 @@
       <c r="AH576" s="4"/>
       <c r="AI576" s="4"/>
     </row>
-    <row r="577" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>816</v>
       </c>
@@ -60440,7 +60441,7 @@
       <c r="AH577" s="4"/>
       <c r="AI577" s="4"/>
     </row>
-    <row r="578" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>817</v>
       </c>
@@ -60501,7 +60502,7 @@
       <c r="AH578" s="4"/>
       <c r="AI578" s="4"/>
     </row>
-    <row r="579" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>820</v>
       </c>
@@ -60562,7 +60563,7 @@
       <c r="AH579" s="4"/>
       <c r="AI579" s="4"/>
     </row>
-    <row r="580" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>821</v>
       </c>
@@ -60623,7 +60624,7 @@
       <c r="AH580" s="4"/>
       <c r="AI580" s="4"/>
     </row>
-    <row r="581" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>822</v>
       </c>
@@ -60684,7 +60685,7 @@
       <c r="AH581" s="4"/>
       <c r="AI581" s="4"/>
     </row>
-    <row r="582" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>825</v>
       </c>
@@ -60745,7 +60746,7 @@
       <c r="AH582" s="4"/>
       <c r="AI582" s="4"/>
     </row>
-    <row r="583" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>826</v>
       </c>
@@ -60806,7 +60807,7 @@
       <c r="AH583" s="4"/>
       <c r="AI583" s="4"/>
     </row>
-    <row r="584" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>827</v>
       </c>
@@ -60867,7 +60868,7 @@
       <c r="AH584" s="4"/>
       <c r="AI584" s="4"/>
     </row>
-    <row r="585" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>831</v>
       </c>
@@ -60928,7 +60929,7 @@
       <c r="AH585" s="4"/>
       <c r="AI585" s="4"/>
     </row>
-    <row r="586" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>832</v>
       </c>
@@ -60989,7 +60990,7 @@
       <c r="AH586" s="4"/>
       <c r="AI586" s="4"/>
     </row>
-    <row r="587" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>833</v>
       </c>
@@ -61050,7 +61051,7 @@
       <c r="AH587" s="4"/>
       <c r="AI587" s="4"/>
     </row>
-    <row r="588" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>836</v>
       </c>
@@ -61111,7 +61112,7 @@
       <c r="AH588" s="4"/>
       <c r="AI588" s="4"/>
     </row>
-    <row r="589" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>837</v>
       </c>
@@ -61172,7 +61173,7 @@
       <c r="AH589" s="4"/>
       <c r="AI589" s="4"/>
     </row>
-    <row r="590" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>838</v>
       </c>
@@ -61233,7 +61234,7 @@
       <c r="AH590" s="4"/>
       <c r="AI590" s="4"/>
     </row>
-    <row r="591" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>841</v>
       </c>
@@ -61294,7 +61295,7 @@
       <c r="AH591" s="4"/>
       <c r="AI591" s="4"/>
     </row>
-    <row r="592" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>842</v>
       </c>
@@ -61355,7 +61356,7 @@
       <c r="AH592" s="4"/>
       <c r="AI592" s="4"/>
     </row>
-    <row r="593" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>843</v>
       </c>
@@ -61416,7 +61417,7 @@
       <c r="AH593" s="4"/>
       <c r="AI593" s="4"/>
     </row>
-    <row r="594" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>846</v>
       </c>
@@ -61477,7 +61478,7 @@
       <c r="AH594" s="4"/>
       <c r="AI594" s="4"/>
     </row>
-    <row r="595" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>847</v>
       </c>
@@ -61538,7 +61539,7 @@
       <c r="AH595" s="4"/>
       <c r="AI595" s="4"/>
     </row>
-    <row r="596" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>848</v>
       </c>
@@ -61599,7 +61600,7 @@
       <c r="AH596" s="4"/>
       <c r="AI596" s="4"/>
     </row>
-    <row r="597" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>849</v>
       </c>
@@ -61660,7 +61661,7 @@
       <c r="AH597" s="4"/>
       <c r="AI597" s="4"/>
     </row>
-    <row r="598" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>853</v>
       </c>
@@ -61721,7 +61722,7 @@
       <c r="AH598" s="4"/>
       <c r="AI598" s="4"/>
     </row>
-    <row r="599" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>854</v>
       </c>
@@ -61782,7 +61783,7 @@
       <c r="AH599" s="4"/>
       <c r="AI599" s="4"/>
     </row>
-    <row r="600" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>855</v>
       </c>
@@ -61843,7 +61844,7 @@
       <c r="AH600" s="4"/>
       <c r="AI600" s="4"/>
     </row>
-    <row r="601" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>856</v>
       </c>
@@ -61904,7 +61905,7 @@
       <c r="AH601" s="4"/>
       <c r="AI601" s="4"/>
     </row>
-    <row r="602" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>857</v>
       </c>
@@ -61965,7 +61966,7 @@
       <c r="AH602" s="4"/>
       <c r="AI602" s="4"/>
     </row>
-    <row r="603" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>860</v>
       </c>
@@ -62026,7 +62027,7 @@
       <c r="AH603" s="4"/>
       <c r="AI603" s="4"/>
     </row>
-    <row r="604" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>861</v>
       </c>
@@ -62087,7 +62088,7 @@
       <c r="AH604" s="4"/>
       <c r="AI604" s="4"/>
     </row>
-    <row r="605" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>862</v>
       </c>
@@ -62148,7 +62149,7 @@
       <c r="AH605" s="4"/>
       <c r="AI605" s="4"/>
     </row>
-    <row r="606" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>865</v>
       </c>
@@ -62209,7 +62210,7 @@
       <c r="AH606" s="4"/>
       <c r="AI606" s="4"/>
     </row>
-    <row r="607" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>866</v>
       </c>
@@ -62270,7 +62271,7 @@
       <c r="AH607" s="4"/>
       <c r="AI607" s="4"/>
     </row>
-    <row r="608" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>867</v>
       </c>
@@ -62331,7 +62332,7 @@
       <c r="AH608" s="4"/>
       <c r="AI608" s="4"/>
     </row>
-    <row r="609" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>870</v>
       </c>
@@ -62392,7 +62393,7 @@
       <c r="AH609" s="4"/>
       <c r="AI609" s="4"/>
     </row>
-    <row r="610" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>871</v>
       </c>
@@ -62453,7 +62454,7 @@
       <c r="AH610" s="4"/>
       <c r="AI610" s="4"/>
     </row>
-    <row r="611" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>872</v>
       </c>
@@ -62514,7 +62515,7 @@
       <c r="AH611" s="4"/>
       <c r="AI611" s="4"/>
     </row>
-    <row r="612" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>875</v>
       </c>
@@ -62575,7 +62576,7 @@
       <c r="AH612" s="4"/>
       <c r="AI612" s="4"/>
     </row>
-    <row r="613" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>876</v>
       </c>
@@ -62636,7 +62637,7 @@
       <c r="AH613" s="4"/>
       <c r="AI613" s="4"/>
     </row>
-    <row r="614" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>877</v>
       </c>
@@ -62697,7 +62698,7 @@
       <c r="AH614" s="4"/>
       <c r="AI614" s="4"/>
     </row>
-    <row r="615" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>880</v>
       </c>
@@ -62758,7 +62759,7 @@
       <c r="AH615" s="4"/>
       <c r="AI615" s="4"/>
     </row>
-    <row r="616" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>881</v>
       </c>
@@ -62819,7 +62820,7 @@
       <c r="AH616" s="4"/>
       <c r="AI616" s="4"/>
     </row>
-    <row r="617" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>882</v>
       </c>
@@ -62880,7 +62881,7 @@
       <c r="AH617" s="4"/>
       <c r="AI617" s="4"/>
     </row>
-    <row r="618" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>885</v>
       </c>
@@ -62941,7 +62942,7 @@
       <c r="AH618" s="4"/>
       <c r="AI618" s="4"/>
     </row>
-    <row r="619" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>886</v>
       </c>
@@ -63002,7 +63003,7 @@
       <c r="AH619" s="4"/>
       <c r="AI619" s="4"/>
     </row>
-    <row r="620" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>887</v>
       </c>
@@ -63063,7 +63064,7 @@
       <c r="AH620" s="4"/>
       <c r="AI620" s="4"/>
     </row>
-    <row r="621" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>890</v>
       </c>
@@ -63124,7 +63125,7 @@
       <c r="AH621" s="4"/>
       <c r="AI621" s="4"/>
     </row>
-    <row r="622" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>891</v>
       </c>
@@ -63185,7 +63186,7 @@
       <c r="AH622" s="4"/>
       <c r="AI622" s="4"/>
     </row>
-    <row r="623" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>892</v>
       </c>
@@ -63246,7 +63247,7 @@
       <c r="AH623" s="4"/>
       <c r="AI623" s="4"/>
     </row>
-    <row r="624" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>895</v>
       </c>
@@ -63307,7 +63308,7 @@
       <c r="AH624" s="4"/>
       <c r="AI624" s="4"/>
     </row>
-    <row r="625" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>896</v>
       </c>
@@ -63368,7 +63369,7 @@
       <c r="AH625" s="4"/>
       <c r="AI625" s="4"/>
     </row>
-    <row r="626" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>897</v>
       </c>
@@ -63429,7 +63430,7 @@
       <c r="AH626" s="4"/>
       <c r="AI626" s="4"/>
     </row>
-    <row r="627" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>898</v>
       </c>
@@ -63490,7 +63491,7 @@
       <c r="AH627" s="4"/>
       <c r="AI627" s="4"/>
     </row>
-    <row r="628" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>901</v>
       </c>
@@ -63551,7 +63552,7 @@
       <c r="AH628" s="4"/>
       <c r="AI628" s="4"/>
     </row>
-    <row r="629" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>903</v>
       </c>
@@ -63612,7 +63613,7 @@
       <c r="AH629" s="4"/>
       <c r="AI629" s="4"/>
     </row>
-    <row r="630" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>905</v>
       </c>
@@ -63673,7 +63674,7 @@
       <c r="AH630" s="4"/>
       <c r="AI630" s="4"/>
     </row>
-    <row r="631" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>907</v>
       </c>
@@ -63734,7 +63735,7 @@
       <c r="AH631" s="4"/>
       <c r="AI631" s="4"/>
     </row>
-    <row r="632" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>911</v>
       </c>
@@ -63795,7 +63796,7 @@
       <c r="AH632" s="4"/>
       <c r="AI632" s="4"/>
     </row>
-    <row r="633" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>913</v>
       </c>
@@ -63856,7 +63857,7 @@
       <c r="AH633" s="4"/>
       <c r="AI633" s="4"/>
     </row>
-    <row r="634" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>915</v>
       </c>
@@ -63917,7 +63918,7 @@
       <c r="AH634" s="4"/>
       <c r="AI634" s="4"/>
     </row>
-    <row r="635" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>917</v>
       </c>
@@ -63978,7 +63979,7 @@
       <c r="AH635" s="4"/>
       <c r="AI635" s="4"/>
     </row>
-    <row r="636" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>919</v>
       </c>
@@ -64039,7 +64040,7 @@
       <c r="AH636" s="4"/>
       <c r="AI636" s="4"/>
     </row>
-    <row r="637" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>922</v>
       </c>
@@ -64100,7 +64101,7 @@
       <c r="AH637" s="4"/>
       <c r="AI637" s="4"/>
     </row>
-    <row r="638" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>923</v>
       </c>
@@ -64161,7 +64162,7 @@
       <c r="AH638" s="4"/>
       <c r="AI638" s="4"/>
     </row>
-    <row r="639" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>924</v>
       </c>
@@ -64222,7 +64223,7 @@
       <c r="AH639" s="4"/>
       <c r="AI639" s="4"/>
     </row>
-    <row r="640" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>925</v>
       </c>
@@ -64283,7 +64284,7 @@
       <c r="AH640" s="4"/>
       <c r="AI640" s="4"/>
     </row>
-    <row r="641" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>926</v>
       </c>
@@ -64344,7 +64345,7 @@
       <c r="AH641" s="4"/>
       <c r="AI641" s="4"/>
     </row>
-    <row r="642" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>929</v>
       </c>
@@ -64405,7 +64406,7 @@
       <c r="AH642" s="4"/>
       <c r="AI642" s="4"/>
     </row>
-    <row r="643" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>933</v>
       </c>
@@ -64466,7 +64467,7 @@
       <c r="AH643" s="4"/>
       <c r="AI643" s="4"/>
     </row>
-    <row r="644" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>934</v>
       </c>
@@ -64527,7 +64528,7 @@
       <c r="AH644" s="4"/>
       <c r="AI644" s="4"/>
     </row>
-    <row r="645" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>937</v>
       </c>
@@ -64588,7 +64589,7 @@
       <c r="AH645" s="4"/>
       <c r="AI645" s="4"/>
     </row>
-    <row r="646" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>938</v>
       </c>
@@ -64649,7 +64650,7 @@
       <c r="AH646" s="4"/>
       <c r="AI646" s="4"/>
     </row>
-    <row r="647" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>941</v>
       </c>
@@ -64710,7 +64711,7 @@
       <c r="AH647" s="4"/>
       <c r="AI647" s="4"/>
     </row>
-    <row r="648" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>944</v>
       </c>
@@ -64771,7 +64772,7 @@
       <c r="AH648" s="4"/>
       <c r="AI648" s="4"/>
     </row>
-    <row r="649" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>946</v>
       </c>
@@ -64832,7 +64833,7 @@
       <c r="AH649" s="4"/>
       <c r="AI649" s="4"/>
     </row>
-    <row r="650" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>949</v>
       </c>
@@ -64893,7 +64894,7 @@
       <c r="AH650" s="4"/>
       <c r="AI650" s="4"/>
     </row>
-    <row r="651" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>952</v>
       </c>
@@ -64954,7 +64955,7 @@
       <c r="AH651" s="4"/>
       <c r="AI651" s="4"/>
     </row>
-    <row r="652" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>955</v>
       </c>
@@ -65015,7 +65016,7 @@
       <c r="AH652" s="4"/>
       <c r="AI652" s="4"/>
     </row>
-    <row r="653" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>956</v>
       </c>
@@ -65076,7 +65077,7 @@
       <c r="AH653" s="4"/>
       <c r="AI653" s="4"/>
     </row>
-    <row r="654" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>957</v>
       </c>
@@ -65137,7 +65138,7 @@
       <c r="AH654" s="4"/>
       <c r="AI654" s="4"/>
     </row>
-    <row r="655" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>960</v>
       </c>
@@ -65198,7 +65199,7 @@
       <c r="AH655" s="4"/>
       <c r="AI655" s="4"/>
     </row>
-    <row r="656" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>962</v>
       </c>
@@ -65259,7 +65260,7 @@
       <c r="AH656" s="4"/>
       <c r="AI656" s="4"/>
     </row>
-    <row r="657" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>963</v>
       </c>
@@ -65320,7 +65321,7 @@
       <c r="AH657" s="4"/>
       <c r="AI657" s="4"/>
     </row>
-    <row r="658" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>964</v>
       </c>
@@ -65381,7 +65382,7 @@
       <c r="AH658" s="4"/>
       <c r="AI658" s="4"/>
     </row>
-    <row r="659" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>965</v>
       </c>
@@ -65442,7 +65443,7 @@
       <c r="AH659" s="4"/>
       <c r="AI659" s="4"/>
     </row>
-    <row r="660" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>968</v>
       </c>
@@ -65503,7 +65504,7 @@
       <c r="AH660" s="4"/>
       <c r="AI660" s="4"/>
     </row>
-    <row r="661" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>969</v>
       </c>
@@ -65564,7 +65565,7 @@
       <c r="AH661" s="4"/>
       <c r="AI661" s="4"/>
     </row>
-    <row r="662" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>971</v>
       </c>
@@ -65625,7 +65626,7 @@
       <c r="AH662" s="4"/>
       <c r="AI662" s="4"/>
     </row>
-    <row r="663" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>972</v>
       </c>
@@ -65686,7 +65687,7 @@
       <c r="AH663" s="4"/>
       <c r="AI663" s="4"/>
     </row>
-    <row r="664" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>973</v>
       </c>
@@ -65747,7 +65748,7 @@
       <c r="AH664" s="4"/>
       <c r="AI664" s="4"/>
     </row>
-    <row r="665" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>976</v>
       </c>
@@ -65808,7 +65809,7 @@
       <c r="AH665" s="4"/>
       <c r="AI665" s="4"/>
     </row>
-    <row r="666" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>978</v>
       </c>
@@ -65869,7 +65870,7 @@
       <c r="AH666" s="4"/>
       <c r="AI666" s="4"/>
     </row>
-    <row r="667" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>980</v>
       </c>
@@ -65930,7 +65931,7 @@
       <c r="AH667" s="4"/>
       <c r="AI667" s="4"/>
     </row>
-    <row r="668" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>983</v>
       </c>
@@ -65991,7 +65992,7 @@
       <c r="AH668" s="4"/>
       <c r="AI668" s="4"/>
     </row>
-    <row r="669" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>986</v>
       </c>
@@ -66052,7 +66053,7 @@
       <c r="AH669" s="4"/>
       <c r="AI669" s="4"/>
     </row>
-    <row r="670" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>989</v>
       </c>
@@ -66113,7 +66114,7 @@
       <c r="AH670" s="4"/>
       <c r="AI670" s="4"/>
     </row>
-    <row r="671" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>990</v>
       </c>
@@ -66174,7 +66175,7 @@
       <c r="AH671" s="4"/>
       <c r="AI671" s="4"/>
     </row>
-    <row r="672" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>993</v>
       </c>
@@ -66235,7 +66236,7 @@
       <c r="AH672" s="4"/>
       <c r="AI672" s="4"/>
     </row>
-    <row r="673" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>994</v>
       </c>
@@ -66296,7 +66297,7 @@
       <c r="AH673" s="4"/>
       <c r="AI673" s="4"/>
     </row>
-    <row r="674" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>995</v>
       </c>
@@ -66357,7 +66358,7 @@
       <c r="AH674" s="4"/>
       <c r="AI674" s="4"/>
     </row>
-    <row r="675" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>996</v>
       </c>
@@ -66418,7 +66419,7 @@
       <c r="AH675" s="4"/>
       <c r="AI675" s="4"/>
     </row>
-    <row r="676" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>999</v>
       </c>
@@ -66479,7 +66480,7 @@
       <c r="AH676" s="4"/>
       <c r="AI676" s="4"/>
     </row>
-    <row r="677" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>1000</v>
       </c>
@@ -66540,7 +66541,7 @@
       <c r="AH677" s="4"/>
       <c r="AI677" s="4"/>
     </row>
-    <row r="678" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>1001</v>
       </c>
@@ -66601,7 +66602,7 @@
       <c r="AH678" s="4"/>
       <c r="AI678" s="4"/>
     </row>
-    <row r="679" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>1002</v>
       </c>
@@ -66662,7 +66663,7 @@
       <c r="AH679" s="4"/>
       <c r="AI679" s="4"/>
     </row>
-    <row r="680" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>1005</v>
       </c>
@@ -66723,7 +66724,7 @@
       <c r="AH680" s="4"/>
       <c r="AI680" s="4"/>
     </row>
-    <row r="681" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>1008</v>
       </c>
@@ -66784,7 +66785,7 @@
       <c r="AH681" s="4"/>
       <c r="AI681" s="4"/>
     </row>
-    <row r="682" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>1009</v>
       </c>
@@ -66845,7 +66846,7 @@
       <c r="AH682" s="4"/>
       <c r="AI682" s="4"/>
     </row>
-    <row r="683" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>1010</v>
       </c>
@@ -66906,7 +66907,7 @@
       <c r="AH683" s="4"/>
       <c r="AI683" s="4"/>
     </row>
-    <row r="684" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>1011</v>
       </c>
@@ -66967,7 +66968,7 @@
       <c r="AH684" s="4"/>
       <c r="AI684" s="4"/>
     </row>
-    <row r="685" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>1012</v>
       </c>
@@ -67028,7 +67029,7 @@
       <c r="AH685" s="4"/>
       <c r="AI685" s="4"/>
     </row>
-    <row r="686" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>1015</v>
       </c>
@@ -67089,7 +67090,7 @@
       <c r="AH686" s="4"/>
       <c r="AI686" s="4"/>
     </row>
-    <row r="687" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>1016</v>
       </c>
@@ -67150,7 +67151,7 @@
       <c r="AH687" s="4"/>
       <c r="AI687" s="4"/>
     </row>
-    <row r="688" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>1019</v>
       </c>
@@ -67211,7 +67212,7 @@
       <c r="AH688" s="4"/>
       <c r="AI688" s="4"/>
     </row>
-    <row r="689" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>1020</v>
       </c>
@@ -67272,7 +67273,7 @@
       <c r="AH689" s="4"/>
       <c r="AI689" s="4"/>
     </row>
-    <row r="690" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1022</v>
       </c>
@@ -67333,7 +67334,7 @@
       <c r="AH690" s="4"/>
       <c r="AI690" s="4"/>
     </row>
-    <row r="691" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1027</v>
       </c>
@@ -67394,7 +67395,7 @@
       <c r="AH691" s="4"/>
       <c r="AI691" s="4"/>
     </row>
-    <row r="692" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1029</v>
       </c>
@@ -67455,7 +67456,7 @@
       <c r="AH692" s="4"/>
       <c r="AI692" s="4"/>
     </row>
-    <row r="693" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1033</v>
       </c>
@@ -67516,7 +67517,7 @@
       <c r="AH693" s="4"/>
       <c r="AI693" s="4"/>
     </row>
-    <row r="694" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1034</v>
       </c>
@@ -67577,7 +67578,7 @@
       <c r="AH694" s="4"/>
       <c r="AI694" s="4"/>
     </row>
-    <row r="695" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1036</v>
       </c>
@@ -67638,7 +67639,7 @@
       <c r="AH695" s="4"/>
       <c r="AI695" s="4"/>
     </row>
-    <row r="696" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1039</v>
       </c>
@@ -67699,7 +67700,7 @@
       <c r="AH696" s="4"/>
       <c r="AI696" s="4"/>
     </row>
-    <row r="697" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1040</v>
       </c>
@@ -67760,7 +67761,7 @@
       <c r="AH697" s="4"/>
       <c r="AI697" s="4"/>
     </row>
-    <row r="698" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1041</v>
       </c>
@@ -67821,7 +67822,7 @@
       <c r="AH698" s="4"/>
       <c r="AI698" s="4"/>
     </row>
-    <row r="699" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1043</v>
       </c>
@@ -67882,7 +67883,7 @@
       <c r="AH699" s="4"/>
       <c r="AI699" s="4"/>
     </row>
-    <row r="700" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1047</v>
       </c>
@@ -67943,7 +67944,7 @@
       <c r="AH700" s="4"/>
       <c r="AI700" s="4"/>
     </row>
-    <row r="701" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>1049</v>
       </c>
@@ -68004,7 +68005,7 @@
       <c r="AH701" s="4"/>
       <c r="AI701" s="4"/>
     </row>
-    <row r="702" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>1052</v>
       </c>
@@ -68065,7 +68066,7 @@
       <c r="AH702" s="4"/>
       <c r="AI702" s="4"/>
     </row>
-    <row r="703" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1053</v>
       </c>
@@ -68126,7 +68127,7 @@
       <c r="AH703" s="4"/>
       <c r="AI703" s="4"/>
     </row>
-    <row r="704" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1056</v>
       </c>
@@ -68187,7 +68188,7 @@
       <c r="AH704" s="4"/>
       <c r="AI704" s="4"/>
     </row>
-    <row r="705" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1057</v>
       </c>
@@ -68248,7 +68249,7 @@
       <c r="AH705" s="4"/>
       <c r="AI705" s="4"/>
     </row>
-    <row r="706" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1058</v>
       </c>
@@ -68309,7 +68310,7 @@
       <c r="AH706" s="4"/>
       <c r="AI706" s="4"/>
     </row>
-    <row r="707" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1060</v>
       </c>
@@ -68370,7 +68371,7 @@
       <c r="AH707" s="4"/>
       <c r="AI707" s="4"/>
     </row>
-    <row r="708" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1061</v>
       </c>
@@ -68431,7 +68432,7 @@
       <c r="AH708" s="4"/>
       <c r="AI708" s="4"/>
     </row>
-    <row r="709" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1062</v>
       </c>
@@ -68492,7 +68493,7 @@
       <c r="AH709" s="4"/>
       <c r="AI709" s="4"/>
     </row>
-    <row r="710" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1066</v>
       </c>
@@ -68553,7 +68554,7 @@
       <c r="AH710" s="4"/>
       <c r="AI710" s="4"/>
     </row>
-    <row r="711" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1068</v>
       </c>
@@ -68614,7 +68615,7 @@
       <c r="AH711" s="4"/>
       <c r="AI711" s="4"/>
     </row>
-    <row r="712" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1070</v>
       </c>
@@ -68675,7 +68676,7 @@
       <c r="AH712" s="4"/>
       <c r="AI712" s="4"/>
     </row>
-    <row r="713" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>1071</v>
       </c>
@@ -68736,7 +68737,7 @@
       <c r="AH713" s="4"/>
       <c r="AI713" s="4"/>
     </row>
-    <row r="714" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>1074</v>
       </c>
@@ -68797,7 +68798,7 @@
       <c r="AH714" s="4"/>
       <c r="AI714" s="4"/>
     </row>
-    <row r="715" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>1077</v>
       </c>
@@ -68858,7 +68859,7 @@
       <c r="AH715" s="4"/>
       <c r="AI715" s="4"/>
     </row>
-    <row r="716" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>1078</v>
       </c>
@@ -68919,7 +68920,7 @@
       <c r="AH716" s="4"/>
       <c r="AI716" s="4"/>
     </row>
-    <row r="717" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>1081</v>
       </c>
@@ -68980,7 +68981,7 @@
       <c r="AH717" s="4"/>
       <c r="AI717" s="4"/>
     </row>
-    <row r="718" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>1085</v>
       </c>
@@ -69041,7 +69042,7 @@
       <c r="AH718" s="4"/>
       <c r="AI718" s="4"/>
     </row>
-    <row r="719" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>1086</v>
       </c>
@@ -69102,7 +69103,7 @@
       <c r="AH719" s="4"/>
       <c r="AI719" s="4"/>
     </row>
-    <row r="720" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>1087</v>
       </c>
@@ -69163,7 +69164,7 @@
       <c r="AH720" s="4"/>
       <c r="AI720" s="4"/>
     </row>
-    <row r="721" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1089</v>
       </c>
@@ -69224,7 +69225,7 @@
       <c r="AH721" s="4"/>
       <c r="AI721" s="4"/>
     </row>
-    <row r="722" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1092</v>
       </c>
@@ -69285,7 +69286,7 @@
       <c r="AH722" s="4"/>
       <c r="AI722" s="4"/>
     </row>
-    <row r="723" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1093</v>
       </c>
@@ -69346,7 +69347,7 @@
       <c r="AH723" s="4"/>
       <c r="AI723" s="4"/>
     </row>
-    <row r="724" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1094</v>
       </c>
@@ -69407,7 +69408,7 @@
       <c r="AH724" s="4"/>
       <c r="AI724" s="4"/>
     </row>
-    <row r="725" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1096</v>
       </c>
@@ -69468,7 +69469,7 @@
       <c r="AH725" s="4"/>
       <c r="AI725" s="4"/>
     </row>
-    <row r="726" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1097</v>
       </c>
@@ -69529,7 +69530,7 @@
       <c r="AH726" s="4"/>
       <c r="AI726" s="4"/>
     </row>
-    <row r="727" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1098</v>
       </c>
@@ -69590,7 +69591,7 @@
       <c r="AH727" s="4"/>
       <c r="AI727" s="4"/>
     </row>
-    <row r="728" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>1099</v>
       </c>
@@ -69651,7 +69652,7 @@
       <c r="AH728" s="4"/>
       <c r="AI728" s="4"/>
     </row>
-    <row r="729" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>1100</v>
       </c>
@@ -69712,7 +69713,7 @@
       <c r="AH729" s="4"/>
       <c r="AI729" s="4"/>
     </row>
-    <row r="730" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>1103</v>
       </c>
@@ -69773,7 +69774,7 @@
       <c r="AH730" s="4"/>
       <c r="AI730" s="4"/>
     </row>
-    <row r="731" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>1104</v>
       </c>
@@ -69834,7 +69835,7 @@
       <c r="AH731" s="4"/>
       <c r="AI731" s="4"/>
     </row>
-    <row r="732" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>1105</v>
       </c>
@@ -69895,7 +69896,7 @@
       <c r="AH732" s="4"/>
       <c r="AI732" s="4"/>
     </row>
-    <row r="733" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>1108</v>
       </c>
@@ -69956,7 +69957,7 @@
       <c r="AH733" s="4"/>
       <c r="AI733" s="4"/>
     </row>
-    <row r="734" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>1110</v>
       </c>
@@ -70017,7 +70018,7 @@
       <c r="AH734" s="4"/>
       <c r="AI734" s="4"/>
     </row>
-    <row r="735" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>1111</v>
       </c>
@@ -70078,7 +70079,7 @@
       <c r="AH735" s="4"/>
       <c r="AI735" s="4"/>
     </row>
-    <row r="736" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>1114</v>
       </c>
@@ -70139,7 +70140,7 @@
       <c r="AH736" s="4"/>
       <c r="AI736" s="4"/>
     </row>
-    <row r="737" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>1116</v>
       </c>
@@ -70200,7 +70201,7 @@
       <c r="AH737" s="4"/>
       <c r="AI737" s="4"/>
     </row>
-    <row r="738" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>1117</v>
       </c>
@@ -70261,7 +70262,7 @@
       <c r="AH738" s="4"/>
       <c r="AI738" s="4"/>
     </row>
-    <row r="739" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>1118</v>
       </c>
@@ -70322,7 +70323,7 @@
       <c r="AH739" s="4"/>
       <c r="AI739" s="4"/>
     </row>
-    <row r="740" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>1121</v>
       </c>
@@ -70383,7 +70384,7 @@
       <c r="AH740" s="4"/>
       <c r="AI740" s="4"/>
     </row>
-    <row r="741" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>1122</v>
       </c>
@@ -70444,7 +70445,7 @@
       <c r="AH741" s="4"/>
       <c r="AI741" s="4"/>
     </row>
-    <row r="742" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>1125</v>
       </c>
@@ -70505,7 +70506,7 @@
       <c r="AH742" s="4"/>
       <c r="AI742" s="4"/>
     </row>
-    <row r="743" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>1126</v>
       </c>
@@ -70566,7 +70567,7 @@
       <c r="AH743" s="4"/>
       <c r="AI743" s="4"/>
     </row>
-    <row r="744" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>1129</v>
       </c>
@@ -70749,7 +70750,7 @@
       <c r="AH746" s="4"/>
       <c r="AI746" s="4"/>
     </row>
-    <row r="747" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>1135</v>
       </c>
@@ -70810,7 +70811,7 @@
       <c r="AH747" s="4"/>
       <c r="AI747" s="4"/>
     </row>
-    <row r="748" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>1138</v>
       </c>
@@ -70871,7 +70872,7 @@
       <c r="AH748" s="4"/>
       <c r="AI748" s="4"/>
     </row>
-    <row r="749" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>1139</v>
       </c>
@@ -70932,7 +70933,7 @@
       <c r="AH749" s="4"/>
       <c r="AI749" s="4"/>
     </row>
-    <row r="750" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>1143</v>
       </c>
@@ -70993,7 +70994,7 @@
       <c r="AH750" s="4"/>
       <c r="AI750" s="4"/>
     </row>
-    <row r="751" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>1144</v>
       </c>
@@ -71054,7 +71055,7 @@
       <c r="AH751" s="4"/>
       <c r="AI751" s="4"/>
     </row>
-    <row r="752" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>1145</v>
       </c>
@@ -71115,7 +71116,7 @@
       <c r="AH752" s="4"/>
       <c r="AI752" s="4"/>
     </row>
-    <row r="753" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>1147</v>
       </c>
@@ -71176,7 +71177,7 @@
       <c r="AH753" s="4"/>
       <c r="AI753" s="4"/>
     </row>
-    <row r="754" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>1148</v>
       </c>
@@ -71237,7 +71238,7 @@
       <c r="AH754" s="4"/>
       <c r="AI754" s="4"/>
     </row>
-    <row r="755" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>1150</v>
       </c>
@@ -71298,7 +71299,7 @@
       <c r="AH755" s="4"/>
       <c r="AI755" s="4"/>
     </row>
-    <row r="756" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>1151</v>
       </c>
@@ -71359,7 +71360,7 @@
       <c r="AH756" s="4"/>
       <c r="AI756" s="4"/>
     </row>
-    <row r="757" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>1154</v>
       </c>
@@ -71420,7 +71421,7 @@
       <c r="AH757" s="4"/>
       <c r="AI757" s="4"/>
     </row>
-    <row r="758" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1156</v>
       </c>
@@ -71481,7 +71482,7 @@
       <c r="AH758" s="4"/>
       <c r="AI758" s="4"/>
     </row>
-    <row r="759" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1157</v>
       </c>
@@ -71542,7 +71543,7 @@
       <c r="AH759" s="4"/>
       <c r="AI759" s="4"/>
     </row>
-    <row r="760" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>1160</v>
       </c>
@@ -71603,7 +71604,7 @@
       <c r="AH760" s="4"/>
       <c r="AI760" s="4"/>
     </row>
-    <row r="761" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>1161</v>
       </c>
@@ -71664,7 +71665,7 @@
       <c r="AH761" s="4"/>
       <c r="AI761" s="4"/>
     </row>
-    <row r="762" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>1162</v>
       </c>
@@ -71725,7 +71726,7 @@
       <c r="AH762" s="4"/>
       <c r="AI762" s="4"/>
     </row>
-    <row r="763" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>1164</v>
       </c>
@@ -71786,7 +71787,7 @@
       <c r="AH763" s="4"/>
       <c r="AI763" s="4"/>
     </row>
-    <row r="764" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>1165</v>
       </c>
@@ -71847,7 +71848,7 @@
       <c r="AH764" s="4"/>
       <c r="AI764" s="4"/>
     </row>
-    <row r="765" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1168</v>
       </c>
@@ -71908,7 +71909,7 @@
       <c r="AH765" s="4"/>
       <c r="AI765" s="4"/>
     </row>
-    <row r="766" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1169</v>
       </c>
@@ -71969,7 +71970,7 @@
       <c r="AH766" s="4"/>
       <c r="AI766" s="4"/>
     </row>
-    <row r="767" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>1170</v>
       </c>
@@ -72030,7 +72031,7 @@
       <c r="AH767" s="4"/>
       <c r="AI767" s="4"/>
     </row>
-    <row r="768" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>1172</v>
       </c>
@@ -72091,7 +72092,7 @@
       <c r="AH768" s="4"/>
       <c r="AI768" s="4"/>
     </row>
-    <row r="769" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>1173</v>
       </c>
@@ -72152,7 +72153,7 @@
       <c r="AH769" s="4"/>
       <c r="AI769" s="4"/>
     </row>
-    <row r="770" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>1174</v>
       </c>
@@ -72213,7 +72214,7 @@
       <c r="AH770" s="4"/>
       <c r="AI770" s="4"/>
     </row>
-    <row r="771" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>1177</v>
       </c>
@@ -72274,7 +72275,7 @@
       <c r="AH771" s="4"/>
       <c r="AI771" s="4"/>
     </row>
-    <row r="772" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>1178</v>
       </c>
@@ -72335,7 +72336,7 @@
       <c r="AH772" s="4"/>
       <c r="AI772" s="4"/>
     </row>
-    <row r="773" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>1179</v>
       </c>
@@ -72396,7 +72397,7 @@
       <c r="AH773" s="4"/>
       <c r="AI773" s="4"/>
     </row>
-    <row r="774" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1180</v>
       </c>
@@ -72457,7 +72458,7 @@
       <c r="AH774" s="4"/>
       <c r="AI774" s="4"/>
     </row>
-    <row r="775" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>1183</v>
       </c>
@@ -72518,7 +72519,7 @@
       <c r="AH775" s="4"/>
       <c r="AI775" s="4"/>
     </row>
-    <row r="776" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>1184</v>
       </c>
@@ -72579,7 +72580,7 @@
       <c r="AH776" s="4"/>
       <c r="AI776" s="4"/>
     </row>
-    <row r="777" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>1185</v>
       </c>
@@ -72640,7 +72641,7 @@
       <c r="AH777" s="4"/>
       <c r="AI777" s="4"/>
     </row>
-    <row r="778" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1186</v>
       </c>
@@ -72701,7 +72702,7 @@
       <c r="AH778" s="4"/>
       <c r="AI778" s="4"/>
     </row>
-    <row r="779" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>1187</v>
       </c>
@@ -72762,7 +72763,7 @@
       <c r="AH779" s="4"/>
       <c r="AI779" s="4"/>
     </row>
-    <row r="780" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1188</v>
       </c>
@@ -72823,7 +72824,7 @@
       <c r="AH780" s="4"/>
       <c r="AI780" s="4"/>
     </row>
-    <row r="781" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1191</v>
       </c>
@@ -72884,7 +72885,7 @@
       <c r="AH781" s="4"/>
       <c r="AI781" s="4"/>
     </row>
-    <row r="782" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>1194</v>
       </c>
@@ -72945,7 +72946,7 @@
       <c r="AH782" s="4"/>
       <c r="AI782" s="4"/>
     </row>
-    <row r="783" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>1195</v>
       </c>
@@ -73006,7 +73007,7 @@
       <c r="AH783" s="4"/>
       <c r="AI783" s="4"/>
     </row>
-    <row r="784" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>1196</v>
       </c>
@@ -73067,7 +73068,7 @@
       <c r="AH784" s="4"/>
       <c r="AI784" s="4"/>
     </row>
-    <row r="785" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>1197</v>
       </c>
@@ -73128,7 +73129,7 @@
       <c r="AH785" s="4"/>
       <c r="AI785" s="4"/>
     </row>
-    <row r="786" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>1200</v>
       </c>
@@ -73189,7 +73190,7 @@
       <c r="AH786" s="4"/>
       <c r="AI786" s="4"/>
     </row>
-    <row r="787" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>1201</v>
       </c>
@@ -73250,7 +73251,7 @@
       <c r="AH787" s="4"/>
       <c r="AI787" s="4"/>
     </row>
-    <row r="788" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1202</v>
       </c>
@@ -73311,7 +73312,7 @@
       <c r="AH788" s="4"/>
       <c r="AI788" s="4"/>
     </row>
-    <row r="789" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>1203</v>
       </c>
@@ -73372,7 +73373,7 @@
       <c r="AH789" s="4"/>
       <c r="AI789" s="4"/>
     </row>
-    <row r="790" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>1206</v>
       </c>
@@ -73555,7 +73556,7 @@
       <c r="AH792" s="4"/>
       <c r="AI792" s="4"/>
     </row>
-    <row r="793" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>1211</v>
       </c>
@@ -73616,7 +73617,7 @@
       <c r="AH793" s="4"/>
       <c r="AI793" s="4"/>
     </row>
-    <row r="794" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>1214</v>
       </c>
@@ -73677,7 +73678,7 @@
       <c r="AH794" s="4"/>
       <c r="AI794" s="4"/>
     </row>
-    <row r="795" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>1217</v>
       </c>
@@ -73738,7 +73739,7 @@
       <c r="AH795" s="4"/>
       <c r="AI795" s="4"/>
     </row>
-    <row r="796" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>1218</v>
       </c>
@@ -73799,7 +73800,7 @@
       <c r="AH796" s="4"/>
       <c r="AI796" s="4"/>
     </row>
-    <row r="797" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
         <v>1222</v>
       </c>
@@ -73860,7 +73861,7 @@
       <c r="AH797" s="4"/>
       <c r="AI797" s="4"/>
     </row>
-    <row r="798" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>1223</v>
       </c>
@@ -73921,7 +73922,7 @@
       <c r="AH798" s="4"/>
       <c r="AI798" s="4"/>
     </row>
-    <row r="799" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>1225</v>
       </c>
@@ -73982,7 +73983,7 @@
       <c r="AH799" s="4"/>
       <c r="AI799" s="4"/>
     </row>
-    <row r="800" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>1228</v>
       </c>
@@ -74043,7 +74044,7 @@
       <c r="AH800" s="4"/>
       <c r="AI800" s="4"/>
     </row>
-    <row r="801" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1229</v>
       </c>
@@ -74104,7 +74105,7 @@
       <c r="AH801" s="4"/>
       <c r="AI801" s="4"/>
     </row>
-    <row r="802" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>1230</v>
       </c>
@@ -74165,7 +74166,7 @@
       <c r="AH802" s="4"/>
       <c r="AI802" s="4"/>
     </row>
-    <row r="803" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>1231</v>
       </c>
@@ -74226,7 +74227,7 @@
       <c r="AH803" s="4"/>
       <c r="AI803" s="4"/>
     </row>
-    <row r="804" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>1234</v>
       </c>
@@ -74287,7 +74288,7 @@
       <c r="AH804" s="4"/>
       <c r="AI804" s="4"/>
     </row>
-    <row r="805" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1235</v>
       </c>
@@ -74348,7 +74349,7 @@
       <c r="AH805" s="4"/>
       <c r="AI805" s="4"/>
     </row>
-    <row r="806" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1236</v>
       </c>
@@ -74409,7 +74410,7 @@
       <c r="AH806" s="4"/>
       <c r="AI806" s="4"/>
     </row>
-    <row r="807" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1239</v>
       </c>
@@ -74470,7 +74471,7 @@
       <c r="AH807" s="4"/>
       <c r="AI807" s="4"/>
     </row>
-    <row r="808" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>1240</v>
       </c>
@@ -74531,7 +74532,7 @@
       <c r="AH808" s="4"/>
       <c r="AI808" s="4"/>
     </row>
-    <row r="809" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>1241</v>
       </c>
@@ -74592,7 +74593,7 @@
       <c r="AH809" s="4"/>
       <c r="AI809" s="4"/>
     </row>
-    <row r="810" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>1244</v>
       </c>
@@ -74653,7 +74654,7 @@
       <c r="AH810" s="4"/>
       <c r="AI810" s="4"/>
     </row>
-    <row r="811" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>1245</v>
       </c>
@@ -74714,7 +74715,7 @@
       <c r="AH811" s="4"/>
       <c r="AI811" s="4"/>
     </row>
-    <row r="812" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>1247</v>
       </c>
@@ -74775,7 +74776,7 @@
       <c r="AH812" s="4"/>
       <c r="AI812" s="4"/>
     </row>
-    <row r="813" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>1248</v>
       </c>
@@ -74836,7 +74837,7 @@
       <c r="AH813" s="4"/>
       <c r="AI813" s="4"/>
     </row>
-    <row r="814" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>1252</v>
       </c>
@@ -74897,7 +74898,7 @@
       <c r="AH814" s="4"/>
       <c r="AI814" s="4"/>
     </row>
-    <row r="815" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>1253</v>
       </c>
@@ -74958,7 +74959,7 @@
       <c r="AH815" s="4"/>
       <c r="AI815" s="4"/>
     </row>
-    <row r="816" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
         <v>1255</v>
       </c>
@@ -75019,7 +75020,7 @@
       <c r="AH816" s="4"/>
       <c r="AI816" s="4"/>
     </row>
-    <row r="817" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
         <v>1256</v>
       </c>
@@ -75080,7 +75081,7 @@
       <c r="AH817" s="4"/>
       <c r="AI817" s="4"/>
     </row>
-    <row r="818" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
         <v>1257</v>
       </c>
@@ -75141,7 +75142,7 @@
       <c r="AH818" s="4"/>
       <c r="AI818" s="4"/>
     </row>
-    <row r="819" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
         <v>1258</v>
       </c>
@@ -75202,7 +75203,7 @@
       <c r="AH819" s="4"/>
       <c r="AI819" s="4"/>
     </row>
-    <row r="820" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
         <v>1261</v>
       </c>
@@ -75263,7 +75264,7 @@
       <c r="AH820" s="4"/>
       <c r="AI820" s="4"/>
     </row>
-    <row r="821" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
         <v>1262</v>
       </c>
@@ -75324,7 +75325,7 @@
       <c r="AH821" s="4"/>
       <c r="AI821" s="4"/>
     </row>
-    <row r="822" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
         <v>1263</v>
       </c>
@@ -75385,7 +75386,7 @@
       <c r="AH822" s="4"/>
       <c r="AI822" s="4"/>
     </row>
-    <row r="823" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
         <v>1266</v>
       </c>
@@ -75446,7 +75447,7 @@
       <c r="AH823" s="4"/>
       <c r="AI823" s="4"/>
     </row>
-    <row r="824" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
         <v>1268</v>
       </c>
@@ -75507,7 +75508,7 @@
       <c r="AH824" s="4"/>
       <c r="AI824" s="4"/>
     </row>
-    <row r="825" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
         <v>1269</v>
       </c>
@@ -75568,7 +75569,7 @@
       <c r="AH825" s="4"/>
       <c r="AI825" s="4"/>
     </row>
-    <row r="826" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
         <v>1272</v>
       </c>
@@ -75629,7 +75630,7 @@
       <c r="AH826" s="4"/>
       <c r="AI826" s="4"/>
     </row>
-    <row r="827" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
         <v>1273</v>
       </c>
@@ -75690,7 +75691,7 @@
       <c r="AH827" s="4"/>
       <c r="AI827" s="4"/>
     </row>
-    <row r="828" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
         <v>1276</v>
       </c>
@@ -75751,7 +75752,7 @@
       <c r="AH828" s="4"/>
       <c r="AI828" s="4"/>
     </row>
-    <row r="829" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
         <v>1277</v>
       </c>
@@ -75812,7 +75813,7 @@
       <c r="AH829" s="4"/>
       <c r="AI829" s="4"/>
     </row>
-    <row r="830" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
         <v>1279</v>
       </c>
@@ -75873,7 +75874,7 @@
       <c r="AH830" s="4"/>
       <c r="AI830" s="4"/>
     </row>
-    <row r="831" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
         <v>1280</v>
       </c>
@@ -75934,7 +75935,7 @@
       <c r="AH831" s="4"/>
       <c r="AI831" s="4"/>
     </row>
-    <row r="832" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
         <v>1281</v>
       </c>
@@ -75995,7 +75996,7 @@
       <c r="AH832" s="4"/>
       <c r="AI832" s="4"/>
     </row>
-    <row r="833" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
         <v>1282</v>
       </c>
@@ -76056,7 +76057,7 @@
       <c r="AH833" s="4"/>
       <c r="AI833" s="4"/>
     </row>
-    <row r="834" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
         <v>1283</v>
       </c>
@@ -76117,7 +76118,7 @@
       <c r="AH834" s="4"/>
       <c r="AI834" s="4"/>
     </row>
-    <row r="835" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
         <v>1286</v>
       </c>
@@ -76178,7 +76179,7 @@
       <c r="AH835" s="4"/>
       <c r="AI835" s="4"/>
     </row>
-    <row r="836" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
         <v>1289</v>
       </c>
@@ -76239,7 +76240,7 @@
       <c r="AH836" s="4"/>
       <c r="AI836" s="4"/>
     </row>
-    <row r="837" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
         <v>1290</v>
       </c>
@@ -76300,7 +76301,7 @@
       <c r="AH837" s="4"/>
       <c r="AI837" s="4"/>
     </row>
-    <row r="838" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
         <v>1291</v>
       </c>
@@ -76361,7 +76362,7 @@
       <c r="AH838" s="4"/>
       <c r="AI838" s="4"/>
     </row>
-    <row r="839" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
         <v>1292</v>
       </c>
@@ -76422,7 +76423,7 @@
       <c r="AH839" s="4"/>
       <c r="AI839" s="4"/>
     </row>
-    <row r="840" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
         <v>1293</v>
       </c>
@@ -76483,7 +76484,7 @@
       <c r="AH840" s="4"/>
       <c r="AI840" s="4"/>
     </row>
-    <row r="841" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
         <v>1297</v>
       </c>
@@ -76544,7 +76545,7 @@
       <c r="AH841" s="4"/>
       <c r="AI841" s="4"/>
     </row>
-    <row r="842" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
         <v>1298</v>
       </c>
@@ -76605,7 +76606,7 @@
       <c r="AH842" s="4"/>
       <c r="AI842" s="4"/>
     </row>
-    <row r="843" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
         <v>1299</v>
       </c>
@@ -76666,7 +76667,7 @@
       <c r="AH843" s="4"/>
       <c r="AI843" s="4"/>
     </row>
-    <row r="844" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
         <v>1300</v>
       </c>
@@ -76727,7 +76728,7 @@
       <c r="AH844" s="4"/>
       <c r="AI844" s="4"/>
     </row>
-    <row r="845" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
         <v>1301</v>
       </c>
@@ -76788,7 +76789,7 @@
       <c r="AH845" s="4"/>
       <c r="AI845" s="4"/>
     </row>
-    <row r="846" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>1302</v>
       </c>
@@ -76849,7 +76850,7 @@
       <c r="AH846" s="4"/>
       <c r="AI846" s="4"/>
     </row>
-    <row r="847" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>1303</v>
       </c>
@@ -76910,7 +76911,7 @@
       <c r="AH847" s="4"/>
       <c r="AI847" s="4"/>
     </row>
-    <row r="848" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>1306</v>
       </c>
@@ -76971,7 +76972,7 @@
       <c r="AH848" s="4"/>
       <c r="AI848" s="4"/>
     </row>
-    <row r="849" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>1308</v>
       </c>
@@ -77032,7 +77033,7 @@
       <c r="AH849" s="4"/>
       <c r="AI849" s="4"/>
     </row>
-    <row r="850" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>1309</v>
       </c>
@@ -77093,7 +77094,7 @@
       <c r="AH850" s="4"/>
       <c r="AI850" s="4"/>
     </row>
-    <row r="851" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>1311</v>
       </c>
@@ -77154,7 +77155,7 @@
       <c r="AH851" s="4"/>
       <c r="AI851" s="4"/>
     </row>
-    <row r="852" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
         <v>1312</v>
       </c>
@@ -77215,7 +77216,7 @@
       <c r="AH852" s="4"/>
       <c r="AI852" s="4"/>
     </row>
-    <row r="853" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
         <v>1314</v>
       </c>
@@ -77276,7 +77277,7 @@
       <c r="AH853" s="4"/>
       <c r="AI853" s="4"/>
     </row>
-    <row r="854" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
         <v>1315</v>
       </c>
@@ -77337,7 +77338,7 @@
       <c r="AH854" s="4"/>
       <c r="AI854" s="4"/>
     </row>
-    <row r="855" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
         <v>1317</v>
       </c>
@@ -77398,7 +77399,7 @@
       <c r="AH855" s="4"/>
       <c r="AI855" s="4"/>
     </row>
-    <row r="856" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
         <v>1319</v>
       </c>
@@ -77459,7 +77460,7 @@
       <c r="AH856" s="4"/>
       <c r="AI856" s="4"/>
     </row>
-    <row r="857" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
         <v>1322</v>
       </c>
@@ -78069,7 +78070,7 @@
       <c r="AH866" s="4"/>
       <c r="AI866" s="4"/>
     </row>
-    <row r="867" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
         <v>1334</v>
       </c>
@@ -78130,7 +78131,7 @@
       <c r="AH867" s="4"/>
       <c r="AI867" s="4"/>
     </row>
-    <row r="868" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
         <v>1337</v>
       </c>
@@ -78191,7 +78192,7 @@
       <c r="AH868" s="4"/>
       <c r="AI868" s="4"/>
     </row>
-    <row r="869" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
         <v>1338</v>
       </c>
@@ -78252,7 +78253,7 @@
       <c r="AH869" s="4"/>
       <c r="AI869" s="4"/>
     </row>
-    <row r="870" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
         <v>1341</v>
       </c>
@@ -78313,7 +78314,7 @@
       <c r="AH870" s="4"/>
       <c r="AI870" s="4"/>
     </row>
-    <row r="871" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
         <v>1344</v>
       </c>
@@ -78374,7 +78375,7 @@
       <c r="AH871" s="4"/>
       <c r="AI871" s="4"/>
     </row>
-    <row r="872" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
         <v>1345</v>
       </c>
@@ -78435,7 +78436,7 @@
       <c r="AH872" s="4"/>
       <c r="AI872" s="4"/>
     </row>
-    <row r="873" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
         <v>1347</v>
       </c>
@@ -78496,7 +78497,7 @@
       <c r="AH873" s="4"/>
       <c r="AI873" s="4"/>
     </row>
-    <row r="874" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
         <v>1349</v>
       </c>
@@ -78557,7 +78558,7 @@
       <c r="AH874" s="4"/>
       <c r="AI874" s="4"/>
     </row>
-    <row r="875" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
         <v>1352</v>
       </c>
@@ -78618,7 +78619,7 @@
       <c r="AH875" s="4"/>
       <c r="AI875" s="4"/>
     </row>
-    <row r="876" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
         <v>1353</v>
       </c>
@@ -78679,7 +78680,7 @@
       <c r="AH876" s="4"/>
       <c r="AI876" s="4"/>
     </row>
-    <row r="877" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
         <v>1355</v>
       </c>
@@ -78740,7 +78741,7 @@
       <c r="AH877" s="4"/>
       <c r="AI877" s="4"/>
     </row>
-    <row r="878" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
         <v>1357</v>
       </c>
@@ -78801,7 +78802,7 @@
       <c r="AH878" s="4"/>
       <c r="AI878" s="4"/>
     </row>
-    <row r="879" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
         <v>1359</v>
       </c>
@@ -78862,7 +78863,7 @@
       <c r="AH879" s="4"/>
       <c r="AI879" s="4"/>
     </row>
-    <row r="880" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
         <v>1362</v>
       </c>
@@ -78923,7 +78924,7 @@
       <c r="AH880" s="4"/>
       <c r="AI880" s="4"/>
     </row>
-    <row r="881" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
         <v>1364</v>
       </c>
@@ -78984,7 +78985,7 @@
       <c r="AH881" s="4"/>
       <c r="AI881" s="4"/>
     </row>
-    <row r="882" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
         <v>1365</v>
       </c>
@@ -79045,7 +79046,7 @@
       <c r="AH882" s="4"/>
       <c r="AI882" s="4"/>
     </row>
-    <row r="883" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
         <v>1366</v>
       </c>
@@ -79106,7 +79107,7 @@
       <c r="AH883" s="4"/>
       <c r="AI883" s="4"/>
     </row>
-    <row r="884" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
         <v>1367</v>
       </c>
@@ -79167,7 +79168,7 @@
       <c r="AH884" s="4"/>
       <c r="AI884" s="4"/>
     </row>
-    <row r="885" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
         <v>1370</v>
       </c>
@@ -79228,7 +79229,7 @@
       <c r="AH885" s="4"/>
       <c r="AI885" s="4"/>
     </row>
-    <row r="886" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
         <v>1371</v>
       </c>
@@ -79289,7 +79290,7 @@
       <c r="AH886" s="4"/>
       <c r="AI886" s="4"/>
     </row>
-    <row r="887" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
         <v>1372</v>
       </c>
@@ -79411,7 +79412,7 @@
       <c r="AH888" s="4"/>
       <c r="AI888" s="4"/>
     </row>
-    <row r="889" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
         <v>1375</v>
       </c>
@@ -79472,7 +79473,7 @@
       <c r="AH889" s="4"/>
       <c r="AI889" s="4"/>
     </row>
-    <row r="890" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
         <v>1378</v>
       </c>
@@ -79533,7 +79534,7 @@
       <c r="AH890" s="4"/>
       <c r="AI890" s="4"/>
     </row>
-    <row r="891" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
         <v>1380</v>
       </c>
@@ -79594,7 +79595,7 @@
       <c r="AH891" s="4"/>
       <c r="AI891" s="4"/>
     </row>
-    <row r="892" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
         <v>1383</v>
       </c>
@@ -79655,7 +79656,7 @@
       <c r="AH892" s="4"/>
       <c r="AI892" s="4"/>
     </row>
-    <row r="893" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
         <v>1384</v>
       </c>
@@ -79777,7 +79778,7 @@
       <c r="AH894" s="4"/>
       <c r="AI894" s="4"/>
     </row>
-    <row r="895" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>1387</v>
       </c>
@@ -79838,7 +79839,7 @@
       <c r="AH895" s="4"/>
       <c r="AI895" s="4"/>
     </row>
-    <row r="896" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>1390</v>
       </c>
@@ -79899,7 +79900,7 @@
       <c r="AH896" s="4"/>
       <c r="AI896" s="4"/>
     </row>
-    <row r="897" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>1391</v>
       </c>
@@ -79960,7 +79961,7 @@
       <c r="AH897" s="4"/>
       <c r="AI897" s="4"/>
     </row>
-    <row r="898" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>1394</v>
       </c>
@@ -80021,7 +80022,7 @@
       <c r="AH898" s="4"/>
       <c r="AI898" s="4"/>
     </row>
-    <row r="899" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>1396</v>
       </c>
@@ -80082,7 +80083,7 @@
       <c r="AH899" s="4"/>
       <c r="AI899" s="4"/>
     </row>
-    <row r="900" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>1399</v>
       </c>
@@ -80143,7 +80144,7 @@
       <c r="AH900" s="4"/>
       <c r="AI900" s="4"/>
     </row>
-    <row r="901" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>1401</v>
       </c>
@@ -80204,7 +80205,7 @@
       <c r="AH901" s="4"/>
       <c r="AI901" s="4"/>
     </row>
-    <row r="902" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>1403</v>
       </c>
@@ -80265,7 +80266,7 @@
       <c r="AH902" s="4"/>
       <c r="AI902" s="4"/>
     </row>
-    <row r="903" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>1404</v>
       </c>
@@ -80326,7 +80327,7 @@
       <c r="AH903" s="4"/>
       <c r="AI903" s="4"/>
     </row>
-    <row r="904" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>1407</v>
       </c>
@@ -80387,7 +80388,7 @@
       <c r="AH904" s="4"/>
       <c r="AI904" s="4"/>
     </row>
-    <row r="905" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>1408</v>
       </c>
@@ -80448,7 +80449,7 @@
       <c r="AH905" s="4"/>
       <c r="AI905" s="4"/>
     </row>
-    <row r="906" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>1412</v>
       </c>
@@ -80509,7 +80510,7 @@
       <c r="AH906" s="4"/>
       <c r="AI906" s="4"/>
     </row>
-    <row r="907" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>1414</v>
       </c>
@@ -80570,7 +80571,7 @@
       <c r="AH907" s="4"/>
       <c r="AI907" s="4"/>
     </row>
-    <row r="908" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>1418</v>
       </c>
@@ -80631,7 +80632,7 @@
       <c r="AH908" s="4"/>
       <c r="AI908" s="4"/>
     </row>
-    <row r="909" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>1420</v>
       </c>
@@ -80692,7 +80693,7 @@
       <c r="AH909" s="4"/>
       <c r="AI909" s="4"/>
     </row>
-    <row r="910" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>1422</v>
       </c>
@@ -80753,7 +80754,7 @@
       <c r="AH910" s="4"/>
       <c r="AI910" s="4"/>
     </row>
-    <row r="911" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>1426</v>
       </c>
@@ -80814,7 +80815,7 @@
       <c r="AH911" s="4"/>
       <c r="AI911" s="4"/>
     </row>
-    <row r="912" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>1428</v>
       </c>
@@ -80875,7 +80876,7 @@
       <c r="AH912" s="4"/>
       <c r="AI912" s="4"/>
     </row>
-    <row r="913" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>1430</v>
       </c>
@@ -80936,7 +80937,7 @@
       <c r="AH913" s="4"/>
       <c r="AI913" s="4"/>
     </row>
-    <row r="914" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>1432</v>
       </c>
@@ -80997,7 +80998,7 @@
       <c r="AH914" s="4"/>
       <c r="AI914" s="4"/>
     </row>
-    <row r="915" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>1435</v>
       </c>
@@ -81058,7 +81059,7 @@
       <c r="AH915" s="4"/>
       <c r="AI915" s="4"/>
     </row>
-    <row r="916" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
         <v>1436</v>
       </c>
@@ -81119,7 +81120,7 @@
       <c r="AH916" s="4"/>
       <c r="AI916" s="4"/>
     </row>
-    <row r="917" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>1437</v>
       </c>
@@ -81180,7 +81181,7 @@
       <c r="AH917" s="4"/>
       <c r="AI917" s="4"/>
     </row>
-    <row r="918" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
         <v>1438</v>
       </c>
@@ -81241,7 +81242,7 @@
       <c r="AH918" s="4"/>
       <c r="AI918" s="4"/>
     </row>
-    <row r="919" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>1441</v>
       </c>
@@ -81302,7 +81303,7 @@
       <c r="AH919" s="4"/>
       <c r="AI919" s="4"/>
     </row>
-    <row r="920" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
         <v>1442</v>
       </c>
@@ -81363,7 +81364,7 @@
       <c r="AH920" s="4"/>
       <c r="AI920" s="4"/>
     </row>
-    <row r="921" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>1445</v>
       </c>
@@ -81424,7 +81425,7 @@
       <c r="AH921" s="4"/>
       <c r="AI921" s="4"/>
     </row>
-    <row r="922" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
         <v>1446</v>
       </c>
@@ -81485,7 +81486,7 @@
       <c r="AH922" s="4"/>
       <c r="AI922" s="4"/>
     </row>
-    <row r="923" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
         <v>1449</v>
       </c>
@@ -81546,7 +81547,7 @@
       <c r="AH923" s="4"/>
       <c r="AI923" s="4"/>
     </row>
-    <row r="924" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
         <v>1450</v>
       </c>
@@ -81607,7 +81608,7 @@
       <c r="AH924" s="4"/>
       <c r="AI924" s="4"/>
     </row>
-    <row r="925" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
         <v>1542</v>
       </c>
@@ -81666,7 +81667,7 @@
       <c r="AH925" s="4"/>
       <c r="AI925" s="4"/>
     </row>
-    <row r="926" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
         <v>1543</v>
       </c>
@@ -81725,7 +81726,7 @@
       <c r="AH926" s="4"/>
       <c r="AI926" s="4"/>
     </row>
-    <row r="927" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
         <v>1544</v>
       </c>
@@ -81784,7 +81785,7 @@
       <c r="AH927" s="4"/>
       <c r="AI927" s="4"/>
     </row>
-    <row r="928" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
         <v>1545</v>
       </c>
@@ -81843,7 +81844,7 @@
       <c r="AH928" s="4"/>
       <c r="AI928" s="4"/>
     </row>
-    <row r="929" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
         <v>1546</v>
       </c>
@@ -81902,7 +81903,7 @@
       <c r="AH929" s="4"/>
       <c r="AI929" s="4"/>
     </row>
-    <row r="930" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
         <v>1547</v>
       </c>
@@ -81961,7 +81962,7 @@
       <c r="AH930" s="4"/>
       <c r="AI930" s="4"/>
     </row>
-    <row r="931" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
         <v>1548</v>
       </c>
@@ -82020,7 +82021,7 @@
       <c r="AH931" s="4"/>
       <c r="AI931" s="4"/>
     </row>
-    <row r="932" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
         <v>1549</v>
       </c>
@@ -82079,7 +82080,7 @@
       <c r="AH932" s="4"/>
       <c r="AI932" s="4"/>
     </row>
-    <row r="933" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
         <v>1550</v>
       </c>
@@ -82138,7 +82139,7 @@
       <c r="AH933" s="4"/>
       <c r="AI933" s="4"/>
     </row>
-    <row r="934" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
         <v>1551</v>
       </c>
@@ -82197,7 +82198,7 @@
       <c r="AH934" s="4"/>
       <c r="AI934" s="4"/>
     </row>
-    <row r="935" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
         <v>1552</v>
       </c>
@@ -82256,7 +82257,7 @@
       <c r="AH935" s="4"/>
       <c r="AI935" s="4"/>
     </row>
-    <row r="936" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
         <v>1553</v>
       </c>
@@ -82315,7 +82316,7 @@
       <c r="AH936" s="4"/>
       <c r="AI936" s="4"/>
     </row>
-    <row r="937" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
         <v>1554</v>
       </c>
@@ -82374,7 +82375,7 @@
       <c r="AH937" s="4"/>
       <c r="AI937" s="4"/>
     </row>
-    <row r="938" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
         <v>1555</v>
       </c>
@@ -82433,7 +82434,7 @@
       <c r="AH938" s="4"/>
       <c r="AI938" s="4"/>
     </row>
-    <row r="939" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
         <v>1556</v>
       </c>
@@ -82492,7 +82493,7 @@
       <c r="AH939" s="4"/>
       <c r="AI939" s="4"/>
     </row>
-    <row r="940" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
         <v>1557</v>
       </c>
@@ -82551,7 +82552,7 @@
       <c r="AH940" s="4"/>
       <c r="AI940" s="4"/>
     </row>
-    <row r="941" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
         <v>1558</v>
       </c>
@@ -82610,7 +82611,7 @@
       <c r="AH941" s="4"/>
       <c r="AI941" s="4"/>
     </row>
-    <row r="942" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
         <v>1559</v>
       </c>
@@ -82669,7 +82670,7 @@
       <c r="AH942" s="4"/>
       <c r="AI942" s="4"/>
     </row>
-    <row r="943" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
         <v>1560</v>
       </c>
@@ -82728,7 +82729,7 @@
       <c r="AH943" s="4"/>
       <c r="AI943" s="4"/>
     </row>
-    <row r="944" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
         <v>1561</v>
       </c>
@@ -82787,7 +82788,7 @@
       <c r="AH944" s="4"/>
       <c r="AI944" s="4"/>
     </row>
-    <row r="945" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
         <v>1562</v>
       </c>
@@ -82846,7 +82847,7 @@
       <c r="AH945" s="4"/>
       <c r="AI945" s="4"/>
     </row>
-    <row r="946" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
         <v>1563</v>
       </c>
@@ -82905,7 +82906,7 @@
       <c r="AH946" s="4"/>
       <c r="AI946" s="4"/>
     </row>
-    <row r="947" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
         <v>1564</v>
       </c>
@@ -82964,7 +82965,7 @@
       <c r="AH947" s="4"/>
       <c r="AI947" s="4"/>
     </row>
-    <row r="948" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
         <v>1565</v>
       </c>
@@ -83023,7 +83024,7 @@
       <c r="AH948" s="4"/>
       <c r="AI948" s="4"/>
     </row>
-    <row r="949" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
         <v>1566</v>
       </c>
@@ -83082,7 +83083,7 @@
       <c r="AH949" s="4"/>
       <c r="AI949" s="4"/>
     </row>
-    <row r="950" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
         <v>1567</v>
       </c>
@@ -83141,7 +83142,7 @@
       <c r="AH950" s="4"/>
       <c r="AI950" s="4"/>
     </row>
-    <row r="951" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
         <v>1568</v>
       </c>
@@ -83200,7 +83201,7 @@
       <c r="AH951" s="4"/>
       <c r="AI951" s="4"/>
     </row>
-    <row r="952" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
         <v>1569</v>
       </c>
@@ -83259,7 +83260,7 @@
       <c r="AH952" s="4"/>
       <c r="AI952" s="4"/>
     </row>
-    <row r="953" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
         <v>1570</v>
       </c>
@@ -83318,7 +83319,7 @@
       <c r="AH953" s="4"/>
       <c r="AI953" s="4"/>
     </row>
-    <row r="954" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
         <v>1571</v>
       </c>
@@ -83377,7 +83378,7 @@
       <c r="AH954" s="4"/>
       <c r="AI954" s="4"/>
     </row>
-    <row r="955" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
         <v>1572</v>
       </c>
@@ -83436,7 +83437,7 @@
       <c r="AH955" s="4"/>
       <c r="AI955" s="4"/>
     </row>
-    <row r="956" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
         <v>1573</v>
       </c>
@@ -83495,7 +83496,7 @@
       <c r="AH956" s="4"/>
       <c r="AI956" s="4"/>
     </row>
-    <row r="957" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
         <v>1574</v>
       </c>
@@ -83554,7 +83555,7 @@
       <c r="AH957" s="4"/>
       <c r="AI957" s="4"/>
     </row>
-    <row r="958" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
         <v>1575</v>
       </c>
@@ -83613,7 +83614,7 @@
       <c r="AH958" s="4"/>
       <c r="AI958" s="4"/>
     </row>
-    <row r="959" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
         <v>1576</v>
       </c>
@@ -83672,7 +83673,7 @@
       <c r="AH959" s="4"/>
       <c r="AI959" s="4"/>
     </row>
-    <row r="960" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
         <v>1577</v>
       </c>
@@ -83731,7 +83732,7 @@
       <c r="AH960" s="4"/>
       <c r="AI960" s="4"/>
     </row>
-    <row r="961" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
         <v>1578</v>
       </c>
@@ -83790,7 +83791,7 @@
       <c r="AH961" s="4"/>
       <c r="AI961" s="4"/>
     </row>
-    <row r="962" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
         <v>1579</v>
       </c>
@@ -83849,7 +83850,7 @@
       <c r="AH962" s="4"/>
       <c r="AI962" s="4"/>
     </row>
-    <row r="963" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
         <v>1580</v>
       </c>
@@ -83908,7 +83909,7 @@
       <c r="AH963" s="4"/>
       <c r="AI963" s="4"/>
     </row>
-    <row r="964" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
         <v>1581</v>
       </c>
@@ -83967,7 +83968,7 @@
       <c r="AH964" s="4"/>
       <c r="AI964" s="4"/>
     </row>
-    <row r="965" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
         <v>1582</v>
       </c>
@@ -84026,7 +84027,7 @@
       <c r="AH965" s="4"/>
       <c r="AI965" s="4"/>
     </row>
-    <row r="966" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
         <v>1583</v>
       </c>
@@ -84085,7 +84086,7 @@
       <c r="AH966" s="4"/>
       <c r="AI966" s="4"/>
     </row>
-    <row r="967" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
         <v>1584</v>
       </c>
@@ -84144,7 +84145,7 @@
       <c r="AH967" s="4"/>
       <c r="AI967" s="4"/>
     </row>
-    <row r="968" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
         <v>1585</v>
       </c>
@@ -84203,7 +84204,7 @@
       <c r="AH968" s="4"/>
       <c r="AI968" s="4"/>
     </row>
-    <row r="969" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
         <v>1586</v>
       </c>
@@ -84262,7 +84263,7 @@
       <c r="AH969" s="4"/>
       <c r="AI969" s="4"/>
     </row>
-    <row r="970" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
         <v>1587</v>
       </c>
@@ -84321,7 +84322,7 @@
       <c r="AH970" s="4"/>
       <c r="AI970" s="4"/>
     </row>
-    <row r="971" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
         <v>1588</v>
       </c>
@@ -84380,7 +84381,7 @@
       <c r="AH971" s="4"/>
       <c r="AI971" s="4"/>
     </row>
-    <row r="972" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
         <v>1589</v>
       </c>
@@ -84439,7 +84440,7 @@
       <c r="AH972" s="4"/>
       <c r="AI972" s="4"/>
     </row>
-    <row r="973" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
         <v>1590</v>
       </c>
@@ -84496,7 +84497,7 @@
       <c r="AH973" s="4"/>
       <c r="AI973" s="4"/>
     </row>
-    <row r="974" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
         <v>1591</v>
       </c>
@@ -84553,7 +84554,7 @@
       <c r="AH974" s="4"/>
       <c r="AI974" s="4"/>
     </row>
-    <row r="975" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
         <v>1592</v>
       </c>
@@ -84610,7 +84611,7 @@
       <c r="AH975" s="4"/>
       <c r="AI975" s="4"/>
     </row>
-    <row r="976" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
         <v>1593</v>
       </c>
@@ -84667,7 +84668,7 @@
       <c r="AH976" s="4"/>
       <c r="AI976" s="4"/>
     </row>
-    <row r="977" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
         <v>1595</v>
       </c>
@@ -84724,7 +84725,7 @@
       <c r="AH977" s="4"/>
       <c r="AI977" s="4"/>
     </row>
-    <row r="978" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
         <v>1596</v>
       </c>
@@ -84781,7 +84782,7 @@
       <c r="AH978" s="4"/>
       <c r="AI978" s="4"/>
     </row>
-    <row r="979" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
         <v>1597</v>
       </c>
@@ -84838,7 +84839,7 @@
       <c r="AH979" s="4"/>
       <c r="AI979" s="4"/>
     </row>
-    <row r="980" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
         <v>1598</v>
       </c>
@@ -84895,7 +84896,7 @@
       <c r="AH980" s="4"/>
       <c r="AI980" s="4"/>
     </row>
-    <row r="981" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
         <v>1599</v>
       </c>
@@ -84952,7 +84953,7 @@
       <c r="AH981" s="4"/>
       <c r="AI981" s="4"/>
     </row>
-    <row r="982" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
         <v>1600</v>
       </c>
@@ -85009,7 +85010,7 @@
       <c r="AH982" s="4"/>
       <c r="AI982" s="4"/>
     </row>
-    <row r="983" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
         <v>1601</v>
       </c>
@@ -85066,7 +85067,7 @@
       <c r="AH983" s="4"/>
       <c r="AI983" s="4"/>
     </row>
-    <row r="984" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
         <v>1602</v>
       </c>
@@ -85123,7 +85124,7 @@
       <c r="AH984" s="4"/>
       <c r="AI984" s="4"/>
     </row>
-    <row r="985" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
         <v>1604</v>
       </c>
@@ -85180,7 +85181,7 @@
       <c r="AH985" s="4"/>
       <c r="AI985" s="4"/>
     </row>
-    <row r="986" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
         <v>1605</v>
       </c>
@@ -85237,7 +85238,7 @@
       <c r="AH986" s="4"/>
       <c r="AI986" s="4"/>
     </row>
-    <row r="987" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
         <v>1606</v>
       </c>
@@ -85294,7 +85295,7 @@
       <c r="AH987" s="4"/>
       <c r="AI987" s="4"/>
     </row>
-    <row r="988" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
         <v>1607</v>
       </c>
@@ -85351,7 +85352,7 @@
       <c r="AH988" s="4"/>
       <c r="AI988" s="4"/>
     </row>
-    <row r="989" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
         <v>1608</v>
       </c>
@@ -85408,7 +85409,7 @@
       <c r="AH989" s="4"/>
       <c r="AI989" s="4"/>
     </row>
-    <row r="990" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
         <v>1609</v>
       </c>
@@ -85465,7 +85466,7 @@
       <c r="AH990" s="4"/>
       <c r="AI990" s="4"/>
     </row>
-    <row r="991" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
         <v>1610</v>
       </c>
@@ -85522,7 +85523,7 @@
       <c r="AH991" s="4"/>
       <c r="AI991" s="4"/>
     </row>
-    <row r="992" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
         <v>1612</v>
       </c>
@@ -85579,7 +85580,7 @@
       <c r="AH992" s="4"/>
       <c r="AI992" s="4"/>
     </row>
-    <row r="993" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
         <v>1613</v>
       </c>
@@ -85636,7 +85637,7 @@
       <c r="AH993" s="4"/>
       <c r="AI993" s="4"/>
     </row>
-    <row r="994" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
         <v>1614</v>
       </c>
@@ -85693,7 +85694,7 @@
       <c r="AH994" s="4"/>
       <c r="AI994" s="4"/>
     </row>
-    <row r="995" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
         <v>1616</v>
       </c>
@@ -85750,7 +85751,7 @@
       <c r="AH995" s="4"/>
       <c r="AI995" s="4"/>
     </row>
-    <row r="996" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
         <v>1618</v>
       </c>
@@ -85807,7 +85808,7 @@
       <c r="AH996" s="4"/>
       <c r="AI996" s="4"/>
     </row>
-    <row r="997" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
         <v>1620</v>
       </c>
@@ -85866,7 +85867,7 @@
       <c r="AH997" s="4"/>
       <c r="AI997" s="4"/>
     </row>
-    <row r="998" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
         <v>1621</v>
       </c>
@@ -85925,7 +85926,7 @@
       <c r="AH998" s="4"/>
       <c r="AI998" s="4"/>
     </row>
-    <row r="999" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
         <v>1622</v>
       </c>
@@ -85982,7 +85983,7 @@
       <c r="AH999" s="4"/>
       <c r="AI999" s="4"/>
     </row>
-    <row r="1000" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
         <v>1623</v>
       </c>
@@ -86039,7 +86040,7 @@
       <c r="AH1000" s="4"/>
       <c r="AI1000" s="4"/>
     </row>
-    <row r="1001" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
         <v>1626</v>
       </c>
@@ -86096,7 +86097,7 @@
       <c r="AH1001" s="4"/>
       <c r="AI1001" s="4"/>
     </row>
-    <row r="1002" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
         <v>1630</v>
       </c>
@@ -86153,7 +86154,7 @@
       <c r="AH1002" s="4"/>
       <c r="AI1002" s="4"/>
     </row>
-    <row r="1003" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
         <v>1631</v>
       </c>
@@ -86210,7 +86211,7 @@
       <c r="AH1003" s="4"/>
       <c r="AI1003" s="4"/>
     </row>
-    <row r="1004" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
         <v>1632</v>
       </c>
@@ -86267,7 +86268,7 @@
       <c r="AH1004" s="4"/>
       <c r="AI1004" s="4"/>
     </row>
-    <row r="1005" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
         <v>1635</v>
       </c>
@@ -86324,7 +86325,7 @@
       <c r="AH1005" s="4"/>
       <c r="AI1005" s="4"/>
     </row>
-    <row r="1006" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
         <v>1636</v>
       </c>
@@ -86381,7 +86382,7 @@
       <c r="AH1006" s="4"/>
       <c r="AI1006" s="4"/>
     </row>
-    <row r="1007" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
         <v>1637</v>
       </c>
@@ -86438,7 +86439,7 @@
       <c r="AH1007" s="4"/>
       <c r="AI1007" s="4"/>
     </row>
-    <row r="1008" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
         <v>1640</v>
       </c>
@@ -86495,7 +86496,7 @@
       <c r="AH1008" s="4"/>
       <c r="AI1008" s="4"/>
     </row>
-    <row r="1009" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
         <v>1641</v>
       </c>
@@ -86552,7 +86553,7 @@
       <c r="AH1009" s="4"/>
       <c r="AI1009" s="4"/>
     </row>
-    <row r="1010" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
         <v>1644</v>
       </c>
@@ -86609,7 +86610,7 @@
       <c r="AH1010" s="4"/>
       <c r="AI1010" s="4"/>
     </row>
-    <row r="1011" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="2" t="s">
         <v>1645</v>
       </c>
@@ -86666,7 +86667,7 @@
       <c r="AH1011" s="4"/>
       <c r="AI1011" s="4"/>
     </row>
-    <row r="1012" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="2" t="s">
         <v>1648</v>
       </c>
@@ -86723,7 +86724,7 @@
       <c r="AH1012" s="4"/>
       <c r="AI1012" s="4"/>
     </row>
-    <row r="1013" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="2" t="s">
         <v>1652</v>
       </c>
@@ -86780,7 +86781,7 @@
       <c r="AH1013" s="4"/>
       <c r="AI1013" s="4"/>
     </row>
-    <row r="1014" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
         <v>1653</v>
       </c>
@@ -86837,7 +86838,7 @@
       <c r="AH1014" s="4"/>
       <c r="AI1014" s="4"/>
     </row>
-    <row r="1015" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="2" t="s">
         <v>1655</v>
       </c>
@@ -86896,7 +86897,7 @@
       <c r="AH1015" s="4"/>
       <c r="AI1015" s="4"/>
     </row>
-    <row r="1016" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="2" t="s">
         <v>1656</v>
       </c>
@@ -86955,7 +86956,7 @@
       <c r="AH1016" s="4"/>
       <c r="AI1016" s="4"/>
     </row>
-    <row r="1017" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="2" t="s">
         <v>1657</v>
       </c>
@@ -87012,7 +87013,7 @@
       <c r="AH1017" s="4"/>
       <c r="AI1017" s="4"/>
     </row>
-    <row r="1018" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
         <v>1660</v>
       </c>
@@ -87069,7 +87070,7 @@
       <c r="AH1018" s="4"/>
       <c r="AI1018" s="4"/>
     </row>
-    <row r="1019" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="2" t="s">
         <v>1661</v>
       </c>
@@ -87126,7 +87127,7 @@
       <c r="AH1019" s="4"/>
       <c r="AI1019" s="4"/>
     </row>
-    <row r="1020" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
         <v>1662</v>
       </c>
@@ -87183,7 +87184,7 @@
       <c r="AH1020" s="4"/>
       <c r="AI1020" s="4"/>
     </row>
-    <row r="1021" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
         <v>1663</v>
       </c>
@@ -87240,7 +87241,7 @@
       <c r="AH1021" s="4"/>
       <c r="AI1021" s="4"/>
     </row>
-    <row r="1022" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
         <v>1664</v>
       </c>
@@ -87297,7 +87298,7 @@
       <c r="AH1022" s="4"/>
       <c r="AI1022" s="4"/>
     </row>
-    <row r="1023" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="2" t="s">
         <v>1665</v>
       </c>
@@ -87354,7 +87355,7 @@
       <c r="AH1023" s="4"/>
       <c r="AI1023" s="4"/>
     </row>
-    <row r="1024" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
         <v>1667</v>
       </c>
@@ -87411,7 +87412,7 @@
       <c r="AH1024" s="4"/>
       <c r="AI1024" s="4"/>
     </row>
-    <row r="1025" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="2" t="s">
         <v>1669</v>
       </c>
@@ -87468,7 +87469,7 @@
       <c r="AH1025" s="4"/>
       <c r="AI1025" s="4"/>
     </row>
-    <row r="1026" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
         <v>1672</v>
       </c>
@@ -87525,7 +87526,7 @@
       <c r="AH1026" s="4"/>
       <c r="AI1026" s="4"/>
     </row>
-    <row r="1027" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="2" t="s">
         <v>1673</v>
       </c>
@@ -87582,7 +87583,7 @@
       <c r="AH1027" s="4"/>
       <c r="AI1027" s="4"/>
     </row>
-    <row r="1028" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="2" t="s">
         <v>1675</v>
       </c>
@@ -87639,7 +87640,7 @@
       <c r="AH1028" s="4"/>
       <c r="AI1028" s="4"/>
     </row>
-    <row r="1029" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="2" t="s">
         <v>1677</v>
       </c>
@@ -87696,7 +87697,7 @@
       <c r="AH1029" s="4"/>
       <c r="AI1029" s="4"/>
     </row>
-    <row r="1030" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="9" t="s">
         <v>1686</v>
       </c>
@@ -87743,7 +87744,7 @@
       <c r="AH1030" s="4"/>
       <c r="AI1030" s="4"/>
     </row>
-    <row r="1031" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="9" t="s">
         <v>1687</v>
       </c>
@@ -87790,7 +87791,7 @@
       <c r="AH1031" s="4"/>
       <c r="AI1031" s="4"/>
     </row>
-    <row r="1032" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="9" t="s">
         <v>1688</v>
       </c>
@@ -87837,7 +87838,7 @@
       <c r="AH1032" s="4"/>
       <c r="AI1032" s="4"/>
     </row>
-    <row r="1033" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="9" t="s">
         <v>1689</v>
       </c>
@@ -87884,7 +87885,7 @@
       <c r="AH1033" s="4"/>
       <c r="AI1033" s="4"/>
     </row>
-    <row r="1034" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="9" t="s">
         <v>1690</v>
       </c>
@@ -87931,7 +87932,7 @@
       <c r="AH1034" s="4"/>
       <c r="AI1034" s="4"/>
     </row>
-    <row r="1035" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="9" t="s">
         <v>1691</v>
       </c>
@@ -87978,7 +87979,7 @@
       <c r="AH1035" s="4"/>
       <c r="AI1035" s="4"/>
     </row>
-    <row r="1036" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="9" t="s">
         <v>1692</v>
       </c>
@@ -88025,7 +88026,7 @@
       <c r="AH1036" s="4"/>
       <c r="AI1036" s="4"/>
     </row>
-    <row r="1037" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="9" t="s">
         <v>1693</v>
       </c>
@@ -88072,7 +88073,7 @@
       <c r="AH1037" s="4"/>
       <c r="AI1037" s="4"/>
     </row>
-    <row r="1038" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="9" t="s">
         <v>1694</v>
       </c>
@@ -88119,7 +88120,7 @@
       <c r="AH1038" s="4"/>
       <c r="AI1038" s="4"/>
     </row>
-    <row r="1039" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="9" t="s">
         <v>1695</v>
       </c>
@@ -88166,7 +88167,7 @@
       <c r="AH1039" s="4"/>
       <c r="AI1039" s="4"/>
     </row>
-    <row r="1040" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1040" s="9" t="s">
         <v>1696</v>
       </c>
@@ -88213,7 +88214,7 @@
       <c r="AH1040" s="4"/>
       <c r="AI1040" s="4"/>
     </row>
-    <row r="1041" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="9" t="s">
         <v>1697</v>
       </c>
@@ -88260,7 +88261,7 @@
       <c r="AH1041" s="4"/>
       <c r="AI1041" s="4"/>
     </row>
-    <row r="1042" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="9" t="s">
         <v>1698</v>
       </c>
@@ -88307,7 +88308,7 @@
       <c r="AH1042" s="4"/>
       <c r="AI1042" s="4"/>
     </row>
-    <row r="1043" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="2" t="s">
         <v>1702</v>
       </c>
@@ -88368,7 +88369,7 @@
       <c r="AH1043" s="4"/>
       <c r="AI1043" s="4"/>
     </row>
-    <row r="1044" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1044" s="2" t="s">
         <v>1699</v>
       </c>
@@ -88429,7 +88430,7 @@
       <c r="AH1044" s="4"/>
       <c r="AI1044" s="4"/>
     </row>
-    <row r="1045" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="2" t="s">
         <v>1700</v>
       </c>
@@ -88490,7 +88491,7 @@
       <c r="AH1045" s="4"/>
       <c r="AI1045" s="4"/>
     </row>
-    <row r="1046" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
         <v>1701</v>
       </c>
@@ -88551,7 +88552,7 @@
       <c r="AH1046" s="4"/>
       <c r="AI1046" s="4"/>
     </row>
-    <row r="1047" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="2" t="s">
         <v>1703</v>
       </c>
@@ -88612,7 +88613,7 @@
       <c r="AH1047" s="4"/>
       <c r="AI1047" s="4"/>
     </row>
-    <row r="1048" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
         <v>1705</v>
       </c>
@@ -88673,7 +88674,7 @@
       <c r="AH1048" s="4"/>
       <c r="AI1048" s="4"/>
     </row>
-    <row r="1049" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="2" t="s">
         <v>1706</v>
       </c>
@@ -88734,7 +88735,7 @@
       <c r="AH1049" s="4"/>
       <c r="AI1049" s="4"/>
     </row>
-    <row r="1050" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="2" t="s">
         <v>1707</v>
       </c>
@@ -88795,7 +88796,7 @@
       <c r="AH1050" s="4"/>
       <c r="AI1050" s="4"/>
     </row>
-    <row r="1051" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1051" s="2" t="s">
         <v>1708</v>
       </c>
@@ -88857,7 +88858,17 @@
       <c r="AI1051" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1051" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R1051" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="CORRE VENTO 3"/>
+        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL F"/>
+        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL M"/>
+        <filter val="JAQUETA QUEBRA-VENTO ESSENTIAL F"/>
+        <filter val="JAQUETA QUEBRA-VENTO ESSENTIAL M"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrativo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A110CF-08B5-46E6-A47B-9F2DE84C87C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAAF728-292C-4068-938E-309795CD2E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="corre" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1048</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1055</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13214" uniqueCount="1711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13284" uniqueCount="1720">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -5170,6 +5170,33 @@
   </si>
   <si>
     <t>OIWB271802_NAVAL</t>
+  </si>
+  <si>
+    <t>43206446_BRANCO</t>
+  </si>
+  <si>
+    <t>CORRE MAX 2</t>
+  </si>
+  <si>
+    <t>CINZA</t>
+  </si>
+  <si>
+    <t>43304478_CINZA</t>
+  </si>
+  <si>
+    <t>43304478_PRETO</t>
+  </si>
+  <si>
+    <t>43304478_VRD_CL</t>
+  </si>
+  <si>
+    <t>43304478_LILAS</t>
+  </si>
+  <si>
+    <t>43304478_ARENIT</t>
+  </si>
+  <si>
+    <t>43304478_MUSGO</t>
   </si>
 </sst>
 </file>
@@ -5631,7 +5658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1048"/>
+  <dimension ref="A1:AI1055"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -76516,7 +76543,7 @@
         <v>40</v>
       </c>
       <c r="L845" s="4" t="s">
-        <v>487</v>
+        <v>42</v>
       </c>
       <c r="M845" s="4"/>
       <c r="N845" s="4"/>
@@ -76544,7 +76571,7 @@
     </row>
     <row r="846" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
-        <v>1301</v>
+        <v>1714</v>
       </c>
       <c r="B846" s="2" t="s">
         <v>35</v>
@@ -76553,31 +76580,31 @@
         <v>1300</v>
       </c>
       <c r="D846" s="4">
-        <v>43758365</v>
+        <v>43304478</v>
       </c>
       <c r="E846" s="5" t="s">
-        <v>639</v>
+        <v>1712</v>
       </c>
       <c r="F846" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G846" s="4" t="s">
-        <v>531</v>
+        <v>1713</v>
       </c>
       <c r="H846" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I846" s="4">
-        <v>549.99</v>
+        <v>599.99</v>
       </c>
       <c r="J846" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K846" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L846" s="4" t="s">
-        <v>487</v>
+        <v>42</v>
       </c>
       <c r="M846" s="4"/>
       <c r="N846" s="4"/>
@@ -76605,7 +76632,7 @@
     </row>
     <row r="847" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
-        <v>1302</v>
+        <v>1715</v>
       </c>
       <c r="B847" s="2" t="s">
         <v>35</v>
@@ -76614,31 +76641,31 @@
         <v>1300</v>
       </c>
       <c r="D847" s="4">
-        <v>43758365</v>
+        <v>43304478</v>
       </c>
       <c r="E847" s="5" t="s">
-        <v>639</v>
+        <v>1712</v>
       </c>
       <c r="F847" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G847" s="4" t="s">
-        <v>1303</v>
+        <v>69</v>
       </c>
       <c r="H847" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I847" s="4">
-        <v>549.99</v>
+        <v>599.99</v>
       </c>
       <c r="J847" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K847" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L847" s="4" t="s">
-        <v>487</v>
+        <v>42</v>
       </c>
       <c r="M847" s="4"/>
       <c r="N847" s="4"/>
@@ -76666,7 +76693,7 @@
     </row>
     <row r="848" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
-        <v>1304</v>
+        <v>1716</v>
       </c>
       <c r="B848" s="2" t="s">
         <v>35</v>
@@ -76675,31 +76702,31 @@
         <v>1300</v>
       </c>
       <c r="D848" s="4">
-        <v>43758365</v>
+        <v>43304478</v>
       </c>
       <c r="E848" s="5" t="s">
-        <v>639</v>
+        <v>1712</v>
       </c>
       <c r="F848" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G848" s="4" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="H848" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I848" s="4">
-        <v>549.99</v>
+        <v>599.99</v>
       </c>
       <c r="J848" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K848" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L848" s="4" t="s">
-        <v>487</v>
+        <v>42</v>
       </c>
       <c r="M848" s="4"/>
       <c r="N848" s="4"/>
@@ -76727,7 +76754,7 @@
     </row>
     <row r="849" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
-        <v>1305</v>
+        <v>1717</v>
       </c>
       <c r="B849" s="2" t="s">
         <v>35</v>
@@ -76736,31 +76763,31 @@
         <v>1300</v>
       </c>
       <c r="D849" s="4">
-        <v>43245330</v>
+        <v>43304478</v>
       </c>
       <c r="E849" s="5" t="s">
-        <v>644</v>
+        <v>1712</v>
       </c>
       <c r="F849" s="4" t="s">
-        <v>645</v>
+        <v>43</v>
       </c>
       <c r="G849" s="4" t="s">
-        <v>1306</v>
+        <v>160</v>
       </c>
       <c r="H849" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I849" s="4">
-        <v>799.99</v>
+        <v>599.99</v>
       </c>
       <c r="J849" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K849" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L849" s="4" t="s">
-        <v>487</v>
+        <v>42</v>
       </c>
       <c r="M849" s="4"/>
       <c r="N849" s="4"/>
@@ -76788,7 +76815,7 @@
     </row>
     <row r="850" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
-        <v>1307</v>
+        <v>1718</v>
       </c>
       <c r="B850" s="2" t="s">
         <v>35</v>
@@ -76797,31 +76824,31 @@
         <v>1300</v>
       </c>
       <c r="D850" s="4">
-        <v>43790399</v>
+        <v>43304478</v>
       </c>
       <c r="E850" s="5" t="s">
-        <v>648</v>
+        <v>1712</v>
       </c>
       <c r="F850" s="4" t="s">
-        <v>636</v>
+        <v>43</v>
       </c>
       <c r="G850" s="4" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="H850" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I850" s="4">
-        <v>699.99</v>
+        <v>599.99</v>
       </c>
       <c r="J850" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K850" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L850" s="4" t="s">
-        <v>487</v>
+        <v>42</v>
       </c>
       <c r="M850" s="4"/>
       <c r="N850" s="4"/>
@@ -76849,7 +76876,7 @@
     </row>
     <row r="851" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
-        <v>1308</v>
+        <v>1719</v>
       </c>
       <c r="B851" s="2" t="s">
         <v>35</v>
@@ -76858,16 +76885,16 @@
         <v>1300</v>
       </c>
       <c r="D851" s="4">
-        <v>43206446</v>
+        <v>43304478</v>
       </c>
       <c r="E851" s="5" t="s">
-        <v>1309</v>
+        <v>1712</v>
       </c>
       <c r="F851" s="4" t="s">
-        <v>645</v>
+        <v>43</v>
       </c>
       <c r="G851" s="4" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="H851" s="4" t="s">
         <v>44</v>
@@ -76876,13 +76903,13 @@
         <v>599.99</v>
       </c>
       <c r="J851" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K851" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L851" s="4" t="s">
-        <v>487</v>
+        <v>42</v>
       </c>
       <c r="M851" s="4"/>
       <c r="N851" s="4"/>
@@ -76910,7 +76937,7 @@
     </row>
     <row r="852" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
-        <v>1310</v>
+        <v>1301</v>
       </c>
       <c r="B852" s="2" t="s">
         <v>35</v>
@@ -76919,22 +76946,22 @@
         <v>1300</v>
       </c>
       <c r="D852" s="4">
-        <v>43206446</v>
+        <v>43758365</v>
       </c>
       <c r="E852" s="5" t="s">
-        <v>1309</v>
+        <v>639</v>
       </c>
       <c r="F852" s="4" t="s">
-        <v>645</v>
+        <v>43</v>
       </c>
       <c r="G852" s="4" t="s">
-        <v>1311</v>
+        <v>531</v>
       </c>
       <c r="H852" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I852" s="4">
-        <v>599.99</v>
+        <v>549.99</v>
       </c>
       <c r="J852" s="4" t="s">
         <v>40</v>
@@ -76971,7 +76998,7 @@
     </row>
     <row r="853" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
-        <v>1312</v>
+        <v>1302</v>
       </c>
       <c r="B853" s="2" t="s">
         <v>35</v>
@@ -76980,16 +77007,16 @@
         <v>1300</v>
       </c>
       <c r="D853" s="4">
-        <v>43340469</v>
+        <v>43758365</v>
       </c>
       <c r="E853" s="5" t="s">
-        <v>1313</v>
+        <v>639</v>
       </c>
       <c r="F853" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G853" s="4" t="s">
-        <v>1314</v>
+        <v>1303</v>
       </c>
       <c r="H853" s="4" t="s">
         <v>44</v>
@@ -77032,7 +77059,7 @@
     </row>
     <row r="854" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
-        <v>1315</v>
+        <v>1304</v>
       </c>
       <c r="B854" s="2" t="s">
         <v>35</v>
@@ -77041,16 +77068,16 @@
         <v>1300</v>
       </c>
       <c r="D854" s="4">
-        <v>43340469</v>
+        <v>43758365</v>
       </c>
       <c r="E854" s="5" t="s">
-        <v>1313</v>
+        <v>639</v>
       </c>
       <c r="F854" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G854" s="4" t="s">
-        <v>1316</v>
+        <v>258</v>
       </c>
       <c r="H854" s="4" t="s">
         <v>44</v>
@@ -77093,7 +77120,7 @@
     </row>
     <row r="855" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
-        <v>1317</v>
+        <v>1305</v>
       </c>
       <c r="B855" s="2" t="s">
         <v>35</v>
@@ -77102,22 +77129,22 @@
         <v>1300</v>
       </c>
       <c r="D855" s="4">
-        <v>43447473</v>
+        <v>43245330</v>
       </c>
       <c r="E855" s="5" t="s">
-        <v>1318</v>
+        <v>644</v>
       </c>
       <c r="F855" s="4" t="s">
-        <v>43</v>
+        <v>645</v>
       </c>
       <c r="G855" s="4" t="s">
-        <v>56</v>
+        <v>1306</v>
       </c>
       <c r="H855" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I855" s="4">
-        <v>399.99</v>
+        <v>799.99</v>
       </c>
       <c r="J855" s="4" t="s">
         <v>40</v>
@@ -77154,7 +77181,7 @@
     </row>
     <row r="856" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
-        <v>1319</v>
+        <v>1307</v>
       </c>
       <c r="B856" s="2" t="s">
         <v>35</v>
@@ -77163,13 +77190,13 @@
         <v>1300</v>
       </c>
       <c r="D856" s="4">
-        <v>43447473</v>
+        <v>43790399</v>
       </c>
       <c r="E856" s="5" t="s">
-        <v>1318</v>
+        <v>648</v>
       </c>
       <c r="F856" s="4" t="s">
-        <v>43</v>
+        <v>636</v>
       </c>
       <c r="G856" s="4" t="s">
         <v>59</v>
@@ -77178,7 +77205,7 @@
         <v>44</v>
       </c>
       <c r="I856" s="4">
-        <v>399.99</v>
+        <v>699.99</v>
       </c>
       <c r="J856" s="4" t="s">
         <v>40</v>
@@ -77215,7 +77242,7 @@
     </row>
     <row r="857" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
-        <v>1320</v>
+        <v>1308</v>
       </c>
       <c r="B857" s="2" t="s">
         <v>35</v>
@@ -77224,22 +77251,22 @@
         <v>1300</v>
       </c>
       <c r="D857" s="4">
-        <v>43447473</v>
+        <v>43206446</v>
       </c>
       <c r="E857" s="5" t="s">
-        <v>1318</v>
+        <v>1309</v>
       </c>
       <c r="F857" s="4" t="s">
-        <v>43</v>
+        <v>645</v>
       </c>
       <c r="G857" s="4" t="s">
-        <v>1321</v>
+        <v>59</v>
       </c>
       <c r="H857" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I857" s="4">
-        <v>399.99</v>
+        <v>599.99</v>
       </c>
       <c r="J857" s="4" t="s">
         <v>40</v>
@@ -77276,7 +77303,7 @@
     </row>
     <row r="858" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
-        <v>1322</v>
+        <v>1310</v>
       </c>
       <c r="B858" s="2" t="s">
         <v>35</v>
@@ -77285,22 +77312,22 @@
         <v>1300</v>
       </c>
       <c r="D858" s="4">
-        <v>43447473</v>
+        <v>43206446</v>
       </c>
       <c r="E858" s="5" t="s">
-        <v>1318</v>
+        <v>1309</v>
       </c>
       <c r="F858" s="4" t="s">
-        <v>43</v>
+        <v>645</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>61</v>
+        <v>1311</v>
       </c>
       <c r="H858" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I858" s="4">
-        <v>399.99</v>
+        <v>599.99</v>
       </c>
       <c r="J858" s="4" t="s">
         <v>40</v>
@@ -77337,7 +77364,7 @@
     </row>
     <row r="859" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
-        <v>1703</v>
+        <v>1312</v>
       </c>
       <c r="B859" s="2" t="s">
         <v>35</v>
@@ -77346,31 +77373,31 @@
         <v>1300</v>
       </c>
       <c r="D859" s="4">
-        <v>43447473</v>
+        <v>43340469</v>
       </c>
       <c r="E859" s="5" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="F859" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G859" s="4" t="s">
-        <v>1701</v>
+        <v>1314</v>
       </c>
       <c r="H859" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I859" s="4">
-        <v>399.99</v>
+        <v>549.99</v>
       </c>
       <c r="J859" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K859" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L859" s="4" t="s">
-        <v>42</v>
+        <v>487</v>
       </c>
       <c r="M859" s="4"/>
       <c r="N859" s="4"/>
@@ -77398,7 +77425,7 @@
     </row>
     <row r="860" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
-        <v>1704</v>
+        <v>1315</v>
       </c>
       <c r="B860" s="2" t="s">
         <v>35</v>
@@ -77407,31 +77434,31 @@
         <v>1300</v>
       </c>
       <c r="D860" s="4">
-        <v>43447473</v>
+        <v>43340469</v>
       </c>
       <c r="E860" s="5" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="F860" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G860" s="4" t="s">
-        <v>112</v>
+        <v>1316</v>
       </c>
       <c r="H860" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I860" s="4">
-        <v>399.99</v>
+        <v>549.99</v>
       </c>
       <c r="J860" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K860" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L860" s="4" t="s">
-        <v>42</v>
+        <v>487</v>
       </c>
       <c r="M860" s="4"/>
       <c r="N860" s="4"/>
@@ -77459,7 +77486,7 @@
     </row>
     <row r="861" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
-        <v>1705</v>
+        <v>1317</v>
       </c>
       <c r="B861" s="2" t="s">
         <v>35</v>
@@ -77477,7 +77504,7 @@
         <v>43</v>
       </c>
       <c r="G861" s="4" t="s">
-        <v>1702</v>
+        <v>56</v>
       </c>
       <c r="H861" s="4" t="s">
         <v>44</v>
@@ -77486,13 +77513,13 @@
         <v>399.99</v>
       </c>
       <c r="J861" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K861" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L861" s="4" t="s">
-        <v>42</v>
+        <v>487</v>
       </c>
       <c r="M861" s="4"/>
       <c r="N861" s="4"/>
@@ -77520,7 +77547,7 @@
     </row>
     <row r="862" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="B862" s="2" t="s">
         <v>35</v>
@@ -77538,7 +77565,7 @@
         <v>43</v>
       </c>
       <c r="G862" s="4" t="s">
-        <v>1324</v>
+        <v>59</v>
       </c>
       <c r="H862" s="4" t="s">
         <v>44</v>
@@ -77581,7 +77608,7 @@
     </row>
     <row r="863" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="B863" s="2" t="s">
         <v>35</v>
@@ -77599,7 +77626,7 @@
         <v>43</v>
       </c>
       <c r="G863" s="4" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="H863" s="4" t="s">
         <v>44</v>
@@ -77642,40 +77669,40 @@
     </row>
     <row r="864" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="B864" s="2" t="s">
-        <v>691</v>
+        <v>35</v>
       </c>
       <c r="C864" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D864" s="4" t="s">
-        <v>951</v>
+        <v>1300</v>
+      </c>
+      <c r="D864" s="4">
+        <v>43447473</v>
       </c>
       <c r="E864" s="5" t="s">
-        <v>1328</v>
+        <v>1318</v>
       </c>
       <c r="F864" s="4" t="s">
-        <v>701</v>
+        <v>43</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1329</v>
+        <v>61</v>
       </c>
       <c r="H864" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I864" s="4">
-        <v>119.99</v>
+        <v>399.99</v>
       </c>
       <c r="J864" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K864" s="4" t="s">
         <v>40</v>
       </c>
       <c r="L864" s="4" t="s">
-        <v>42</v>
+        <v>487</v>
       </c>
       <c r="M864" s="4"/>
       <c r="N864" s="4"/>
@@ -77703,37 +77730,37 @@
     </row>
     <row r="865" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
-        <v>1330</v>
+        <v>1703</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>691</v>
+        <v>35</v>
       </c>
       <c r="C865" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D865" s="4" t="s">
-        <v>959</v>
+        <v>1300</v>
+      </c>
+      <c r="D865" s="4">
+        <v>43447473</v>
       </c>
       <c r="E865" s="5" t="s">
-        <v>960</v>
+        <v>1318</v>
       </c>
       <c r="F865" s="4" t="s">
-        <v>701</v>
+        <v>43</v>
       </c>
       <c r="G865" s="4" t="s">
-        <v>1329</v>
+        <v>1701</v>
       </c>
       <c r="H865" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I865" s="4">
-        <v>109.99</v>
+        <v>399.99</v>
       </c>
       <c r="J865" s="4" t="s">
         <v>41</v>
       </c>
       <c r="K865" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L865" s="4" t="s">
         <v>42</v>
@@ -77764,37 +77791,37 @@
     </row>
     <row r="866" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
-        <v>1331</v>
+        <v>1704</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>691</v>
+        <v>35</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D866" s="4" t="s">
-        <v>967</v>
+        <v>1300</v>
+      </c>
+      <c r="D866" s="4">
+        <v>43447473</v>
       </c>
       <c r="E866" s="5" t="s">
-        <v>1332</v>
+        <v>1318</v>
       </c>
       <c r="F866" s="4" t="s">
-        <v>701</v>
+        <v>43</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1333</v>
+        <v>112</v>
       </c>
       <c r="H866" s="4" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I866" s="4">
-        <v>169.99</v>
+        <v>399.99</v>
       </c>
       <c r="J866" s="4" t="s">
         <v>41</v>
       </c>
       <c r="K866" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L866" s="4" t="s">
         <v>42</v>
@@ -77825,37 +77852,37 @@
     </row>
     <row r="867" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
-        <v>1334</v>
+        <v>1705</v>
       </c>
       <c r="B867" s="2" t="s">
-        <v>691</v>
+        <v>35</v>
       </c>
       <c r="C867" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D867" s="4" t="s">
-        <v>984</v>
+        <v>1300</v>
+      </c>
+      <c r="D867" s="4">
+        <v>43447473</v>
       </c>
       <c r="E867" s="5" t="s">
-        <v>1335</v>
+        <v>1318</v>
       </c>
       <c r="F867" s="4" t="s">
-        <v>701</v>
+        <v>43</v>
       </c>
       <c r="G867" s="4" t="s">
-        <v>1336</v>
+        <v>1702</v>
       </c>
       <c r="H867" s="4" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I867" s="4">
-        <v>119.99</v>
+        <v>399.99</v>
       </c>
       <c r="J867" s="4" t="s">
         <v>41</v>
       </c>
       <c r="K867" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L867" s="4" t="s">
         <v>42</v>
@@ -77886,40 +77913,40 @@
     </row>
     <row r="868" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
-        <v>1337</v>
+        <v>1323</v>
       </c>
       <c r="B868" s="2" t="s">
-        <v>691</v>
+        <v>35</v>
       </c>
       <c r="C868" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D868" s="4" t="s">
-        <v>990</v>
+        <v>1300</v>
+      </c>
+      <c r="D868" s="4">
+        <v>43447473</v>
       </c>
       <c r="E868" s="5" t="s">
-        <v>991</v>
+        <v>1318</v>
       </c>
       <c r="F868" s="4" t="s">
-        <v>701</v>
+        <v>43</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1336</v>
+        <v>1324</v>
       </c>
       <c r="H868" s="4" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I868" s="4">
-        <v>109.99</v>
+        <v>399.99</v>
       </c>
       <c r="J868" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K868" s="4" t="s">
         <v>40</v>
       </c>
       <c r="L868" s="4" t="s">
-        <v>42</v>
+        <v>487</v>
       </c>
       <c r="M868" s="4"/>
       <c r="N868" s="4"/>
@@ -77947,40 +77974,40 @@
     </row>
     <row r="869" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
-        <v>1338</v>
+        <v>1325</v>
       </c>
       <c r="B869" s="2" t="s">
-        <v>691</v>
+        <v>35</v>
       </c>
       <c r="C869" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D869" s="4" t="s">
-        <v>1065</v>
+        <v>1300</v>
+      </c>
+      <c r="D869" s="4">
+        <v>43447473</v>
       </c>
       <c r="E869" s="5" t="s">
-        <v>1066</v>
+        <v>1318</v>
       </c>
       <c r="F869" s="4" t="s">
-        <v>701</v>
+        <v>43</v>
       </c>
       <c r="G869" s="4" t="s">
-        <v>1339</v>
+        <v>1326</v>
       </c>
       <c r="H869" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I869" s="4">
-        <v>119.99</v>
+        <v>399.99</v>
       </c>
       <c r="J869" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K869" s="4" t="s">
         <v>40</v>
       </c>
       <c r="L869" s="4" t="s">
-        <v>42</v>
+        <v>487</v>
       </c>
       <c r="M869" s="4"/>
       <c r="N869" s="4"/>
@@ -78008,25 +78035,25 @@
     </row>
     <row r="870" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
-        <v>1340</v>
+        <v>1327</v>
       </c>
       <c r="B870" s="2" t="s">
         <v>691</v>
       </c>
       <c r="C870" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D870" s="4" t="s">
-        <v>1065</v>
+        <v>951</v>
       </c>
       <c r="E870" s="5" t="s">
-        <v>1066</v>
+        <v>1328</v>
       </c>
       <c r="F870" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G870" s="4" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
       <c r="H870" s="4" t="s">
         <v>39</v>
@@ -78069,31 +78096,31 @@
     </row>
     <row r="871" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
-        <v>1342</v>
+        <v>1330</v>
       </c>
       <c r="B871" s="2" t="s">
         <v>691</v>
       </c>
       <c r="C871" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D871" s="4" t="s">
-        <v>1343</v>
+        <v>959</v>
       </c>
       <c r="E871" s="5" t="s">
-        <v>1344</v>
+        <v>960</v>
       </c>
       <c r="F871" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G871" s="4" t="s">
-        <v>1339</v>
+        <v>1329</v>
       </c>
       <c r="H871" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I871" s="4">
-        <v>149.99</v>
+        <v>109.99</v>
       </c>
       <c r="J871" s="4" t="s">
         <v>41</v>
@@ -78130,31 +78157,31 @@
     </row>
     <row r="872" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
-        <v>1345</v>
+        <v>1331</v>
       </c>
       <c r="B872" s="2" t="s">
         <v>691</v>
       </c>
       <c r="C872" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D872" s="4" t="s">
-        <v>1072</v>
+        <v>967</v>
       </c>
       <c r="E872" s="5" t="s">
-        <v>1073</v>
+        <v>1332</v>
       </c>
       <c r="F872" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="H872" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I872" s="4">
-        <v>159.99</v>
+        <v>169.99</v>
       </c>
       <c r="J872" s="4" t="s">
         <v>41</v>
@@ -78191,31 +78218,31 @@
     </row>
     <row r="873" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
-        <v>1346</v>
+        <v>1334</v>
       </c>
       <c r="B873" s="2" t="s">
         <v>691</v>
       </c>
       <c r="C873" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D873" s="4" t="s">
-        <v>1068</v>
+        <v>984</v>
       </c>
       <c r="E873" s="5" t="s">
-        <v>1347</v>
+        <v>1335</v>
       </c>
       <c r="F873" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G873" s="4" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H873" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I873" s="4">
-        <v>139.99</v>
+        <v>119.99</v>
       </c>
       <c r="J873" s="4" t="s">
         <v>41</v>
@@ -78252,31 +78279,31 @@
     </row>
     <row r="874" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
-        <v>1348</v>
+        <v>1337</v>
       </c>
       <c r="B874" s="2" t="s">
         <v>691</v>
       </c>
       <c r="C874" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D874" s="4" t="s">
-        <v>1075</v>
+        <v>990</v>
       </c>
       <c r="E874" s="5" t="s">
-        <v>1076</v>
+        <v>991</v>
       </c>
       <c r="F874" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1349</v>
+        <v>1336</v>
       </c>
       <c r="H874" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I874" s="4">
-        <v>139.99</v>
+        <v>109.99</v>
       </c>
       <c r="J874" s="4" t="s">
         <v>41</v>
@@ -78313,7 +78340,7 @@
     </row>
     <row r="875" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
-        <v>1350</v>
+        <v>1338</v>
       </c>
       <c r="B875" s="2" t="s">
         <v>691</v>
@@ -78322,22 +78349,22 @@
         <v>102</v>
       </c>
       <c r="D875" s="4" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
       <c r="E875" s="5" t="s">
-        <v>1076</v>
+        <v>1066</v>
       </c>
       <c r="F875" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G875" s="4" t="s">
-        <v>1351</v>
+        <v>1339</v>
       </c>
       <c r="H875" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I875" s="4">
-        <v>139.99</v>
+        <v>119.99</v>
       </c>
       <c r="J875" s="4" t="s">
         <v>41</v>
@@ -78374,7 +78401,7 @@
     </row>
     <row r="876" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
-        <v>1352</v>
+        <v>1340</v>
       </c>
       <c r="B876" s="2" t="s">
         <v>691</v>
@@ -78383,22 +78410,22 @@
         <v>102</v>
       </c>
       <c r="D876" s="4" t="s">
-        <v>1083</v>
+        <v>1065</v>
       </c>
       <c r="E876" s="5" t="s">
-        <v>1353</v>
+        <v>1066</v>
       </c>
       <c r="F876" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G876" s="4" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="H876" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I876" s="4">
-        <v>99.99</v>
+        <v>119.99</v>
       </c>
       <c r="J876" s="4" t="s">
         <v>41</v>
@@ -78435,7 +78462,7 @@
     </row>
     <row r="877" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
-        <v>1355</v>
+        <v>1342</v>
       </c>
       <c r="B877" s="2" t="s">
         <v>691</v>
@@ -78444,22 +78471,22 @@
         <v>102</v>
       </c>
       <c r="D877" s="4" t="s">
-        <v>1094</v>
+        <v>1343</v>
       </c>
       <c r="E877" s="5" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
       <c r="F877" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G877" s="4" t="s">
-        <v>69</v>
+        <v>1339</v>
       </c>
       <c r="H877" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I877" s="4">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="J877" s="4" t="s">
         <v>41</v>
@@ -78496,7 +78523,7 @@
     </row>
     <row r="878" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
-        <v>1357</v>
+        <v>1345</v>
       </c>
       <c r="B878" s="2" t="s">
         <v>691</v>
@@ -78505,13 +78532,13 @@
         <v>102</v>
       </c>
       <c r="D878" s="4" t="s">
-        <v>1094</v>
+        <v>1072</v>
       </c>
       <c r="E878" s="5" t="s">
-        <v>1356</v>
+        <v>1073</v>
       </c>
       <c r="F878" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G878" s="4" t="s">
         <v>1339</v>
@@ -78520,7 +78547,7 @@
         <v>39</v>
       </c>
       <c r="I878" s="4">
-        <v>89.99</v>
+        <v>159.99</v>
       </c>
       <c r="J878" s="4" t="s">
         <v>41</v>
@@ -78557,7 +78584,7 @@
     </row>
     <row r="879" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
-        <v>1358</v>
+        <v>1346</v>
       </c>
       <c r="B879" s="2" t="s">
         <v>691</v>
@@ -78566,22 +78593,22 @@
         <v>102</v>
       </c>
       <c r="D879" s="4" t="s">
-        <v>1094</v>
+        <v>1068</v>
       </c>
       <c r="E879" s="5" t="s">
-        <v>1356</v>
+        <v>1347</v>
       </c>
       <c r="F879" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G879" s="4" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="H879" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I879" s="4">
-        <v>89.99</v>
+        <v>139.99</v>
       </c>
       <c r="J879" s="4" t="s">
         <v>41</v>
@@ -78618,7 +78645,7 @@
     </row>
     <row r="880" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
-        <v>1359</v>
+        <v>1348</v>
       </c>
       <c r="B880" s="2" t="s">
         <v>691</v>
@@ -78627,22 +78654,22 @@
         <v>102</v>
       </c>
       <c r="D880" s="4" t="s">
-        <v>1094</v>
+        <v>1075</v>
       </c>
       <c r="E880" s="5" t="s">
-        <v>1356</v>
+        <v>1076</v>
       </c>
       <c r="F880" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G880" s="4" t="s">
-        <v>377</v>
+        <v>1349</v>
       </c>
       <c r="H880" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I880" s="4">
-        <v>89.99</v>
+        <v>139.99</v>
       </c>
       <c r="J880" s="4" t="s">
         <v>41</v>
@@ -78679,7 +78706,7 @@
     </row>
     <row r="881" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
-        <v>1360</v>
+        <v>1350</v>
       </c>
       <c r="B881" s="2" t="s">
         <v>691</v>
@@ -78688,22 +78715,22 @@
         <v>102</v>
       </c>
       <c r="D881" s="4" t="s">
-        <v>1361</v>
+        <v>1075</v>
       </c>
       <c r="E881" s="5" t="s">
-        <v>1362</v>
+        <v>1076</v>
       </c>
       <c r="F881" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G881" s="4" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="H881" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I881" s="4">
-        <v>79.989999999999995</v>
+        <v>139.99</v>
       </c>
       <c r="J881" s="4" t="s">
         <v>41</v>
@@ -78740,7 +78767,7 @@
     </row>
     <row r="882" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
-        <v>1363</v>
+        <v>1352</v>
       </c>
       <c r="B882" s="2" t="s">
         <v>691</v>
@@ -78749,22 +78776,22 @@
         <v>102</v>
       </c>
       <c r="D882" s="4" t="s">
-        <v>1361</v>
+        <v>1083</v>
       </c>
       <c r="E882" s="5" t="s">
-        <v>1362</v>
+        <v>1353</v>
       </c>
       <c r="F882" s="4" t="s">
         <v>1354</v>
       </c>
       <c r="G882" s="4" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="H882" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I882" s="4">
-        <v>79.989999999999995</v>
+        <v>99.99</v>
       </c>
       <c r="J882" s="4" t="s">
         <v>41</v>
@@ -78801,7 +78828,7 @@
     </row>
     <row r="883" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
-        <v>1364</v>
+        <v>1355</v>
       </c>
       <c r="B883" s="2" t="s">
         <v>691</v>
@@ -78810,22 +78837,22 @@
         <v>102</v>
       </c>
       <c r="D883" s="4" t="s">
-        <v>1116</v>
+        <v>1094</v>
       </c>
       <c r="E883" s="5" t="s">
-        <v>1117</v>
+        <v>1356</v>
       </c>
       <c r="F883" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G883" s="4" t="s">
-        <v>1339</v>
+        <v>69</v>
       </c>
       <c r="H883" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I883" s="4">
-        <v>169.99</v>
+        <v>89.99</v>
       </c>
       <c r="J883" s="4" t="s">
         <v>41</v>
@@ -78862,7 +78889,7 @@
     </row>
     <row r="884" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
       <c r="B884" s="2" t="s">
         <v>691</v>
@@ -78871,22 +78898,22 @@
         <v>102</v>
       </c>
       <c r="D884" s="4" t="s">
-        <v>1116</v>
+        <v>1094</v>
       </c>
       <c r="E884" s="5" t="s">
-        <v>1117</v>
+        <v>1356</v>
       </c>
       <c r="F884" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G884" s="4" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="H884" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I884" s="4">
-        <v>169.99</v>
+        <v>89.99</v>
       </c>
       <c r="J884" s="4" t="s">
         <v>41</v>
@@ -78923,7 +78950,7 @@
     </row>
     <row r="885" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="B885" s="2" t="s">
         <v>691</v>
@@ -78932,22 +78959,22 @@
         <v>102</v>
       </c>
       <c r="D885" s="4" t="s">
-        <v>1125</v>
+        <v>1094</v>
       </c>
       <c r="E885" s="5" t="s">
-        <v>1367</v>
+        <v>1356</v>
       </c>
       <c r="F885" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G885" s="4" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="H885" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I885" s="4">
-        <v>199.99</v>
+        <v>89.99</v>
       </c>
       <c r="J885" s="4" t="s">
         <v>41</v>
@@ -78984,7 +79011,7 @@
     </row>
     <row r="886" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
-        <v>1368</v>
+        <v>1359</v>
       </c>
       <c r="B886" s="2" t="s">
         <v>691</v>
@@ -78993,22 +79020,22 @@
         <v>102</v>
       </c>
       <c r="D886" s="4" t="s">
-        <v>1159</v>
+        <v>1094</v>
       </c>
       <c r="E886" s="5" t="s">
-        <v>1369</v>
+        <v>1356</v>
       </c>
       <c r="F886" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>1370</v>
+        <v>377</v>
       </c>
       <c r="H886" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I886" s="4">
-        <v>99.99</v>
+        <v>89.99</v>
       </c>
       <c r="J886" s="4" t="s">
         <v>41</v>
@@ -79045,7 +79072,7 @@
     </row>
     <row r="887" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
-        <v>1371</v>
+        <v>1360</v>
       </c>
       <c r="B887" s="2" t="s">
         <v>691</v>
@@ -79054,22 +79081,22 @@
         <v>102</v>
       </c>
       <c r="D887" s="4" t="s">
-        <v>1174</v>
+        <v>1361</v>
       </c>
       <c r="E887" s="5" t="s">
-        <v>1372</v>
+        <v>1362</v>
       </c>
       <c r="F887" s="4" t="s">
         <v>1354</v>
       </c>
       <c r="G887" s="4" t="s">
-        <v>1370</v>
+        <v>1339</v>
       </c>
       <c r="H887" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I887" s="4">
-        <v>89.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J887" s="4" t="s">
         <v>41</v>
@@ -79106,7 +79133,7 @@
     </row>
     <row r="888" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
-        <v>1373</v>
+        <v>1363</v>
       </c>
       <c r="B888" s="2" t="s">
         <v>691</v>
@@ -79115,19 +79142,19 @@
         <v>102</v>
       </c>
       <c r="D888" s="4" t="s">
-        <v>1374</v>
+        <v>1361</v>
       </c>
       <c r="E888" s="5" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="F888" s="4" t="s">
         <v>1354</v>
       </c>
       <c r="G888" s="4" t="s">
-        <v>1370</v>
+        <v>1341</v>
       </c>
       <c r="H888" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I888" s="4">
         <v>79.989999999999995</v>
@@ -79167,7 +79194,7 @@
     </row>
     <row r="889" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
-        <v>1376</v>
+        <v>1364</v>
       </c>
       <c r="B889" s="2" t="s">
         <v>691</v>
@@ -79176,22 +79203,22 @@
         <v>102</v>
       </c>
       <c r="D889" s="4" t="s">
-        <v>1191</v>
+        <v>1116</v>
       </c>
       <c r="E889" s="5" t="s">
-        <v>1192</v>
+        <v>1117</v>
       </c>
       <c r="F889" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G889" s="4" t="s">
-        <v>1370</v>
+        <v>1339</v>
       </c>
       <c r="H889" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I889" s="4">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="J889" s="4" t="s">
         <v>41</v>
@@ -79228,7 +79255,7 @@
     </row>
     <row r="890" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
-        <v>1377</v>
+        <v>1365</v>
       </c>
       <c r="B890" s="2" t="s">
         <v>691</v>
@@ -79237,22 +79264,22 @@
         <v>102</v>
       </c>
       <c r="D890" s="4" t="s">
-        <v>1197</v>
+        <v>1116</v>
       </c>
       <c r="E890" s="5" t="s">
-        <v>1198</v>
+        <v>1117</v>
       </c>
       <c r="F890" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G890" s="4" t="s">
-        <v>1370</v>
+        <v>1341</v>
       </c>
       <c r="H890" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I890" s="4">
-        <v>109.99</v>
+        <v>169.99</v>
       </c>
       <c r="J890" s="4" t="s">
         <v>41</v>
@@ -79289,7 +79316,7 @@
     </row>
     <row r="891" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="B891" s="2" t="s">
         <v>691</v>
@@ -79298,19 +79325,19 @@
         <v>102</v>
       </c>
       <c r="D891" s="4" t="s">
-        <v>1201</v>
+        <v>1125</v>
       </c>
       <c r="E891" s="5" t="s">
-        <v>1379</v>
+        <v>1367</v>
       </c>
       <c r="F891" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G891" s="4" t="s">
-        <v>1370</v>
+        <v>1339</v>
       </c>
       <c r="H891" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I891" s="4">
         <v>199.99</v>
@@ -79350,7 +79377,7 @@
     </row>
     <row r="892" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
-        <v>1380</v>
+        <v>1368</v>
       </c>
       <c r="B892" s="2" t="s">
         <v>691</v>
@@ -79359,22 +79386,22 @@
         <v>102</v>
       </c>
       <c r="D892" s="4" t="s">
-        <v>1381</v>
+        <v>1159</v>
       </c>
       <c r="E892" s="5" t="s">
-        <v>1382</v>
+        <v>1369</v>
       </c>
       <c r="F892" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G892" s="4" t="s">
-        <v>1339</v>
+        <v>1370</v>
       </c>
       <c r="H892" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I892" s="4">
-        <v>119.99</v>
+        <v>99.99</v>
       </c>
       <c r="J892" s="4" t="s">
         <v>41</v>
@@ -79411,7 +79438,7 @@
     </row>
     <row r="893" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="B893" s="2" t="s">
         <v>691</v>
@@ -79420,22 +79447,22 @@
         <v>102</v>
       </c>
       <c r="D893" s="4" t="s">
-        <v>1219</v>
+        <v>1174</v>
       </c>
       <c r="E893" s="5" t="s">
-        <v>1220</v>
+        <v>1372</v>
       </c>
       <c r="F893" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G893" s="4" t="s">
-        <v>1339</v>
+        <v>1370</v>
       </c>
       <c r="H893" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I893" s="4">
-        <v>109.99</v>
+        <v>89.99</v>
       </c>
       <c r="J893" s="4" t="s">
         <v>41</v>
@@ -79472,31 +79499,31 @@
     </row>
     <row r="894" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
-        <v>1384</v>
+        <v>1373</v>
       </c>
       <c r="B894" s="2" t="s">
-        <v>788</v>
+        <v>691</v>
       </c>
       <c r="C894" s="2" t="s">
-        <v>1016</v>
+        <v>102</v>
       </c>
       <c r="D894" s="4" t="s">
-        <v>1030</v>
+        <v>1374</v>
       </c>
       <c r="E894" s="5" t="s">
-        <v>1385</v>
+        <v>1375</v>
       </c>
       <c r="F894" s="4" t="s">
-        <v>791</v>
+        <v>1354</v>
       </c>
       <c r="G894" s="4" t="s">
-        <v>1386</v>
+        <v>1370</v>
       </c>
       <c r="H894" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I894" s="4">
-        <v>59.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J894" s="4" t="s">
         <v>41</v>
@@ -79533,31 +79560,31 @@
     </row>
     <row r="895" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
-        <v>1387</v>
+        <v>1376</v>
       </c>
       <c r="B895" s="2" t="s">
-        <v>788</v>
+        <v>691</v>
       </c>
       <c r="C895" s="2" t="s">
-        <v>1016</v>
+        <v>102</v>
       </c>
       <c r="D895" s="4" t="s">
-        <v>1030</v>
+        <v>1191</v>
       </c>
       <c r="E895" s="5" t="s">
-        <v>1385</v>
+        <v>1192</v>
       </c>
       <c r="F895" s="4" t="s">
-        <v>791</v>
+        <v>1354</v>
       </c>
       <c r="G895" s="4" t="s">
-        <v>1388</v>
+        <v>1370</v>
       </c>
       <c r="H895" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I895" s="4">
-        <v>59.99</v>
+        <v>119.99</v>
       </c>
       <c r="J895" s="4" t="s">
         <v>41</v>
@@ -79594,31 +79621,31 @@
     </row>
     <row r="896" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
-        <v>1389</v>
+        <v>1377</v>
       </c>
       <c r="B896" s="2" t="s">
-        <v>788</v>
+        <v>691</v>
       </c>
       <c r="C896" s="2" t="s">
-        <v>1016</v>
+        <v>102</v>
       </c>
       <c r="D896" s="4" t="s">
-        <v>1037</v>
+        <v>1197</v>
       </c>
       <c r="E896" s="5" t="s">
-        <v>1390</v>
+        <v>1198</v>
       </c>
       <c r="F896" s="4" t="s">
-        <v>791</v>
+        <v>701</v>
       </c>
       <c r="G896" s="4" t="s">
-        <v>1391</v>
+        <v>1370</v>
       </c>
       <c r="H896" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I896" s="4">
-        <v>59.99</v>
+        <v>109.99</v>
       </c>
       <c r="J896" s="4" t="s">
         <v>41</v>
@@ -79655,31 +79682,31 @@
     </row>
     <row r="897" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
-        <v>1392</v>
+        <v>1378</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>788</v>
+        <v>691</v>
       </c>
       <c r="C897" s="2" t="s">
-        <v>1016</v>
+        <v>102</v>
       </c>
       <c r="D897" s="4" t="s">
-        <v>1037</v>
+        <v>1201</v>
       </c>
       <c r="E897" s="5" t="s">
-        <v>1390</v>
+        <v>1379</v>
       </c>
       <c r="F897" s="4" t="s">
-        <v>791</v>
+        <v>701</v>
       </c>
       <c r="G897" s="4" t="s">
-        <v>1393</v>
+        <v>1370</v>
       </c>
       <c r="H897" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I897" s="4">
-        <v>59.99</v>
+        <v>199.99</v>
       </c>
       <c r="J897" s="4" t="s">
         <v>41</v>
@@ -79716,31 +79743,31 @@
     </row>
     <row r="898" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
-        <v>1394</v>
+        <v>1380</v>
       </c>
       <c r="B898" s="2" t="s">
-        <v>788</v>
+        <v>691</v>
       </c>
       <c r="C898" s="2" t="s">
-        <v>1016</v>
+        <v>102</v>
       </c>
       <c r="D898" s="4" t="s">
-        <v>1052</v>
+        <v>1381</v>
       </c>
       <c r="E898" s="5" t="s">
-        <v>1395</v>
+        <v>1382</v>
       </c>
       <c r="F898" s="4" t="s">
-        <v>845</v>
+        <v>701</v>
       </c>
       <c r="G898" s="4" t="s">
-        <v>1386</v>
+        <v>1339</v>
       </c>
       <c r="H898" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I898" s="4">
-        <v>59.99</v>
+        <v>119.99</v>
       </c>
       <c r="J898" s="4" t="s">
         <v>41</v>
@@ -79777,31 +79804,31 @@
     </row>
     <row r="899" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
-        <v>1396</v>
+        <v>1383</v>
       </c>
       <c r="B899" s="2" t="s">
-        <v>788</v>
+        <v>691</v>
       </c>
       <c r="C899" s="2" t="s">
-        <v>1016</v>
+        <v>102</v>
       </c>
       <c r="D899" s="4" t="s">
-        <v>1052</v>
+        <v>1219</v>
       </c>
       <c r="E899" s="5" t="s">
-        <v>1395</v>
+        <v>1220</v>
       </c>
       <c r="F899" s="4" t="s">
-        <v>845</v>
+        <v>701</v>
       </c>
       <c r="G899" s="4" t="s">
-        <v>1388</v>
+        <v>1339</v>
       </c>
       <c r="H899" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I899" s="4">
-        <v>59.99</v>
+        <v>109.99</v>
       </c>
       <c r="J899" s="4" t="s">
         <v>41</v>
@@ -79838,7 +79865,7 @@
     </row>
     <row r="900" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
-        <v>1397</v>
+        <v>1384</v>
       </c>
       <c r="B900" s="2" t="s">
         <v>788</v>
@@ -79847,19 +79874,19 @@
         <v>1016</v>
       </c>
       <c r="D900" s="4" t="s">
-        <v>1056</v>
+        <v>1030</v>
       </c>
       <c r="E900" s="5" t="s">
-        <v>1398</v>
+        <v>1385</v>
       </c>
       <c r="F900" s="4" t="s">
-        <v>845</v>
+        <v>791</v>
       </c>
       <c r="G900" s="4" t="s">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="H900" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I900" s="4">
         <v>59.99</v>
@@ -79899,7 +79926,7 @@
     </row>
     <row r="901" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
-        <v>1400</v>
+        <v>1387</v>
       </c>
       <c r="B901" s="2" t="s">
         <v>788</v>
@@ -79908,19 +79935,19 @@
         <v>1016</v>
       </c>
       <c r="D901" s="4" t="s">
-        <v>1056</v>
+        <v>1030</v>
       </c>
       <c r="E901" s="5" t="s">
-        <v>1398</v>
+        <v>1385</v>
       </c>
       <c r="F901" s="4" t="s">
-        <v>845</v>
+        <v>791</v>
       </c>
       <c r="G901" s="4" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="H901" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I901" s="4">
         <v>59.99</v>
@@ -79960,37 +79987,37 @@
     </row>
     <row r="902" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
-        <v>1401</v>
+        <v>1389</v>
       </c>
       <c r="B902" s="2" t="s">
-        <v>722</v>
+        <v>788</v>
       </c>
       <c r="C902" s="2" t="s">
-        <v>36</v>
+        <v>1016</v>
       </c>
       <c r="D902" s="4" t="s">
-        <v>1402</v>
+        <v>1037</v>
       </c>
       <c r="E902" s="5" t="s">
-        <v>1403</v>
+        <v>1390</v>
       </c>
       <c r="F902" s="4" t="s">
-        <v>725</v>
+        <v>791</v>
       </c>
       <c r="G902" s="4" t="s">
-        <v>1404</v>
+        <v>1391</v>
       </c>
       <c r="H902" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I902" s="4">
-        <v>119.99</v>
+        <v>59.99</v>
       </c>
       <c r="J902" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K902" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L902" s="4" t="s">
         <v>42</v>
@@ -80021,37 +80048,37 @@
     </row>
     <row r="903" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
-        <v>1405</v>
+        <v>1392</v>
       </c>
       <c r="B903" s="2" t="s">
-        <v>722</v>
+        <v>788</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>36</v>
+        <v>1016</v>
       </c>
       <c r="D903" s="4" t="s">
-        <v>1402</v>
+        <v>1037</v>
       </c>
       <c r="E903" s="5" t="s">
-        <v>1403</v>
+        <v>1390</v>
       </c>
       <c r="F903" s="4" t="s">
-        <v>725</v>
+        <v>791</v>
       </c>
       <c r="G903" s="4" t="s">
-        <v>1406</v>
+        <v>1393</v>
       </c>
       <c r="H903" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I903" s="4">
-        <v>119.99</v>
+        <v>59.99</v>
       </c>
       <c r="J903" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K903" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L903" s="4" t="s">
         <v>42</v>
@@ -80082,37 +80109,37 @@
     </row>
     <row r="904" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
-        <v>1407</v>
+        <v>1394</v>
       </c>
       <c r="B904" s="2" t="s">
         <v>788</v>
       </c>
       <c r="C904" s="2" t="s">
-        <v>36</v>
+        <v>1016</v>
       </c>
       <c r="D904" s="4" t="s">
-        <v>1408</v>
+        <v>1052</v>
       </c>
       <c r="E904" s="5" t="s">
-        <v>1409</v>
+        <v>1395</v>
       </c>
       <c r="F904" s="4" t="s">
-        <v>136</v>
+        <v>845</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1410</v>
+        <v>1386</v>
       </c>
       <c r="H904" s="4" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="I904" s="4">
-        <v>99.99</v>
+        <v>59.99</v>
       </c>
       <c r="J904" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K904" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L904" s="4" t="s">
         <v>42</v>
@@ -80143,37 +80170,37 @@
     </row>
     <row r="905" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
-        <v>1411</v>
+        <v>1396</v>
       </c>
       <c r="B905" s="2" t="s">
         <v>788</v>
       </c>
       <c r="C905" s="2" t="s">
-        <v>36</v>
+        <v>1016</v>
       </c>
       <c r="D905" s="4" t="s">
-        <v>1408</v>
+        <v>1052</v>
       </c>
       <c r="E905" s="5" t="s">
-        <v>1409</v>
+        <v>1395</v>
       </c>
       <c r="F905" s="4" t="s">
-        <v>136</v>
+        <v>845</v>
       </c>
       <c r="G905" s="4" t="s">
-        <v>1412</v>
+        <v>1388</v>
       </c>
       <c r="H905" s="4" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="I905" s="4">
-        <v>99.99</v>
+        <v>59.99</v>
       </c>
       <c r="J905" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K905" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L905" s="4" t="s">
         <v>42</v>
@@ -80204,37 +80231,37 @@
     </row>
     <row r="906" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
-        <v>1413</v>
+        <v>1397</v>
       </c>
       <c r="B906" s="2" t="s">
         <v>788</v>
       </c>
       <c r="C906" s="2" t="s">
-        <v>36</v>
+        <v>1016</v>
       </c>
       <c r="D906" s="4" t="s">
-        <v>1408</v>
+        <v>1056</v>
       </c>
       <c r="E906" s="5" t="s">
-        <v>1409</v>
+        <v>1398</v>
       </c>
       <c r="F906" s="4" t="s">
-        <v>136</v>
+        <v>845</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1414</v>
+        <v>1399</v>
       </c>
       <c r="H906" s="4" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="I906" s="4">
-        <v>99.99</v>
+        <v>59.99</v>
       </c>
       <c r="J906" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K906" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L906" s="4" t="s">
         <v>42</v>
@@ -80265,37 +80292,37 @@
     </row>
     <row r="907" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
-        <v>1415</v>
+        <v>1400</v>
       </c>
       <c r="B907" s="2" t="s">
         <v>788</v>
       </c>
       <c r="C907" s="2" t="s">
-        <v>36</v>
+        <v>1016</v>
       </c>
       <c r="D907" s="4" t="s">
-        <v>1416</v>
+        <v>1056</v>
       </c>
       <c r="E907" s="5" t="s">
-        <v>1417</v>
+        <v>1398</v>
       </c>
       <c r="F907" s="4" t="s">
-        <v>791</v>
+        <v>845</v>
       </c>
       <c r="G907" s="4" t="s">
-        <v>1418</v>
+        <v>1393</v>
       </c>
       <c r="H907" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I907" s="4">
         <v>59.99</v>
       </c>
       <c r="J907" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K907" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L907" s="4" t="s">
         <v>42</v>
@@ -80326,31 +80353,31 @@
     </row>
     <row r="908" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
-        <v>1419</v>
+        <v>1401</v>
       </c>
       <c r="B908" s="2" t="s">
-        <v>788</v>
+        <v>722</v>
       </c>
       <c r="C908" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D908" s="4" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="E908" s="5" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="F908" s="4" t="s">
-        <v>791</v>
+        <v>725</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1420</v>
+        <v>1404</v>
       </c>
       <c r="H908" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I908" s="4">
-        <v>59.99</v>
+        <v>119.99</v>
       </c>
       <c r="J908" s="4" t="s">
         <v>40</v>
@@ -80387,31 +80414,31 @@
     </row>
     <row r="909" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
       <c r="B909" s="2" t="s">
-        <v>788</v>
+        <v>722</v>
       </c>
       <c r="C909" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D909" s="4" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="E909" s="5" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="F909" s="4" t="s">
-        <v>791</v>
+        <v>725</v>
       </c>
       <c r="G909" s="4" t="s">
-        <v>1422</v>
+        <v>1406</v>
       </c>
       <c r="H909" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I909" s="4">
-        <v>59.99</v>
+        <v>119.99</v>
       </c>
       <c r="J909" s="4" t="s">
         <v>40</v>
@@ -80448,7 +80475,7 @@
     </row>
     <row r="910" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
-        <v>1423</v>
+        <v>1407</v>
       </c>
       <c r="B910" s="2" t="s">
         <v>788</v>
@@ -80457,22 +80484,22 @@
         <v>36</v>
       </c>
       <c r="D910" s="4" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
       <c r="E910" s="5" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
       <c r="F910" s="4" t="s">
-        <v>791</v>
+        <v>136</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="H910" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I910" s="4">
-        <v>59.99</v>
+        <v>99.99</v>
       </c>
       <c r="J910" s="4" t="s">
         <v>40</v>
@@ -80509,7 +80536,7 @@
     </row>
     <row r="911" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B911" s="2" t="s">
         <v>788</v>
@@ -80518,22 +80545,22 @@
         <v>36</v>
       </c>
       <c r="D911" s="4" t="s">
-        <v>1426</v>
+        <v>1408</v>
       </c>
       <c r="E911" s="5" t="s">
-        <v>1427</v>
+        <v>1409</v>
       </c>
       <c r="F911" s="4" t="s">
-        <v>845</v>
+        <v>136</v>
       </c>
       <c r="G911" s="4" t="s">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="H911" s="4" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I911" s="4">
-        <v>59.99</v>
+        <v>99.99</v>
       </c>
       <c r="J911" s="4" t="s">
         <v>40</v>
@@ -80570,7 +80597,7 @@
     </row>
     <row r="912" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
-        <v>1428</v>
+        <v>1413</v>
       </c>
       <c r="B912" s="2" t="s">
         <v>788</v>
@@ -80579,22 +80606,22 @@
         <v>36</v>
       </c>
       <c r="D912" s="4" t="s">
-        <v>1426</v>
+        <v>1408</v>
       </c>
       <c r="E912" s="5" t="s">
-        <v>1427</v>
+        <v>1409</v>
       </c>
       <c r="F912" s="4" t="s">
-        <v>845</v>
+        <v>136</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="H912" s="4" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I912" s="4">
-        <v>59.99</v>
+        <v>99.99</v>
       </c>
       <c r="J912" s="4" t="s">
         <v>40</v>
@@ -80631,7 +80658,7 @@
     </row>
     <row r="913" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
-        <v>1429</v>
+        <v>1415</v>
       </c>
       <c r="B913" s="2" t="s">
         <v>788</v>
@@ -80640,19 +80667,19 @@
         <v>36</v>
       </c>
       <c r="D913" s="4" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="E913" s="5" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="F913" s="4" t="s">
-        <v>845</v>
+        <v>791</v>
       </c>
       <c r="G913" s="4" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="H913" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I913" s="4">
         <v>59.99</v>
@@ -80692,7 +80719,7 @@
     </row>
     <row r="914" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
-        <v>1430</v>
+        <v>1419</v>
       </c>
       <c r="B914" s="2" t="s">
         <v>788</v>
@@ -80701,19 +80728,19 @@
         <v>36</v>
       </c>
       <c r="D914" s="4" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="E914" s="5" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="F914" s="4" t="s">
-        <v>845</v>
+        <v>791</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="H914" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I914" s="4">
         <v>59.99</v>
@@ -80753,31 +80780,31 @@
     </row>
     <row r="915" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B915" s="2" t="s">
-        <v>691</v>
+        <v>788</v>
       </c>
       <c r="C915" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D915" s="4" t="s">
-        <v>1432</v>
+        <v>1416</v>
       </c>
       <c r="E915" s="5" t="s">
-        <v>1433</v>
+        <v>1417</v>
       </c>
       <c r="F915" s="4" t="s">
-        <v>1354</v>
+        <v>791</v>
       </c>
       <c r="G915" s="4" t="s">
-        <v>69</v>
+        <v>1422</v>
       </c>
       <c r="H915" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I915" s="4">
-        <v>159.99</v>
+        <v>59.99</v>
       </c>
       <c r="J915" s="4" t="s">
         <v>40</v>
@@ -80814,31 +80841,31 @@
     </row>
     <row r="916" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
-        <v>1434</v>
+        <v>1423</v>
       </c>
       <c r="B916" s="2" t="s">
-        <v>691</v>
+        <v>788</v>
       </c>
       <c r="C916" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D916" s="4" t="s">
-        <v>1432</v>
+        <v>1416</v>
       </c>
       <c r="E916" s="5" t="s">
-        <v>1433</v>
+        <v>1417</v>
       </c>
       <c r="F916" s="4" t="s">
-        <v>1354</v>
+        <v>791</v>
       </c>
       <c r="G916" s="4" t="s">
-        <v>1341</v>
+        <v>1424</v>
       </c>
       <c r="H916" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I916" s="4">
-        <v>159.99</v>
+        <v>59.99</v>
       </c>
       <c r="J916" s="4" t="s">
         <v>40</v>
@@ -80875,31 +80902,31 @@
     </row>
     <row r="917" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B917" s="2" t="s">
-        <v>691</v>
+        <v>788</v>
       </c>
       <c r="C917" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D917" s="4" t="s">
-        <v>1436</v>
+        <v>1426</v>
       </c>
       <c r="E917" s="5" t="s">
-        <v>1437</v>
+        <v>1427</v>
       </c>
       <c r="F917" s="4" t="s">
-        <v>1354</v>
+        <v>845</v>
       </c>
       <c r="G917" s="4" t="s">
-        <v>69</v>
+        <v>1418</v>
       </c>
       <c r="H917" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I917" s="4">
-        <v>189.99</v>
+        <v>59.99</v>
       </c>
       <c r="J917" s="4" t="s">
         <v>40</v>
@@ -80936,31 +80963,31 @@
     </row>
     <row r="918" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B918" s="2" t="s">
-        <v>691</v>
+        <v>788</v>
       </c>
       <c r="C918" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D918" s="4" t="s">
-        <v>1436</v>
+        <v>1426</v>
       </c>
       <c r="E918" s="5" t="s">
-        <v>1437</v>
+        <v>1427</v>
       </c>
       <c r="F918" s="4" t="s">
-        <v>1354</v>
+        <v>845</v>
       </c>
       <c r="G918" s="4" t="s">
-        <v>1341</v>
+        <v>1420</v>
       </c>
       <c r="H918" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I918" s="4">
-        <v>189.99</v>
+        <v>59.99</v>
       </c>
       <c r="J918" s="4" t="s">
         <v>40</v>
@@ -80997,31 +81024,31 @@
     </row>
     <row r="919" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
-        <v>1439</v>
+        <v>1429</v>
       </c>
       <c r="B919" s="2" t="s">
-        <v>691</v>
+        <v>788</v>
       </c>
       <c r="C919" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D919" s="4" t="s">
-        <v>1440</v>
+        <v>1426</v>
       </c>
       <c r="E919" s="5" t="s">
-        <v>1441</v>
+        <v>1427</v>
       </c>
       <c r="F919" s="4" t="s">
-        <v>701</v>
+        <v>845</v>
       </c>
       <c r="G919" s="4" t="s">
-        <v>69</v>
+        <v>1422</v>
       </c>
       <c r="H919" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I919" s="4">
-        <v>109.99</v>
+        <v>59.99</v>
       </c>
       <c r="J919" s="4" t="s">
         <v>40</v>
@@ -81058,31 +81085,31 @@
     </row>
     <row r="920" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
-        <v>1442</v>
+        <v>1430</v>
       </c>
       <c r="B920" s="2" t="s">
-        <v>691</v>
+        <v>788</v>
       </c>
       <c r="C920" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D920" s="4" t="s">
-        <v>1440</v>
+        <v>1426</v>
       </c>
       <c r="E920" s="5" t="s">
-        <v>1441</v>
+        <v>1427</v>
       </c>
       <c r="F920" s="4" t="s">
-        <v>701</v>
+        <v>845</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>1370</v>
+        <v>1424</v>
       </c>
       <c r="H920" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I920" s="4">
-        <v>109.99</v>
+        <v>59.99</v>
       </c>
       <c r="J920" s="4" t="s">
         <v>40</v>
@@ -81119,7 +81146,7 @@
     </row>
     <row r="921" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="B921" s="2" t="s">
         <v>691</v>
@@ -81128,22 +81155,22 @@
         <v>102</v>
       </c>
       <c r="D921" s="4" t="s">
-        <v>1440</v>
+        <v>1432</v>
       </c>
       <c r="E921" s="5" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="F921" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G921" s="4" t="s">
-        <v>1339</v>
+        <v>69</v>
       </c>
       <c r="H921" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I921" s="4">
-        <v>109.99</v>
+        <v>159.99</v>
       </c>
       <c r="J921" s="4" t="s">
         <v>40</v>
@@ -81180,32 +81207,34 @@
     </row>
     <row r="922" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
-        <v>1535</v>
-      </c>
-      <c r="B922" s="2"/>
+        <v>1434</v>
+      </c>
+      <c r="B922" s="2" t="s">
+        <v>691</v>
+      </c>
       <c r="C922" s="2" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D922" s="4" t="s">
-        <v>1480</v>
+        <v>1432</v>
       </c>
       <c r="E922" s="5" t="s">
-        <v>1481</v>
+        <v>1433</v>
       </c>
       <c r="F922" s="4" t="s">
-        <v>1135</v>
+        <v>1354</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>1404</v>
+        <v>1341</v>
       </c>
       <c r="H922" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I922" s="4">
-        <v>229.99</v>
+        <v>159.99</v>
       </c>
       <c r="J922" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K922" s="4" t="s">
         <v>41</v>
@@ -81239,32 +81268,34 @@
     </row>
     <row r="923" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
-        <v>1536</v>
-      </c>
-      <c r="B923" s="2"/>
+        <v>1435</v>
+      </c>
+      <c r="B923" s="2" t="s">
+        <v>691</v>
+      </c>
       <c r="C923" s="2" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D923" s="4" t="s">
-        <v>1480</v>
+        <v>1436</v>
       </c>
       <c r="E923" s="5" t="s">
-        <v>1481</v>
+        <v>1437</v>
       </c>
       <c r="F923" s="4" t="s">
-        <v>1135</v>
+        <v>1354</v>
       </c>
       <c r="G923" s="4" t="s">
-        <v>1333</v>
+        <v>69</v>
       </c>
       <c r="H923" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I923" s="4">
-        <v>229.99</v>
+        <v>189.99</v>
       </c>
       <c r="J923" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K923" s="4" t="s">
         <v>41</v>
@@ -81298,32 +81329,34 @@
     </row>
     <row r="924" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
-        <v>1537</v>
-      </c>
-      <c r="B924" s="2"/>
+        <v>1438</v>
+      </c>
+      <c r="B924" s="2" t="s">
+        <v>691</v>
+      </c>
       <c r="C924" s="2" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D924" s="4" t="s">
-        <v>1482</v>
+        <v>1436</v>
       </c>
       <c r="E924" s="5" t="s">
-        <v>1483</v>
+        <v>1437</v>
       </c>
       <c r="F924" s="4" t="s">
-        <v>1135</v>
+        <v>1354</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1404</v>
+        <v>1341</v>
       </c>
       <c r="H924" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I924" s="4">
-        <v>229.99</v>
+        <v>189.99</v>
       </c>
       <c r="J924" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K924" s="4" t="s">
         <v>41</v>
@@ -81357,32 +81390,34 @@
     </row>
     <row r="925" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
-        <v>1538</v>
-      </c>
-      <c r="B925" s="2"/>
+        <v>1439</v>
+      </c>
+      <c r="B925" s="2" t="s">
+        <v>691</v>
+      </c>
       <c r="C925" s="2" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D925" s="4" t="s">
-        <v>1482</v>
+        <v>1440</v>
       </c>
       <c r="E925" s="5" t="s">
-        <v>1483</v>
+        <v>1441</v>
       </c>
       <c r="F925" s="4" t="s">
-        <v>1135</v>
+        <v>701</v>
       </c>
       <c r="G925" s="4" t="s">
-        <v>1484</v>
+        <v>69</v>
       </c>
       <c r="H925" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I925" s="4">
-        <v>229.99</v>
+        <v>109.99</v>
       </c>
       <c r="J925" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K925" s="4" t="s">
         <v>41</v>
@@ -81416,32 +81451,34 @@
     </row>
     <row r="926" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
-        <v>1539</v>
-      </c>
-      <c r="B926" s="2"/>
+        <v>1442</v>
+      </c>
+      <c r="B926" s="2" t="s">
+        <v>691</v>
+      </c>
       <c r="C926" s="2" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D926" s="4" t="s">
-        <v>1485</v>
+        <v>1440</v>
       </c>
       <c r="E926" s="5" t="s">
-        <v>1486</v>
+        <v>1441</v>
       </c>
       <c r="F926" s="4" t="s">
-        <v>1135</v>
+        <v>701</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1404</v>
+        <v>1370</v>
       </c>
       <c r="H926" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I926" s="4">
-        <v>199.99</v>
+        <v>109.99</v>
       </c>
       <c r="J926" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K926" s="4" t="s">
         <v>41</v>
@@ -81475,32 +81512,34 @@
     </row>
     <row r="927" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
-        <v>1540</v>
-      </c>
-      <c r="B927" s="2"/>
+        <v>1443</v>
+      </c>
+      <c r="B927" s="2" t="s">
+        <v>691</v>
+      </c>
       <c r="C927" s="2" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D927" s="4" t="s">
-        <v>1485</v>
+        <v>1440</v>
       </c>
       <c r="E927" s="5" t="s">
-        <v>1486</v>
+        <v>1441</v>
       </c>
       <c r="F927" s="4" t="s">
-        <v>1135</v>
+        <v>701</v>
       </c>
       <c r="G927" s="4" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="H927" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I927" s="4">
-        <v>199.99</v>
+        <v>109.99</v>
       </c>
       <c r="J927" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K927" s="4" t="s">
         <v>41</v>
@@ -81534,23 +81573,23 @@
     </row>
     <row r="928" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="B928" s="2"/>
       <c r="C928" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D928" s="4" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="E928" s="5" t="s">
-        <v>1488</v>
+        <v>1481</v>
       </c>
       <c r="F928" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>1414</v>
+        <v>1404</v>
       </c>
       <c r="H928" s="4" t="s">
         <v>39</v>
@@ -81593,17 +81632,17 @@
     </row>
     <row r="929" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
-        <v>1542</v>
+        <v>1536</v>
       </c>
       <c r="B929" s="2"/>
       <c r="C929" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D929" s="4" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="E929" s="5" t="s">
-        <v>1488</v>
+        <v>1481</v>
       </c>
       <c r="F929" s="4" t="s">
         <v>1135</v>
@@ -81652,17 +81691,17 @@
     </row>
     <row r="930" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="B930" s="2"/>
       <c r="C930" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D930" s="4" t="s">
-        <v>1489</v>
+        <v>1482</v>
       </c>
       <c r="E930" s="5" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="F930" s="4" t="s">
         <v>1135</v>
@@ -81674,7 +81713,7 @@
         <v>39</v>
       </c>
       <c r="I930" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J930" s="4" t="s">
         <v>41</v>
@@ -81711,17 +81750,17 @@
     </row>
     <row r="931" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
       <c r="B931" s="2"/>
       <c r="C931" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D931" s="4" t="s">
-        <v>1489</v>
+        <v>1482</v>
       </c>
       <c r="E931" s="5" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="F931" s="4" t="s">
         <v>1135</v>
@@ -81733,7 +81772,7 @@
         <v>39</v>
       </c>
       <c r="I931" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J931" s="4" t="s">
         <v>41</v>
@@ -81770,23 +81809,23 @@
     </row>
     <row r="932" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="B932" s="2"/>
       <c r="C932" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D932" s="4" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="E932" s="5" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="F932" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G932" s="4" t="s">
-        <v>1333</v>
+        <v>1404</v>
       </c>
       <c r="H932" s="4" t="s">
         <v>39</v>
@@ -81829,29 +81868,29 @@
     </row>
     <row r="933" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="B933" s="2"/>
       <c r="C933" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D933" s="4" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
       <c r="E933" s="5" t="s">
-        <v>1492</v>
+        <v>1486</v>
       </c>
       <c r="F933" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G933" s="4" t="s">
-        <v>1404</v>
+        <v>1333</v>
       </c>
       <c r="H933" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I933" s="4">
-        <v>259.99</v>
+        <v>199.99</v>
       </c>
       <c r="J933" s="4" t="s">
         <v>41</v>
@@ -81888,29 +81927,29 @@
     </row>
     <row r="934" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="B934" s="2"/>
       <c r="C934" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D934" s="4" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="E934" s="5" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="F934" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G934" s="4" t="s">
-        <v>1333</v>
+        <v>1414</v>
       </c>
       <c r="H934" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I934" s="4">
-        <v>259.99</v>
+        <v>229.99</v>
       </c>
       <c r="J934" s="4" t="s">
         <v>41</v>
@@ -81947,29 +81986,29 @@
     </row>
     <row r="935" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="B935" s="2"/>
       <c r="C935" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D935" s="4" t="s">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="E935" s="5" t="s">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="F935" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G935" s="4" t="s">
-        <v>1404</v>
+        <v>1333</v>
       </c>
       <c r="H935" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I935" s="4">
-        <v>249.99</v>
+        <v>229.99</v>
       </c>
       <c r="J935" s="4" t="s">
         <v>41</v>
@@ -82006,29 +82045,29 @@
     </row>
     <row r="936" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="B936" s="2"/>
       <c r="C936" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D936" s="4" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="E936" s="5" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="F936" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G936" s="4" t="s">
-        <v>1484</v>
+        <v>1404</v>
       </c>
       <c r="H936" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I936" s="4">
-        <v>249.99</v>
+        <v>199.99</v>
       </c>
       <c r="J936" s="4" t="s">
         <v>41</v>
@@ -82065,29 +82104,29 @@
     </row>
     <row r="937" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="B937" s="2"/>
       <c r="C937" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D937" s="4" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="E937" s="5" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="F937" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G937" s="4" t="s">
-        <v>1404</v>
+        <v>1484</v>
       </c>
       <c r="H937" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I937" s="4">
-        <v>229.99</v>
+        <v>199.99</v>
       </c>
       <c r="J937" s="4" t="s">
         <v>41</v>
@@ -82124,17 +82163,17 @@
     </row>
     <row r="938" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="B938" s="2"/>
       <c r="C938" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D938" s="4" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="E938" s="5" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="F938" s="4" t="s">
         <v>1135</v>
@@ -82146,7 +82185,7 @@
         <v>39</v>
       </c>
       <c r="I938" s="4">
-        <v>229.99</v>
+        <v>199.99</v>
       </c>
       <c r="J938" s="4" t="s">
         <v>41</v>
@@ -82183,29 +82222,29 @@
     </row>
     <row r="939" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
       <c r="B939" s="2"/>
       <c r="C939" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D939" s="4" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="E939" s="5" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="F939" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G939" s="4" t="s">
-        <v>1333</v>
+        <v>1404</v>
       </c>
       <c r="H939" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I939" s="4">
-        <v>379.99</v>
+        <v>259.99</v>
       </c>
       <c r="J939" s="4" t="s">
         <v>41</v>
@@ -82242,29 +82281,29 @@
     </row>
     <row r="940" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="B940" s="2"/>
       <c r="C940" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D940" s="4" t="s">
-        <v>1499</v>
+        <v>1491</v>
       </c>
       <c r="E940" s="5" t="s">
-        <v>1500</v>
+        <v>1492</v>
       </c>
       <c r="F940" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G940" s="4" t="s">
-        <v>1414</v>
+        <v>1333</v>
       </c>
       <c r="H940" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I940" s="4">
-        <v>229.99</v>
+        <v>259.99</v>
       </c>
       <c r="J940" s="4" t="s">
         <v>41</v>
@@ -82301,29 +82340,29 @@
     </row>
     <row r="941" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="B941" s="2"/>
       <c r="C941" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D941" s="4" t="s">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="E941" s="5" t="s">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="F941" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G941" s="4" t="s">
-        <v>1333</v>
+        <v>1404</v>
       </c>
       <c r="H941" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I941" s="4">
-        <v>229.99</v>
+        <v>249.99</v>
       </c>
       <c r="J941" s="4" t="s">
         <v>41</v>
@@ -82360,29 +82399,29 @@
     </row>
     <row r="942" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="B942" s="2"/>
       <c r="C942" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D942" s="4" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="E942" s="5" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
       <c r="F942" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>69</v>
+        <v>1484</v>
       </c>
       <c r="H942" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I942" s="4">
-        <v>199.99</v>
+        <v>249.99</v>
       </c>
       <c r="J942" s="4" t="s">
         <v>41</v>
@@ -82419,29 +82458,29 @@
     </row>
     <row r="943" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="B943" s="2"/>
       <c r="C943" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D943" s="4" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="E943" s="5" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="F943" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G943" s="4" t="s">
-        <v>1333</v>
+        <v>1404</v>
       </c>
       <c r="H943" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I943" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J943" s="4" t="s">
         <v>41</v>
@@ -82478,29 +82517,29 @@
     </row>
     <row r="944" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="B944" s="2"/>
       <c r="C944" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D944" s="4" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="E944" s="5" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="F944" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H944" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I944" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J944" s="4" t="s">
         <v>41</v>
@@ -82537,29 +82576,29 @@
     </row>
     <row r="945" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="B945" s="2"/>
       <c r="C945" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D945" s="4" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="E945" s="5" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
       <c r="F945" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G945" s="4" t="s">
-        <v>1404</v>
+        <v>1333</v>
       </c>
       <c r="H945" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I945" s="4">
-        <v>259.99</v>
+        <v>379.99</v>
       </c>
       <c r="J945" s="4" t="s">
         <v>41</v>
@@ -82596,29 +82635,29 @@
     </row>
     <row r="946" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="B946" s="2"/>
       <c r="C946" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D946" s="4" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="E946" s="5" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="F946" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1333</v>
+        <v>1414</v>
       </c>
       <c r="H946" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I946" s="4">
-        <v>259.99</v>
+        <v>229.99</v>
       </c>
       <c r="J946" s="4" t="s">
         <v>41</v>
@@ -82655,29 +82694,29 @@
     </row>
     <row r="947" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
-        <v>1560</v>
+        <v>1554</v>
       </c>
       <c r="B947" s="2"/>
       <c r="C947" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D947" s="4" t="s">
-        <v>1505</v>
+        <v>1499</v>
       </c>
       <c r="E947" s="5" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="F947" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G947" s="4" t="s">
-        <v>1404</v>
+        <v>1333</v>
       </c>
       <c r="H947" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I947" s="4">
-        <v>249.99</v>
+        <v>229.99</v>
       </c>
       <c r="J947" s="4" t="s">
         <v>41</v>
@@ -82714,29 +82753,29 @@
     </row>
     <row r="948" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="B948" s="2"/>
       <c r="C948" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D948" s="4" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="E948" s="5" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="F948" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1333</v>
+        <v>69</v>
       </c>
       <c r="H948" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I948" s="4">
-        <v>249.99</v>
+        <v>199.99</v>
       </c>
       <c r="J948" s="4" t="s">
         <v>41</v>
@@ -82773,29 +82812,29 @@
     </row>
     <row r="949" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="B949" s="2"/>
       <c r="C949" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D949" s="4" t="s">
-        <v>1507</v>
+        <v>1501</v>
       </c>
       <c r="E949" s="5" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
       <c r="F949" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G949" s="4" t="s">
-        <v>1404</v>
+        <v>1333</v>
       </c>
       <c r="H949" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I949" s="4">
-        <v>239.99</v>
+        <v>199.99</v>
       </c>
       <c r="J949" s="4" t="s">
         <v>41</v>
@@ -82832,29 +82871,29 @@
     </row>
     <row r="950" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
-        <v>1563</v>
+        <v>1557</v>
       </c>
       <c r="B950" s="2"/>
       <c r="C950" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D950" s="4" t="s">
-        <v>1507</v>
+        <v>1501</v>
       </c>
       <c r="E950" s="5" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
       <c r="F950" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G950" s="4" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="H950" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I950" s="4">
-        <v>239.99</v>
+        <v>199.99</v>
       </c>
       <c r="J950" s="4" t="s">
         <v>41</v>
@@ -82891,17 +82930,17 @@
     </row>
     <row r="951" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="B951" s="2"/>
       <c r="C951" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D951" s="4" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="E951" s="5" t="s">
-        <v>1510</v>
+        <v>1504</v>
       </c>
       <c r="F951" s="4" t="s">
         <v>1135</v>
@@ -82913,7 +82952,7 @@
         <v>88</v>
       </c>
       <c r="I951" s="4">
-        <v>219.99</v>
+        <v>259.99</v>
       </c>
       <c r="J951" s="4" t="s">
         <v>41</v>
@@ -82950,17 +82989,17 @@
     </row>
     <row r="952" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
-        <v>1565</v>
+        <v>1559</v>
       </c>
       <c r="B952" s="2"/>
       <c r="C952" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D952" s="4" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
       <c r="E952" s="5" t="s">
-        <v>1512</v>
+        <v>1504</v>
       </c>
       <c r="F952" s="4" t="s">
         <v>1135</v>
@@ -82972,7 +83011,7 @@
         <v>88</v>
       </c>
       <c r="I952" s="4">
-        <v>379.99</v>
+        <v>259.99</v>
       </c>
       <c r="J952" s="4" t="s">
         <v>41</v>
@@ -83009,17 +83048,17 @@
     </row>
     <row r="953" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="B953" s="2"/>
       <c r="C953" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D953" s="4" t="s">
-        <v>1513</v>
+        <v>1505</v>
       </c>
       <c r="E953" s="5" t="s">
-        <v>1514</v>
+        <v>1506</v>
       </c>
       <c r="F953" s="4" t="s">
         <v>1135</v>
@@ -83028,10 +83067,10 @@
         <v>1404</v>
       </c>
       <c r="H953" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I953" s="4">
-        <v>169.99</v>
+        <v>249.99</v>
       </c>
       <c r="J953" s="4" t="s">
         <v>41</v>
@@ -83068,29 +83107,29 @@
     </row>
     <row r="954" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="B954" s="2"/>
       <c r="C954" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D954" s="4" t="s">
-        <v>1513</v>
+        <v>1505</v>
       </c>
       <c r="E954" s="5" t="s">
-        <v>1514</v>
+        <v>1506</v>
       </c>
       <c r="F954" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="H954" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I954" s="4">
-        <v>169.99</v>
+        <v>249.99</v>
       </c>
       <c r="J954" s="4" t="s">
         <v>41</v>
@@ -83127,17 +83166,17 @@
     </row>
     <row r="955" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="B955" s="2"/>
       <c r="C955" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D955" s="4" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
       <c r="E955" s="5" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
       <c r="F955" s="4" t="s">
         <v>1135</v>
@@ -83146,10 +83185,10 @@
         <v>1404</v>
       </c>
       <c r="H955" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I955" s="4">
-        <v>149.99</v>
+        <v>239.99</v>
       </c>
       <c r="J955" s="4" t="s">
         <v>41</v>
@@ -83186,29 +83225,29 @@
     </row>
     <row r="956" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="B956" s="2"/>
       <c r="C956" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D956" s="4" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
       <c r="E956" s="5" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
       <c r="F956" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1517</v>
+        <v>1333</v>
       </c>
       <c r="H956" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I956" s="4">
-        <v>149.99</v>
+        <v>239.99</v>
       </c>
       <c r="J956" s="4" t="s">
         <v>41</v>
@@ -83245,17 +83284,17 @@
     </row>
     <row r="957" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="B957" s="2"/>
       <c r="C957" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D957" s="4" t="s">
-        <v>1518</v>
+        <v>1509</v>
       </c>
       <c r="E957" s="5" t="s">
-        <v>1519</v>
+        <v>1510</v>
       </c>
       <c r="F957" s="4" t="s">
         <v>1135</v>
@@ -83264,10 +83303,10 @@
         <v>1404</v>
       </c>
       <c r="H957" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I957" s="4">
-        <v>249.99</v>
+        <v>219.99</v>
       </c>
       <c r="J957" s="4" t="s">
         <v>41</v>
@@ -83304,17 +83343,17 @@
     </row>
     <row r="958" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
-        <v>1571</v>
+        <v>1565</v>
       </c>
       <c r="B958" s="2"/>
       <c r="C958" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D958" s="4" t="s">
-        <v>1518</v>
+        <v>1511</v>
       </c>
       <c r="E958" s="5" t="s">
-        <v>1519</v>
+        <v>1512</v>
       </c>
       <c r="F958" s="4" t="s">
         <v>1135</v>
@@ -83323,10 +83362,10 @@
         <v>1333</v>
       </c>
       <c r="H958" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I958" s="4">
-        <v>249.99</v>
+        <v>379.99</v>
       </c>
       <c r="J958" s="4" t="s">
         <v>41</v>
@@ -83363,17 +83402,17 @@
     </row>
     <row r="959" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="B959" s="2"/>
       <c r="C959" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D959" s="4" t="s">
-        <v>1520</v>
+        <v>1513</v>
       </c>
       <c r="E959" s="5" t="s">
-        <v>1521</v>
+        <v>1514</v>
       </c>
       <c r="F959" s="4" t="s">
         <v>1135</v>
@@ -83385,7 +83424,7 @@
         <v>39</v>
       </c>
       <c r="I959" s="4">
-        <v>179.99</v>
+        <v>169.99</v>
       </c>
       <c r="J959" s="4" t="s">
         <v>41</v>
@@ -83422,29 +83461,29 @@
     </row>
     <row r="960" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="B960" s="2"/>
       <c r="C960" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D960" s="4" t="s">
-        <v>1520</v>
+        <v>1513</v>
       </c>
       <c r="E960" s="5" t="s">
-        <v>1521</v>
+        <v>1514</v>
       </c>
       <c r="F960" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G960" s="4" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H960" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I960" s="4">
-        <v>179.99</v>
+        <v>169.99</v>
       </c>
       <c r="J960" s="4" t="s">
         <v>41</v>
@@ -83481,29 +83520,29 @@
     </row>
     <row r="961" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="B961" s="2"/>
       <c r="C961" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D961" s="4" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="E961" s="5" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="F961" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G961" s="4" t="s">
-        <v>1329</v>
+        <v>1404</v>
       </c>
       <c r="H961" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I961" s="4">
-        <v>179.99</v>
+        <v>149.99</v>
       </c>
       <c r="J961" s="4" t="s">
         <v>41</v>
@@ -83540,29 +83579,29 @@
     </row>
     <row r="962" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="B962" s="2"/>
       <c r="C962" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D962" s="4" t="s">
-        <v>1522</v>
+        <v>1515</v>
       </c>
       <c r="E962" s="5" t="s">
-        <v>1523</v>
+        <v>1516</v>
       </c>
       <c r="F962" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G962" s="4" t="s">
-        <v>1404</v>
+        <v>1517</v>
       </c>
       <c r="H962" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I962" s="4">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="J962" s="4" t="s">
         <v>41</v>
@@ -83599,23 +83638,23 @@
     </row>
     <row r="963" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
-        <v>1576</v>
+        <v>1570</v>
       </c>
       <c r="B963" s="2"/>
       <c r="C963" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D963" s="4" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="E963" s="5" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="F963" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G963" s="4" t="s">
-        <v>1333</v>
+        <v>1404</v>
       </c>
       <c r="H963" s="4" t="s">
         <v>39</v>
@@ -83658,29 +83697,29 @@
     </row>
     <row r="964" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="B964" s="2"/>
       <c r="C964" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D964" s="4" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
       <c r="E964" s="5" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="F964" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G964" s="4" t="s">
-        <v>1404</v>
+        <v>1333</v>
       </c>
       <c r="H964" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I964" s="4">
-        <v>149.99</v>
+        <v>249.99</v>
       </c>
       <c r="J964" s="4" t="s">
         <v>41</v>
@@ -83717,29 +83756,29 @@
     </row>
     <row r="965" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="B965" s="2"/>
       <c r="C965" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D965" s="4" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="E965" s="5" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="F965" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G965" s="4" t="s">
-        <v>1517</v>
+        <v>1404</v>
       </c>
       <c r="H965" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I965" s="4">
-        <v>149.99</v>
+        <v>179.99</v>
       </c>
       <c r="J965" s="4" t="s">
         <v>41</v>
@@ -83776,29 +83815,29 @@
     </row>
     <row r="966" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="B966" s="2"/>
       <c r="C966" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D966" s="4" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="E966" s="5" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="F966" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>1404</v>
+        <v>1333</v>
       </c>
       <c r="H966" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I966" s="4">
-        <v>219.99</v>
+        <v>179.99</v>
       </c>
       <c r="J966" s="4" t="s">
         <v>41</v>
@@ -83835,29 +83874,29 @@
     </row>
     <row r="967" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="B967" s="2"/>
       <c r="C967" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D967" s="4" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="E967" s="5" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="F967" s="4" t="s">
         <v>1135</v>
       </c>
       <c r="G967" s="4" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H967" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I967" s="4">
-        <v>219.99</v>
+        <v>179.99</v>
       </c>
       <c r="J967" s="4" t="s">
         <v>41</v>
@@ -83894,29 +83933,29 @@
     </row>
     <row r="968" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="B968" s="2"/>
       <c r="C968" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D968" s="4" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="E968" s="5" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="F968" s="4" t="s">
-        <v>725</v>
+        <v>1135</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>771</v>
+        <v>1404</v>
       </c>
       <c r="H968" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I968" s="4">
-        <v>79.989999999999995</v>
+        <v>249.99</v>
       </c>
       <c r="J968" s="4" t="s">
         <v>41</v>
@@ -83953,29 +83992,29 @@
     </row>
     <row r="969" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="B969" s="2"/>
       <c r="C969" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D969" s="4" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="E969" s="5" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="F969" s="4" t="s">
-        <v>725</v>
+        <v>1135</v>
       </c>
       <c r="G969" s="4" t="s">
-        <v>69</v>
+        <v>1333</v>
       </c>
       <c r="H969" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I969" s="4">
-        <v>79.989999999999995</v>
+        <v>249.99</v>
       </c>
       <c r="J969" s="4" t="s">
         <v>41</v>
@@ -84012,34 +84051,36 @@
     </row>
     <row r="970" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="B970" s="2"/>
       <c r="C970" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D970" s="4" t="s">
-        <v>1343</v>
+        <v>1524</v>
       </c>
       <c r="E970" s="5" t="s">
-        <v>1344</v>
+        <v>1525</v>
       </c>
       <c r="F970" s="4" t="s">
-        <v>701</v>
+        <v>1135</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>69</v>
+        <v>1404</v>
       </c>
       <c r="H970" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I970" s="4">
         <v>149.99</v>
       </c>
       <c r="J970" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K970" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K970" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L970" s="4" t="s">
         <v>42</v>
       </c>
@@ -84069,34 +84110,36 @@
     </row>
     <row r="971" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="B971" s="2"/>
       <c r="C971" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D971" s="4" t="s">
-        <v>1083</v>
+        <v>1524</v>
       </c>
       <c r="E971" s="5" t="s">
-        <v>1353</v>
+        <v>1525</v>
       </c>
       <c r="F971" s="4" t="s">
-        <v>1354</v>
+        <v>1135</v>
       </c>
       <c r="G971" s="4" t="s">
-        <v>771</v>
+        <v>1517</v>
       </c>
       <c r="H971" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I971" s="4">
-        <v>99.99</v>
+        <v>149.99</v>
       </c>
       <c r="J971" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K971" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K971" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L971" s="4" t="s">
         <v>42</v>
       </c>
@@ -84126,34 +84169,36 @@
     </row>
     <row r="972" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
-        <v>1585</v>
+        <v>1579</v>
       </c>
       <c r="B972" s="2"/>
       <c r="C972" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D972" s="4" t="s">
-        <v>1094</v>
+        <v>1526</v>
       </c>
       <c r="E972" s="5" t="s">
-        <v>1356</v>
+        <v>1527</v>
       </c>
       <c r="F972" s="4" t="s">
-        <v>1354</v>
+        <v>1135</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>771</v>
+        <v>1404</v>
       </c>
       <c r="H972" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I972" s="4">
-        <v>89.99</v>
+        <v>219.99</v>
       </c>
       <c r="J972" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K972" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K972" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L972" s="4" t="s">
         <v>42</v>
       </c>
@@ -84183,34 +84228,36 @@
     </row>
     <row r="973" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="B973" s="2"/>
       <c r="C973" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D973" s="4" t="s">
-        <v>1587</v>
+        <v>1526</v>
       </c>
       <c r="E973" s="5" t="s">
-        <v>1356</v>
+        <v>1527</v>
       </c>
       <c r="F973" s="4" t="s">
-        <v>701</v>
+        <v>1135</v>
       </c>
       <c r="G973" s="4" t="s">
-        <v>726</v>
+        <v>1333</v>
       </c>
       <c r="H973" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I973" s="4">
-        <v>89.99</v>
+        <v>219.99</v>
       </c>
       <c r="J973" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K973" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K973" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L973" s="4" t="s">
         <v>42</v>
       </c>
@@ -84240,34 +84287,36 @@
     </row>
     <row r="974" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
       <c r="B974" s="2"/>
       <c r="C974" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D974" s="4" t="s">
-        <v>1587</v>
+        <v>1528</v>
       </c>
       <c r="E974" s="5" t="s">
-        <v>1356</v>
+        <v>1529</v>
       </c>
       <c r="F974" s="4" t="s">
-        <v>701</v>
+        <v>725</v>
       </c>
       <c r="G974" s="4" t="s">
-        <v>69</v>
+        <v>771</v>
       </c>
       <c r="H974" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I974" s="4">
-        <v>89.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J974" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K974" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K974" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L974" s="4" t="s">
         <v>42</v>
       </c>
@@ -84297,34 +84346,36 @@
     </row>
     <row r="975" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="B975" s="2"/>
       <c r="C975" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D975" s="4" t="s">
-        <v>1587</v>
+        <v>1528</v>
       </c>
       <c r="E975" s="5" t="s">
-        <v>1356</v>
+        <v>1529</v>
       </c>
       <c r="F975" s="4" t="s">
-        <v>701</v>
+        <v>725</v>
       </c>
       <c r="G975" s="4" t="s">
-        <v>925</v>
+        <v>69</v>
       </c>
       <c r="H975" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I975" s="4">
-        <v>89.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J975" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K975" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K975" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L975" s="4" t="s">
         <v>42</v>
       </c>
@@ -84354,20 +84405,20 @@
     </row>
     <row r="976" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="B976" s="2"/>
       <c r="C976" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D976" s="4" t="s">
-        <v>1361</v>
+        <v>1343</v>
       </c>
       <c r="E976" s="5" t="s">
-        <v>1362</v>
+        <v>1344</v>
       </c>
       <c r="F976" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G976" s="4" t="s">
         <v>69</v>
@@ -84376,7 +84427,7 @@
         <v>39</v>
       </c>
       <c r="I976" s="4">
-        <v>79.989999999999995</v>
+        <v>149.99</v>
       </c>
       <c r="J976" s="4" t="s">
         <v>40</v>
@@ -84411,17 +84462,17 @@
     </row>
     <row r="977" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="B977" s="2"/>
       <c r="C977" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D977" s="4" t="s">
-        <v>1361</v>
+        <v>1083</v>
       </c>
       <c r="E977" s="5" t="s">
-        <v>1362</v>
+        <v>1353</v>
       </c>
       <c r="F977" s="4" t="s">
         <v>1354</v>
@@ -84433,7 +84484,7 @@
         <v>39</v>
       </c>
       <c r="I977" s="4">
-        <v>79.989999999999995</v>
+        <v>99.99</v>
       </c>
       <c r="J977" s="4" t="s">
         <v>40</v>
@@ -84468,29 +84519,29 @@
     </row>
     <row r="978" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="B978" s="2"/>
       <c r="C978" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D978" s="4" t="s">
-        <v>1361</v>
+        <v>1094</v>
       </c>
       <c r="E978" s="5" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="F978" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>377</v>
+        <v>771</v>
       </c>
       <c r="H978" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I978" s="4">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="J978" s="4" t="s">
         <v>40</v>
@@ -84525,29 +84576,29 @@
     </row>
     <row r="979" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="B979" s="2"/>
       <c r="C979" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D979" s="4" t="s">
-        <v>1361</v>
+        <v>1587</v>
       </c>
       <c r="E979" s="5" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="F979" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G979" s="4" t="s">
-        <v>972</v>
+        <v>726</v>
       </c>
       <c r="H979" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I979" s="4">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="J979" s="4" t="s">
         <v>40</v>
@@ -84582,29 +84633,29 @@
     </row>
     <row r="980" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
       <c r="B980" s="2"/>
       <c r="C980" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D980" s="4" t="s">
-        <v>1361</v>
+        <v>1587</v>
       </c>
       <c r="E980" s="5" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="F980" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>368</v>
+        <v>69</v>
       </c>
       <c r="H980" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I980" s="4">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="J980" s="4" t="s">
         <v>40</v>
@@ -84639,29 +84690,29 @@
     </row>
     <row r="981" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="B981" s="2"/>
       <c r="C981" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D981" s="4" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="E981" s="5" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="F981" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G981" s="4" t="s">
-        <v>69</v>
+        <v>925</v>
       </c>
       <c r="H981" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I981" s="4">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="J981" s="4" t="s">
         <v>40</v>
@@ -84696,23 +84747,23 @@
     </row>
     <row r="982" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="B982" s="2"/>
       <c r="C982" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D982" s="4" t="s">
-        <v>1596</v>
+        <v>1361</v>
       </c>
       <c r="E982" s="5" t="s">
         <v>1362</v>
       </c>
       <c r="F982" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>726</v>
+        <v>69</v>
       </c>
       <c r="H982" s="4" t="s">
         <v>39</v>
@@ -84753,26 +84804,26 @@
     </row>
     <row r="983" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="B983" s="2"/>
       <c r="C983" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D983" s="4" t="s">
-        <v>1374</v>
+        <v>1361</v>
       </c>
       <c r="E983" s="5" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="F983" s="4" t="s">
         <v>1354</v>
       </c>
       <c r="G983" s="4" t="s">
-        <v>69</v>
+        <v>771</v>
       </c>
       <c r="H983" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I983" s="4">
         <v>79.989999999999995</v>
@@ -84810,26 +84861,26 @@
     </row>
     <row r="984" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="B984" s="2"/>
       <c r="C984" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D984" s="4" t="s">
-        <v>1374</v>
+        <v>1361</v>
       </c>
       <c r="E984" s="5" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="F984" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>771</v>
+        <v>377</v>
       </c>
       <c r="H984" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I984" s="4">
         <v>79.989999999999995</v>
@@ -84867,26 +84918,26 @@
     </row>
     <row r="985" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
-        <v>1600</v>
+        <v>1593</v>
       </c>
       <c r="B985" s="2"/>
       <c r="C985" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D985" s="4" t="s">
-        <v>1374</v>
+        <v>1361</v>
       </c>
       <c r="E985" s="5" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="F985" s="4" t="s">
-        <v>1354</v>
+        <v>701</v>
       </c>
       <c r="G985" s="4" t="s">
-        <v>377</v>
+        <v>972</v>
       </c>
       <c r="H985" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I985" s="4">
         <v>79.989999999999995</v>
@@ -84924,17 +84975,17 @@
     </row>
     <row r="986" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
-        <v>1601</v>
+        <v>1594</v>
       </c>
       <c r="B986" s="2"/>
       <c r="C986" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D986" s="4" t="s">
-        <v>1374</v>
+        <v>1361</v>
       </c>
       <c r="E986" s="5" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="F986" s="4" t="s">
         <v>701</v>
@@ -84943,7 +84994,7 @@
         <v>368</v>
       </c>
       <c r="H986" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I986" s="4">
         <v>79.989999999999995</v>
@@ -84981,26 +85032,26 @@
     </row>
     <row r="987" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="B987" s="2"/>
       <c r="C987" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D987" s="4" t="s">
-        <v>1374</v>
+        <v>1596</v>
       </c>
       <c r="E987" s="5" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="F987" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G987" s="4" t="s">
-        <v>938</v>
+        <v>69</v>
       </c>
       <c r="H987" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I987" s="4">
         <v>79.989999999999995</v>
@@ -85038,26 +85089,26 @@
     </row>
     <row r="988" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="B988" s="2"/>
       <c r="C988" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D988" s="4" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="E988" s="5" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="F988" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1183</v>
+        <v>726</v>
       </c>
       <c r="H988" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I988" s="4">
         <v>79.989999999999995</v>
@@ -85095,23 +85146,23 @@
     </row>
     <row r="989" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
-        <v>1605</v>
+        <v>1598</v>
       </c>
       <c r="B989" s="2"/>
       <c r="C989" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D989" s="4" t="s">
-        <v>1604</v>
+        <v>1374</v>
       </c>
       <c r="E989" s="5" t="s">
         <v>1375</v>
       </c>
       <c r="F989" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G989" s="4" t="s">
-        <v>771</v>
+        <v>69</v>
       </c>
       <c r="H989" s="4" t="s">
         <v>88</v>
@@ -85152,29 +85203,29 @@
     </row>
     <row r="990" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="B990" s="2"/>
       <c r="C990" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D990" s="4" t="s">
-        <v>1197</v>
+        <v>1374</v>
       </c>
       <c r="E990" s="5" t="s">
-        <v>1198</v>
+        <v>1375</v>
       </c>
       <c r="F990" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>69</v>
+        <v>771</v>
       </c>
       <c r="H990" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I990" s="4">
-        <v>109.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J990" s="4" t="s">
         <v>40</v>
@@ -85209,29 +85260,29 @@
     </row>
     <row r="991" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
-        <v>1607</v>
+        <v>1600</v>
       </c>
       <c r="B991" s="2"/>
       <c r="C991" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D991" s="4" t="s">
-        <v>1212</v>
+        <v>1374</v>
       </c>
       <c r="E991" s="5" t="s">
-        <v>1441</v>
+        <v>1375</v>
       </c>
       <c r="F991" s="4" t="s">
-        <v>701</v>
+        <v>1354</v>
       </c>
       <c r="G991" s="4" t="s">
-        <v>1608</v>
+        <v>377</v>
       </c>
       <c r="H991" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I991" s="4">
-        <v>99.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J991" s="4" t="s">
         <v>40</v>
@@ -85266,29 +85317,29 @@
     </row>
     <row r="992" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="B992" s="2"/>
       <c r="C992" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D992" s="4" t="s">
-        <v>1212</v>
+        <v>1374</v>
       </c>
       <c r="E992" s="5" t="s">
-        <v>1441</v>
+        <v>1375</v>
       </c>
       <c r="F992" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1610</v>
+        <v>368</v>
       </c>
       <c r="H992" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I992" s="4">
-        <v>99.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J992" s="4" t="s">
         <v>40</v>
@@ -85323,29 +85374,29 @@
     </row>
     <row r="993" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
-        <v>1611</v>
+        <v>1602</v>
       </c>
       <c r="B993" s="2"/>
       <c r="C993" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D993" s="4" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="E993" s="5" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
       <c r="F993" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G993" s="4" t="s">
-        <v>1612</v>
+        <v>938</v>
       </c>
       <c r="H993" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I993" s="4">
-        <v>119.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J993" s="4" t="s">
         <v>40</v>
@@ -85380,36 +85431,34 @@
     </row>
     <row r="994" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
-        <v>1613</v>
+        <v>1603</v>
       </c>
       <c r="B994" s="2"/>
       <c r="C994" s="2" t="s">
-        <v>584</v>
+        <v>102</v>
       </c>
       <c r="D994" s="4" t="s">
-        <v>1530</v>
+        <v>1604</v>
       </c>
       <c r="E994" s="5" t="s">
-        <v>1531</v>
+        <v>1375</v>
       </c>
       <c r="F994" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>69</v>
+        <v>1183</v>
       </c>
       <c r="H994" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I994" s="4">
-        <v>149.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J994" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K994" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K994" s="4"/>
       <c r="L994" s="4" t="s">
         <v>42</v>
       </c>
@@ -85439,36 +85488,34 @@
     </row>
     <row r="995" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
-        <v>1614</v>
+        <v>1605</v>
       </c>
       <c r="B995" s="2"/>
       <c r="C995" s="2" t="s">
-        <v>584</v>
+        <v>102</v>
       </c>
       <c r="D995" s="4" t="s">
-        <v>1530</v>
+        <v>1604</v>
       </c>
       <c r="E995" s="5" t="s">
-        <v>1531</v>
+        <v>1375</v>
       </c>
       <c r="F995" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G995" s="4" t="s">
-        <v>755</v>
+        <v>771</v>
       </c>
       <c r="H995" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I995" s="4">
-        <v>149.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J995" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K995" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K995" s="4"/>
       <c r="L995" s="4" t="s">
         <v>42</v>
       </c>
@@ -85498,29 +85545,29 @@
     </row>
     <row r="996" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
-        <v>1615</v>
+        <v>1606</v>
       </c>
       <c r="B996" s="2"/>
       <c r="C996" s="2" t="s">
-        <v>584</v>
+        <v>102</v>
       </c>
       <c r="D996" s="4" t="s">
-        <v>1444</v>
+        <v>1197</v>
       </c>
       <c r="E996" s="5" t="s">
-        <v>1445</v>
+        <v>1198</v>
       </c>
       <c r="F996" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>702</v>
+        <v>69</v>
       </c>
       <c r="H996" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I996" s="4">
-        <v>129.99</v>
+        <v>109.99</v>
       </c>
       <c r="J996" s="4" t="s">
         <v>40</v>
@@ -85555,29 +85602,29 @@
     </row>
     <row r="997" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
-        <v>1616</v>
+        <v>1607</v>
       </c>
       <c r="B997" s="2"/>
       <c r="C997" s="2" t="s">
-        <v>584</v>
+        <v>102</v>
       </c>
       <c r="D997" s="4" t="s">
-        <v>1617</v>
+        <v>1212</v>
       </c>
       <c r="E997" s="5" t="s">
-        <v>1618</v>
+        <v>1441</v>
       </c>
       <c r="F997" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G997" s="4" t="s">
-        <v>69</v>
+        <v>1608</v>
       </c>
       <c r="H997" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I997" s="4">
-        <v>119.99</v>
+        <v>99.99</v>
       </c>
       <c r="J997" s="4" t="s">
         <v>40</v>
@@ -85612,29 +85659,29 @@
     </row>
     <row r="998" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
-        <v>1619</v>
+        <v>1609</v>
       </c>
       <c r="B998" s="2"/>
       <c r="C998" s="2" t="s">
-        <v>584</v>
+        <v>102</v>
       </c>
       <c r="D998" s="4" t="s">
-        <v>1620</v>
+        <v>1212</v>
       </c>
       <c r="E998" s="5" t="s">
-        <v>1621</v>
+        <v>1441</v>
       </c>
       <c r="F998" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G998" s="4" t="s">
-        <v>1622</v>
+        <v>1610</v>
       </c>
       <c r="H998" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I998" s="4">
-        <v>169.99</v>
+        <v>99.99</v>
       </c>
       <c r="J998" s="4" t="s">
         <v>40</v>
@@ -85669,29 +85716,29 @@
     </row>
     <row r="999" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
-        <v>1623</v>
+        <v>1611</v>
       </c>
       <c r="B999" s="2"/>
       <c r="C999" s="2" t="s">
-        <v>584</v>
+        <v>102</v>
       </c>
       <c r="D999" s="4" t="s">
-        <v>1620</v>
+        <v>1381</v>
       </c>
       <c r="E999" s="5" t="s">
-        <v>1621</v>
+        <v>1382</v>
       </c>
       <c r="F999" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G999" s="4" t="s">
-        <v>695</v>
+        <v>1612</v>
       </c>
       <c r="H999" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I999" s="4">
-        <v>169.99</v>
+        <v>119.99</v>
       </c>
       <c r="J999" s="4" t="s">
         <v>40</v>
@@ -85726,17 +85773,17 @@
     </row>
     <row r="1000" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
-        <v>1624</v>
+        <v>1613</v>
       </c>
       <c r="B1000" s="2"/>
       <c r="C1000" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1000" s="4" t="s">
-        <v>1620</v>
+        <v>1530</v>
       </c>
       <c r="E1000" s="5" t="s">
-        <v>1621</v>
+        <v>1531</v>
       </c>
       <c r="F1000" s="4" t="s">
         <v>701</v>
@@ -85748,12 +85795,14 @@
         <v>39</v>
       </c>
       <c r="I1000" s="4">
-        <v>169.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1000" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1000" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K1000" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L1000" s="4" t="s">
         <v>42</v>
       </c>
@@ -85783,23 +85832,23 @@
     </row>
     <row r="1001" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
-        <v>1625</v>
+        <v>1614</v>
       </c>
       <c r="B1001" s="2"/>
       <c r="C1001" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1001" s="4" t="s">
-        <v>1626</v>
+        <v>1530</v>
       </c>
       <c r="E1001" s="5" t="s">
-        <v>1627</v>
+        <v>1531</v>
       </c>
       <c r="F1001" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G1001" s="4" t="s">
-        <v>1622</v>
+        <v>755</v>
       </c>
       <c r="H1001" s="4" t="s">
         <v>39</v>
@@ -85808,9 +85857,11 @@
         <v>149.99</v>
       </c>
       <c r="J1001" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1001" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K1001" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L1001" s="4" t="s">
         <v>42</v>
       </c>
@@ -85840,29 +85891,29 @@
     </row>
     <row r="1002" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
-        <v>1628</v>
+        <v>1615</v>
       </c>
       <c r="B1002" s="2"/>
       <c r="C1002" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1002" s="4" t="s">
-        <v>1626</v>
+        <v>1444</v>
       </c>
       <c r="E1002" s="5" t="s">
-        <v>1627</v>
+        <v>1445</v>
       </c>
       <c r="F1002" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G1002" s="4" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="H1002" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I1002" s="4">
-        <v>149.99</v>
+        <v>129.99</v>
       </c>
       <c r="J1002" s="4" t="s">
         <v>40</v>
@@ -85897,17 +85948,17 @@
     </row>
     <row r="1003" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
-        <v>1629</v>
+        <v>1616</v>
       </c>
       <c r="B1003" s="2"/>
       <c r="C1003" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1003" s="4" t="s">
-        <v>1626</v>
+        <v>1617</v>
       </c>
       <c r="E1003" s="5" t="s">
-        <v>1627</v>
+        <v>1618</v>
       </c>
       <c r="F1003" s="4" t="s">
         <v>701</v>
@@ -85919,7 +85970,7 @@
         <v>39</v>
       </c>
       <c r="I1003" s="4">
-        <v>149.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1003" s="4" t="s">
         <v>40</v>
@@ -85954,29 +86005,29 @@
     </row>
     <row r="1004" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
-        <v>1630</v>
+        <v>1619</v>
       </c>
       <c r="B1004" s="2"/>
       <c r="C1004" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1004" s="4" t="s">
-        <v>1631</v>
+        <v>1620</v>
       </c>
       <c r="E1004" s="5" t="s">
-        <v>1632</v>
+        <v>1621</v>
       </c>
       <c r="F1004" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>377</v>
+        <v>1622</v>
       </c>
       <c r="H1004" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I1004" s="4">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="J1004" s="4" t="s">
         <v>40</v>
@@ -86011,29 +86062,29 @@
     </row>
     <row r="1005" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
-        <v>1633</v>
+        <v>1623</v>
       </c>
       <c r="B1005" s="2"/>
       <c r="C1005" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1005" s="4" t="s">
-        <v>1631</v>
+        <v>1620</v>
       </c>
       <c r="E1005" s="5" t="s">
-        <v>1632</v>
+        <v>1621</v>
       </c>
       <c r="F1005" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G1005" s="4" t="s">
-        <v>69</v>
+        <v>695</v>
       </c>
       <c r="H1005" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I1005" s="4">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="J1005" s="4" t="s">
         <v>40</v>
@@ -86068,29 +86119,29 @@
     </row>
     <row r="1006" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
-        <v>1634</v>
+        <v>1624</v>
       </c>
       <c r="B1006" s="2"/>
       <c r="C1006" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1006" s="4" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="E1006" s="5" t="s">
-        <v>1636</v>
+        <v>1621</v>
       </c>
       <c r="F1006" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G1006" s="4" t="s">
-        <v>753</v>
+        <v>69</v>
       </c>
       <c r="H1006" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I1006" s="4">
-        <v>179.99</v>
+        <v>169.99</v>
       </c>
       <c r="J1006" s="4" t="s">
         <v>40</v>
@@ -86125,29 +86176,29 @@
     </row>
     <row r="1007" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
-        <v>1637</v>
+        <v>1625</v>
       </c>
       <c r="B1007" s="2"/>
       <c r="C1007" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1007" s="4" t="s">
-        <v>1635</v>
+        <v>1626</v>
       </c>
       <c r="E1007" s="5" t="s">
-        <v>1636</v>
+        <v>1627</v>
       </c>
       <c r="F1007" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G1007" s="4" t="s">
-        <v>69</v>
+        <v>1622</v>
       </c>
       <c r="H1007" s="4" t="s">
         <v>39</v>
       </c>
       <c r="I1007" s="4">
-        <v>179.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1007" s="4" t="s">
         <v>40</v>
@@ -86182,17 +86233,17 @@
     </row>
     <row r="1008" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
-        <v>1638</v>
+        <v>1628</v>
       </c>
       <c r="B1008" s="2"/>
       <c r="C1008" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1008" s="4" t="s">
-        <v>1639</v>
+        <v>1626</v>
       </c>
       <c r="E1008" s="5" t="s">
-        <v>1640</v>
+        <v>1627</v>
       </c>
       <c r="F1008" s="4" t="s">
         <v>701</v>
@@ -86239,29 +86290,29 @@
     </row>
     <row r="1009" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
-        <v>1641</v>
+        <v>1629</v>
       </c>
       <c r="B1009" s="2"/>
       <c r="C1009" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1009" s="4" t="s">
-        <v>1642</v>
+        <v>1626</v>
       </c>
       <c r="E1009" s="5" t="s">
-        <v>1643</v>
+        <v>1627</v>
       </c>
       <c r="F1009" s="4" t="s">
-        <v>1135</v>
+        <v>701</v>
       </c>
       <c r="G1009" s="4" t="s">
-        <v>1644</v>
+        <v>69</v>
       </c>
       <c r="H1009" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I1009" s="4">
-        <v>119.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1009" s="4" t="s">
         <v>40</v>
@@ -86296,26 +86347,26 @@
     </row>
     <row r="1010" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
-        <v>1645</v>
+        <v>1630</v>
       </c>
       <c r="B1010" s="2"/>
       <c r="C1010" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1010" s="4" t="s">
-        <v>1642</v>
+        <v>1631</v>
       </c>
       <c r="E1010" s="5" t="s">
-        <v>1643</v>
+        <v>1632</v>
       </c>
       <c r="F1010" s="4" t="s">
-        <v>1135</v>
+        <v>701</v>
       </c>
       <c r="G1010" s="4" t="s">
-        <v>1077</v>
+        <v>377</v>
       </c>
       <c r="H1010" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I1010" s="4">
         <v>119.99</v>
@@ -86353,26 +86404,26 @@
     </row>
     <row r="1011" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="2" t="s">
-        <v>1646</v>
+        <v>1633</v>
       </c>
       <c r="B1011" s="2"/>
       <c r="C1011" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1011" s="4" t="s">
-        <v>1642</v>
+        <v>1631</v>
       </c>
       <c r="E1011" s="5" t="s">
-        <v>1643</v>
+        <v>1632</v>
       </c>
       <c r="F1011" s="4" t="s">
-        <v>1135</v>
+        <v>701</v>
       </c>
       <c r="G1011" s="4" t="s">
-        <v>1647</v>
+        <v>69</v>
       </c>
       <c r="H1011" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I1011" s="4">
         <v>119.99</v>
@@ -86410,36 +86461,34 @@
     </row>
     <row r="1012" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="2" t="s">
-        <v>1648</v>
+        <v>1634</v>
       </c>
       <c r="B1012" s="2"/>
       <c r="C1012" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1012" s="4" t="s">
-        <v>1532</v>
+        <v>1635</v>
       </c>
       <c r="E1012" s="5" t="s">
-        <v>1533</v>
+        <v>1636</v>
       </c>
       <c r="F1012" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G1012" s="4" t="s">
-        <v>69</v>
+        <v>753</v>
       </c>
       <c r="H1012" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I1012" s="4">
-        <v>149.99</v>
+        <v>179.99</v>
       </c>
       <c r="J1012" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1012" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K1012" s="4"/>
       <c r="L1012" s="4" t="s">
         <v>42</v>
       </c>
@@ -86469,36 +86518,34 @@
     </row>
     <row r="1013" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="2" t="s">
-        <v>1649</v>
+        <v>1637</v>
       </c>
       <c r="B1013" s="2"/>
       <c r="C1013" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1013" s="4" t="s">
-        <v>1532</v>
+        <v>1635</v>
       </c>
       <c r="E1013" s="5" t="s">
-        <v>1533</v>
+        <v>1636</v>
       </c>
       <c r="F1013" s="4" t="s">
         <v>701</v>
       </c>
       <c r="G1013" s="4" t="s">
-        <v>755</v>
+        <v>69</v>
       </c>
       <c r="H1013" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I1013" s="4">
-        <v>149.99</v>
+        <v>179.99</v>
       </c>
       <c r="J1013" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1013" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K1013" s="4"/>
       <c r="L1013" s="4" t="s">
         <v>42</v>
       </c>
@@ -86528,17 +86575,17 @@
     </row>
     <row r="1014" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
-        <v>1650</v>
+        <v>1638</v>
       </c>
       <c r="B1014" s="2"/>
       <c r="C1014" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1014" s="4" t="s">
-        <v>1651</v>
+        <v>1639</v>
       </c>
       <c r="E1014" s="5" t="s">
-        <v>1652</v>
+        <v>1640</v>
       </c>
       <c r="F1014" s="4" t="s">
         <v>701</v>
@@ -86547,10 +86594,10 @@
         <v>695</v>
       </c>
       <c r="H1014" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I1014" s="4">
-        <v>179.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1014" s="4" t="s">
         <v>40</v>
@@ -86585,29 +86632,29 @@
     </row>
     <row r="1015" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="2" t="s">
-        <v>1653</v>
+        <v>1641</v>
       </c>
       <c r="B1015" s="2"/>
       <c r="C1015" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1015" s="4" t="s">
-        <v>1651</v>
+        <v>1642</v>
       </c>
       <c r="E1015" s="5" t="s">
-        <v>1652</v>
+        <v>1643</v>
       </c>
       <c r="F1015" s="4" t="s">
-        <v>701</v>
+        <v>1135</v>
       </c>
       <c r="G1015" s="4" t="s">
-        <v>69</v>
+        <v>1644</v>
       </c>
       <c r="H1015" s="4" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I1015" s="4">
-        <v>179.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1015" s="4" t="s">
         <v>40</v>
@@ -86642,29 +86689,29 @@
     </row>
     <row r="1016" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="2" t="s">
-        <v>1654</v>
+        <v>1645</v>
       </c>
       <c r="B1016" s="2"/>
       <c r="C1016" s="2" t="s">
-        <v>102</v>
+        <v>584</v>
       </c>
       <c r="D1016" s="4" t="s">
-        <v>1230</v>
+        <v>1642</v>
       </c>
       <c r="E1016" s="5" t="s">
-        <v>1231</v>
+        <v>1643</v>
       </c>
       <c r="F1016" s="4" t="s">
-        <v>725</v>
+        <v>1135</v>
       </c>
       <c r="G1016" s="4" t="s">
-        <v>771</v>
+        <v>1077</v>
       </c>
       <c r="H1016" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I1016" s="4">
-        <v>249.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1016" s="4" t="s">
         <v>40</v>
@@ -86699,29 +86746,29 @@
     </row>
     <row r="1017" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="2" t="s">
-        <v>1655</v>
+        <v>1646</v>
       </c>
       <c r="B1017" s="2"/>
       <c r="C1017" s="2" t="s">
-        <v>102</v>
+        <v>584</v>
       </c>
       <c r="D1017" s="4" t="s">
-        <v>1235</v>
+        <v>1642</v>
       </c>
       <c r="E1017" s="5" t="s">
-        <v>1236</v>
+        <v>1643</v>
       </c>
       <c r="F1017" s="4" t="s">
-        <v>725</v>
+        <v>1135</v>
       </c>
       <c r="G1017" s="4" t="s">
-        <v>69</v>
+        <v>1647</v>
       </c>
       <c r="H1017" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I1017" s="4">
-        <v>199.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1017" s="4" t="s">
         <v>40</v>
@@ -86756,34 +86803,36 @@
     </row>
     <row r="1018" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
       <c r="B1018" s="2"/>
       <c r="C1018" s="2" t="s">
-        <v>102</v>
+        <v>584</v>
       </c>
       <c r="D1018" s="4" t="s">
-        <v>1242</v>
+        <v>1532</v>
       </c>
       <c r="E1018" s="5" t="s">
-        <v>1243</v>
+        <v>1533</v>
       </c>
       <c r="F1018" s="4" t="s">
-        <v>725</v>
+        <v>701</v>
       </c>
       <c r="G1018" s="4" t="s">
-        <v>1404</v>
+        <v>69</v>
       </c>
       <c r="H1018" s="4" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="I1018" s="4">
-        <v>179.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1018" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1018" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K1018" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L1018" s="4" t="s">
         <v>42</v>
       </c>
@@ -86813,34 +86862,36 @@
     </row>
     <row r="1019" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="2" t="s">
-        <v>1657</v>
+        <v>1649</v>
       </c>
       <c r="B1019" s="2"/>
       <c r="C1019" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1019" s="4" t="s">
-        <v>744</v>
+        <v>1532</v>
       </c>
       <c r="E1019" s="5" t="s">
-        <v>745</v>
+        <v>1533</v>
       </c>
       <c r="F1019" s="4" t="s">
-        <v>725</v>
+        <v>701</v>
       </c>
       <c r="G1019" s="4" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="H1019" s="4" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="I1019" s="4">
-        <v>169.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1019" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1019" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="K1019" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="L1019" s="4" t="s">
         <v>42</v>
       </c>
@@ -86870,29 +86921,29 @@
     </row>
     <row r="1020" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
-        <v>1658</v>
+        <v>1650</v>
       </c>
       <c r="B1020" s="2"/>
       <c r="C1020" s="2" t="s">
-        <v>1016</v>
+        <v>584</v>
       </c>
       <c r="D1020" s="4" t="s">
-        <v>1017</v>
+        <v>1651</v>
       </c>
       <c r="E1020" s="5" t="s">
-        <v>1659</v>
+        <v>1652</v>
       </c>
       <c r="F1020" s="4" t="s">
-        <v>791</v>
+        <v>701</v>
       </c>
       <c r="G1020" s="4" t="s">
-        <v>1414</v>
+        <v>695</v>
       </c>
       <c r="H1020" s="4" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I1020" s="4">
-        <v>69.989999999999995</v>
+        <v>179.99</v>
       </c>
       <c r="J1020" s="4" t="s">
         <v>40</v>
@@ -86927,29 +86978,29 @@
     </row>
     <row r="1021" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
-        <v>1660</v>
+        <v>1653</v>
       </c>
       <c r="B1021" s="2"/>
       <c r="C1021" s="2" t="s">
-        <v>1016</v>
+        <v>584</v>
       </c>
       <c r="D1021" s="4" t="s">
-        <v>1043</v>
+        <v>1651</v>
       </c>
       <c r="E1021" s="5" t="s">
-        <v>1661</v>
+        <v>1652</v>
       </c>
       <c r="F1021" s="4" t="s">
-        <v>845</v>
+        <v>701</v>
       </c>
       <c r="G1021" s="4" t="s">
-        <v>1414</v>
+        <v>69</v>
       </c>
       <c r="H1021" s="4" t="s">
         <v>88</v>
       </c>
       <c r="I1021" s="4">
-        <v>69.989999999999995</v>
+        <v>179.99</v>
       </c>
       <c r="J1021" s="4" t="s">
         <v>40</v>
@@ -86984,29 +87035,29 @@
     </row>
     <row r="1022" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
-        <v>1662</v>
+        <v>1654</v>
       </c>
       <c r="B1022" s="2"/>
       <c r="C1022" s="2" t="s">
-        <v>584</v>
+        <v>102</v>
       </c>
       <c r="D1022" s="4" t="s">
-        <v>789</v>
+        <v>1230</v>
       </c>
       <c r="E1022" s="5" t="s">
-        <v>1663</v>
+        <v>1231</v>
       </c>
       <c r="F1022" s="4" t="s">
-        <v>791</v>
+        <v>725</v>
       </c>
       <c r="G1022" s="4" t="s">
-        <v>1664</v>
+        <v>771</v>
       </c>
       <c r="H1022" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I1022" s="4">
-        <v>24.99</v>
+        <v>249.99</v>
       </c>
       <c r="J1022" s="4" t="s">
         <v>40</v>
@@ -87041,29 +87092,29 @@
     </row>
     <row r="1023" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="2" t="s">
-        <v>1665</v>
+        <v>1655</v>
       </c>
       <c r="B1023" s="2"/>
       <c r="C1023" s="2" t="s">
-        <v>584</v>
+        <v>102</v>
       </c>
       <c r="D1023" s="4" t="s">
-        <v>789</v>
+        <v>1235</v>
       </c>
       <c r="E1023" s="5" t="s">
-        <v>1663</v>
+        <v>1236</v>
       </c>
       <c r="F1023" s="4" t="s">
-        <v>791</v>
+        <v>725</v>
       </c>
       <c r="G1023" s="4" t="s">
-        <v>1612</v>
+        <v>69</v>
       </c>
       <c r="H1023" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I1023" s="4">
-        <v>24.99</v>
+        <v>199.99</v>
       </c>
       <c r="J1023" s="4" t="s">
         <v>40</v>
@@ -87098,29 +87149,29 @@
     </row>
     <row r="1024" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
-        <v>1666</v>
+        <v>1656</v>
       </c>
       <c r="B1024" s="2"/>
       <c r="C1024" s="2" t="s">
-        <v>584</v>
+        <v>102</v>
       </c>
       <c r="D1024" s="4" t="s">
-        <v>789</v>
+        <v>1242</v>
       </c>
       <c r="E1024" s="5" t="s">
-        <v>1663</v>
+        <v>1243</v>
       </c>
       <c r="F1024" s="4" t="s">
-        <v>791</v>
+        <v>725</v>
       </c>
       <c r="G1024" s="4" t="s">
-        <v>1667</v>
+        <v>1404</v>
       </c>
       <c r="H1024" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I1024" s="4">
-        <v>24.99</v>
+        <v>179.99</v>
       </c>
       <c r="J1024" s="4" t="s">
         <v>40</v>
@@ -87155,29 +87206,29 @@
     </row>
     <row r="1025" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="2" t="s">
-        <v>1668</v>
+        <v>1657</v>
       </c>
       <c r="B1025" s="2"/>
       <c r="C1025" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D1025" s="4" t="s">
-        <v>843</v>
+        <v>744</v>
       </c>
       <c r="E1025" s="5" t="s">
-        <v>1669</v>
+        <v>745</v>
       </c>
       <c r="F1025" s="4" t="s">
-        <v>845</v>
+        <v>725</v>
       </c>
       <c r="G1025" s="4" t="s">
-        <v>1612</v>
+        <v>771</v>
       </c>
       <c r="H1025" s="4" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="I1025" s="4">
-        <v>24.99</v>
+        <v>169.99</v>
       </c>
       <c r="J1025" s="4" t="s">
         <v>40</v>
@@ -87212,29 +87263,29 @@
     </row>
     <row r="1026" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
-        <v>1670</v>
+        <v>1658</v>
       </c>
       <c r="B1026" s="2"/>
       <c r="C1026" s="2" t="s">
-        <v>584</v>
+        <v>1016</v>
       </c>
       <c r="D1026" s="4" t="s">
-        <v>843</v>
+        <v>1017</v>
       </c>
       <c r="E1026" s="5" t="s">
-        <v>1669</v>
+        <v>1659</v>
       </c>
       <c r="F1026" s="4" t="s">
-        <v>845</v>
+        <v>791</v>
       </c>
       <c r="G1026" s="4" t="s">
-        <v>1667</v>
+        <v>1414</v>
       </c>
       <c r="H1026" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I1026" s="4">
-        <v>24.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="J1026" s="4" t="s">
         <v>40</v>
@@ -87268,28 +87319,38 @@
       <c r="AI1026" s="4"/>
     </row>
     <row r="1027" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1027" s="8" t="s">
-        <v>1678</v>
+      <c r="A1027" s="2" t="s">
+        <v>1660</v>
       </c>
       <c r="B1027" s="2"/>
-      <c r="C1027" s="2"/>
+      <c r="C1027" s="2" t="s">
+        <v>1016</v>
+      </c>
       <c r="D1027" s="4" t="s">
-        <v>1487</v>
+        <v>1043</v>
       </c>
       <c r="E1027" s="5" t="s">
-        <v>1488</v>
-      </c>
-      <c r="F1027" s="4"/>
+        <v>1661</v>
+      </c>
+      <c r="F1027" s="4" t="s">
+        <v>845</v>
+      </c>
       <c r="G1027" s="4" t="s">
-        <v>1019</v>
-      </c>
-      <c r="H1027" s="4"/>
+        <v>1414</v>
+      </c>
+      <c r="H1027" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="I1027" s="4">
-        <v>229.99</v>
-      </c>
-      <c r="J1027" s="4"/>
+        <v>69.989999999999995</v>
+      </c>
+      <c r="J1027" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="K1027" s="4"/>
-      <c r="L1027" s="4"/>
+      <c r="L1027" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="M1027" s="4"/>
       <c r="N1027" s="4"/>
       <c r="O1027" s="4"/>
@@ -87315,28 +87376,38 @@
       <c r="AI1027" s="4"/>
     </row>
     <row r="1028" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1028" s="8" t="s">
-        <v>1679</v>
+      <c r="A1028" s="2" t="s">
+        <v>1662</v>
       </c>
       <c r="B1028" s="2"/>
-      <c r="C1028" s="2"/>
+      <c r="C1028" s="2" t="s">
+        <v>584</v>
+      </c>
       <c r="D1028" s="4" t="s">
-        <v>1491</v>
+        <v>789</v>
       </c>
       <c r="E1028" s="5" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F1028" s="4"/>
+        <v>1663</v>
+      </c>
+      <c r="F1028" s="4" t="s">
+        <v>791</v>
+      </c>
       <c r="G1028" s="4" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H1028" s="4"/>
+        <v>1664</v>
+      </c>
+      <c r="H1028" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="I1028" s="4">
-        <v>259.99</v>
-      </c>
-      <c r="J1028" s="4"/>
+        <v>24.99</v>
+      </c>
+      <c r="J1028" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="K1028" s="4"/>
-      <c r="L1028" s="4"/>
+      <c r="L1028" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="M1028" s="4"/>
       <c r="N1028" s="4"/>
       <c r="O1028" s="4"/>
@@ -87362,28 +87433,38 @@
       <c r="AI1028" s="4"/>
     </row>
     <row r="1029" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1029" s="8" t="s">
-        <v>1680</v>
+      <c r="A1029" s="2" t="s">
+        <v>1665</v>
       </c>
       <c r="B1029" s="2"/>
-      <c r="C1029" s="2"/>
+      <c r="C1029" s="2" t="s">
+        <v>584</v>
+      </c>
       <c r="D1029" s="4" t="s">
-        <v>1493</v>
+        <v>789</v>
       </c>
       <c r="E1029" s="5" t="s">
-        <v>1671</v>
-      </c>
-      <c r="F1029" s="4"/>
+        <v>1663</v>
+      </c>
+      <c r="F1029" s="4" t="s">
+        <v>791</v>
+      </c>
       <c r="G1029" s="4" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H1029" s="4"/>
+        <v>1612</v>
+      </c>
+      <c r="H1029" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="I1029" s="4">
-        <v>249.99</v>
-      </c>
-      <c r="J1029" s="4"/>
+        <v>24.99</v>
+      </c>
+      <c r="J1029" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="K1029" s="4"/>
-      <c r="L1029" s="4"/>
+      <c r="L1029" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="M1029" s="4"/>
       <c r="N1029" s="4"/>
       <c r="O1029" s="4"/>
@@ -87409,28 +87490,38 @@
       <c r="AI1029" s="4"/>
     </row>
     <row r="1030" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1030" s="8" t="s">
-        <v>1681</v>
+      <c r="A1030" s="2" t="s">
+        <v>1666</v>
       </c>
       <c r="B1030" s="2"/>
-      <c r="C1030" s="2"/>
+      <c r="C1030" s="2" t="s">
+        <v>584</v>
+      </c>
       <c r="D1030" s="4" t="s">
-        <v>1480</v>
+        <v>789</v>
       </c>
       <c r="E1030" s="5" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F1030" s="4"/>
+        <v>1663</v>
+      </c>
+      <c r="F1030" s="4" t="s">
+        <v>791</v>
+      </c>
       <c r="G1030" s="4" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H1030" s="4"/>
+        <v>1667</v>
+      </c>
+      <c r="H1030" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="I1030" s="4">
-        <v>229.99</v>
-      </c>
-      <c r="J1030" s="4"/>
+        <v>24.99</v>
+      </c>
+      <c r="J1030" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="K1030" s="4"/>
-      <c r="L1030" s="4"/>
+      <c r="L1030" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="M1030" s="4"/>
       <c r="N1030" s="4"/>
       <c r="O1030" s="4"/>
@@ -87456,28 +87547,38 @@
       <c r="AI1030" s="4"/>
     </row>
     <row r="1031" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1031" s="8" t="s">
-        <v>1682</v>
+      <c r="A1031" s="2" t="s">
+        <v>1668</v>
       </c>
       <c r="B1031" s="2"/>
-      <c r="C1031" s="2"/>
+      <c r="C1031" s="2" t="s">
+        <v>584</v>
+      </c>
       <c r="D1031" s="4" t="s">
-        <v>1482</v>
+        <v>843</v>
       </c>
       <c r="E1031" s="5" t="s">
-        <v>1672</v>
-      </c>
-      <c r="F1031" s="4"/>
+        <v>1669</v>
+      </c>
+      <c r="F1031" s="4" t="s">
+        <v>845</v>
+      </c>
       <c r="G1031" s="4" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H1031" s="4"/>
+        <v>1612</v>
+      </c>
+      <c r="H1031" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="I1031" s="4">
-        <v>229.99</v>
-      </c>
-      <c r="J1031" s="4"/>
+        <v>24.99</v>
+      </c>
+      <c r="J1031" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="K1031" s="4"/>
-      <c r="L1031" s="4"/>
+      <c r="L1031" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="M1031" s="4"/>
       <c r="N1031" s="4"/>
       <c r="O1031" s="4"/>
@@ -87503,28 +87604,38 @@
       <c r="AI1031" s="4"/>
     </row>
     <row r="1032" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1032" s="8" t="s">
-        <v>1683</v>
+      <c r="A1032" s="2" t="s">
+        <v>1670</v>
       </c>
       <c r="B1032" s="2"/>
-      <c r="C1032" s="2"/>
+      <c r="C1032" s="2" t="s">
+        <v>584</v>
+      </c>
       <c r="D1032" s="4" t="s">
-        <v>1495</v>
+        <v>843</v>
       </c>
       <c r="E1032" s="5" t="s">
-        <v>1673</v>
-      </c>
-      <c r="F1032" s="4"/>
+        <v>1669</v>
+      </c>
+      <c r="F1032" s="4" t="s">
+        <v>845</v>
+      </c>
       <c r="G1032" s="4" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H1032" s="4"/>
+        <v>1667</v>
+      </c>
+      <c r="H1032" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="I1032" s="4">
-        <v>229.99</v>
-      </c>
-      <c r="J1032" s="4"/>
+        <v>24.99</v>
+      </c>
+      <c r="J1032" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="K1032" s="4"/>
-      <c r="L1032" s="4"/>
+      <c r="L1032" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="M1032" s="4"/>
       <c r="N1032" s="4"/>
       <c r="O1032" s="4"/>
@@ -87551,23 +87662,23 @@
     </row>
     <row r="1033" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="8" t="s">
-        <v>1684</v>
+        <v>1678</v>
       </c>
       <c r="B1033" s="2"/>
       <c r="C1033" s="2"/>
       <c r="D1033" s="4" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="E1033" s="5" t="s">
-        <v>1674</v>
+        <v>1488</v>
       </c>
       <c r="F1033" s="4"/>
       <c r="G1033" s="4" t="s">
-        <v>1244</v>
+        <v>1019</v>
       </c>
       <c r="H1033" s="4"/>
       <c r="I1033" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J1033" s="4"/>
       <c r="K1033" s="4"/>
@@ -87598,15 +87709,15 @@
     </row>
     <row r="1034" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="8" t="s">
-        <v>1685</v>
+        <v>1679</v>
       </c>
       <c r="B1034" s="2"/>
       <c r="C1034" s="2"/>
       <c r="D1034" s="4" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="E1034" s="5" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="F1034" s="4"/>
       <c r="G1034" s="4" t="s">
@@ -87614,7 +87725,7 @@
       </c>
       <c r="H1034" s="4"/>
       <c r="I1034" s="4">
-        <v>199.99</v>
+        <v>259.99</v>
       </c>
       <c r="J1034" s="4"/>
       <c r="K1034" s="4"/>
@@ -87645,23 +87756,23 @@
     </row>
     <row r="1035" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="8" t="s">
-        <v>1686</v>
+        <v>1680</v>
       </c>
       <c r="B1035" s="2"/>
       <c r="C1035" s="2"/>
       <c r="D1035" s="4" t="s">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="E1035" s="5" t="s">
-        <v>1500</v>
+        <v>1671</v>
       </c>
       <c r="F1035" s="4"/>
       <c r="G1035" s="4" t="s">
-        <v>1019</v>
+        <v>1244</v>
       </c>
       <c r="H1035" s="4"/>
       <c r="I1035" s="4">
-        <v>229.99</v>
+        <v>249.99</v>
       </c>
       <c r="J1035" s="4"/>
       <c r="K1035" s="4"/>
@@ -87692,15 +87803,15 @@
     </row>
     <row r="1036" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="8" t="s">
-        <v>1687</v>
+        <v>1681</v>
       </c>
       <c r="B1036" s="2"/>
       <c r="C1036" s="2"/>
       <c r="D1036" s="4" t="s">
-        <v>1505</v>
+        <v>1480</v>
       </c>
       <c r="E1036" s="5" t="s">
-        <v>1675</v>
+        <v>1481</v>
       </c>
       <c r="F1036" s="4"/>
       <c r="G1036" s="4" t="s">
@@ -87708,7 +87819,7 @@
       </c>
       <c r="H1036" s="4"/>
       <c r="I1036" s="4">
-        <v>249.99</v>
+        <v>229.99</v>
       </c>
       <c r="J1036" s="4"/>
       <c r="K1036" s="4"/>
@@ -87739,15 +87850,15 @@
     </row>
     <row r="1037" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="8" t="s">
-        <v>1688</v>
+        <v>1682</v>
       </c>
       <c r="B1037" s="2"/>
       <c r="C1037" s="2"/>
       <c r="D1037" s="4" t="s">
-        <v>1507</v>
+        <v>1482</v>
       </c>
       <c r="E1037" s="5" t="s">
-        <v>1508</v>
+        <v>1672</v>
       </c>
       <c r="F1037" s="4"/>
       <c r="G1037" s="4" t="s">
@@ -87755,7 +87866,7 @@
       </c>
       <c r="H1037" s="4"/>
       <c r="I1037" s="4">
-        <v>239.99</v>
+        <v>229.99</v>
       </c>
       <c r="J1037" s="4"/>
       <c r="K1037" s="4"/>
@@ -87786,15 +87897,15 @@
     </row>
     <row r="1038" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="8" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="B1038" s="2"/>
       <c r="C1038" s="2"/>
       <c r="D1038" s="4" t="s">
-        <v>1509</v>
+        <v>1495</v>
       </c>
       <c r="E1038" s="5" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="F1038" s="4"/>
       <c r="G1038" s="4" t="s">
@@ -87802,7 +87913,7 @@
       </c>
       <c r="H1038" s="4"/>
       <c r="I1038" s="4">
-        <v>219.99</v>
+        <v>229.99</v>
       </c>
       <c r="J1038" s="4"/>
       <c r="K1038" s="4"/>
@@ -87833,15 +87944,15 @@
     </row>
     <row r="1039" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="8" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="B1039" s="2"/>
       <c r="C1039" s="2"/>
       <c r="D1039" s="4" t="s">
-        <v>1402</v>
+        <v>1485</v>
       </c>
       <c r="E1039" s="5" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="F1039" s="4"/>
       <c r="G1039" s="4" t="s">
@@ -87849,7 +87960,7 @@
       </c>
       <c r="H1039" s="4"/>
       <c r="I1039" s="4">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
       <c r="J1039" s="4"/>
       <c r="K1039" s="4"/>
@@ -87879,42 +87990,28 @@
       <c r="AI1039" s="4"/>
     </row>
     <row r="1040" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1040" s="2" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B1040" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1040" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D1040" s="4">
-        <v>43206446</v>
+      <c r="A1040" s="8" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B1040" s="2"/>
+      <c r="C1040" s="2"/>
+      <c r="D1040" s="4" t="s">
+        <v>1489</v>
       </c>
       <c r="E1040" s="5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F1040" s="4" t="s">
-        <v>645</v>
-      </c>
+        <v>1490</v>
+      </c>
+      <c r="F1040" s="4"/>
       <c r="G1040" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1040" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>1244</v>
+      </c>
+      <c r="H1040" s="4"/>
       <c r="I1040" s="4">
-        <v>599.99</v>
-      </c>
-      <c r="J1040" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1040" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1040" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>199.99</v>
+      </c>
+      <c r="J1040" s="4"/>
+      <c r="K1040" s="4"/>
+      <c r="L1040" s="4"/>
       <c r="M1040" s="4"/>
       <c r="N1040" s="4"/>
       <c r="O1040" s="4"/>
@@ -87940,42 +88037,28 @@
       <c r="AI1040" s="4"/>
     </row>
     <row r="1041" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1041" s="2" t="s">
-        <v>1691</v>
-      </c>
-      <c r="B1041" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1041" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D1041" s="4">
-        <v>43206446</v>
+      <c r="A1041" s="8" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B1041" s="2"/>
+      <c r="C1041" s="2"/>
+      <c r="D1041" s="4" t="s">
+        <v>1499</v>
       </c>
       <c r="E1041" s="5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F1041" s="4" t="s">
-        <v>645</v>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="F1041" s="4"/>
       <c r="G1041" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1041" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>1019</v>
+      </c>
+      <c r="H1041" s="4"/>
       <c r="I1041" s="4">
-        <v>599.99</v>
-      </c>
-      <c r="J1041" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1041" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1041" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>229.99</v>
+      </c>
+      <c r="J1041" s="4"/>
+      <c r="K1041" s="4"/>
+      <c r="L1041" s="4"/>
       <c r="M1041" s="4"/>
       <c r="N1041" s="4"/>
       <c r="O1041" s="4"/>
@@ -88001,42 +88084,28 @@
       <c r="AI1041" s="4"/>
     </row>
     <row r="1042" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1042" s="2" t="s">
-        <v>1692</v>
-      </c>
-      <c r="B1042" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1042" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D1042" s="4">
-        <v>43206446</v>
+      <c r="A1042" s="8" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B1042" s="2"/>
+      <c r="C1042" s="2"/>
+      <c r="D1042" s="4" t="s">
+        <v>1505</v>
       </c>
       <c r="E1042" s="5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F1042" s="4" t="s">
-        <v>645</v>
-      </c>
+        <v>1675</v>
+      </c>
+      <c r="F1042" s="4"/>
       <c r="G1042" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1042" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>1244</v>
+      </c>
+      <c r="H1042" s="4"/>
       <c r="I1042" s="4">
-        <v>599.99</v>
-      </c>
-      <c r="J1042" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1042" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1042" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>249.99</v>
+      </c>
+      <c r="J1042" s="4"/>
+      <c r="K1042" s="4"/>
+      <c r="L1042" s="4"/>
       <c r="M1042" s="4"/>
       <c r="N1042" s="4"/>
       <c r="O1042" s="4"/>
@@ -88062,42 +88131,28 @@
       <c r="AI1042" s="4"/>
     </row>
     <row r="1043" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1043" s="2" t="s">
-        <v>1693</v>
-      </c>
-      <c r="B1043" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1043" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D1043" s="4">
-        <v>43206446</v>
+      <c r="A1043" s="8" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B1043" s="2"/>
+      <c r="C1043" s="2"/>
+      <c r="D1043" s="4" t="s">
+        <v>1507</v>
       </c>
       <c r="E1043" s="5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F1043" s="4" t="s">
-        <v>645</v>
-      </c>
+        <v>1508</v>
+      </c>
+      <c r="F1043" s="4"/>
       <c r="G1043" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1043" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>1244</v>
+      </c>
+      <c r="H1043" s="4"/>
       <c r="I1043" s="4">
-        <v>599.99</v>
-      </c>
-      <c r="J1043" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1043" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1043" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>239.99</v>
+      </c>
+      <c r="J1043" s="4"/>
+      <c r="K1043" s="4"/>
+      <c r="L1043" s="4"/>
       <c r="M1043" s="4"/>
       <c r="N1043" s="4"/>
       <c r="O1043" s="4"/>
@@ -88123,42 +88178,28 @@
       <c r="AI1043" s="4"/>
     </row>
     <row r="1044" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1044" s="2" t="s">
-        <v>1695</v>
-      </c>
-      <c r="B1044" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1044" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D1044" s="4">
-        <v>43206446</v>
+      <c r="A1044" s="8" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B1044" s="2"/>
+      <c r="C1044" s="2"/>
+      <c r="D1044" s="4" t="s">
+        <v>1509</v>
       </c>
       <c r="E1044" s="5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F1044" s="4" t="s">
-        <v>645</v>
-      </c>
+        <v>1676</v>
+      </c>
+      <c r="F1044" s="4"/>
       <c r="G1044" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1044" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>1244</v>
+      </c>
+      <c r="H1044" s="4"/>
       <c r="I1044" s="4">
-        <v>599.99</v>
-      </c>
-      <c r="J1044" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1044" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1044" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>219.99</v>
+      </c>
+      <c r="J1044" s="4"/>
+      <c r="K1044" s="4"/>
+      <c r="L1044" s="4"/>
       <c r="M1044" s="4"/>
       <c r="N1044" s="4"/>
       <c r="O1044" s="4"/>
@@ -88184,42 +88225,28 @@
       <c r="AI1044" s="4"/>
     </row>
     <row r="1045" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1045" s="2" t="s">
-        <v>1697</v>
-      </c>
-      <c r="B1045" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C1045" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D1045" s="4">
-        <v>54111405</v>
+      <c r="A1045" s="8" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B1045" s="2"/>
+      <c r="C1045" s="2"/>
+      <c r="D1045" s="4" t="s">
+        <v>1402</v>
       </c>
       <c r="E1045" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="F1045" s="4" t="s">
-        <v>615</v>
-      </c>
+        <v>1677</v>
+      </c>
+      <c r="F1045" s="4"/>
       <c r="G1045" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="H1045" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>1244</v>
+      </c>
+      <c r="H1045" s="4"/>
       <c r="I1045" s="4">
-        <v>199.99</v>
-      </c>
-      <c r="J1045" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1045" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1045" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>119.99</v>
+      </c>
+      <c r="J1045" s="4"/>
+      <c r="K1045" s="4"/>
+      <c r="L1045" s="4"/>
       <c r="M1045" s="4"/>
       <c r="N1045" s="4"/>
       <c r="O1045" s="4"/>
@@ -88246,31 +88273,31 @@
     </row>
     <row r="1046" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
-        <v>1698</v>
+        <v>1694</v>
       </c>
       <c r="B1046" s="2" t="s">
-        <v>443</v>
+        <v>35</v>
       </c>
       <c r="C1046" s="2" t="s">
-        <v>612</v>
+        <v>1300</v>
       </c>
       <c r="D1046" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1046" s="5" t="s">
-        <v>614</v>
+        <v>1309</v>
       </c>
       <c r="F1046" s="4" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="G1046" s="4" t="s">
-        <v>1696</v>
+        <v>71</v>
       </c>
       <c r="H1046" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I1046" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1046" s="4" t="s">
         <v>41</v>
@@ -88307,31 +88334,31 @@
     </row>
     <row r="1047" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="2" t="s">
-        <v>1699</v>
+        <v>1691</v>
       </c>
       <c r="B1047" s="2" t="s">
-        <v>443</v>
+        <v>35</v>
       </c>
       <c r="C1047" s="2" t="s">
-        <v>612</v>
+        <v>1300</v>
       </c>
       <c r="D1047" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1047" s="5" t="s">
-        <v>614</v>
+        <v>1309</v>
       </c>
       <c r="F1047" s="4" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="G1047" s="4" t="s">
-        <v>368</v>
+        <v>61</v>
       </c>
       <c r="H1047" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I1047" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1047" s="4" t="s">
         <v>41</v>
@@ -88368,31 +88395,31 @@
     </row>
     <row r="1048" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
-        <v>1700</v>
+        <v>1692</v>
       </c>
       <c r="B1048" s="2" t="s">
-        <v>443</v>
+        <v>35</v>
       </c>
       <c r="C1048" s="2" t="s">
-        <v>612</v>
+        <v>1300</v>
       </c>
       <c r="D1048" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1048" s="5" t="s">
-        <v>614</v>
+        <v>1309</v>
       </c>
       <c r="F1048" s="4" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="G1048" s="4" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="H1048" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I1048" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1048" s="4" t="s">
         <v>41</v>
@@ -88427,8 +88454,435 @@
       <c r="AH1048" s="4"/>
       <c r="AI1048" s="4"/>
     </row>
+    <row r="1049" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1049" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B1049" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1049" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D1049" s="4">
+        <v>43206446</v>
+      </c>
+      <c r="E1049" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F1049" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G1049" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1049" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1049" s="4">
+        <v>599.99</v>
+      </c>
+      <c r="J1049" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1049" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1049" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1049" s="4"/>
+      <c r="N1049" s="4"/>
+      <c r="O1049" s="4"/>
+      <c r="P1049" s="4"/>
+      <c r="Q1049" s="4"/>
+      <c r="R1049" s="4"/>
+      <c r="S1049" s="4"/>
+      <c r="T1049" s="4"/>
+      <c r="U1049" s="4"/>
+      <c r="V1049" s="4"/>
+      <c r="W1049" s="4"/>
+      <c r="X1049" s="4"/>
+      <c r="Y1049" s="4"/>
+      <c r="Z1049" s="4"/>
+      <c r="AA1049" s="4"/>
+      <c r="AB1049" s="4"/>
+      <c r="AC1049" s="4"/>
+      <c r="AD1049" s="4"/>
+      <c r="AE1049" s="4"/>
+      <c r="AF1049" s="4"/>
+      <c r="AG1049" s="4"/>
+      <c r="AH1049" s="4"/>
+      <c r="AI1049" s="4"/>
+    </row>
+    <row r="1050" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1050" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B1050" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1050" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D1050" s="4">
+        <v>43206446</v>
+      </c>
+      <c r="E1050" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F1050" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G1050" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H1050" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1050" s="4">
+        <v>599.99</v>
+      </c>
+      <c r="J1050" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1050" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1050" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1050" s="4"/>
+      <c r="N1050" s="4"/>
+      <c r="O1050" s="4"/>
+      <c r="P1050" s="4"/>
+      <c r="Q1050" s="4"/>
+      <c r="R1050" s="4"/>
+      <c r="S1050" s="4"/>
+      <c r="T1050" s="4"/>
+      <c r="U1050" s="4"/>
+      <c r="V1050" s="4"/>
+      <c r="W1050" s="4"/>
+      <c r="X1050" s="4"/>
+      <c r="Y1050" s="4"/>
+      <c r="Z1050" s="4"/>
+      <c r="AA1050" s="4"/>
+      <c r="AB1050" s="4"/>
+      <c r="AC1050" s="4"/>
+      <c r="AD1050" s="4"/>
+      <c r="AE1050" s="4"/>
+      <c r="AF1050" s="4"/>
+      <c r="AG1050" s="4"/>
+      <c r="AH1050" s="4"/>
+      <c r="AI1050" s="4"/>
+    </row>
+    <row r="1051" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1051" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1051" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1051" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D1051" s="4">
+        <v>43206446</v>
+      </c>
+      <c r="E1051" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F1051" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G1051" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1051" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1051" s="4">
+        <v>599.99</v>
+      </c>
+      <c r="J1051" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1051" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1051" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1051" s="4"/>
+      <c r="N1051" s="4"/>
+      <c r="O1051" s="4"/>
+      <c r="P1051" s="4"/>
+      <c r="Q1051" s="4"/>
+      <c r="R1051" s="4"/>
+      <c r="S1051" s="4"/>
+      <c r="T1051" s="4"/>
+      <c r="U1051" s="4"/>
+      <c r="V1051" s="4"/>
+      <c r="W1051" s="4"/>
+      <c r="X1051" s="4"/>
+      <c r="Y1051" s="4"/>
+      <c r="Z1051" s="4"/>
+      <c r="AA1051" s="4"/>
+      <c r="AB1051" s="4"/>
+      <c r="AC1051" s="4"/>
+      <c r="AD1051" s="4"/>
+      <c r="AE1051" s="4"/>
+      <c r="AF1051" s="4"/>
+      <c r="AG1051" s="4"/>
+      <c r="AH1051" s="4"/>
+      <c r="AI1051" s="4"/>
+    </row>
+    <row r="1052" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1052" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B1052" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1052" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D1052" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1052" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F1052" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="G1052" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="H1052" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1052" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1052" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1052" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1052" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1052" s="4"/>
+      <c r="N1052" s="4"/>
+      <c r="O1052" s="4"/>
+      <c r="P1052" s="4"/>
+      <c r="Q1052" s="4"/>
+      <c r="R1052" s="4"/>
+      <c r="S1052" s="4"/>
+      <c r="T1052" s="4"/>
+      <c r="U1052" s="4"/>
+      <c r="V1052" s="4"/>
+      <c r="W1052" s="4"/>
+      <c r="X1052" s="4"/>
+      <c r="Y1052" s="4"/>
+      <c r="Z1052" s="4"/>
+      <c r="AA1052" s="4"/>
+      <c r="AB1052" s="4"/>
+      <c r="AC1052" s="4"/>
+      <c r="AD1052" s="4"/>
+      <c r="AE1052" s="4"/>
+      <c r="AF1052" s="4"/>
+      <c r="AG1052" s="4"/>
+      <c r="AH1052" s="4"/>
+      <c r="AI1052" s="4"/>
+    </row>
+    <row r="1053" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1053" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B1053" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1053" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D1053" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1053" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F1053" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="G1053" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H1053" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1053" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1053" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1053" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1053" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1053" s="4"/>
+      <c r="N1053" s="4"/>
+      <c r="O1053" s="4"/>
+      <c r="P1053" s="4"/>
+      <c r="Q1053" s="4"/>
+      <c r="R1053" s="4"/>
+      <c r="S1053" s="4"/>
+      <c r="T1053" s="4"/>
+      <c r="U1053" s="4"/>
+      <c r="V1053" s="4"/>
+      <c r="W1053" s="4"/>
+      <c r="X1053" s="4"/>
+      <c r="Y1053" s="4"/>
+      <c r="Z1053" s="4"/>
+      <c r="AA1053" s="4"/>
+      <c r="AB1053" s="4"/>
+      <c r="AC1053" s="4"/>
+      <c r="AD1053" s="4"/>
+      <c r="AE1053" s="4"/>
+      <c r="AF1053" s="4"/>
+      <c r="AG1053" s="4"/>
+      <c r="AH1053" s="4"/>
+      <c r="AI1053" s="4"/>
+    </row>
+    <row r="1054" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1054" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1054" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1054" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D1054" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1054" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F1054" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="G1054" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1054" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1054" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1054" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1054" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1054" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1054" s="4"/>
+      <c r="N1054" s="4"/>
+      <c r="O1054" s="4"/>
+      <c r="P1054" s="4"/>
+      <c r="Q1054" s="4"/>
+      <c r="R1054" s="4"/>
+      <c r="S1054" s="4"/>
+      <c r="T1054" s="4"/>
+      <c r="U1054" s="4"/>
+      <c r="V1054" s="4"/>
+      <c r="W1054" s="4"/>
+      <c r="X1054" s="4"/>
+      <c r="Y1054" s="4"/>
+      <c r="Z1054" s="4"/>
+      <c r="AA1054" s="4"/>
+      <c r="AB1054" s="4"/>
+      <c r="AC1054" s="4"/>
+      <c r="AD1054" s="4"/>
+      <c r="AE1054" s="4"/>
+      <c r="AF1054" s="4"/>
+      <c r="AG1054" s="4"/>
+      <c r="AH1054" s="4"/>
+      <c r="AI1054" s="4"/>
+    </row>
+    <row r="1055" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1055" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B1055" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1055" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D1055" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1055" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F1055" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="G1055" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1055" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1055" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1055" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1055" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1055" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1055" s="4"/>
+      <c r="N1055" s="4"/>
+      <c r="O1055" s="4"/>
+      <c r="P1055" s="4"/>
+      <c r="Q1055" s="4"/>
+      <c r="R1055" s="4"/>
+      <c r="S1055" s="4"/>
+      <c r="T1055" s="4"/>
+      <c r="U1055" s="4"/>
+      <c r="V1055" s="4"/>
+      <c r="W1055" s="4"/>
+      <c r="X1055" s="4"/>
+      <c r="Y1055" s="4"/>
+      <c r="Z1055" s="4"/>
+      <c r="AA1055" s="4"/>
+      <c r="AB1055" s="4"/>
+      <c r="AC1055" s="4"/>
+      <c r="AD1055" s="4"/>
+      <c r="AE1055" s="4"/>
+      <c r="AF1055" s="4"/>
+      <c r="AG1055" s="4"/>
+      <c r="AH1055" s="4"/>
+      <c r="AI1055" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R1048" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R1055" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrativo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAAF728-292C-4068-938E-309795CD2E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C34284-1849-4947-8F22-76BA70815D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="corre" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1055</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1057</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13284" uniqueCount="1720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13304" uniqueCount="1723">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -5197,6 +5197,15 @@
   </si>
   <si>
     <t>43304478_MUSGO</t>
+  </si>
+  <si>
+    <t>AREAML</t>
+  </si>
+  <si>
+    <t>43206446_LIMATL</t>
+  </si>
+  <si>
+    <t>43206446_AREAML</t>
   </si>
 </sst>
 </file>
@@ -5658,7 +5667,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1055"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AI1057"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -5779,7 +5789,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>46</v>
       </c>
@@ -5886,7 +5896,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>49</v>
       </c>
@@ -5993,7 +6003,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>51</v>
       </c>
@@ -6100,7 +6110,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
@@ -6207,7 +6217,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>55</v>
       </c>
@@ -6314,7 +6324,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>57</v>
       </c>
@@ -6421,7 +6431,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
@@ -6528,7 +6538,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -6635,7 +6645,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>64</v>
       </c>
@@ -6742,7 +6752,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -6849,7 +6859,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
@@ -6956,7 +6966,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
@@ -7063,7 +7073,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>72</v>
       </c>
@@ -7170,7 +7180,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>75</v>
       </c>
@@ -7277,7 +7287,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>76</v>
       </c>
@@ -7384,7 +7394,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -7491,7 +7501,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>80</v>
       </c>
@@ -7598,7 +7608,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>81</v>
       </c>
@@ -7705,7 +7715,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>82</v>
       </c>
@@ -7812,7 +7822,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>86</v>
       </c>
@@ -7919,7 +7929,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>89</v>
       </c>
@@ -8026,7 +8036,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>91</v>
       </c>
@@ -8133,7 +8143,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>93</v>
       </c>
@@ -8240,7 +8250,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>94</v>
       </c>
@@ -8347,7 +8357,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>96</v>
       </c>
@@ -8454,7 +8464,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>98</v>
       </c>
@@ -8561,7 +8571,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>99</v>
       </c>
@@ -8668,7 +8678,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>101</v>
       </c>
@@ -8775,7 +8785,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>106</v>
       </c>
@@ -8882,7 +8892,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>107</v>
       </c>
@@ -8989,7 +8999,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>109</v>
       </c>
@@ -9096,7 +9106,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>110</v>
       </c>
@@ -9203,7 +9213,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>111</v>
       </c>
@@ -9310,7 +9320,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>113</v>
       </c>
@@ -9417,7 +9427,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>115</v>
       </c>
@@ -9524,7 +9534,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>119</v>
       </c>
@@ -9631,7 +9641,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>121</v>
       </c>
@@ -9738,7 +9748,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>122</v>
       </c>
@@ -9845,7 +9855,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>124</v>
       </c>
@@ -9952,7 +9962,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>125</v>
       </c>
@@ -10059,7 +10069,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
@@ -10166,7 +10176,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>129</v>
       </c>
@@ -10273,7 +10283,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>131</v>
       </c>
@@ -10380,7 +10390,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>133</v>
       </c>
@@ -10487,7 +10497,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>134</v>
       </c>
@@ -10594,7 +10604,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>138</v>
       </c>
@@ -10701,7 +10711,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>139</v>
       </c>
@@ -10808,7 +10818,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>140</v>
       </c>
@@ -10915,7 +10925,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>142</v>
       </c>
@@ -11022,7 +11032,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>143</v>
       </c>
@@ -11129,7 +11139,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>145</v>
       </c>
@@ -11236,7 +11246,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>147</v>
       </c>
@@ -11343,7 +11353,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>149</v>
       </c>
@@ -11450,7 +11460,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>151</v>
       </c>
@@ -11557,7 +11567,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>153</v>
       </c>
@@ -11664,7 +11674,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>154</v>
       </c>
@@ -11771,7 +11781,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>156</v>
       </c>
@@ -11878,7 +11888,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>159</v>
       </c>
@@ -11985,7 +11995,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>161</v>
       </c>
@@ -12092,7 +12102,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>163</v>
       </c>
@@ -12199,7 +12209,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>165</v>
       </c>
@@ -12306,7 +12316,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>166</v>
       </c>
@@ -12413,7 +12423,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>168</v>
       </c>
@@ -12520,7 +12530,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>171</v>
       </c>
@@ -12627,7 +12637,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>172</v>
       </c>
@@ -12734,7 +12744,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>173</v>
       </c>
@@ -12841,7 +12851,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>174</v>
       </c>
@@ -12948,7 +12958,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>177</v>
       </c>
@@ -13055,7 +13065,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>179</v>
       </c>
@@ -13162,7 +13172,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>181</v>
       </c>
@@ -13269,7 +13279,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>183</v>
       </c>
@@ -13376,7 +13386,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>184</v>
       </c>
@@ -13483,7 +13493,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>187</v>
       </c>
@@ -13590,7 +13600,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>189</v>
       </c>
@@ -13697,7 +13707,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>190</v>
       </c>
@@ -13804,7 +13814,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>193</v>
       </c>
@@ -13911,7 +13921,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>194</v>
       </c>
@@ -14018,7 +14028,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>195</v>
       </c>
@@ -14125,7 +14135,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>198</v>
       </c>
@@ -14232,7 +14242,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>199</v>
       </c>
@@ -14339,7 +14349,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>201</v>
       </c>
@@ -14446,7 +14456,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>203</v>
       </c>
@@ -14553,7 +14563,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>206</v>
       </c>
@@ -14660,7 +14670,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>208</v>
       </c>
@@ -14767,7 +14777,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>209</v>
       </c>
@@ -14874,7 +14884,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -14981,7 +14991,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>213</v>
       </c>
@@ -15088,7 +15098,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>214</v>
       </c>
@@ -15195,7 +15205,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>216</v>
       </c>
@@ -15302,7 +15312,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>218</v>
       </c>
@@ -15409,7 +15419,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>222</v>
       </c>
@@ -15516,7 +15526,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>224</v>
       </c>
@@ -15623,7 +15633,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>226</v>
       </c>
@@ -15730,7 +15740,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>227</v>
       </c>
@@ -15837,7 +15847,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>230</v>
       </c>
@@ -15944,7 +15954,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>232</v>
       </c>
@@ -16051,7 +16061,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>233</v>
       </c>
@@ -16158,7 +16168,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>234</v>
       </c>
@@ -16265,7 +16275,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>236</v>
       </c>
@@ -16372,7 +16382,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>238</v>
       </c>
@@ -16479,7 +16489,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>241</v>
       </c>
@@ -16586,7 +16596,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>242</v>
       </c>
@@ -16693,7 +16703,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>243</v>
       </c>
@@ -16800,7 +16810,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>245</v>
       </c>
@@ -16907,7 +16917,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>246</v>
       </c>
@@ -17014,7 +17024,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>248</v>
       </c>
@@ -17121,7 +17131,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>250</v>
       </c>
@@ -17228,7 +17238,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>252</v>
       </c>
@@ -17335,7 +17345,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>253</v>
       </c>
@@ -17442,7 +17452,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>255</v>
       </c>
@@ -17549,7 +17559,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>257</v>
       </c>
@@ -17656,7 +17666,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>259</v>
       </c>
@@ -17763,7 +17773,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>261</v>
       </c>
@@ -17870,7 +17880,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>263</v>
       </c>
@@ -17977,7 +17987,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>264</v>
       </c>
@@ -18084,7 +18094,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>266</v>
       </c>
@@ -18191,7 +18201,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>268</v>
       </c>
@@ -18298,7 +18308,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>270</v>
       </c>
@@ -18405,7 +18415,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>271</v>
       </c>
@@ -18512,7 +18522,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>274</v>
       </c>
@@ -18619,7 +18629,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>275</v>
       </c>
@@ -18726,7 +18736,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>276</v>
       </c>
@@ -18833,7 +18843,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>277</v>
       </c>
@@ -18940,7 +18950,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>279</v>
       </c>
@@ -19047,7 +19057,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>281</v>
       </c>
@@ -19154,7 +19164,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>283</v>
       </c>
@@ -19261,7 +19271,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>284</v>
       </c>
@@ -19368,7 +19378,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>286</v>
       </c>
@@ -19475,7 +19485,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>287</v>
       </c>
@@ -19582,7 +19592,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>288</v>
       </c>
@@ -19689,7 +19699,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>289</v>
       </c>
@@ -19796,7 +19806,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>292</v>
       </c>
@@ -19903,7 +19913,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>293</v>
       </c>
@@ -20010,7 +20020,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>294</v>
       </c>
@@ -20117,7 +20127,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>295</v>
       </c>
@@ -20224,7 +20234,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>298</v>
       </c>
@@ -20331,7 +20341,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>300</v>
       </c>
@@ -20438,7 +20448,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>301</v>
       </c>
@@ -20545,7 +20555,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>303</v>
       </c>
@@ -20652,7 +20662,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>305</v>
       </c>
@@ -20759,7 +20769,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>306</v>
       </c>
@@ -20866,7 +20876,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>307</v>
       </c>
@@ -20973,7 +20983,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>309</v>
       </c>
@@ -21080,7 +21090,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>310</v>
       </c>
@@ -21187,7 +21197,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>311</v>
       </c>
@@ -21294,7 +21304,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>314</v>
       </c>
@@ -21401,7 +21411,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>315</v>
       </c>
@@ -21508,7 +21518,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>317</v>
       </c>
@@ -21615,7 +21625,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>318</v>
       </c>
@@ -21722,7 +21732,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>320</v>
       </c>
@@ -21829,7 +21839,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>321</v>
       </c>
@@ -21936,7 +21946,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>322</v>
       </c>
@@ -22043,7 +22053,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>323</v>
       </c>
@@ -22150,7 +22160,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>325</v>
       </c>
@@ -22257,7 +22267,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>327</v>
       </c>
@@ -22364,7 +22374,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>329</v>
       </c>
@@ -22471,7 +22481,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>330</v>
       </c>
@@ -22578,7 +22588,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>333</v>
       </c>
@@ -22685,7 +22695,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>335</v>
       </c>
@@ -22792,7 +22802,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>337</v>
       </c>
@@ -22899,7 +22909,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>339</v>
       </c>
@@ -23006,7 +23016,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="163" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>341</v>
       </c>
@@ -23113,7 +23123,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>342</v>
       </c>
@@ -23220,7 +23230,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>344</v>
       </c>
@@ -23327,7 +23337,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>345</v>
       </c>
@@ -23434,7 +23444,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>348</v>
       </c>
@@ -23541,7 +23551,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>349</v>
       </c>
@@ -23648,7 +23658,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>350</v>
       </c>
@@ -23755,7 +23765,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>351</v>
       </c>
@@ -23862,7 +23872,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>353</v>
       </c>
@@ -23969,7 +23979,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>354</v>
       </c>
@@ -24076,7 +24086,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>355</v>
       </c>
@@ -24183,7 +24193,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="174" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>358</v>
       </c>
@@ -24290,7 +24300,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>360</v>
       </c>
@@ -24397,7 +24407,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>361</v>
       </c>
@@ -24504,7 +24514,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="177" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>362</v>
       </c>
@@ -24611,7 +24621,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>365</v>
       </c>
@@ -24718,7 +24728,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>367</v>
       </c>
@@ -24825,7 +24835,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>369</v>
       </c>
@@ -24932,7 +24942,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>372</v>
       </c>
@@ -25039,7 +25049,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="182" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>373</v>
       </c>
@@ -25146,7 +25156,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>374</v>
       </c>
@@ -25253,7 +25263,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="184" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>378</v>
       </c>
@@ -25360,7 +25370,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>380</v>
       </c>
@@ -25467,7 +25477,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>382</v>
       </c>
@@ -25574,7 +25584,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="187" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>384</v>
       </c>
@@ -25681,7 +25691,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>385</v>
       </c>
@@ -25788,7 +25798,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>386</v>
       </c>
@@ -25895,7 +25905,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>389</v>
       </c>
@@ -26002,7 +26012,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>390</v>
       </c>
@@ -26109,7 +26119,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>393</v>
       </c>
@@ -26216,7 +26226,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>394</v>
       </c>
@@ -26323,7 +26333,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>395</v>
       </c>
@@ -26430,7 +26440,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>396</v>
       </c>
@@ -26537,7 +26547,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>397</v>
       </c>
@@ -26644,7 +26654,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>399</v>
       </c>
@@ -26751,7 +26761,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>401</v>
       </c>
@@ -26858,7 +26868,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="199" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>402</v>
       </c>
@@ -26965,7 +26975,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="200" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>403</v>
       </c>
@@ -27072,7 +27082,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="201" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>404</v>
       </c>
@@ -27179,7 +27189,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="202" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>405</v>
       </c>
@@ -27286,7 +27296,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="203" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>406</v>
       </c>
@@ -27393,7 +27403,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="204" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>410</v>
       </c>
@@ -27500,7 +27510,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="205" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>411</v>
       </c>
@@ -27607,7 +27617,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="206" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>412</v>
       </c>
@@ -27714,7 +27724,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="207" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>413</v>
       </c>
@@ -27821,7 +27831,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="208" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>414</v>
       </c>
@@ -27928,7 +27938,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="209" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>416</v>
       </c>
@@ -28035,7 +28045,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="210" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>417</v>
       </c>
@@ -28142,7 +28152,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>418</v>
       </c>
@@ -28249,7 +28259,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="212" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>419</v>
       </c>
@@ -28356,7 +28366,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="213" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>420</v>
       </c>
@@ -28463,7 +28473,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="214" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>421</v>
       </c>
@@ -28570,7 +28580,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>423</v>
       </c>
@@ -28677,7 +28687,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="216" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>425</v>
       </c>
@@ -28784,7 +28794,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="217" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>427</v>
       </c>
@@ -28891,7 +28901,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="218" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>428</v>
       </c>
@@ -28998,7 +29008,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="219" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>429</v>
       </c>
@@ -29105,7 +29115,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="220" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>431</v>
       </c>
@@ -29212,7 +29222,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="221" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>432</v>
       </c>
@@ -29319,7 +29329,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="222" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>433</v>
       </c>
@@ -29426,7 +29436,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="223" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>434</v>
       </c>
@@ -29533,7 +29543,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="224" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>435</v>
       </c>
@@ -29640,7 +29650,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="225" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>436</v>
       </c>
@@ -29747,7 +29757,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="226" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>438</v>
       </c>
@@ -29854,7 +29864,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="227" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>439</v>
       </c>
@@ -29961,7 +29971,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>440</v>
       </c>
@@ -30068,7 +30078,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="229" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>441</v>
       </c>
@@ -30175,7 +30185,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="230" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>442</v>
       </c>
@@ -30282,7 +30292,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="231" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>448</v>
       </c>
@@ -30389,7 +30399,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>449</v>
       </c>
@@ -30496,7 +30506,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="233" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>451</v>
       </c>
@@ -30603,7 +30613,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="234" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>453</v>
       </c>
@@ -30710,7 +30720,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="235" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>454</v>
       </c>
@@ -30817,7 +30827,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="236" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>455</v>
       </c>
@@ -30924,7 +30934,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="237" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>458</v>
       </c>
@@ -31031,7 +31041,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="238" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>459</v>
       </c>
@@ -31138,7 +31148,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>461</v>
       </c>
@@ -31245,7 +31255,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="240" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>462</v>
       </c>
@@ -31352,7 +31362,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="241" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>464</v>
       </c>
@@ -31459,7 +31469,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="242" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>465</v>
       </c>
@@ -31566,7 +31576,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="243" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>466</v>
       </c>
@@ -31673,7 +31683,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="244" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>467</v>
       </c>
@@ -31780,7 +31790,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="245" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>468</v>
       </c>
@@ -31887,7 +31897,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="246" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>471</v>
       </c>
@@ -31994,7 +32004,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="247" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>472</v>
       </c>
@@ -32101,7 +32111,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="248" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>474</v>
       </c>
@@ -32208,7 +32218,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="249" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>475</v>
       </c>
@@ -32315,7 +32325,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="250" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>478</v>
       </c>
@@ -32422,7 +32432,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="251" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>480</v>
       </c>
@@ -32529,7 +32539,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>482</v>
       </c>
@@ -32636,7 +32646,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="253" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>483</v>
       </c>
@@ -32743,7 +32753,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="254" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>485</v>
       </c>
@@ -32838,7 +32848,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="255" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>488</v>
       </c>
@@ -32933,7 +32943,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>489</v>
       </c>
@@ -33028,7 +33038,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="257" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>491</v>
       </c>
@@ -33123,7 +33133,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="258" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>492</v>
       </c>
@@ -33218,7 +33228,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>494</v>
       </c>
@@ -33313,7 +33323,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>496</v>
       </c>
@@ -33408,7 +33418,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="261" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>498</v>
       </c>
@@ -33503,7 +33513,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="262" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>499</v>
       </c>
@@ -33598,7 +33608,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="263" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>500</v>
       </c>
@@ -33693,7 +33703,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="264" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>501</v>
       </c>
@@ -33788,7 +33798,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="265" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>503</v>
       </c>
@@ -33883,7 +33893,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="266" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>504</v>
       </c>
@@ -33978,7 +33988,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="267" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>505</v>
       </c>
@@ -34073,7 +34083,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="268" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>506</v>
       </c>
@@ -34134,7 +34144,7 @@
       <c r="AH268" s="4"/>
       <c r="AI268" s="4"/>
     </row>
-    <row r="269" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>508</v>
       </c>
@@ -34195,7 +34205,7 @@
       <c r="AH269" s="4"/>
       <c r="AI269" s="4"/>
     </row>
-    <row r="270" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>509</v>
       </c>
@@ -34256,7 +34266,7 @@
       <c r="AH270" s="4"/>
       <c r="AI270" s="4"/>
     </row>
-    <row r="271" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>510</v>
       </c>
@@ -34317,7 +34327,7 @@
       <c r="AH271" s="4"/>
       <c r="AI271" s="4"/>
     </row>
-    <row r="272" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>511</v>
       </c>
@@ -34378,7 +34388,7 @@
       <c r="AH272" s="4"/>
       <c r="AI272" s="4"/>
     </row>
-    <row r="273" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>513</v>
       </c>
@@ -34473,7 +34483,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="274" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>515</v>
       </c>
@@ -34568,7 +34578,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>517</v>
       </c>
@@ -34663,7 +34673,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>518</v>
       </c>
@@ -34758,7 +34768,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>173</v>
       </c>
@@ -34853,7 +34863,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="278" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>172</v>
       </c>
@@ -34948,7 +34958,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="279" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>171</v>
       </c>
@@ -35043,7 +35053,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="280" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>168</v>
       </c>
@@ -35138,7 +35148,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="281" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>183</v>
       </c>
@@ -35233,7 +35243,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>519</v>
       </c>
@@ -35328,7 +35338,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="283" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>179</v>
       </c>
@@ -35423,7 +35433,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>174</v>
       </c>
@@ -35518,7 +35528,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="285" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>177</v>
       </c>
@@ -35613,7 +35623,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="286" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>521</v>
       </c>
@@ -35708,7 +35718,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="287" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>523</v>
       </c>
@@ -35803,7 +35813,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="288" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>524</v>
       </c>
@@ -35898,7 +35908,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="289" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>526</v>
       </c>
@@ -35959,7 +35969,7 @@
       <c r="AH289" s="4"/>
       <c r="AI289" s="4"/>
     </row>
-    <row r="290" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>528</v>
       </c>
@@ -36020,7 +36030,7 @@
       <c r="AH290" s="4"/>
       <c r="AI290" s="4"/>
     </row>
-    <row r="291" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>529</v>
       </c>
@@ -36081,7 +36091,7 @@
       <c r="AH291" s="4"/>
       <c r="AI291" s="4"/>
     </row>
-    <row r="292" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>213</v>
       </c>
@@ -36176,7 +36186,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="293" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>214</v>
       </c>
@@ -36271,7 +36281,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="294" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>210</v>
       </c>
@@ -36366,7 +36376,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="295" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>216</v>
       </c>
@@ -36461,7 +36471,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="296" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>198</v>
       </c>
@@ -36556,7 +36566,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="297" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>195</v>
       </c>
@@ -36651,7 +36661,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="298" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>530</v>
       </c>
@@ -36746,7 +36756,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="299" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>532</v>
       </c>
@@ -36841,7 +36851,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="300" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>534</v>
       </c>
@@ -36936,7 +36946,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="301" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>245</v>
       </c>
@@ -37031,7 +37041,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="302" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>243</v>
       </c>
@@ -37126,7 +37136,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="303" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>241</v>
       </c>
@@ -37221,7 +37231,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="304" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>238</v>
       </c>
@@ -37316,7 +37326,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="305" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>242</v>
       </c>
@@ -37411,7 +37421,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="306" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>250</v>
       </c>
@@ -37506,7 +37516,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="307" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>252</v>
       </c>
@@ -37601,7 +37611,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="308" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>248</v>
       </c>
@@ -37696,7 +37706,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="309" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>246</v>
       </c>
@@ -37791,7 +37801,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="310" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>536</v>
       </c>
@@ -37886,7 +37896,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="311" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>275</v>
       </c>
@@ -37981,7 +37991,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="312" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>274</v>
       </c>
@@ -38076,7 +38086,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="313" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>271</v>
       </c>
@@ -38171,7 +38181,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="314" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>283</v>
       </c>
@@ -38266,7 +38276,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="315" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>279</v>
       </c>
@@ -38361,7 +38371,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="316" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>277</v>
       </c>
@@ -38456,7 +38466,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>281</v>
       </c>
@@ -38551,7 +38561,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="318" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>537</v>
       </c>
@@ -38646,7 +38656,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="319" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>539</v>
       </c>
@@ -38741,7 +38751,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="320" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>541</v>
       </c>
@@ -38836,7 +38846,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="321" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>543</v>
       </c>
@@ -38931,7 +38941,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="322" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>544</v>
       </c>
@@ -39026,7 +39036,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="323" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>547</v>
       </c>
@@ -39121,7 +39131,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="324" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>548</v>
       </c>
@@ -39216,7 +39226,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="325" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>287</v>
       </c>
@@ -39311,7 +39321,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="326" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>286</v>
       </c>
@@ -39406,7 +39416,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="327" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>284</v>
       </c>
@@ -39501,7 +39511,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="328" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>288</v>
       </c>
@@ -39596,7 +39606,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="329" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>322</v>
       </c>
@@ -39691,7 +39701,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="330" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>320</v>
       </c>
@@ -39786,7 +39796,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="331" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>318</v>
       </c>
@@ -39881,7 +39891,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="332" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>321</v>
       </c>
@@ -39976,7 +39986,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="333" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>311</v>
       </c>
@@ -40071,7 +40081,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="334" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>315</v>
       </c>
@@ -40166,7 +40176,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="335" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>314</v>
       </c>
@@ -40261,7 +40271,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="336" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>317</v>
       </c>
@@ -40356,7 +40366,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="337" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>323</v>
       </c>
@@ -40451,7 +40461,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="338" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>329</v>
       </c>
@@ -40546,7 +40556,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="339" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>325</v>
       </c>
@@ -40641,7 +40651,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="340" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>550</v>
       </c>
@@ -40736,7 +40746,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="341" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>333</v>
       </c>
@@ -40831,7 +40841,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="342" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>337</v>
       </c>
@@ -40926,7 +40936,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="343" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>335</v>
       </c>
@@ -41021,7 +41031,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="344" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>330</v>
       </c>
@@ -41116,7 +41126,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="345" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>552</v>
       </c>
@@ -41223,7 +41233,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="346" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>554</v>
       </c>
@@ -41330,7 +41340,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="347" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>555</v>
       </c>
@@ -41437,7 +41447,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="348" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>557</v>
       </c>
@@ -41532,7 +41542,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="349" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>362</v>
       </c>
@@ -41627,7 +41637,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="350" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>365</v>
       </c>
@@ -41722,7 +41732,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="351" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>558</v>
       </c>
@@ -41817,7 +41827,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="352" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>358</v>
       </c>
@@ -41912,7 +41922,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="353" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>559</v>
       </c>
@@ -42007,7 +42017,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="354" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>355</v>
       </c>
@@ -42102,7 +42112,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="355" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>560</v>
       </c>
@@ -42197,7 +42207,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="356" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>561</v>
       </c>
@@ -42292,7 +42302,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="357" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>369</v>
       </c>
@@ -42387,7 +42397,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="358" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>140</v>
       </c>
@@ -42482,7 +42492,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="359" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>563</v>
       </c>
@@ -42577,7 +42587,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="360" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>143</v>
       </c>
@@ -42672,7 +42682,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="361" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>142</v>
       </c>
@@ -42767,7 +42777,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="362" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>134</v>
       </c>
@@ -42862,7 +42872,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="363" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>138</v>
       </c>
@@ -42957,7 +42967,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="364" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>139</v>
       </c>
@@ -43052,7 +43062,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="365" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>147</v>
       </c>
@@ -43147,7 +43157,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="366" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>564</v>
       </c>
@@ -43242,7 +43252,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="367" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>565</v>
       </c>
@@ -43337,7 +43347,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="368" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>566</v>
       </c>
@@ -43432,7 +43442,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="369" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>568</v>
       </c>
@@ -43527,7 +43537,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="370" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>222</v>
       </c>
@@ -43622,7 +43632,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="371" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>226</v>
       </c>
@@ -43717,7 +43727,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="372" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>218</v>
       </c>
@@ -43812,7 +43822,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="373" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>224</v>
       </c>
@@ -43907,7 +43917,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="374" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>305</v>
       </c>
@@ -44002,7 +44012,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="375" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>306</v>
       </c>
@@ -44097,7 +44107,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="376" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>303</v>
       </c>
@@ -44192,7 +44202,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="377" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>301</v>
       </c>
@@ -44287,7 +44297,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="378" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>570</v>
       </c>
@@ -44382,7 +44392,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="379" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>572</v>
       </c>
@@ -44477,7 +44487,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="380" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>574</v>
       </c>
@@ -44572,7 +44582,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="381" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>576</v>
       </c>
@@ -44667,7 +44677,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="382" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>427</v>
       </c>
@@ -44762,7 +44772,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="383" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>425</v>
       </c>
@@ -44857,7 +44867,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="384" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>428</v>
       </c>
@@ -44952,7 +44962,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="385" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>421</v>
       </c>
@@ -45047,7 +45057,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="386" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>423</v>
       </c>
@@ -45142,7 +45152,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="387" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>440</v>
       </c>
@@ -45237,7 +45247,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="388" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>438</v>
       </c>
@@ -45332,7 +45342,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="389" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>436</v>
       </c>
@@ -45427,7 +45437,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="390" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>578</v>
       </c>
@@ -45522,7 +45532,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="391" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>580</v>
       </c>
@@ -45617,7 +45627,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="392" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>581</v>
       </c>
@@ -45712,7 +45722,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="393" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>582</v>
       </c>
@@ -45807,7 +45817,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="394" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>583</v>
       </c>
@@ -45868,7 +45878,7 @@
       <c r="AH394" s="4"/>
       <c r="AI394" s="4"/>
     </row>
-    <row r="395" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>587</v>
       </c>
@@ -45929,7 +45939,7 @@
       <c r="AH395" s="4"/>
       <c r="AI395" s="4"/>
     </row>
-    <row r="396" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>589</v>
       </c>
@@ -45990,7 +46000,7 @@
       <c r="AH396" s="4"/>
       <c r="AI396" s="4"/>
     </row>
-    <row r="397" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>591</v>
       </c>
@@ -46051,7 +46061,7 @@
       <c r="AH397" s="4"/>
       <c r="AI397" s="4"/>
     </row>
-    <row r="398" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>374</v>
       </c>
@@ -46146,7 +46156,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="399" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>385</v>
       </c>
@@ -46241,7 +46251,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="400" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>384</v>
       </c>
@@ -46336,7 +46346,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="401" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>382</v>
       </c>
@@ -46431,7 +46441,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="402" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>378</v>
       </c>
@@ -46526,7 +46536,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="403" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>380</v>
       </c>
@@ -46621,7 +46631,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="404" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>189</v>
       </c>
@@ -46716,7 +46726,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="405" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>184</v>
       </c>
@@ -46811,7 +46821,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="406" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>187</v>
       </c>
@@ -46906,7 +46916,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="407" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>593</v>
       </c>
@@ -47001,7 +47011,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="408" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>595</v>
       </c>
@@ -47096,7 +47106,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="409" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>596</v>
       </c>
@@ -47191,7 +47201,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="410" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>597</v>
       </c>
@@ -47286,7 +47296,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="411" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>598</v>
       </c>
@@ -47381,7 +47391,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="412" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>600</v>
       </c>
@@ -47476,7 +47486,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="413" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>601</v>
       </c>
@@ -47571,7 +47581,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="414" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>602</v>
       </c>
@@ -47666,7 +47676,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="415" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>354</v>
       </c>
@@ -47761,7 +47771,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="416" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>353</v>
       </c>
@@ -47856,7 +47866,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="417" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>351</v>
       </c>
@@ -47951,7 +47961,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="418" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>350</v>
       </c>
@@ -48046,7 +48056,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="419" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>349</v>
       </c>
@@ -48141,7 +48151,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="420" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>348</v>
       </c>
@@ -48236,7 +48246,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="421" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>345</v>
       </c>
@@ -48331,7 +48341,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="422" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>603</v>
       </c>
@@ -48426,7 +48436,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="423" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>606</v>
       </c>
@@ -48521,7 +48531,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="424" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>607</v>
       </c>
@@ -48616,7 +48626,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="425" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>609</v>
       </c>
@@ -48711,7 +48721,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="426" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>399</v>
       </c>
@@ -48806,7 +48816,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="427" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>405</v>
       </c>
@@ -48901,7 +48911,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="428" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>404</v>
       </c>
@@ -48996,7 +49006,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="429" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>402</v>
       </c>
@@ -49091,7 +49101,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="430" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>610</v>
       </c>
@@ -49186,7 +49196,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="431" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>403</v>
       </c>
@@ -49281,7 +49291,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="432" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>389</v>
       </c>
@@ -49376,7 +49386,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="433" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>386</v>
       </c>
@@ -49471,7 +49481,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="434" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>429</v>
       </c>
@@ -49566,7 +49576,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="435" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>435</v>
       </c>
@@ -49661,7 +49671,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="436" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>434</v>
       </c>
@@ -49756,7 +49766,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="437" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>432</v>
       </c>
@@ -49851,7 +49861,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="438" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>433</v>
       </c>
@@ -49946,7 +49956,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="439" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>483</v>
       </c>
@@ -50041,7 +50051,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="440" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>482</v>
       </c>
@@ -50136,7 +50146,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="441" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>480</v>
       </c>
@@ -50231,7 +50241,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="442" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>478</v>
       </c>
@@ -50326,7 +50336,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="443" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>475</v>
       </c>
@@ -50421,7 +50431,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="444" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>454</v>
       </c>
@@ -50516,7 +50526,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="445" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>453</v>
       </c>
@@ -50611,7 +50621,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="446" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>451</v>
       </c>
@@ -50706,7 +50716,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="447" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>448</v>
       </c>
@@ -50801,7 +50811,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="448" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>449</v>
       </c>
@@ -50896,7 +50906,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="449" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>442</v>
       </c>
@@ -50991,7 +51001,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="450" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>613</v>
       </c>
@@ -51052,7 +51062,7 @@
       <c r="AH450" s="4"/>
       <c r="AI450" s="4"/>
     </row>
-    <row r="451" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>616</v>
       </c>
@@ -51113,7 +51123,7 @@
       <c r="AH451" s="4"/>
       <c r="AI451" s="4"/>
     </row>
-    <row r="452" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>618</v>
       </c>
@@ -51174,7 +51184,7 @@
       <c r="AH452" s="4"/>
       <c r="AI452" s="4"/>
     </row>
-    <row r="453" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>620</v>
       </c>
@@ -51235,7 +51245,7 @@
       <c r="AH453" s="4"/>
       <c r="AI453" s="4"/>
     </row>
-    <row r="454" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>467</v>
       </c>
@@ -51330,7 +51340,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="455" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>466</v>
       </c>
@@ -51425,7 +51435,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="456" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>462</v>
       </c>
@@ -51520,7 +51530,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="457" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>464</v>
       </c>
@@ -51615,7 +51625,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="458" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>465</v>
       </c>
@@ -51710,7 +51720,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="459" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>621</v>
       </c>
@@ -51805,7 +51815,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="460" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>468</v>
       </c>
@@ -51900,7 +51910,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="461" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>623</v>
       </c>
@@ -51995,7 +52005,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="462" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>624</v>
       </c>
@@ -52090,7 +52100,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="463" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>625</v>
       </c>
@@ -52185,7 +52195,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="464" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>626</v>
       </c>
@@ -52280,7 +52290,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="465" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>628</v>
       </c>
@@ -52375,7 +52385,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="466" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>630</v>
       </c>
@@ -52470,7 +52480,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="467" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>632</v>
       </c>
@@ -52565,7 +52575,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="468" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>634</v>
       </c>
@@ -52626,7 +52636,7 @@
       <c r="AH468" s="4"/>
       <c r="AI468" s="4"/>
     </row>
-    <row r="469" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>637</v>
       </c>
@@ -52687,7 +52697,7 @@
       <c r="AH469" s="4"/>
       <c r="AI469" s="4"/>
     </row>
-    <row r="470" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>638</v>
       </c>
@@ -52748,7 +52758,7 @@
       <c r="AH470" s="4"/>
       <c r="AI470" s="4"/>
     </row>
-    <row r="471" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>640</v>
       </c>
@@ -52809,7 +52819,7 @@
       <c r="AH471" s="4"/>
       <c r="AI471" s="4"/>
     </row>
-    <row r="472" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>642</v>
       </c>
@@ -52870,7 +52880,7 @@
       <c r="AH472" s="4"/>
       <c r="AI472" s="4"/>
     </row>
-    <row r="473" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>643</v>
       </c>
@@ -52931,7 +52941,7 @@
       <c r="AH473" s="4"/>
       <c r="AI473" s="4"/>
     </row>
-    <row r="474" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>647</v>
       </c>
@@ -52992,7 +53002,7 @@
       <c r="AH474" s="4"/>
       <c r="AI474" s="4"/>
     </row>
-    <row r="475" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>650</v>
       </c>
@@ -53053,7 +53063,7 @@
       <c r="AH475" s="4"/>
       <c r="AI475" s="4"/>
     </row>
-    <row r="476" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>652</v>
       </c>
@@ -53114,7 +53124,7 @@
       <c r="AH476" s="4"/>
       <c r="AI476" s="4"/>
     </row>
-    <row r="477" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>654</v>
       </c>
@@ -53175,7 +53185,7 @@
       <c r="AH477" s="4"/>
       <c r="AI477" s="4"/>
     </row>
-    <row r="478" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>655</v>
       </c>
@@ -53236,7 +53246,7 @@
       <c r="AH478" s="4"/>
       <c r="AI478" s="4"/>
     </row>
-    <row r="479" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>70</v>
       </c>
@@ -53331,7 +53341,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="480" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>68</v>
       </c>
@@ -53426,7 +53436,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="481" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>66</v>
       </c>
@@ -53521,7 +53531,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="482" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>62</v>
       </c>
@@ -53616,7 +53626,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="483" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>57</v>
       </c>
@@ -53711,7 +53721,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="484" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>64</v>
       </c>
@@ -53806,7 +53816,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="485" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>60</v>
       </c>
@@ -53901,7 +53911,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="486" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>656</v>
       </c>
@@ -53962,7 +53972,7 @@
       <c r="AH486" s="4"/>
       <c r="AI486" s="4"/>
     </row>
-    <row r="487" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>658</v>
       </c>
@@ -54023,7 +54033,7 @@
       <c r="AH487" s="4"/>
       <c r="AI487" s="4"/>
     </row>
-    <row r="488" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>660</v>
       </c>
@@ -54084,7 +54094,7 @@
       <c r="AH488" s="4"/>
       <c r="AI488" s="4"/>
     </row>
-    <row r="489" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>661</v>
       </c>
@@ -54145,7 +54155,7 @@
       <c r="AH489" s="4"/>
       <c r="AI489" s="4"/>
     </row>
-    <row r="490" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>662</v>
       </c>
@@ -54206,7 +54216,7 @@
       <c r="AH490" s="4"/>
       <c r="AI490" s="4"/>
     </row>
-    <row r="491" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>663</v>
       </c>
@@ -54267,7 +54277,7 @@
       <c r="AH491" s="4"/>
       <c r="AI491" s="4"/>
     </row>
-    <row r="492" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>664</v>
       </c>
@@ -54328,7 +54338,7 @@
       <c r="AH492" s="4"/>
       <c r="AI492" s="4"/>
     </row>
-    <row r="493" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>666</v>
       </c>
@@ -54389,7 +54399,7 @@
       <c r="AH493" s="4"/>
       <c r="AI493" s="4"/>
     </row>
-    <row r="494" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>667</v>
       </c>
@@ -54450,7 +54460,7 @@
       <c r="AH494" s="4"/>
       <c r="AI494" s="4"/>
     </row>
-    <row r="495" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>668</v>
       </c>
@@ -54511,7 +54521,7 @@
       <c r="AH495" s="4"/>
       <c r="AI495" s="4"/>
     </row>
-    <row r="496" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>263</v>
       </c>
@@ -54606,7 +54616,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="497" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>259</v>
       </c>
@@ -54701,7 +54711,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="498" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>261</v>
       </c>
@@ -54796,7 +54806,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="499" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>255</v>
       </c>
@@ -54891,7 +54901,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="500" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>257</v>
       </c>
@@ -54986,7 +54996,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="501" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>669</v>
       </c>
@@ -55081,7 +55091,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="502" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>86</v>
       </c>
@@ -55176,7 +55186,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="503" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>82</v>
       </c>
@@ -55271,7 +55281,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="504" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>670</v>
       </c>
@@ -55366,7 +55376,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="505" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>672</v>
       </c>
@@ -55461,7 +55471,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="506" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>673</v>
       </c>
@@ -55556,7 +55566,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="507" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>674</v>
       </c>
@@ -55651,7 +55661,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="508" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>676</v>
       </c>
@@ -55746,7 +55756,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="509" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>678</v>
       </c>
@@ -55841,7 +55851,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="510" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>680</v>
       </c>
@@ -55936,7 +55946,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="511" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>681</v>
       </c>
@@ -56031,7 +56041,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="512" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>682</v>
       </c>
@@ -56126,7 +56136,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="513" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>684</v>
       </c>
@@ -56221,7 +56231,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="514" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>685</v>
       </c>
@@ -56316,7 +56326,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="515" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>687</v>
       </c>
@@ -56411,7 +56421,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="516" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>688</v>
       </c>
@@ -56506,7 +56516,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="517" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>690</v>
       </c>
@@ -56567,7 +56577,7 @@
       <c r="AH517" s="4"/>
       <c r="AI517" s="4"/>
     </row>
-    <row r="518" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>696</v>
       </c>
@@ -56628,7 +56638,7 @@
       <c r="AH518" s="4"/>
       <c r="AI518" s="4"/>
     </row>
-    <row r="519" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>698</v>
       </c>
@@ -56689,7 +56699,7 @@
       <c r="AH519" s="4"/>
       <c r="AI519" s="4"/>
     </row>
-    <row r="520" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>703</v>
       </c>
@@ -56750,7 +56760,7 @@
       <c r="AH520" s="4"/>
       <c r="AI520" s="4"/>
     </row>
-    <row r="521" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>704</v>
       </c>
@@ -56811,7 +56821,7 @@
       <c r="AH521" s="4"/>
       <c r="AI521" s="4"/>
     </row>
-    <row r="522" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>705</v>
       </c>
@@ -56872,7 +56882,7 @@
       <c r="AH522" s="4"/>
       <c r="AI522" s="4"/>
     </row>
-    <row r="523" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>708</v>
       </c>
@@ -56933,7 +56943,7 @@
       <c r="AH523" s="4"/>
       <c r="AI523" s="4"/>
     </row>
-    <row r="524" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>709</v>
       </c>
@@ -56994,7 +57004,7 @@
       <c r="AH524" s="4"/>
       <c r="AI524" s="4"/>
     </row>
-    <row r="525" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>712</v>
       </c>
@@ -57055,7 +57065,7 @@
       <c r="AH525" s="4"/>
       <c r="AI525" s="4"/>
     </row>
-    <row r="526" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>713</v>
       </c>
@@ -57116,7 +57126,7 @@
       <c r="AH526" s="4"/>
       <c r="AI526" s="4"/>
     </row>
-    <row r="527" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>715</v>
       </c>
@@ -57177,7 +57187,7 @@
       <c r="AH527" s="4"/>
       <c r="AI527" s="4"/>
     </row>
-    <row r="528" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>716</v>
       </c>
@@ -57238,7 +57248,7 @@
       <c r="AH528" s="4"/>
       <c r="AI528" s="4"/>
     </row>
-    <row r="529" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>719</v>
       </c>
@@ -57299,7 +57309,7 @@
       <c r="AH529" s="4"/>
       <c r="AI529" s="4"/>
     </row>
-    <row r="530" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>720</v>
       </c>
@@ -57360,7 +57370,7 @@
       <c r="AH530" s="4"/>
       <c r="AI530" s="4"/>
     </row>
-    <row r="531" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>721</v>
       </c>
@@ -57421,7 +57431,7 @@
       <c r="AH531" s="4"/>
       <c r="AI531" s="4"/>
     </row>
-    <row r="532" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>1707</v>
       </c>
@@ -57482,7 +57492,7 @@
       <c r="AH532" s="4"/>
       <c r="AI532" s="4"/>
     </row>
-    <row r="533" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>1534</v>
       </c>
@@ -57543,7 +57553,7 @@
       <c r="AH533" s="4"/>
       <c r="AI533" s="4"/>
     </row>
-    <row r="534" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>727</v>
       </c>
@@ -57604,7 +57614,7 @@
       <c r="AH534" s="4"/>
       <c r="AI534" s="4"/>
     </row>
-    <row r="535" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>728</v>
       </c>
@@ -57665,7 +57675,7 @@
       <c r="AH535" s="4"/>
       <c r="AI535" s="4"/>
     </row>
-    <row r="536" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>732</v>
       </c>
@@ -57726,7 +57736,7 @@
       <c r="AH536" s="4"/>
       <c r="AI536" s="4"/>
     </row>
-    <row r="537" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>735</v>
       </c>
@@ -57787,7 +57797,7 @@
       <c r="AH537" s="4"/>
       <c r="AI537" s="4"/>
     </row>
-    <row r="538" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>737</v>
       </c>
@@ -57848,7 +57858,7 @@
       <c r="AH538" s="4"/>
       <c r="AI538" s="4"/>
     </row>
-    <row r="539" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>739</v>
       </c>
@@ -57909,7 +57919,7 @@
       <c r="AH539" s="4"/>
       <c r="AI539" s="4"/>
     </row>
-    <row r="540" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>741</v>
       </c>
@@ -57970,7 +57980,7 @@
       <c r="AH540" s="4"/>
       <c r="AI540" s="4"/>
     </row>
-    <row r="541" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>742</v>
       </c>
@@ -58031,7 +58041,7 @@
       <c r="AH541" s="4"/>
       <c r="AI541" s="4"/>
     </row>
-    <row r="542" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>1710</v>
       </c>
@@ -58086,7 +58096,7 @@
       <c r="AH542" s="4"/>
       <c r="AI542" s="4"/>
     </row>
-    <row r="543" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>743</v>
       </c>
@@ -58147,7 +58157,7 @@
       <c r="AH543" s="4"/>
       <c r="AI543" s="4"/>
     </row>
-    <row r="544" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>746</v>
       </c>
@@ -58208,7 +58218,7 @@
       <c r="AH544" s="4"/>
       <c r="AI544" s="4"/>
     </row>
-    <row r="545" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>747</v>
       </c>
@@ -58269,7 +58279,7 @@
       <c r="AH545" s="4"/>
       <c r="AI545" s="4"/>
     </row>
-    <row r="546" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>749</v>
       </c>
@@ -58330,7 +58340,7 @@
       <c r="AH546" s="4"/>
       <c r="AI546" s="4"/>
     </row>
-    <row r="547" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>751</v>
       </c>
@@ -58391,7 +58401,7 @@
       <c r="AH547" s="4"/>
       <c r="AI547" s="4"/>
     </row>
-    <row r="548" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>752</v>
       </c>
@@ -58452,7 +58462,7 @@
       <c r="AH548" s="4"/>
       <c r="AI548" s="4"/>
     </row>
-    <row r="549" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>754</v>
       </c>
@@ -58513,7 +58523,7 @@
       <c r="AH549" s="4"/>
       <c r="AI549" s="4"/>
     </row>
-    <row r="550" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>756</v>
       </c>
@@ -58574,7 +58584,7 @@
       <c r="AH550" s="4"/>
       <c r="AI550" s="4"/>
     </row>
-    <row r="551" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>759</v>
       </c>
@@ -58635,7 +58645,7 @@
       <c r="AH551" s="4"/>
       <c r="AI551" s="4"/>
     </row>
-    <row r="552" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>761</v>
       </c>
@@ -58696,7 +58706,7 @@
       <c r="AH552" s="4"/>
       <c r="AI552" s="4"/>
     </row>
-    <row r="553" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>762</v>
       </c>
@@ -58757,7 +58767,7 @@
       <c r="AH553" s="4"/>
       <c r="AI553" s="4"/>
     </row>
-    <row r="554" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>765</v>
       </c>
@@ -58818,7 +58828,7 @@
       <c r="AH554" s="4"/>
       <c r="AI554" s="4"/>
     </row>
-    <row r="555" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>766</v>
       </c>
@@ -58879,7 +58889,7 @@
       <c r="AH555" s="4"/>
       <c r="AI555" s="4"/>
     </row>
-    <row r="556" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>769</v>
       </c>
@@ -58940,7 +58950,7 @@
       <c r="AH556" s="4"/>
       <c r="AI556" s="4"/>
     </row>
-    <row r="557" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>770</v>
       </c>
@@ -59001,7 +59011,7 @@
       <c r="AH557" s="4"/>
       <c r="AI557" s="4"/>
     </row>
-    <row r="558" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>772</v>
       </c>
@@ -59062,7 +59072,7 @@
       <c r="AH558" s="4"/>
       <c r="AI558" s="4"/>
     </row>
-    <row r="559" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>775</v>
       </c>
@@ -59123,7 +59133,7 @@
       <c r="AH559" s="4"/>
       <c r="AI559" s="4"/>
     </row>
-    <row r="560" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>776</v>
       </c>
@@ -59184,7 +59194,7 @@
       <c r="AH560" s="4"/>
       <c r="AI560" s="4"/>
     </row>
-    <row r="561" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>779</v>
       </c>
@@ -59245,7 +59255,7 @@
       <c r="AH561" s="4"/>
       <c r="AI561" s="4"/>
     </row>
-    <row r="562" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>780</v>
       </c>
@@ -59306,7 +59316,7 @@
       <c r="AH562" s="4"/>
       <c r="AI562" s="4"/>
     </row>
-    <row r="563" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>784</v>
       </c>
@@ -59367,7 +59377,7 @@
       <c r="AH563" s="4"/>
       <c r="AI563" s="4"/>
     </row>
-    <row r="564" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>787</v>
       </c>
@@ -59428,7 +59438,7 @@
       <c r="AH564" s="4"/>
       <c r="AI564" s="4"/>
     </row>
-    <row r="565" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>793</v>
       </c>
@@ -59489,7 +59499,7 @@
       <c r="AH565" s="4"/>
       <c r="AI565" s="4"/>
     </row>
-    <row r="566" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>794</v>
       </c>
@@ -59550,7 +59560,7 @@
       <c r="AH566" s="4"/>
       <c r="AI566" s="4"/>
     </row>
-    <row r="567" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>796</v>
       </c>
@@ -59611,7 +59621,7 @@
       <c r="AH567" s="4"/>
       <c r="AI567" s="4"/>
     </row>
-    <row r="568" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>798</v>
       </c>
@@ -59672,7 +59682,7 @@
       <c r="AH568" s="4"/>
       <c r="AI568" s="4"/>
     </row>
-    <row r="569" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>800</v>
       </c>
@@ -59733,7 +59743,7 @@
       <c r="AH569" s="4"/>
       <c r="AI569" s="4"/>
     </row>
-    <row r="570" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>803</v>
       </c>
@@ -59794,7 +59804,7 @@
       <c r="AH570" s="4"/>
       <c r="AI570" s="4"/>
     </row>
-    <row r="571" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>804</v>
       </c>
@@ -59855,7 +59865,7 @@
       <c r="AH571" s="4"/>
       <c r="AI571" s="4"/>
     </row>
-    <row r="572" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>805</v>
       </c>
@@ -59916,7 +59926,7 @@
       <c r="AH572" s="4"/>
       <c r="AI572" s="4"/>
     </row>
-    <row r="573" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>808</v>
       </c>
@@ -59977,7 +59987,7 @@
       <c r="AH573" s="4"/>
       <c r="AI573" s="4"/>
     </row>
-    <row r="574" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>809</v>
       </c>
@@ -60038,7 +60048,7 @@
       <c r="AH574" s="4"/>
       <c r="AI574" s="4"/>
     </row>
-    <row r="575" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>810</v>
       </c>
@@ -60099,7 +60109,7 @@
       <c r="AH575" s="4"/>
       <c r="AI575" s="4"/>
     </row>
-    <row r="576" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>813</v>
       </c>
@@ -60160,7 +60170,7 @@
       <c r="AH576" s="4"/>
       <c r="AI576" s="4"/>
     </row>
-    <row r="577" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>814</v>
       </c>
@@ -60221,7 +60231,7 @@
       <c r="AH577" s="4"/>
       <c r="AI577" s="4"/>
     </row>
-    <row r="578" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>815</v>
       </c>
@@ -60282,7 +60292,7 @@
       <c r="AH578" s="4"/>
       <c r="AI578" s="4"/>
     </row>
-    <row r="579" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>818</v>
       </c>
@@ -60343,7 +60353,7 @@
       <c r="AH579" s="4"/>
       <c r="AI579" s="4"/>
     </row>
-    <row r="580" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>819</v>
       </c>
@@ -60404,7 +60414,7 @@
       <c r="AH580" s="4"/>
       <c r="AI580" s="4"/>
     </row>
-    <row r="581" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>820</v>
       </c>
@@ -60465,7 +60475,7 @@
       <c r="AH581" s="4"/>
       <c r="AI581" s="4"/>
     </row>
-    <row r="582" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>824</v>
       </c>
@@ -60526,7 +60536,7 @@
       <c r="AH582" s="4"/>
       <c r="AI582" s="4"/>
     </row>
-    <row r="583" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>825</v>
       </c>
@@ -60587,7 +60597,7 @@
       <c r="AH583" s="4"/>
       <c r="AI583" s="4"/>
     </row>
-    <row r="584" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>826</v>
       </c>
@@ -60648,7 +60658,7 @@
       <c r="AH584" s="4"/>
       <c r="AI584" s="4"/>
     </row>
-    <row r="585" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>829</v>
       </c>
@@ -60709,7 +60719,7 @@
       <c r="AH585" s="4"/>
       <c r="AI585" s="4"/>
     </row>
-    <row r="586" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>830</v>
       </c>
@@ -60770,7 +60780,7 @@
       <c r="AH586" s="4"/>
       <c r="AI586" s="4"/>
     </row>
-    <row r="587" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>831</v>
       </c>
@@ -60831,7 +60841,7 @@
       <c r="AH587" s="4"/>
       <c r="AI587" s="4"/>
     </row>
-    <row r="588" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>834</v>
       </c>
@@ -60892,7 +60902,7 @@
       <c r="AH588" s="4"/>
       <c r="AI588" s="4"/>
     </row>
-    <row r="589" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>835</v>
       </c>
@@ -60953,7 +60963,7 @@
       <c r="AH589" s="4"/>
       <c r="AI589" s="4"/>
     </row>
-    <row r="590" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>836</v>
       </c>
@@ -61014,7 +61024,7 @@
       <c r="AH590" s="4"/>
       <c r="AI590" s="4"/>
     </row>
-    <row r="591" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>839</v>
       </c>
@@ -61075,7 +61085,7 @@
       <c r="AH591" s="4"/>
       <c r="AI591" s="4"/>
     </row>
-    <row r="592" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>840</v>
       </c>
@@ -61136,7 +61146,7 @@
       <c r="AH592" s="4"/>
       <c r="AI592" s="4"/>
     </row>
-    <row r="593" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>841</v>
       </c>
@@ -61197,7 +61207,7 @@
       <c r="AH593" s="4"/>
       <c r="AI593" s="4"/>
     </row>
-    <row r="594" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>842</v>
       </c>
@@ -61258,7 +61268,7 @@
       <c r="AH594" s="4"/>
       <c r="AI594" s="4"/>
     </row>
-    <row r="595" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>846</v>
       </c>
@@ -61319,7 +61329,7 @@
       <c r="AH595" s="4"/>
       <c r="AI595" s="4"/>
     </row>
-    <row r="596" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>847</v>
       </c>
@@ -61380,7 +61390,7 @@
       <c r="AH596" s="4"/>
       <c r="AI596" s="4"/>
     </row>
-    <row r="597" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>848</v>
       </c>
@@ -61441,7 +61451,7 @@
       <c r="AH597" s="4"/>
       <c r="AI597" s="4"/>
     </row>
-    <row r="598" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>849</v>
       </c>
@@ -61502,7 +61512,7 @@
       <c r="AH598" s="4"/>
       <c r="AI598" s="4"/>
     </row>
-    <row r="599" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>850</v>
       </c>
@@ -61563,7 +61573,7 @@
       <c r="AH599" s="4"/>
       <c r="AI599" s="4"/>
     </row>
-    <row r="600" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>853</v>
       </c>
@@ -61624,7 +61634,7 @@
       <c r="AH600" s="4"/>
       <c r="AI600" s="4"/>
     </row>
-    <row r="601" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>854</v>
       </c>
@@ -61685,7 +61695,7 @@
       <c r="AH601" s="4"/>
       <c r="AI601" s="4"/>
     </row>
-    <row r="602" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>855</v>
       </c>
@@ -61746,7 +61756,7 @@
       <c r="AH602" s="4"/>
       <c r="AI602" s="4"/>
     </row>
-    <row r="603" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>858</v>
       </c>
@@ -61807,7 +61817,7 @@
       <c r="AH603" s="4"/>
       <c r="AI603" s="4"/>
     </row>
-    <row r="604" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>859</v>
       </c>
@@ -61868,7 +61878,7 @@
       <c r="AH604" s="4"/>
       <c r="AI604" s="4"/>
     </row>
-    <row r="605" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>860</v>
       </c>
@@ -61929,7 +61939,7 @@
       <c r="AH605" s="4"/>
       <c r="AI605" s="4"/>
     </row>
-    <row r="606" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>863</v>
       </c>
@@ -61990,7 +62000,7 @@
       <c r="AH606" s="4"/>
       <c r="AI606" s="4"/>
     </row>
-    <row r="607" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>864</v>
       </c>
@@ -62051,7 +62061,7 @@
       <c r="AH607" s="4"/>
       <c r="AI607" s="4"/>
     </row>
-    <row r="608" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>865</v>
       </c>
@@ -62112,7 +62122,7 @@
       <c r="AH608" s="4"/>
       <c r="AI608" s="4"/>
     </row>
-    <row r="609" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>868</v>
       </c>
@@ -62173,7 +62183,7 @@
       <c r="AH609" s="4"/>
       <c r="AI609" s="4"/>
     </row>
-    <row r="610" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>869</v>
       </c>
@@ -62234,7 +62244,7 @@
       <c r="AH610" s="4"/>
       <c r="AI610" s="4"/>
     </row>
-    <row r="611" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>870</v>
       </c>
@@ -62295,7 +62305,7 @@
       <c r="AH611" s="4"/>
       <c r="AI611" s="4"/>
     </row>
-    <row r="612" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>873</v>
       </c>
@@ -62356,7 +62366,7 @@
       <c r="AH612" s="4"/>
       <c r="AI612" s="4"/>
     </row>
-    <row r="613" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>874</v>
       </c>
@@ -62417,7 +62427,7 @@
       <c r="AH613" s="4"/>
       <c r="AI613" s="4"/>
     </row>
-    <row r="614" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>875</v>
       </c>
@@ -62478,7 +62488,7 @@
       <c r="AH614" s="4"/>
       <c r="AI614" s="4"/>
     </row>
-    <row r="615" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>878</v>
       </c>
@@ -62539,7 +62549,7 @@
       <c r="AH615" s="4"/>
       <c r="AI615" s="4"/>
     </row>
-    <row r="616" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>879</v>
       </c>
@@ -62600,7 +62610,7 @@
       <c r="AH616" s="4"/>
       <c r="AI616" s="4"/>
     </row>
-    <row r="617" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>880</v>
       </c>
@@ -62661,7 +62671,7 @@
       <c r="AH617" s="4"/>
       <c r="AI617" s="4"/>
     </row>
-    <row r="618" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>883</v>
       </c>
@@ -62722,7 +62732,7 @@
       <c r="AH618" s="4"/>
       <c r="AI618" s="4"/>
     </row>
-    <row r="619" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>884</v>
       </c>
@@ -62783,7 +62793,7 @@
       <c r="AH619" s="4"/>
       <c r="AI619" s="4"/>
     </row>
-    <row r="620" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>885</v>
       </c>
@@ -62844,7 +62854,7 @@
       <c r="AH620" s="4"/>
       <c r="AI620" s="4"/>
     </row>
-    <row r="621" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>888</v>
       </c>
@@ -62905,7 +62915,7 @@
       <c r="AH621" s="4"/>
       <c r="AI621" s="4"/>
     </row>
-    <row r="622" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>889</v>
       </c>
@@ -62966,7 +62976,7 @@
       <c r="AH622" s="4"/>
       <c r="AI622" s="4"/>
     </row>
-    <row r="623" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>890</v>
       </c>
@@ -63027,7 +63037,7 @@
       <c r="AH623" s="4"/>
       <c r="AI623" s="4"/>
     </row>
-    <row r="624" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>891</v>
       </c>
@@ -63088,7 +63098,7 @@
       <c r="AH624" s="4"/>
       <c r="AI624" s="4"/>
     </row>
-    <row r="625" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>894</v>
       </c>
@@ -63149,7 +63159,7 @@
       <c r="AH625" s="4"/>
       <c r="AI625" s="4"/>
     </row>
-    <row r="626" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>896</v>
       </c>
@@ -63210,7 +63220,7 @@
       <c r="AH626" s="4"/>
       <c r="AI626" s="4"/>
     </row>
-    <row r="627" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>898</v>
       </c>
@@ -63271,7 +63281,7 @@
       <c r="AH627" s="4"/>
       <c r="AI627" s="4"/>
     </row>
-    <row r="628" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>900</v>
       </c>
@@ -63332,7 +63342,7 @@
       <c r="AH628" s="4"/>
       <c r="AI628" s="4"/>
     </row>
-    <row r="629" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>904</v>
       </c>
@@ -63393,7 +63403,7 @@
       <c r="AH629" s="4"/>
       <c r="AI629" s="4"/>
     </row>
-    <row r="630" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>906</v>
       </c>
@@ -63454,7 +63464,7 @@
       <c r="AH630" s="4"/>
       <c r="AI630" s="4"/>
     </row>
-    <row r="631" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>908</v>
       </c>
@@ -63515,7 +63525,7 @@
       <c r="AH631" s="4"/>
       <c r="AI631" s="4"/>
     </row>
-    <row r="632" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>910</v>
       </c>
@@ -63576,7 +63586,7 @@
       <c r="AH632" s="4"/>
       <c r="AI632" s="4"/>
     </row>
-    <row r="633" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>912</v>
       </c>
@@ -63637,7 +63647,7 @@
       <c r="AH633" s="4"/>
       <c r="AI633" s="4"/>
     </row>
-    <row r="634" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>915</v>
       </c>
@@ -63698,7 +63708,7 @@
       <c r="AH634" s="4"/>
       <c r="AI634" s="4"/>
     </row>
-    <row r="635" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>916</v>
       </c>
@@ -63759,7 +63769,7 @@
       <c r="AH635" s="4"/>
       <c r="AI635" s="4"/>
     </row>
-    <row r="636" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>917</v>
       </c>
@@ -63820,7 +63830,7 @@
       <c r="AH636" s="4"/>
       <c r="AI636" s="4"/>
     </row>
-    <row r="637" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>918</v>
       </c>
@@ -63881,7 +63891,7 @@
       <c r="AH637" s="4"/>
       <c r="AI637" s="4"/>
     </row>
-    <row r="638" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>919</v>
       </c>
@@ -63942,7 +63952,7 @@
       <c r="AH638" s="4"/>
       <c r="AI638" s="4"/>
     </row>
-    <row r="639" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>922</v>
       </c>
@@ -64003,7 +64013,7 @@
       <c r="AH639" s="4"/>
       <c r="AI639" s="4"/>
     </row>
-    <row r="640" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>926</v>
       </c>
@@ -64064,7 +64074,7 @@
       <c r="AH640" s="4"/>
       <c r="AI640" s="4"/>
     </row>
-    <row r="641" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>927</v>
       </c>
@@ -64125,7 +64135,7 @@
       <c r="AH641" s="4"/>
       <c r="AI641" s="4"/>
     </row>
-    <row r="642" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>930</v>
       </c>
@@ -64186,7 +64196,7 @@
       <c r="AH642" s="4"/>
       <c r="AI642" s="4"/>
     </row>
-    <row r="643" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>931</v>
       </c>
@@ -64247,7 +64257,7 @@
       <c r="AH643" s="4"/>
       <c r="AI643" s="4"/>
     </row>
-    <row r="644" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>934</v>
       </c>
@@ -64308,7 +64318,7 @@
       <c r="AH644" s="4"/>
       <c r="AI644" s="4"/>
     </row>
-    <row r="645" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>937</v>
       </c>
@@ -64369,7 +64379,7 @@
       <c r="AH645" s="4"/>
       <c r="AI645" s="4"/>
     </row>
-    <row r="646" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>939</v>
       </c>
@@ -64430,7 +64440,7 @@
       <c r="AH646" s="4"/>
       <c r="AI646" s="4"/>
     </row>
-    <row r="647" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>942</v>
       </c>
@@ -64491,7 +64501,7 @@
       <c r="AH647" s="4"/>
       <c r="AI647" s="4"/>
     </row>
-    <row r="648" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>945</v>
       </c>
@@ -64552,7 +64562,7 @@
       <c r="AH648" s="4"/>
       <c r="AI648" s="4"/>
     </row>
-    <row r="649" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>948</v>
       </c>
@@ -64613,7 +64623,7 @@
       <c r="AH649" s="4"/>
       <c r="AI649" s="4"/>
     </row>
-    <row r="650" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>949</v>
       </c>
@@ -64674,7 +64684,7 @@
       <c r="AH650" s="4"/>
       <c r="AI650" s="4"/>
     </row>
-    <row r="651" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>950</v>
       </c>
@@ -64735,7 +64745,7 @@
       <c r="AH651" s="4"/>
       <c r="AI651" s="4"/>
     </row>
-    <row r="652" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>953</v>
       </c>
@@ -64796,7 +64806,7 @@
       <c r="AH652" s="4"/>
       <c r="AI652" s="4"/>
     </row>
-    <row r="653" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>955</v>
       </c>
@@ -64857,7 +64867,7 @@
       <c r="AH653" s="4"/>
       <c r="AI653" s="4"/>
     </row>
-    <row r="654" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>956</v>
       </c>
@@ -64918,7 +64928,7 @@
       <c r="AH654" s="4"/>
       <c r="AI654" s="4"/>
     </row>
-    <row r="655" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>957</v>
       </c>
@@ -64979,7 +64989,7 @@
       <c r="AH655" s="4"/>
       <c r="AI655" s="4"/>
     </row>
-    <row r="656" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>958</v>
       </c>
@@ -65040,7 +65050,7 @@
       <c r="AH656" s="4"/>
       <c r="AI656" s="4"/>
     </row>
-    <row r="657" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>961</v>
       </c>
@@ -65101,7 +65111,7 @@
       <c r="AH657" s="4"/>
       <c r="AI657" s="4"/>
     </row>
-    <row r="658" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>962</v>
       </c>
@@ -65162,7 +65172,7 @@
       <c r="AH658" s="4"/>
       <c r="AI658" s="4"/>
     </row>
-    <row r="659" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>964</v>
       </c>
@@ -65223,7 +65233,7 @@
       <c r="AH659" s="4"/>
       <c r="AI659" s="4"/>
     </row>
-    <row r="660" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>965</v>
       </c>
@@ -65284,7 +65294,7 @@
       <c r="AH660" s="4"/>
       <c r="AI660" s="4"/>
     </row>
-    <row r="661" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>966</v>
       </c>
@@ -65345,7 +65355,7 @@
       <c r="AH661" s="4"/>
       <c r="AI661" s="4"/>
     </row>
-    <row r="662" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>969</v>
       </c>
@@ -65406,7 +65416,7 @@
       <c r="AH662" s="4"/>
       <c r="AI662" s="4"/>
     </row>
-    <row r="663" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>971</v>
       </c>
@@ -65467,7 +65477,7 @@
       <c r="AH663" s="4"/>
       <c r="AI663" s="4"/>
     </row>
-    <row r="664" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>973</v>
       </c>
@@ -65528,7 +65538,7 @@
       <c r="AH664" s="4"/>
       <c r="AI664" s="4"/>
     </row>
-    <row r="665" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>976</v>
       </c>
@@ -65589,7 +65599,7 @@
       <c r="AH665" s="4"/>
       <c r="AI665" s="4"/>
     </row>
-    <row r="666" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>979</v>
       </c>
@@ -65650,7 +65660,7 @@
       <c r="AH666" s="4"/>
       <c r="AI666" s="4"/>
     </row>
-    <row r="667" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>982</v>
       </c>
@@ -65711,7 +65721,7 @@
       <c r="AH667" s="4"/>
       <c r="AI667" s="4"/>
     </row>
-    <row r="668" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>983</v>
       </c>
@@ -65772,7 +65782,7 @@
       <c r="AH668" s="4"/>
       <c r="AI668" s="4"/>
     </row>
-    <row r="669" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>986</v>
       </c>
@@ -65833,7 +65843,7 @@
       <c r="AH669" s="4"/>
       <c r="AI669" s="4"/>
     </row>
-    <row r="670" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>987</v>
       </c>
@@ -65894,7 +65904,7 @@
       <c r="AH670" s="4"/>
       <c r="AI670" s="4"/>
     </row>
-    <row r="671" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>988</v>
       </c>
@@ -65955,7 +65965,7 @@
       <c r="AH671" s="4"/>
       <c r="AI671" s="4"/>
     </row>
-    <row r="672" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>989</v>
       </c>
@@ -66016,7 +66026,7 @@
       <c r="AH672" s="4"/>
       <c r="AI672" s="4"/>
     </row>
-    <row r="673" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>992</v>
       </c>
@@ -66077,7 +66087,7 @@
       <c r="AH673" s="4"/>
       <c r="AI673" s="4"/>
     </row>
-    <row r="674" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>993</v>
       </c>
@@ -66138,7 +66148,7 @@
       <c r="AH674" s="4"/>
       <c r="AI674" s="4"/>
     </row>
-    <row r="675" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>994</v>
       </c>
@@ -66199,7 +66209,7 @@
       <c r="AH675" s="4"/>
       <c r="AI675" s="4"/>
     </row>
-    <row r="676" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>995</v>
       </c>
@@ -66260,7 +66270,7 @@
       <c r="AH676" s="4"/>
       <c r="AI676" s="4"/>
     </row>
-    <row r="677" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>998</v>
       </c>
@@ -66321,7 +66331,7 @@
       <c r="AH677" s="4"/>
       <c r="AI677" s="4"/>
     </row>
-    <row r="678" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>1001</v>
       </c>
@@ -66382,7 +66392,7 @@
       <c r="AH678" s="4"/>
       <c r="AI678" s="4"/>
     </row>
-    <row r="679" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>1002</v>
       </c>
@@ -66443,7 +66453,7 @@
       <c r="AH679" s="4"/>
       <c r="AI679" s="4"/>
     </row>
-    <row r="680" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>1003</v>
       </c>
@@ -66504,7 +66514,7 @@
       <c r="AH680" s="4"/>
       <c r="AI680" s="4"/>
     </row>
-    <row r="681" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>1004</v>
       </c>
@@ -66565,7 +66575,7 @@
       <c r="AH681" s="4"/>
       <c r="AI681" s="4"/>
     </row>
-    <row r="682" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>1005</v>
       </c>
@@ -66626,7 +66636,7 @@
       <c r="AH682" s="4"/>
       <c r="AI682" s="4"/>
     </row>
-    <row r="683" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>1008</v>
       </c>
@@ -66687,7 +66697,7 @@
       <c r="AH683" s="4"/>
       <c r="AI683" s="4"/>
     </row>
-    <row r="684" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>1009</v>
       </c>
@@ -66748,7 +66758,7 @@
       <c r="AH684" s="4"/>
       <c r="AI684" s="4"/>
     </row>
-    <row r="685" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>1012</v>
       </c>
@@ -66809,7 +66819,7 @@
       <c r="AH685" s="4"/>
       <c r="AI685" s="4"/>
     </row>
-    <row r="686" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>1013</v>
       </c>
@@ -66870,7 +66880,7 @@
       <c r="AH686" s="4"/>
       <c r="AI686" s="4"/>
     </row>
-    <row r="687" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>1015</v>
       </c>
@@ -66931,7 +66941,7 @@
       <c r="AH687" s="4"/>
       <c r="AI687" s="4"/>
     </row>
-    <row r="688" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>1020</v>
       </c>
@@ -66992,7 +67002,7 @@
       <c r="AH688" s="4"/>
       <c r="AI688" s="4"/>
     </row>
-    <row r="689" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>1022</v>
       </c>
@@ -67053,7 +67063,7 @@
       <c r="AH689" s="4"/>
       <c r="AI689" s="4"/>
     </row>
-    <row r="690" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1026</v>
       </c>
@@ -67114,7 +67124,7 @@
       <c r="AH690" s="4"/>
       <c r="AI690" s="4"/>
     </row>
-    <row r="691" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1027</v>
       </c>
@@ -67175,7 +67185,7 @@
       <c r="AH691" s="4"/>
       <c r="AI691" s="4"/>
     </row>
-    <row r="692" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1029</v>
       </c>
@@ -67236,7 +67246,7 @@
       <c r="AH692" s="4"/>
       <c r="AI692" s="4"/>
     </row>
-    <row r="693" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1032</v>
       </c>
@@ -67297,7 +67307,7 @@
       <c r="AH693" s="4"/>
       <c r="AI693" s="4"/>
     </row>
-    <row r="694" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1033</v>
       </c>
@@ -67358,7 +67368,7 @@
       <c r="AH694" s="4"/>
       <c r="AI694" s="4"/>
     </row>
-    <row r="695" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1034</v>
       </c>
@@ -67419,7 +67429,7 @@
       <c r="AH695" s="4"/>
       <c r="AI695" s="4"/>
     </row>
-    <row r="696" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1036</v>
       </c>
@@ -67480,7 +67490,7 @@
       <c r="AH696" s="4"/>
       <c r="AI696" s="4"/>
     </row>
-    <row r="697" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1040</v>
       </c>
@@ -67541,7 +67551,7 @@
       <c r="AH697" s="4"/>
       <c r="AI697" s="4"/>
     </row>
-    <row r="698" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1042</v>
       </c>
@@ -67602,7 +67612,7 @@
       <c r="AH698" s="4"/>
       <c r="AI698" s="4"/>
     </row>
-    <row r="699" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1045</v>
       </c>
@@ -67663,7 +67673,7 @@
       <c r="AH699" s="4"/>
       <c r="AI699" s="4"/>
     </row>
-    <row r="700" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1046</v>
       </c>
@@ -67724,7 +67734,7 @@
       <c r="AH700" s="4"/>
       <c r="AI700" s="4"/>
     </row>
-    <row r="701" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>1049</v>
       </c>
@@ -67785,7 +67795,7 @@
       <c r="AH701" s="4"/>
       <c r="AI701" s="4"/>
     </row>
-    <row r="702" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>1050</v>
       </c>
@@ -67846,7 +67856,7 @@
       <c r="AH702" s="4"/>
       <c r="AI702" s="4"/>
     </row>
-    <row r="703" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1051</v>
       </c>
@@ -67907,7 +67917,7 @@
       <c r="AH703" s="4"/>
       <c r="AI703" s="4"/>
     </row>
-    <row r="704" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1053</v>
       </c>
@@ -67968,7 +67978,7 @@
       <c r="AH704" s="4"/>
       <c r="AI704" s="4"/>
     </row>
-    <row r="705" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1054</v>
       </c>
@@ -68029,7 +68039,7 @@
       <c r="AH705" s="4"/>
       <c r="AI705" s="4"/>
     </row>
-    <row r="706" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1055</v>
       </c>
@@ -68090,7 +68100,7 @@
       <c r="AH706" s="4"/>
       <c r="AI706" s="4"/>
     </row>
-    <row r="707" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1059</v>
       </c>
@@ -68151,7 +68161,7 @@
       <c r="AH707" s="4"/>
       <c r="AI707" s="4"/>
     </row>
-    <row r="708" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1061</v>
       </c>
@@ -68212,7 +68222,7 @@
       <c r="AH708" s="4"/>
       <c r="AI708" s="4"/>
     </row>
-    <row r="709" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1063</v>
       </c>
@@ -68273,7 +68283,7 @@
       <c r="AH709" s="4"/>
       <c r="AI709" s="4"/>
     </row>
-    <row r="710" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1064</v>
       </c>
@@ -68334,7 +68344,7 @@
       <c r="AH710" s="4"/>
       <c r="AI710" s="4"/>
     </row>
-    <row r="711" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1067</v>
       </c>
@@ -68395,7 +68405,7 @@
       <c r="AH711" s="4"/>
       <c r="AI711" s="4"/>
     </row>
-    <row r="712" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1070</v>
       </c>
@@ -68456,7 +68466,7 @@
       <c r="AH712" s="4"/>
       <c r="AI712" s="4"/>
     </row>
-    <row r="713" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>1071</v>
       </c>
@@ -68517,7 +68527,7 @@
       <c r="AH713" s="4"/>
       <c r="AI713" s="4"/>
     </row>
-    <row r="714" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>1074</v>
       </c>
@@ -68578,7 +68588,7 @@
       <c r="AH714" s="4"/>
       <c r="AI714" s="4"/>
     </row>
-    <row r="715" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>1078</v>
       </c>
@@ -68639,7 +68649,7 @@
       <c r="AH715" s="4"/>
       <c r="AI715" s="4"/>
     </row>
-    <row r="716" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>1079</v>
       </c>
@@ -68700,7 +68710,7 @@
       <c r="AH716" s="4"/>
       <c r="AI716" s="4"/>
     </row>
-    <row r="717" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>1080</v>
       </c>
@@ -68761,7 +68771,7 @@
       <c r="AH717" s="4"/>
       <c r="AI717" s="4"/>
     </row>
-    <row r="718" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>1082</v>
       </c>
@@ -68822,7 +68832,7 @@
       <c r="AH718" s="4"/>
       <c r="AI718" s="4"/>
     </row>
-    <row r="719" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>1085</v>
       </c>
@@ -68883,7 +68893,7 @@
       <c r="AH719" s="4"/>
       <c r="AI719" s="4"/>
     </row>
-    <row r="720" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>1086</v>
       </c>
@@ -68944,7 +68954,7 @@
       <c r="AH720" s="4"/>
       <c r="AI720" s="4"/>
     </row>
-    <row r="721" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1087</v>
       </c>
@@ -69005,7 +69015,7 @@
       <c r="AH721" s="4"/>
       <c r="AI721" s="4"/>
     </row>
-    <row r="722" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1089</v>
       </c>
@@ -69066,7 +69076,7 @@
       <c r="AH722" s="4"/>
       <c r="AI722" s="4"/>
     </row>
-    <row r="723" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1090</v>
       </c>
@@ -69127,7 +69137,7 @@
       <c r="AH723" s="4"/>
       <c r="AI723" s="4"/>
     </row>
-    <row r="724" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1091</v>
       </c>
@@ -69188,7 +69198,7 @@
       <c r="AH724" s="4"/>
       <c r="AI724" s="4"/>
     </row>
-    <row r="725" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1092</v>
       </c>
@@ -69249,7 +69259,7 @@
       <c r="AH725" s="4"/>
       <c r="AI725" s="4"/>
     </row>
-    <row r="726" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1093</v>
       </c>
@@ -69310,7 +69320,7 @@
       <c r="AH726" s="4"/>
       <c r="AI726" s="4"/>
     </row>
-    <row r="727" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1096</v>
       </c>
@@ -69371,7 +69381,7 @@
       <c r="AH727" s="4"/>
       <c r="AI727" s="4"/>
     </row>
-    <row r="728" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>1097</v>
       </c>
@@ -69432,7 +69442,7 @@
       <c r="AH728" s="4"/>
       <c r="AI728" s="4"/>
     </row>
-    <row r="729" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>1098</v>
       </c>
@@ -69493,7 +69503,7 @@
       <c r="AH729" s="4"/>
       <c r="AI729" s="4"/>
     </row>
-    <row r="730" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>1101</v>
       </c>
@@ -69554,7 +69564,7 @@
       <c r="AH730" s="4"/>
       <c r="AI730" s="4"/>
     </row>
-    <row r="731" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>1103</v>
       </c>
@@ -69615,7 +69625,7 @@
       <c r="AH731" s="4"/>
       <c r="AI731" s="4"/>
     </row>
-    <row r="732" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>1104</v>
       </c>
@@ -69676,7 +69686,7 @@
       <c r="AH732" s="4"/>
       <c r="AI732" s="4"/>
     </row>
-    <row r="733" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>1107</v>
       </c>
@@ -69737,7 +69747,7 @@
       <c r="AH733" s="4"/>
       <c r="AI733" s="4"/>
     </row>
-    <row r="734" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>1109</v>
       </c>
@@ -69798,7 +69808,7 @@
       <c r="AH734" s="4"/>
       <c r="AI734" s="4"/>
     </row>
-    <row r="735" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>1110</v>
       </c>
@@ -69859,7 +69869,7 @@
       <c r="AH735" s="4"/>
       <c r="AI735" s="4"/>
     </row>
-    <row r="736" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>1111</v>
       </c>
@@ -69920,7 +69930,7 @@
       <c r="AH736" s="4"/>
       <c r="AI736" s="4"/>
     </row>
-    <row r="737" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>1114</v>
       </c>
@@ -69981,7 +69991,7 @@
       <c r="AH737" s="4"/>
       <c r="AI737" s="4"/>
     </row>
-    <row r="738" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>1115</v>
       </c>
@@ -70042,7 +70052,7 @@
       <c r="AH738" s="4"/>
       <c r="AI738" s="4"/>
     </row>
-    <row r="739" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>1118</v>
       </c>
@@ -70103,7 +70113,7 @@
       <c r="AH739" s="4"/>
       <c r="AI739" s="4"/>
     </row>
-    <row r="740" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>1119</v>
       </c>
@@ -70164,7 +70174,7 @@
       <c r="AH740" s="4"/>
       <c r="AI740" s="4"/>
     </row>
-    <row r="741" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>1122</v>
       </c>
@@ -70225,7 +70235,7 @@
       <c r="AH741" s="4"/>
       <c r="AI741" s="4"/>
     </row>
-    <row r="742" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>1124</v>
       </c>
@@ -70286,7 +70296,7 @@
       <c r="AH742" s="4"/>
       <c r="AI742" s="4"/>
     </row>
-    <row r="743" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>1127</v>
       </c>
@@ -70347,7 +70357,7 @@
       <c r="AH743" s="4"/>
       <c r="AI743" s="4"/>
     </row>
-    <row r="744" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>1128</v>
       </c>
@@ -70408,7 +70418,7 @@
       <c r="AH744" s="4"/>
       <c r="AI744" s="4"/>
     </row>
-    <row r="745" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>1131</v>
       </c>
@@ -70469,7 +70479,7 @@
       <c r="AH745" s="4"/>
       <c r="AI745" s="4"/>
     </row>
-    <row r="746" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>1132</v>
       </c>
@@ -70530,7 +70540,7 @@
       <c r="AH746" s="4"/>
       <c r="AI746" s="4"/>
     </row>
-    <row r="747" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>1136</v>
       </c>
@@ -70591,7 +70601,7 @@
       <c r="AH747" s="4"/>
       <c r="AI747" s="4"/>
     </row>
-    <row r="748" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>1137</v>
       </c>
@@ -70652,7 +70662,7 @@
       <c r="AH748" s="4"/>
       <c r="AI748" s="4"/>
     </row>
-    <row r="749" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>1138</v>
       </c>
@@ -70713,7 +70723,7 @@
       <c r="AH749" s="4"/>
       <c r="AI749" s="4"/>
     </row>
-    <row r="750" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>1140</v>
       </c>
@@ -70774,7 +70784,7 @@
       <c r="AH750" s="4"/>
       <c r="AI750" s="4"/>
     </row>
-    <row r="751" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>1141</v>
       </c>
@@ -70835,7 +70845,7 @@
       <c r="AH751" s="4"/>
       <c r="AI751" s="4"/>
     </row>
-    <row r="752" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>1143</v>
       </c>
@@ -70896,7 +70906,7 @@
       <c r="AH752" s="4"/>
       <c r="AI752" s="4"/>
     </row>
-    <row r="753" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>1144</v>
       </c>
@@ -70957,7 +70967,7 @@
       <c r="AH753" s="4"/>
       <c r="AI753" s="4"/>
     </row>
-    <row r="754" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>1147</v>
       </c>
@@ -71018,7 +71028,7 @@
       <c r="AH754" s="4"/>
       <c r="AI754" s="4"/>
     </row>
-    <row r="755" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>1149</v>
       </c>
@@ -71079,7 +71089,7 @@
       <c r="AH755" s="4"/>
       <c r="AI755" s="4"/>
     </row>
-    <row r="756" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>1150</v>
       </c>
@@ -71140,7 +71150,7 @@
       <c r="AH756" s="4"/>
       <c r="AI756" s="4"/>
     </row>
-    <row r="757" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>1153</v>
       </c>
@@ -71201,7 +71211,7 @@
       <c r="AH757" s="4"/>
       <c r="AI757" s="4"/>
     </row>
-    <row r="758" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1154</v>
       </c>
@@ -71262,7 +71272,7 @@
       <c r="AH758" s="4"/>
       <c r="AI758" s="4"/>
     </row>
-    <row r="759" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1155</v>
       </c>
@@ -71323,7 +71333,7 @@
       <c r="AH759" s="4"/>
       <c r="AI759" s="4"/>
     </row>
-    <row r="760" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>1157</v>
       </c>
@@ -71384,7 +71394,7 @@
       <c r="AH760" s="4"/>
       <c r="AI760" s="4"/>
     </row>
-    <row r="761" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>1158</v>
       </c>
@@ -71445,7 +71455,7 @@
       <c r="AH761" s="4"/>
       <c r="AI761" s="4"/>
     </row>
-    <row r="762" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>1161</v>
       </c>
@@ -71506,7 +71516,7 @@
       <c r="AH762" s="4"/>
       <c r="AI762" s="4"/>
     </row>
-    <row r="763" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>1162</v>
       </c>
@@ -71567,7 +71577,7 @@
       <c r="AH763" s="4"/>
       <c r="AI763" s="4"/>
     </row>
-    <row r="764" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>1163</v>
       </c>
@@ -71628,7 +71638,7 @@
       <c r="AH764" s="4"/>
       <c r="AI764" s="4"/>
     </row>
-    <row r="765" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1165</v>
       </c>
@@ -71689,7 +71699,7 @@
       <c r="AH765" s="4"/>
       <c r="AI765" s="4"/>
     </row>
-    <row r="766" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1166</v>
       </c>
@@ -71750,7 +71760,7 @@
       <c r="AH766" s="4"/>
       <c r="AI766" s="4"/>
     </row>
-    <row r="767" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>1167</v>
       </c>
@@ -71811,7 +71821,7 @@
       <c r="AH767" s="4"/>
       <c r="AI767" s="4"/>
     </row>
-    <row r="768" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>1170</v>
       </c>
@@ -71872,7 +71882,7 @@
       <c r="AH768" s="4"/>
       <c r="AI768" s="4"/>
     </row>
-    <row r="769" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>1171</v>
       </c>
@@ -71933,7 +71943,7 @@
       <c r="AH769" s="4"/>
       <c r="AI769" s="4"/>
     </row>
-    <row r="770" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>1172</v>
       </c>
@@ -71994,7 +72004,7 @@
       <c r="AH770" s="4"/>
       <c r="AI770" s="4"/>
     </row>
-    <row r="771" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>1173</v>
       </c>
@@ -72055,7 +72065,7 @@
       <c r="AH771" s="4"/>
       <c r="AI771" s="4"/>
     </row>
-    <row r="772" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>1176</v>
       </c>
@@ -72116,7 +72126,7 @@
       <c r="AH772" s="4"/>
       <c r="AI772" s="4"/>
     </row>
-    <row r="773" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>1177</v>
       </c>
@@ -72177,7 +72187,7 @@
       <c r="AH773" s="4"/>
       <c r="AI773" s="4"/>
     </row>
-    <row r="774" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1178</v>
       </c>
@@ -72238,7 +72248,7 @@
       <c r="AH774" s="4"/>
       <c r="AI774" s="4"/>
     </row>
-    <row r="775" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>1179</v>
       </c>
@@ -72299,7 +72309,7 @@
       <c r="AH775" s="4"/>
       <c r="AI775" s="4"/>
     </row>
-    <row r="776" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>1180</v>
       </c>
@@ -72360,7 +72370,7 @@
       <c r="AH776" s="4"/>
       <c r="AI776" s="4"/>
     </row>
-    <row r="777" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>1181</v>
       </c>
@@ -72421,7 +72431,7 @@
       <c r="AH777" s="4"/>
       <c r="AI777" s="4"/>
     </row>
-    <row r="778" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1184</v>
       </c>
@@ -72482,7 +72492,7 @@
       <c r="AH778" s="4"/>
       <c r="AI778" s="4"/>
     </row>
-    <row r="779" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>1187</v>
       </c>
@@ -72543,7 +72553,7 @@
       <c r="AH779" s="4"/>
       <c r="AI779" s="4"/>
     </row>
-    <row r="780" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1188</v>
       </c>
@@ -72604,7 +72614,7 @@
       <c r="AH780" s="4"/>
       <c r="AI780" s="4"/>
     </row>
-    <row r="781" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1189</v>
       </c>
@@ -72665,7 +72675,7 @@
       <c r="AH781" s="4"/>
       <c r="AI781" s="4"/>
     </row>
-    <row r="782" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>1190</v>
       </c>
@@ -72726,7 +72736,7 @@
       <c r="AH782" s="4"/>
       <c r="AI782" s="4"/>
     </row>
-    <row r="783" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>1193</v>
       </c>
@@ -72787,7 +72797,7 @@
       <c r="AH783" s="4"/>
       <c r="AI783" s="4"/>
     </row>
-    <row r="784" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>1194</v>
       </c>
@@ -72848,7 +72858,7 @@
       <c r="AH784" s="4"/>
       <c r="AI784" s="4"/>
     </row>
-    <row r="785" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>1195</v>
       </c>
@@ -72909,7 +72919,7 @@
       <c r="AH785" s="4"/>
       <c r="AI785" s="4"/>
     </row>
-    <row r="786" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>1196</v>
       </c>
@@ -72970,7 +72980,7 @@
       <c r="AH786" s="4"/>
       <c r="AI786" s="4"/>
     </row>
-    <row r="787" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>1199</v>
       </c>
@@ -73031,7 +73041,7 @@
       <c r="AH787" s="4"/>
       <c r="AI787" s="4"/>
     </row>
-    <row r="788" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1200</v>
       </c>
@@ -73092,7 +73102,7 @@
       <c r="AH788" s="4"/>
       <c r="AI788" s="4"/>
     </row>
-    <row r="789" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>1203</v>
       </c>
@@ -73153,7 +73163,7 @@
       <c r="AH789" s="4"/>
       <c r="AI789" s="4"/>
     </row>
-    <row r="790" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>1204</v>
       </c>
@@ -73214,7 +73224,7 @@
       <c r="AH790" s="4"/>
       <c r="AI790" s="4"/>
     </row>
-    <row r="791" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>1207</v>
       </c>
@@ -73275,7 +73285,7 @@
       <c r="AH791" s="4"/>
       <c r="AI791" s="4"/>
     </row>
-    <row r="792" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>1210</v>
       </c>
@@ -73336,7 +73346,7 @@
       <c r="AH792" s="4"/>
       <c r="AI792" s="4"/>
     </row>
-    <row r="793" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>1211</v>
       </c>
@@ -73397,7 +73407,7 @@
       <c r="AH793" s="4"/>
       <c r="AI793" s="4"/>
     </row>
-    <row r="794" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>1215</v>
       </c>
@@ -73458,7 +73468,7 @@
       <c r="AH794" s="4"/>
       <c r="AI794" s="4"/>
     </row>
-    <row r="795" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>1216</v>
       </c>
@@ -73519,7 +73529,7 @@
       <c r="AH795" s="4"/>
       <c r="AI795" s="4"/>
     </row>
-    <row r="796" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>1218</v>
       </c>
@@ -73580,7 +73590,7 @@
       <c r="AH796" s="4"/>
       <c r="AI796" s="4"/>
     </row>
-    <row r="797" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
         <v>1221</v>
       </c>
@@ -73641,7 +73651,7 @@
       <c r="AH797" s="4"/>
       <c r="AI797" s="4"/>
     </row>
-    <row r="798" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>1222</v>
       </c>
@@ -73702,7 +73712,7 @@
       <c r="AH798" s="4"/>
       <c r="AI798" s="4"/>
     </row>
-    <row r="799" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>1223</v>
       </c>
@@ -73763,7 +73773,7 @@
       <c r="AH799" s="4"/>
       <c r="AI799" s="4"/>
     </row>
-    <row r="800" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>1224</v>
       </c>
@@ -73824,7 +73834,7 @@
       <c r="AH800" s="4"/>
       <c r="AI800" s="4"/>
     </row>
-    <row r="801" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1227</v>
       </c>
@@ -73885,7 +73895,7 @@
       <c r="AH801" s="4"/>
       <c r="AI801" s="4"/>
     </row>
-    <row r="802" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>1228</v>
       </c>
@@ -73946,7 +73956,7 @@
       <c r="AH802" s="4"/>
       <c r="AI802" s="4"/>
     </row>
-    <row r="803" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>1229</v>
       </c>
@@ -74007,7 +74017,7 @@
       <c r="AH803" s="4"/>
       <c r="AI803" s="4"/>
     </row>
-    <row r="804" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>1232</v>
       </c>
@@ -74068,7 +74078,7 @@
       <c r="AH804" s="4"/>
       <c r="AI804" s="4"/>
     </row>
-    <row r="805" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1233</v>
       </c>
@@ -74129,7 +74139,7 @@
       <c r="AH805" s="4"/>
       <c r="AI805" s="4"/>
     </row>
-    <row r="806" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1234</v>
       </c>
@@ -74190,7 +74200,7 @@
       <c r="AH806" s="4"/>
       <c r="AI806" s="4"/>
     </row>
-    <row r="807" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1237</v>
       </c>
@@ -74251,7 +74261,7 @@
       <c r="AH807" s="4"/>
       <c r="AI807" s="4"/>
     </row>
-    <row r="808" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>1238</v>
       </c>
@@ -74312,7 +74322,7 @@
       <c r="AH808" s="4"/>
       <c r="AI808" s="4"/>
     </row>
-    <row r="809" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>1240</v>
       </c>
@@ -74373,7 +74383,7 @@
       <c r="AH809" s="4"/>
       <c r="AI809" s="4"/>
     </row>
-    <row r="810" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>1241</v>
       </c>
@@ -74434,7 +74444,7 @@
       <c r="AH810" s="4"/>
       <c r="AI810" s="4"/>
     </row>
-    <row r="811" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>1245</v>
       </c>
@@ -74495,7 +74505,7 @@
       <c r="AH811" s="4"/>
       <c r="AI811" s="4"/>
     </row>
-    <row r="812" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>1246</v>
       </c>
@@ -74556,7 +74566,7 @@
       <c r="AH812" s="4"/>
       <c r="AI812" s="4"/>
     </row>
-    <row r="813" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>1248</v>
       </c>
@@ -74617,7 +74627,7 @@
       <c r="AH813" s="4"/>
       <c r="AI813" s="4"/>
     </row>
-    <row r="814" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>1249</v>
       </c>
@@ -74678,7 +74688,7 @@
       <c r="AH814" s="4"/>
       <c r="AI814" s="4"/>
     </row>
-    <row r="815" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>1250</v>
       </c>
@@ -74739,7 +74749,7 @@
       <c r="AH815" s="4"/>
       <c r="AI815" s="4"/>
     </row>
-    <row r="816" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
         <v>1251</v>
       </c>
@@ -74800,7 +74810,7 @@
       <c r="AH816" s="4"/>
       <c r="AI816" s="4"/>
     </row>
-    <row r="817" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
         <v>1254</v>
       </c>
@@ -74861,7 +74871,7 @@
       <c r="AH817" s="4"/>
       <c r="AI817" s="4"/>
     </row>
-    <row r="818" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
         <v>1255</v>
       </c>
@@ -74922,7 +74932,7 @@
       <c r="AH818" s="4"/>
       <c r="AI818" s="4"/>
     </row>
-    <row r="819" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
         <v>1256</v>
       </c>
@@ -74983,7 +74993,7 @@
       <c r="AH819" s="4"/>
       <c r="AI819" s="4"/>
     </row>
-    <row r="820" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
         <v>1259</v>
       </c>
@@ -75044,7 +75054,7 @@
       <c r="AH820" s="4"/>
       <c r="AI820" s="4"/>
     </row>
-    <row r="821" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
         <v>1261</v>
       </c>
@@ -75105,7 +75115,7 @@
       <c r="AH821" s="4"/>
       <c r="AI821" s="4"/>
     </row>
-    <row r="822" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
         <v>1262</v>
       </c>
@@ -75166,7 +75176,7 @@
       <c r="AH822" s="4"/>
       <c r="AI822" s="4"/>
     </row>
-    <row r="823" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
         <v>1265</v>
       </c>
@@ -75227,7 +75237,7 @@
       <c r="AH823" s="4"/>
       <c r="AI823" s="4"/>
     </row>
-    <row r="824" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
         <v>1266</v>
       </c>
@@ -75288,7 +75298,7 @@
       <c r="AH824" s="4"/>
       <c r="AI824" s="4"/>
     </row>
-    <row r="825" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
         <v>1269</v>
       </c>
@@ -75349,7 +75359,7 @@
       <c r="AH825" s="4"/>
       <c r="AI825" s="4"/>
     </row>
-    <row r="826" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
         <v>1270</v>
       </c>
@@ -75410,7 +75420,7 @@
       <c r="AH826" s="4"/>
       <c r="AI826" s="4"/>
     </row>
-    <row r="827" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
         <v>1272</v>
       </c>
@@ -75471,7 +75481,7 @@
       <c r="AH827" s="4"/>
       <c r="AI827" s="4"/>
     </row>
-    <row r="828" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
         <v>1273</v>
       </c>
@@ -75532,7 +75542,7 @@
       <c r="AH828" s="4"/>
       <c r="AI828" s="4"/>
     </row>
-    <row r="829" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
         <v>1274</v>
       </c>
@@ -75593,7 +75603,7 @@
       <c r="AH829" s="4"/>
       <c r="AI829" s="4"/>
     </row>
-    <row r="830" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
         <v>1275</v>
       </c>
@@ -75654,7 +75664,7 @@
       <c r="AH830" s="4"/>
       <c r="AI830" s="4"/>
     </row>
-    <row r="831" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
         <v>1276</v>
       </c>
@@ -75715,7 +75725,7 @@
       <c r="AH831" s="4"/>
       <c r="AI831" s="4"/>
     </row>
-    <row r="832" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
         <v>1279</v>
       </c>
@@ -75776,7 +75786,7 @@
       <c r="AH832" s="4"/>
       <c r="AI832" s="4"/>
     </row>
-    <row r="833" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
         <v>1282</v>
       </c>
@@ -75837,7 +75847,7 @@
       <c r="AH833" s="4"/>
       <c r="AI833" s="4"/>
     </row>
-    <row r="834" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
         <v>1283</v>
       </c>
@@ -75898,7 +75908,7 @@
       <c r="AH834" s="4"/>
       <c r="AI834" s="4"/>
     </row>
-    <row r="835" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
         <v>1284</v>
       </c>
@@ -75959,7 +75969,7 @@
       <c r="AH835" s="4"/>
       <c r="AI835" s="4"/>
     </row>
-    <row r="836" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
         <v>1285</v>
       </c>
@@ -76020,7 +76030,7 @@
       <c r="AH836" s="4"/>
       <c r="AI836" s="4"/>
     </row>
-    <row r="837" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
         <v>1286</v>
       </c>
@@ -76081,7 +76091,7 @@
       <c r="AH837" s="4"/>
       <c r="AI837" s="4"/>
     </row>
-    <row r="838" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
         <v>1290</v>
       </c>
@@ -76142,7 +76152,7 @@
       <c r="AH838" s="4"/>
       <c r="AI838" s="4"/>
     </row>
-    <row r="839" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
         <v>1291</v>
       </c>
@@ -76203,7 +76213,7 @@
       <c r="AH839" s="4"/>
       <c r="AI839" s="4"/>
     </row>
-    <row r="840" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
         <v>1292</v>
       </c>
@@ -76264,7 +76274,7 @@
       <c r="AH840" s="4"/>
       <c r="AI840" s="4"/>
     </row>
-    <row r="841" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
         <v>1293</v>
       </c>
@@ -76325,7 +76335,7 @@
       <c r="AH841" s="4"/>
       <c r="AI841" s="4"/>
     </row>
-    <row r="842" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
         <v>1294</v>
       </c>
@@ -76386,7 +76396,7 @@
       <c r="AH842" s="4"/>
       <c r="AI842" s="4"/>
     </row>
-    <row r="843" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
         <v>1295</v>
       </c>
@@ -76447,7 +76457,7 @@
       <c r="AH843" s="4"/>
       <c r="AI843" s="4"/>
     </row>
-    <row r="844" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
         <v>1296</v>
       </c>
@@ -76508,7 +76518,7 @@
       <c r="AH844" s="4"/>
       <c r="AI844" s="4"/>
     </row>
-    <row r="845" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
         <v>1299</v>
       </c>
@@ -76569,7 +76579,7 @@
       <c r="AH845" s="4"/>
       <c r="AI845" s="4"/>
     </row>
-    <row r="846" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>1714</v>
       </c>
@@ -76630,7 +76640,7 @@
       <c r="AH846" s="4"/>
       <c r="AI846" s="4"/>
     </row>
-    <row r="847" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>1715</v>
       </c>
@@ -76691,7 +76701,7 @@
       <c r="AH847" s="4"/>
       <c r="AI847" s="4"/>
     </row>
-    <row r="848" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>1716</v>
       </c>
@@ -76752,7 +76762,7 @@
       <c r="AH848" s="4"/>
       <c r="AI848" s="4"/>
     </row>
-    <row r="849" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>1717</v>
       </c>
@@ -76813,7 +76823,7 @@
       <c r="AH849" s="4"/>
       <c r="AI849" s="4"/>
     </row>
-    <row r="850" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>1718</v>
       </c>
@@ -76874,7 +76884,7 @@
       <c r="AH850" s="4"/>
       <c r="AI850" s="4"/>
     </row>
-    <row r="851" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>1719</v>
       </c>
@@ -76935,7 +76945,7 @@
       <c r="AH851" s="4"/>
       <c r="AI851" s="4"/>
     </row>
-    <row r="852" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
         <v>1301</v>
       </c>
@@ -76996,7 +77006,7 @@
       <c r="AH852" s="4"/>
       <c r="AI852" s="4"/>
     </row>
-    <row r="853" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
         <v>1302</v>
       </c>
@@ -77057,7 +77067,7 @@
       <c r="AH853" s="4"/>
       <c r="AI853" s="4"/>
     </row>
-    <row r="854" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
         <v>1304</v>
       </c>
@@ -77118,7 +77128,7 @@
       <c r="AH854" s="4"/>
       <c r="AI854" s="4"/>
     </row>
-    <row r="855" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
         <v>1305</v>
       </c>
@@ -77179,7 +77189,7 @@
       <c r="AH855" s="4"/>
       <c r="AI855" s="4"/>
     </row>
-    <row r="856" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
         <v>1307</v>
       </c>
@@ -77362,7 +77372,7 @@
       <c r="AH858" s="4"/>
       <c r="AI858" s="4"/>
     </row>
-    <row r="859" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
         <v>1312</v>
       </c>
@@ -77423,7 +77433,7 @@
       <c r="AH859" s="4"/>
       <c r="AI859" s="4"/>
     </row>
-    <row r="860" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
         <v>1315</v>
       </c>
@@ -77484,7 +77494,7 @@
       <c r="AH860" s="4"/>
       <c r="AI860" s="4"/>
     </row>
-    <row r="861" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
         <v>1317</v>
       </c>
@@ -77545,7 +77555,7 @@
       <c r="AH861" s="4"/>
       <c r="AI861" s="4"/>
     </row>
-    <row r="862" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
         <v>1319</v>
       </c>
@@ -77606,7 +77616,7 @@
       <c r="AH862" s="4"/>
       <c r="AI862" s="4"/>
     </row>
-    <row r="863" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
         <v>1320</v>
       </c>
@@ -77667,7 +77677,7 @@
       <c r="AH863" s="4"/>
       <c r="AI863" s="4"/>
     </row>
-    <row r="864" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
         <v>1322</v>
       </c>
@@ -77728,7 +77738,7 @@
       <c r="AH864" s="4"/>
       <c r="AI864" s="4"/>
     </row>
-    <row r="865" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
         <v>1703</v>
       </c>
@@ -77789,7 +77799,7 @@
       <c r="AH865" s="4"/>
       <c r="AI865" s="4"/>
     </row>
-    <row r="866" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
         <v>1704</v>
       </c>
@@ -77850,7 +77860,7 @@
       <c r="AH866" s="4"/>
       <c r="AI866" s="4"/>
     </row>
-    <row r="867" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
         <v>1705</v>
       </c>
@@ -77911,7 +77921,7 @@
       <c r="AH867" s="4"/>
       <c r="AI867" s="4"/>
     </row>
-    <row r="868" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
         <v>1323</v>
       </c>
@@ -77972,7 +77982,7 @@
       <c r="AH868" s="4"/>
       <c r="AI868" s="4"/>
     </row>
-    <row r="869" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
         <v>1325</v>
       </c>
@@ -78033,7 +78043,7 @@
       <c r="AH869" s="4"/>
       <c r="AI869" s="4"/>
     </row>
-    <row r="870" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
         <v>1327</v>
       </c>
@@ -78094,7 +78104,7 @@
       <c r="AH870" s="4"/>
       <c r="AI870" s="4"/>
     </row>
-    <row r="871" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
         <v>1330</v>
       </c>
@@ -78155,7 +78165,7 @@
       <c r="AH871" s="4"/>
       <c r="AI871" s="4"/>
     </row>
-    <row r="872" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
         <v>1331</v>
       </c>
@@ -78216,7 +78226,7 @@
       <c r="AH872" s="4"/>
       <c r="AI872" s="4"/>
     </row>
-    <row r="873" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
         <v>1334</v>
       </c>
@@ -78277,7 +78287,7 @@
       <c r="AH873" s="4"/>
       <c r="AI873" s="4"/>
     </row>
-    <row r="874" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
         <v>1337</v>
       </c>
@@ -78338,7 +78348,7 @@
       <c r="AH874" s="4"/>
       <c r="AI874" s="4"/>
     </row>
-    <row r="875" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
         <v>1338</v>
       </c>
@@ -78399,7 +78409,7 @@
       <c r="AH875" s="4"/>
       <c r="AI875" s="4"/>
     </row>
-    <row r="876" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
         <v>1340</v>
       </c>
@@ -78460,7 +78470,7 @@
       <c r="AH876" s="4"/>
       <c r="AI876" s="4"/>
     </row>
-    <row r="877" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
         <v>1342</v>
       </c>
@@ -78521,7 +78531,7 @@
       <c r="AH877" s="4"/>
       <c r="AI877" s="4"/>
     </row>
-    <row r="878" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
         <v>1345</v>
       </c>
@@ -78582,7 +78592,7 @@
       <c r="AH878" s="4"/>
       <c r="AI878" s="4"/>
     </row>
-    <row r="879" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
         <v>1346</v>
       </c>
@@ -78643,7 +78653,7 @@
       <c r="AH879" s="4"/>
       <c r="AI879" s="4"/>
     </row>
-    <row r="880" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
         <v>1348</v>
       </c>
@@ -78704,7 +78714,7 @@
       <c r="AH880" s="4"/>
       <c r="AI880" s="4"/>
     </row>
-    <row r="881" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
         <v>1350</v>
       </c>
@@ -78765,7 +78775,7 @@
       <c r="AH881" s="4"/>
       <c r="AI881" s="4"/>
     </row>
-    <row r="882" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
         <v>1352</v>
       </c>
@@ -78826,7 +78836,7 @@
       <c r="AH882" s="4"/>
       <c r="AI882" s="4"/>
     </row>
-    <row r="883" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
         <v>1355</v>
       </c>
@@ -78887,7 +78897,7 @@
       <c r="AH883" s="4"/>
       <c r="AI883" s="4"/>
     </row>
-    <row r="884" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
         <v>1357</v>
       </c>
@@ -78948,7 +78958,7 @@
       <c r="AH884" s="4"/>
       <c r="AI884" s="4"/>
     </row>
-    <row r="885" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
         <v>1358</v>
       </c>
@@ -79009,7 +79019,7 @@
       <c r="AH885" s="4"/>
       <c r="AI885" s="4"/>
     </row>
-    <row r="886" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
         <v>1359</v>
       </c>
@@ -79070,7 +79080,7 @@
       <c r="AH886" s="4"/>
       <c r="AI886" s="4"/>
     </row>
-    <row r="887" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
         <v>1360</v>
       </c>
@@ -79131,7 +79141,7 @@
       <c r="AH887" s="4"/>
       <c r="AI887" s="4"/>
     </row>
-    <row r="888" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
         <v>1363</v>
       </c>
@@ -79192,7 +79202,7 @@
       <c r="AH888" s="4"/>
       <c r="AI888" s="4"/>
     </row>
-    <row r="889" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
         <v>1364</v>
       </c>
@@ -79253,7 +79263,7 @@
       <c r="AH889" s="4"/>
       <c r="AI889" s="4"/>
     </row>
-    <row r="890" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
         <v>1365</v>
       </c>
@@ -79314,7 +79324,7 @@
       <c r="AH890" s="4"/>
       <c r="AI890" s="4"/>
     </row>
-    <row r="891" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
         <v>1366</v>
       </c>
@@ -79375,7 +79385,7 @@
       <c r="AH891" s="4"/>
       <c r="AI891" s="4"/>
     </row>
-    <row r="892" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
         <v>1368</v>
       </c>
@@ -79436,7 +79446,7 @@
       <c r="AH892" s="4"/>
       <c r="AI892" s="4"/>
     </row>
-    <row r="893" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
         <v>1371</v>
       </c>
@@ -79497,7 +79507,7 @@
       <c r="AH893" s="4"/>
       <c r="AI893" s="4"/>
     </row>
-    <row r="894" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
         <v>1373</v>
       </c>
@@ -79558,7 +79568,7 @@
       <c r="AH894" s="4"/>
       <c r="AI894" s="4"/>
     </row>
-    <row r="895" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>1376</v>
       </c>
@@ -79619,7 +79629,7 @@
       <c r="AH895" s="4"/>
       <c r="AI895" s="4"/>
     </row>
-    <row r="896" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>1377</v>
       </c>
@@ -79680,7 +79690,7 @@
       <c r="AH896" s="4"/>
       <c r="AI896" s="4"/>
     </row>
-    <row r="897" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>1378</v>
       </c>
@@ -79741,7 +79751,7 @@
       <c r="AH897" s="4"/>
       <c r="AI897" s="4"/>
     </row>
-    <row r="898" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>1380</v>
       </c>
@@ -79802,7 +79812,7 @@
       <c r="AH898" s="4"/>
       <c r="AI898" s="4"/>
     </row>
-    <row r="899" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>1383</v>
       </c>
@@ -79863,7 +79873,7 @@
       <c r="AH899" s="4"/>
       <c r="AI899" s="4"/>
     </row>
-    <row r="900" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>1384</v>
       </c>
@@ -79924,7 +79934,7 @@
       <c r="AH900" s="4"/>
       <c r="AI900" s="4"/>
     </row>
-    <row r="901" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>1387</v>
       </c>
@@ -79985,7 +79995,7 @@
       <c r="AH901" s="4"/>
       <c r="AI901" s="4"/>
     </row>
-    <row r="902" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>1389</v>
       </c>
@@ -80046,7 +80056,7 @@
       <c r="AH902" s="4"/>
       <c r="AI902" s="4"/>
     </row>
-    <row r="903" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>1392</v>
       </c>
@@ -80107,7 +80117,7 @@
       <c r="AH903" s="4"/>
       <c r="AI903" s="4"/>
     </row>
-    <row r="904" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>1394</v>
       </c>
@@ -80168,7 +80178,7 @@
       <c r="AH904" s="4"/>
       <c r="AI904" s="4"/>
     </row>
-    <row r="905" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>1396</v>
       </c>
@@ -80229,7 +80239,7 @@
       <c r="AH905" s="4"/>
       <c r="AI905" s="4"/>
     </row>
-    <row r="906" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>1397</v>
       </c>
@@ -80290,7 +80300,7 @@
       <c r="AH906" s="4"/>
       <c r="AI906" s="4"/>
     </row>
-    <row r="907" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>1400</v>
       </c>
@@ -80351,7 +80361,7 @@
       <c r="AH907" s="4"/>
       <c r="AI907" s="4"/>
     </row>
-    <row r="908" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>1401</v>
       </c>
@@ -80412,7 +80422,7 @@
       <c r="AH908" s="4"/>
       <c r="AI908" s="4"/>
     </row>
-    <row r="909" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>1405</v>
       </c>
@@ -80473,7 +80483,7 @@
       <c r="AH909" s="4"/>
       <c r="AI909" s="4"/>
     </row>
-    <row r="910" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>1407</v>
       </c>
@@ -80534,7 +80544,7 @@
       <c r="AH910" s="4"/>
       <c r="AI910" s="4"/>
     </row>
-    <row r="911" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>1411</v>
       </c>
@@ -80595,7 +80605,7 @@
       <c r="AH911" s="4"/>
       <c r="AI911" s="4"/>
     </row>
-    <row r="912" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>1413</v>
       </c>
@@ -80656,7 +80666,7 @@
       <c r="AH912" s="4"/>
       <c r="AI912" s="4"/>
     </row>
-    <row r="913" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>1415</v>
       </c>
@@ -80717,7 +80727,7 @@
       <c r="AH913" s="4"/>
       <c r="AI913" s="4"/>
     </row>
-    <row r="914" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>1419</v>
       </c>
@@ -80778,7 +80788,7 @@
       <c r="AH914" s="4"/>
       <c r="AI914" s="4"/>
     </row>
-    <row r="915" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>1421</v>
       </c>
@@ -80839,7 +80849,7 @@
       <c r="AH915" s="4"/>
       <c r="AI915" s="4"/>
     </row>
-    <row r="916" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
         <v>1423</v>
       </c>
@@ -80900,7 +80910,7 @@
       <c r="AH916" s="4"/>
       <c r="AI916" s="4"/>
     </row>
-    <row r="917" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>1425</v>
       </c>
@@ -80961,7 +80971,7 @@
       <c r="AH917" s="4"/>
       <c r="AI917" s="4"/>
     </row>
-    <row r="918" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
         <v>1428</v>
       </c>
@@ -81022,7 +81032,7 @@
       <c r="AH918" s="4"/>
       <c r="AI918" s="4"/>
     </row>
-    <row r="919" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>1429</v>
       </c>
@@ -81083,7 +81093,7 @@
       <c r="AH919" s="4"/>
       <c r="AI919" s="4"/>
     </row>
-    <row r="920" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
         <v>1430</v>
       </c>
@@ -81144,7 +81154,7 @@
       <c r="AH920" s="4"/>
       <c r="AI920" s="4"/>
     </row>
-    <row r="921" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>1431</v>
       </c>
@@ -81205,7 +81215,7 @@
       <c r="AH921" s="4"/>
       <c r="AI921" s="4"/>
     </row>
-    <row r="922" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
         <v>1434</v>
       </c>
@@ -81266,7 +81276,7 @@
       <c r="AH922" s="4"/>
       <c r="AI922" s="4"/>
     </row>
-    <row r="923" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
         <v>1435</v>
       </c>
@@ -81327,7 +81337,7 @@
       <c r="AH923" s="4"/>
       <c r="AI923" s="4"/>
     </row>
-    <row r="924" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
         <v>1438</v>
       </c>
@@ -81388,7 +81398,7 @@
       <c r="AH924" s="4"/>
       <c r="AI924" s="4"/>
     </row>
-    <row r="925" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
         <v>1439</v>
       </c>
@@ -81449,7 +81459,7 @@
       <c r="AH925" s="4"/>
       <c r="AI925" s="4"/>
     </row>
-    <row r="926" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
         <v>1442</v>
       </c>
@@ -81510,7 +81520,7 @@
       <c r="AH926" s="4"/>
       <c r="AI926" s="4"/>
     </row>
-    <row r="927" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
         <v>1443</v>
       </c>
@@ -81571,7 +81581,7 @@
       <c r="AH927" s="4"/>
       <c r="AI927" s="4"/>
     </row>
-    <row r="928" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
         <v>1535</v>
       </c>
@@ -81630,7 +81640,7 @@
       <c r="AH928" s="4"/>
       <c r="AI928" s="4"/>
     </row>
-    <row r="929" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
         <v>1536</v>
       </c>
@@ -81689,7 +81699,7 @@
       <c r="AH929" s="4"/>
       <c r="AI929" s="4"/>
     </row>
-    <row r="930" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
         <v>1537</v>
       </c>
@@ -81748,7 +81758,7 @@
       <c r="AH930" s="4"/>
       <c r="AI930" s="4"/>
     </row>
-    <row r="931" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
         <v>1538</v>
       </c>
@@ -81807,7 +81817,7 @@
       <c r="AH931" s="4"/>
       <c r="AI931" s="4"/>
     </row>
-    <row r="932" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
         <v>1539</v>
       </c>
@@ -81866,7 +81876,7 @@
       <c r="AH932" s="4"/>
       <c r="AI932" s="4"/>
     </row>
-    <row r="933" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
         <v>1540</v>
       </c>
@@ -81925,7 +81935,7 @@
       <c r="AH933" s="4"/>
       <c r="AI933" s="4"/>
     </row>
-    <row r="934" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
         <v>1541</v>
       </c>
@@ -81984,7 +81994,7 @@
       <c r="AH934" s="4"/>
       <c r="AI934" s="4"/>
     </row>
-    <row r="935" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
         <v>1542</v>
       </c>
@@ -82043,7 +82053,7 @@
       <c r="AH935" s="4"/>
       <c r="AI935" s="4"/>
     </row>
-    <row r="936" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
         <v>1543</v>
       </c>
@@ -82102,7 +82112,7 @@
       <c r="AH936" s="4"/>
       <c r="AI936" s="4"/>
     </row>
-    <row r="937" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
         <v>1544</v>
       </c>
@@ -82161,7 +82171,7 @@
       <c r="AH937" s="4"/>
       <c r="AI937" s="4"/>
     </row>
-    <row r="938" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
         <v>1545</v>
       </c>
@@ -82220,7 +82230,7 @@
       <c r="AH938" s="4"/>
       <c r="AI938" s="4"/>
     </row>
-    <row r="939" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
         <v>1546</v>
       </c>
@@ -82279,7 +82289,7 @@
       <c r="AH939" s="4"/>
       <c r="AI939" s="4"/>
     </row>
-    <row r="940" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
         <v>1547</v>
       </c>
@@ -82338,7 +82348,7 @@
       <c r="AH940" s="4"/>
       <c r="AI940" s="4"/>
     </row>
-    <row r="941" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
         <v>1548</v>
       </c>
@@ -82397,7 +82407,7 @@
       <c r="AH941" s="4"/>
       <c r="AI941" s="4"/>
     </row>
-    <row r="942" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
         <v>1549</v>
       </c>
@@ -82456,7 +82466,7 @@
       <c r="AH942" s="4"/>
       <c r="AI942" s="4"/>
     </row>
-    <row r="943" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
         <v>1550</v>
       </c>
@@ -82515,7 +82525,7 @@
       <c r="AH943" s="4"/>
       <c r="AI943" s="4"/>
     </row>
-    <row r="944" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
         <v>1551</v>
       </c>
@@ -82574,7 +82584,7 @@
       <c r="AH944" s="4"/>
       <c r="AI944" s="4"/>
     </row>
-    <row r="945" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
         <v>1552</v>
       </c>
@@ -82633,7 +82643,7 @@
       <c r="AH945" s="4"/>
       <c r="AI945" s="4"/>
     </row>
-    <row r="946" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
         <v>1553</v>
       </c>
@@ -82692,7 +82702,7 @@
       <c r="AH946" s="4"/>
       <c r="AI946" s="4"/>
     </row>
-    <row r="947" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
         <v>1554</v>
       </c>
@@ -82751,7 +82761,7 @@
       <c r="AH947" s="4"/>
       <c r="AI947" s="4"/>
     </row>
-    <row r="948" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
         <v>1555</v>
       </c>
@@ -82810,7 +82820,7 @@
       <c r="AH948" s="4"/>
       <c r="AI948" s="4"/>
     </row>
-    <row r="949" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
         <v>1556</v>
       </c>
@@ -82869,7 +82879,7 @@
       <c r="AH949" s="4"/>
       <c r="AI949" s="4"/>
     </row>
-    <row r="950" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
         <v>1557</v>
       </c>
@@ -82928,7 +82938,7 @@
       <c r="AH950" s="4"/>
       <c r="AI950" s="4"/>
     </row>
-    <row r="951" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
         <v>1558</v>
       </c>
@@ -82987,7 +82997,7 @@
       <c r="AH951" s="4"/>
       <c r="AI951" s="4"/>
     </row>
-    <row r="952" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
         <v>1559</v>
       </c>
@@ -83046,7 +83056,7 @@
       <c r="AH952" s="4"/>
       <c r="AI952" s="4"/>
     </row>
-    <row r="953" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
         <v>1560</v>
       </c>
@@ -83105,7 +83115,7 @@
       <c r="AH953" s="4"/>
       <c r="AI953" s="4"/>
     </row>
-    <row r="954" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
         <v>1561</v>
       </c>
@@ -83164,7 +83174,7 @@
       <c r="AH954" s="4"/>
       <c r="AI954" s="4"/>
     </row>
-    <row r="955" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
         <v>1562</v>
       </c>
@@ -83223,7 +83233,7 @@
       <c r="AH955" s="4"/>
       <c r="AI955" s="4"/>
     </row>
-    <row r="956" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
         <v>1563</v>
       </c>
@@ -83282,7 +83292,7 @@
       <c r="AH956" s="4"/>
       <c r="AI956" s="4"/>
     </row>
-    <row r="957" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
         <v>1564</v>
       </c>
@@ -83341,7 +83351,7 @@
       <c r="AH957" s="4"/>
       <c r="AI957" s="4"/>
     </row>
-    <row r="958" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
         <v>1565</v>
       </c>
@@ -83400,7 +83410,7 @@
       <c r="AH958" s="4"/>
       <c r="AI958" s="4"/>
     </row>
-    <row r="959" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
         <v>1566</v>
       </c>
@@ -83459,7 +83469,7 @@
       <c r="AH959" s="4"/>
       <c r="AI959" s="4"/>
     </row>
-    <row r="960" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
         <v>1567</v>
       </c>
@@ -83518,7 +83528,7 @@
       <c r="AH960" s="4"/>
       <c r="AI960" s="4"/>
     </row>
-    <row r="961" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
         <v>1568</v>
       </c>
@@ -83577,7 +83587,7 @@
       <c r="AH961" s="4"/>
       <c r="AI961" s="4"/>
     </row>
-    <row r="962" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
         <v>1569</v>
       </c>
@@ -83636,7 +83646,7 @@
       <c r="AH962" s="4"/>
       <c r="AI962" s="4"/>
     </row>
-    <row r="963" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
         <v>1570</v>
       </c>
@@ -83695,7 +83705,7 @@
       <c r="AH963" s="4"/>
       <c r="AI963" s="4"/>
     </row>
-    <row r="964" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
         <v>1571</v>
       </c>
@@ -83754,7 +83764,7 @@
       <c r="AH964" s="4"/>
       <c r="AI964" s="4"/>
     </row>
-    <row r="965" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
         <v>1572</v>
       </c>
@@ -83813,7 +83823,7 @@
       <c r="AH965" s="4"/>
       <c r="AI965" s="4"/>
     </row>
-    <row r="966" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
         <v>1573</v>
       </c>
@@ -83872,7 +83882,7 @@
       <c r="AH966" s="4"/>
       <c r="AI966" s="4"/>
     </row>
-    <row r="967" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
         <v>1574</v>
       </c>
@@ -83931,7 +83941,7 @@
       <c r="AH967" s="4"/>
       <c r="AI967" s="4"/>
     </row>
-    <row r="968" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
         <v>1575</v>
       </c>
@@ -83990,7 +84000,7 @@
       <c r="AH968" s="4"/>
       <c r="AI968" s="4"/>
     </row>
-    <row r="969" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
         <v>1576</v>
       </c>
@@ -84049,7 +84059,7 @@
       <c r="AH969" s="4"/>
       <c r="AI969" s="4"/>
     </row>
-    <row r="970" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
         <v>1577</v>
       </c>
@@ -84108,7 +84118,7 @@
       <c r="AH970" s="4"/>
       <c r="AI970" s="4"/>
     </row>
-    <row r="971" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
         <v>1578</v>
       </c>
@@ -84167,7 +84177,7 @@
       <c r="AH971" s="4"/>
       <c r="AI971" s="4"/>
     </row>
-    <row r="972" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
         <v>1579</v>
       </c>
@@ -84226,7 +84236,7 @@
       <c r="AH972" s="4"/>
       <c r="AI972" s="4"/>
     </row>
-    <row r="973" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
         <v>1580</v>
       </c>
@@ -84285,7 +84295,7 @@
       <c r="AH973" s="4"/>
       <c r="AI973" s="4"/>
     </row>
-    <row r="974" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
         <v>1581</v>
       </c>
@@ -84344,7 +84354,7 @@
       <c r="AH974" s="4"/>
       <c r="AI974" s="4"/>
     </row>
-    <row r="975" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
         <v>1582</v>
       </c>
@@ -84403,7 +84413,7 @@
       <c r="AH975" s="4"/>
       <c r="AI975" s="4"/>
     </row>
-    <row r="976" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
         <v>1583</v>
       </c>
@@ -84460,7 +84470,7 @@
       <c r="AH976" s="4"/>
       <c r="AI976" s="4"/>
     </row>
-    <row r="977" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
         <v>1584</v>
       </c>
@@ -84517,7 +84527,7 @@
       <c r="AH977" s="4"/>
       <c r="AI977" s="4"/>
     </row>
-    <row r="978" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
         <v>1585</v>
       </c>
@@ -84574,7 +84584,7 @@
       <c r="AH978" s="4"/>
       <c r="AI978" s="4"/>
     </row>
-    <row r="979" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
         <v>1586</v>
       </c>
@@ -84631,7 +84641,7 @@
       <c r="AH979" s="4"/>
       <c r="AI979" s="4"/>
     </row>
-    <row r="980" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
         <v>1588</v>
       </c>
@@ -84688,7 +84698,7 @@
       <c r="AH980" s="4"/>
       <c r="AI980" s="4"/>
     </row>
-    <row r="981" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
         <v>1589</v>
       </c>
@@ -84745,7 +84755,7 @@
       <c r="AH981" s="4"/>
       <c r="AI981" s="4"/>
     </row>
-    <row r="982" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
         <v>1590</v>
       </c>
@@ -84802,7 +84812,7 @@
       <c r="AH982" s="4"/>
       <c r="AI982" s="4"/>
     </row>
-    <row r="983" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
         <v>1591</v>
       </c>
@@ -84859,7 +84869,7 @@
       <c r="AH983" s="4"/>
       <c r="AI983" s="4"/>
     </row>
-    <row r="984" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
         <v>1592</v>
       </c>
@@ -84916,7 +84926,7 @@
       <c r="AH984" s="4"/>
       <c r="AI984" s="4"/>
     </row>
-    <row r="985" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
         <v>1593</v>
       </c>
@@ -84973,7 +84983,7 @@
       <c r="AH985" s="4"/>
       <c r="AI985" s="4"/>
     </row>
-    <row r="986" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
         <v>1594</v>
       </c>
@@ -85030,7 +85040,7 @@
       <c r="AH986" s="4"/>
       <c r="AI986" s="4"/>
     </row>
-    <row r="987" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
         <v>1595</v>
       </c>
@@ -85087,7 +85097,7 @@
       <c r="AH987" s="4"/>
       <c r="AI987" s="4"/>
     </row>
-    <row r="988" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
         <v>1597</v>
       </c>
@@ -85144,7 +85154,7 @@
       <c r="AH988" s="4"/>
       <c r="AI988" s="4"/>
     </row>
-    <row r="989" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
         <v>1598</v>
       </c>
@@ -85201,7 +85211,7 @@
       <c r="AH989" s="4"/>
       <c r="AI989" s="4"/>
     </row>
-    <row r="990" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
         <v>1599</v>
       </c>
@@ -85258,7 +85268,7 @@
       <c r="AH990" s="4"/>
       <c r="AI990" s="4"/>
     </row>
-    <row r="991" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
         <v>1600</v>
       </c>
@@ -85315,7 +85325,7 @@
       <c r="AH991" s="4"/>
       <c r="AI991" s="4"/>
     </row>
-    <row r="992" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
         <v>1601</v>
       </c>
@@ -85372,7 +85382,7 @@
       <c r="AH992" s="4"/>
       <c r="AI992" s="4"/>
     </row>
-    <row r="993" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
         <v>1602</v>
       </c>
@@ -85429,7 +85439,7 @@
       <c r="AH993" s="4"/>
       <c r="AI993" s="4"/>
     </row>
-    <row r="994" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
         <v>1603</v>
       </c>
@@ -85486,7 +85496,7 @@
       <c r="AH994" s="4"/>
       <c r="AI994" s="4"/>
     </row>
-    <row r="995" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
         <v>1605</v>
       </c>
@@ -85543,7 +85553,7 @@
       <c r="AH995" s="4"/>
       <c r="AI995" s="4"/>
     </row>
-    <row r="996" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
         <v>1606</v>
       </c>
@@ -85600,7 +85610,7 @@
       <c r="AH996" s="4"/>
       <c r="AI996" s="4"/>
     </row>
-    <row r="997" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
         <v>1607</v>
       </c>
@@ -85657,7 +85667,7 @@
       <c r="AH997" s="4"/>
       <c r="AI997" s="4"/>
     </row>
-    <row r="998" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
         <v>1609</v>
       </c>
@@ -85714,7 +85724,7 @@
       <c r="AH998" s="4"/>
       <c r="AI998" s="4"/>
     </row>
-    <row r="999" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
         <v>1611</v>
       </c>
@@ -85771,7 +85781,7 @@
       <c r="AH999" s="4"/>
       <c r="AI999" s="4"/>
     </row>
-    <row r="1000" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
         <v>1613</v>
       </c>
@@ -85830,7 +85840,7 @@
       <c r="AH1000" s="4"/>
       <c r="AI1000" s="4"/>
     </row>
-    <row r="1001" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
         <v>1614</v>
       </c>
@@ -85889,7 +85899,7 @@
       <c r="AH1001" s="4"/>
       <c r="AI1001" s="4"/>
     </row>
-    <row r="1002" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
         <v>1615</v>
       </c>
@@ -85946,7 +85956,7 @@
       <c r="AH1002" s="4"/>
       <c r="AI1002" s="4"/>
     </row>
-    <row r="1003" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
         <v>1616</v>
       </c>
@@ -86003,7 +86013,7 @@
       <c r="AH1003" s="4"/>
       <c r="AI1003" s="4"/>
     </row>
-    <row r="1004" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
         <v>1619</v>
       </c>
@@ -86060,7 +86070,7 @@
       <c r="AH1004" s="4"/>
       <c r="AI1004" s="4"/>
     </row>
-    <row r="1005" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
         <v>1623</v>
       </c>
@@ -86117,7 +86127,7 @@
       <c r="AH1005" s="4"/>
       <c r="AI1005" s="4"/>
     </row>
-    <row r="1006" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
         <v>1624</v>
       </c>
@@ -86174,7 +86184,7 @@
       <c r="AH1006" s="4"/>
       <c r="AI1006" s="4"/>
     </row>
-    <row r="1007" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
         <v>1625</v>
       </c>
@@ -86231,7 +86241,7 @@
       <c r="AH1007" s="4"/>
       <c r="AI1007" s="4"/>
     </row>
-    <row r="1008" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
         <v>1628</v>
       </c>
@@ -86288,7 +86298,7 @@
       <c r="AH1008" s="4"/>
       <c r="AI1008" s="4"/>
     </row>
-    <row r="1009" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
         <v>1629</v>
       </c>
@@ -86345,7 +86355,7 @@
       <c r="AH1009" s="4"/>
       <c r="AI1009" s="4"/>
     </row>
-    <row r="1010" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
         <v>1630</v>
       </c>
@@ -86402,7 +86412,7 @@
       <c r="AH1010" s="4"/>
       <c r="AI1010" s="4"/>
     </row>
-    <row r="1011" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="2" t="s">
         <v>1633</v>
       </c>
@@ -86459,7 +86469,7 @@
       <c r="AH1011" s="4"/>
       <c r="AI1011" s="4"/>
     </row>
-    <row r="1012" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="2" t="s">
         <v>1634</v>
       </c>
@@ -86516,7 +86526,7 @@
       <c r="AH1012" s="4"/>
       <c r="AI1012" s="4"/>
     </row>
-    <row r="1013" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="2" t="s">
         <v>1637</v>
       </c>
@@ -86573,7 +86583,7 @@
       <c r="AH1013" s="4"/>
       <c r="AI1013" s="4"/>
     </row>
-    <row r="1014" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
         <v>1638</v>
       </c>
@@ -86630,7 +86640,7 @@
       <c r="AH1014" s="4"/>
       <c r="AI1014" s="4"/>
     </row>
-    <row r="1015" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="2" t="s">
         <v>1641</v>
       </c>
@@ -86687,7 +86697,7 @@
       <c r="AH1015" s="4"/>
       <c r="AI1015" s="4"/>
     </row>
-    <row r="1016" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="2" t="s">
         <v>1645</v>
       </c>
@@ -86744,7 +86754,7 @@
       <c r="AH1016" s="4"/>
       <c r="AI1016" s="4"/>
     </row>
-    <row r="1017" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="2" t="s">
         <v>1646</v>
       </c>
@@ -86801,7 +86811,7 @@
       <c r="AH1017" s="4"/>
       <c r="AI1017" s="4"/>
     </row>
-    <row r="1018" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
         <v>1648</v>
       </c>
@@ -86860,7 +86870,7 @@
       <c r="AH1018" s="4"/>
       <c r="AI1018" s="4"/>
     </row>
-    <row r="1019" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="2" t="s">
         <v>1649</v>
       </c>
@@ -86919,7 +86929,7 @@
       <c r="AH1019" s="4"/>
       <c r="AI1019" s="4"/>
     </row>
-    <row r="1020" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
         <v>1650</v>
       </c>
@@ -86976,7 +86986,7 @@
       <c r="AH1020" s="4"/>
       <c r="AI1020" s="4"/>
     </row>
-    <row r="1021" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
         <v>1653</v>
       </c>
@@ -87033,7 +87043,7 @@
       <c r="AH1021" s="4"/>
       <c r="AI1021" s="4"/>
     </row>
-    <row r="1022" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
         <v>1654</v>
       </c>
@@ -87090,7 +87100,7 @@
       <c r="AH1022" s="4"/>
       <c r="AI1022" s="4"/>
     </row>
-    <row r="1023" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="2" t="s">
         <v>1655</v>
       </c>
@@ -87147,7 +87157,7 @@
       <c r="AH1023" s="4"/>
       <c r="AI1023" s="4"/>
     </row>
-    <row r="1024" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
         <v>1656</v>
       </c>
@@ -87204,7 +87214,7 @@
       <c r="AH1024" s="4"/>
       <c r="AI1024" s="4"/>
     </row>
-    <row r="1025" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="2" t="s">
         <v>1657</v>
       </c>
@@ -87261,7 +87271,7 @@
       <c r="AH1025" s="4"/>
       <c r="AI1025" s="4"/>
     </row>
-    <row r="1026" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
         <v>1658</v>
       </c>
@@ -87318,7 +87328,7 @@
       <c r="AH1026" s="4"/>
       <c r="AI1026" s="4"/>
     </row>
-    <row r="1027" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="2" t="s">
         <v>1660</v>
       </c>
@@ -87375,7 +87385,7 @@
       <c r="AH1027" s="4"/>
       <c r="AI1027" s="4"/>
     </row>
-    <row r="1028" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="2" t="s">
         <v>1662</v>
       </c>
@@ -87432,7 +87442,7 @@
       <c r="AH1028" s="4"/>
       <c r="AI1028" s="4"/>
     </row>
-    <row r="1029" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="2" t="s">
         <v>1665</v>
       </c>
@@ -87489,7 +87499,7 @@
       <c r="AH1029" s="4"/>
       <c r="AI1029" s="4"/>
     </row>
-    <row r="1030" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="2" t="s">
         <v>1666</v>
       </c>
@@ -87546,7 +87556,7 @@
       <c r="AH1030" s="4"/>
       <c r="AI1030" s="4"/>
     </row>
-    <row r="1031" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="2" t="s">
         <v>1668</v>
       </c>
@@ -87603,7 +87613,7 @@
       <c r="AH1031" s="4"/>
       <c r="AI1031" s="4"/>
     </row>
-    <row r="1032" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="2" t="s">
         <v>1670</v>
       </c>
@@ -87660,7 +87670,7 @@
       <c r="AH1032" s="4"/>
       <c r="AI1032" s="4"/>
     </row>
-    <row r="1033" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="8" t="s">
         <v>1678</v>
       </c>
@@ -87707,7 +87717,7 @@
       <c r="AH1033" s="4"/>
       <c r="AI1033" s="4"/>
     </row>
-    <row r="1034" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="8" t="s">
         <v>1679</v>
       </c>
@@ -87754,7 +87764,7 @@
       <c r="AH1034" s="4"/>
       <c r="AI1034" s="4"/>
     </row>
-    <row r="1035" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="8" t="s">
         <v>1680</v>
       </c>
@@ -87801,7 +87811,7 @@
       <c r="AH1035" s="4"/>
       <c r="AI1035" s="4"/>
     </row>
-    <row r="1036" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="8" t="s">
         <v>1681</v>
       </c>
@@ -87848,7 +87858,7 @@
       <c r="AH1036" s="4"/>
       <c r="AI1036" s="4"/>
     </row>
-    <row r="1037" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="8" t="s">
         <v>1682</v>
       </c>
@@ -87895,7 +87905,7 @@
       <c r="AH1037" s="4"/>
       <c r="AI1037" s="4"/>
     </row>
-    <row r="1038" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="8" t="s">
         <v>1683</v>
       </c>
@@ -87942,7 +87952,7 @@
       <c r="AH1038" s="4"/>
       <c r="AI1038" s="4"/>
     </row>
-    <row r="1039" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="8" t="s">
         <v>1684</v>
       </c>
@@ -87989,7 +87999,7 @@
       <c r="AH1039" s="4"/>
       <c r="AI1039" s="4"/>
     </row>
-    <row r="1040" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1040" s="8" t="s">
         <v>1685</v>
       </c>
@@ -88036,7 +88046,7 @@
       <c r="AH1040" s="4"/>
       <c r="AI1040" s="4"/>
     </row>
-    <row r="1041" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="8" t="s">
         <v>1686</v>
       </c>
@@ -88083,7 +88093,7 @@
       <c r="AH1041" s="4"/>
       <c r="AI1041" s="4"/>
     </row>
-    <row r="1042" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="8" t="s">
         <v>1687</v>
       </c>
@@ -88130,7 +88140,7 @@
       <c r="AH1042" s="4"/>
       <c r="AI1042" s="4"/>
     </row>
-    <row r="1043" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="8" t="s">
         <v>1688</v>
       </c>
@@ -88177,7 +88187,7 @@
       <c r="AH1043" s="4"/>
       <c r="AI1043" s="4"/>
     </row>
-    <row r="1044" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1044" s="8" t="s">
         <v>1689</v>
       </c>
@@ -88224,7 +88234,7 @@
       <c r="AH1044" s="4"/>
       <c r="AI1044" s="4"/>
     </row>
-    <row r="1045" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="8" t="s">
         <v>1690</v>
       </c>
@@ -88395,7 +88405,7 @@
     </row>
     <row r="1048" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
-        <v>1692</v>
+        <v>1721</v>
       </c>
       <c r="B1048" s="2" t="s">
         <v>35</v>
@@ -88413,7 +88423,7 @@
         <v>645</v>
       </c>
       <c r="G1048" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H1048" s="4" t="s">
         <v>44</v>
@@ -88456,7 +88466,7 @@
     </row>
     <row r="1049" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="2" t="s">
-        <v>1693</v>
+        <v>1722</v>
       </c>
       <c r="B1049" s="2" t="s">
         <v>35</v>
@@ -88474,7 +88484,7 @@
         <v>645</v>
       </c>
       <c r="G1049" s="4" t="s">
-        <v>54</v>
+        <v>1720</v>
       </c>
       <c r="H1049" s="4" t="s">
         <v>44</v>
@@ -88517,7 +88527,7 @@
     </row>
     <row r="1050" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="2" t="s">
-        <v>1711</v>
+        <v>1692</v>
       </c>
       <c r="B1050" s="2" t="s">
         <v>35</v>
@@ -88535,7 +88545,7 @@
         <v>645</v>
       </c>
       <c r="G1050" s="4" t="s">
-        <v>377</v>
+        <v>48</v>
       </c>
       <c r="H1050" s="4" t="s">
         <v>44</v>
@@ -88578,7 +88588,7 @@
     </row>
     <row r="1051" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1051" s="2" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="B1051" s="2" t="s">
         <v>35</v>
@@ -88596,7 +88606,7 @@
         <v>645</v>
       </c>
       <c r="G1051" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H1051" s="4" t="s">
         <v>44</v>
@@ -88639,31 +88649,31 @@
     </row>
     <row r="1052" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1052" s="2" t="s">
-        <v>1697</v>
+        <v>1711</v>
       </c>
       <c r="B1052" s="2" t="s">
-        <v>443</v>
+        <v>35</v>
       </c>
       <c r="C1052" s="2" t="s">
-        <v>612</v>
+        <v>1300</v>
       </c>
       <c r="D1052" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1052" s="5" t="s">
-        <v>614</v>
+        <v>1309</v>
       </c>
       <c r="F1052" s="4" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="G1052" s="4" t="s">
-        <v>531</v>
+        <v>377</v>
       </c>
       <c r="H1052" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I1052" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1052" s="4" t="s">
         <v>41</v>
@@ -88700,31 +88710,31 @@
     </row>
     <row r="1053" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1053" s="2" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="B1053" s="2" t="s">
-        <v>443</v>
+        <v>35</v>
       </c>
       <c r="C1053" s="2" t="s">
-        <v>612</v>
+        <v>1300</v>
       </c>
       <c r="D1053" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1053" s="5" t="s">
-        <v>614</v>
+        <v>1309</v>
       </c>
       <c r="F1053" s="4" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="G1053" s="4" t="s">
-        <v>1696</v>
+        <v>56</v>
       </c>
       <c r="H1053" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I1053" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1053" s="4" t="s">
         <v>41</v>
@@ -88759,9 +88769,9 @@
       <c r="AH1053" s="4"/>
       <c r="AI1053" s="4"/>
     </row>
-    <row r="1054" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1054" s="2" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="B1054" s="2" t="s">
         <v>443</v>
@@ -88779,7 +88789,7 @@
         <v>615</v>
       </c>
       <c r="G1054" s="4" t="s">
-        <v>368</v>
+        <v>531</v>
       </c>
       <c r="H1054" s="4" t="s">
         <v>44</v>
@@ -88820,9 +88830,9 @@
       <c r="AH1054" s="4"/>
       <c r="AI1054" s="4"/>
     </row>
-    <row r="1055" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1055" s="2" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="B1055" s="2" t="s">
         <v>443</v>
@@ -88840,7 +88850,7 @@
         <v>615</v>
       </c>
       <c r="G1055" s="4" t="s">
-        <v>164</v>
+        <v>1696</v>
       </c>
       <c r="H1055" s="4" t="s">
         <v>44</v>
@@ -88881,8 +88891,136 @@
       <c r="AH1055" s="4"/>
       <c r="AI1055" s="4"/>
     </row>
+    <row r="1056" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1056" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1056" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1056" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D1056" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1056" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F1056" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="G1056" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1056" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1056" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1056" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1056" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1056" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1056" s="4"/>
+      <c r="N1056" s="4"/>
+      <c r="O1056" s="4"/>
+      <c r="P1056" s="4"/>
+      <c r="Q1056" s="4"/>
+      <c r="R1056" s="4"/>
+      <c r="S1056" s="4"/>
+      <c r="T1056" s="4"/>
+      <c r="U1056" s="4"/>
+      <c r="V1056" s="4"/>
+      <c r="W1056" s="4"/>
+      <c r="X1056" s="4"/>
+      <c r="Y1056" s="4"/>
+      <c r="Z1056" s="4"/>
+      <c r="AA1056" s="4"/>
+      <c r="AB1056" s="4"/>
+      <c r="AC1056" s="4"/>
+      <c r="AD1056" s="4"/>
+      <c r="AE1056" s="4"/>
+      <c r="AF1056" s="4"/>
+      <c r="AG1056" s="4"/>
+      <c r="AH1056" s="4"/>
+      <c r="AI1056" s="4"/>
+    </row>
+    <row r="1057" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1057" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B1057" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1057" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D1057" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1057" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F1057" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="G1057" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1057" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1057" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1057" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1057" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1057" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1057" s="4"/>
+      <c r="N1057" s="4"/>
+      <c r="O1057" s="4"/>
+      <c r="P1057" s="4"/>
+      <c r="Q1057" s="4"/>
+      <c r="R1057" s="4"/>
+      <c r="S1057" s="4"/>
+      <c r="T1057" s="4"/>
+      <c r="U1057" s="4"/>
+      <c r="V1057" s="4"/>
+      <c r="W1057" s="4"/>
+      <c r="X1057" s="4"/>
+      <c r="Y1057" s="4"/>
+      <c r="Z1057" s="4"/>
+      <c r="AA1057" s="4"/>
+      <c r="AB1057" s="4"/>
+      <c r="AC1057" s="4"/>
+      <c r="AD1057" s="4"/>
+      <c r="AE1057" s="4"/>
+      <c r="AF1057" s="4"/>
+      <c r="AG1057" s="4"/>
+      <c r="AH1057" s="4"/>
+      <c r="AI1057" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R1055" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R1057" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="CORRE 5"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
